--- a/Data/FlightPlan/FPL_15SEP26.xlsx
+++ b/Data/FlightPlan/FPL_15SEP26.xlsx
@@ -71,6 +71,12 @@
     <t>13:35</t>
   </si>
   <si>
+    <t>11:40</t>
+  </si>
+  <si>
+    <t>14:20</t>
+  </si>
+  <si>
     <t>HGH</t>
   </si>
   <si>
@@ -626,9 +632,6 @@
     <t>10:25</t>
   </si>
   <si>
-    <t>14:20</t>
-  </si>
-  <si>
     <t>15:00</t>
   </si>
   <si>
@@ -1067,9 +1070,6 @@
     <t>VN-A674</t>
   </si>
   <si>
-    <t>11:40</t>
-  </si>
-  <si>
     <t>VN-A675</t>
   </si>
   <si>
@@ -1184,7 +1184,7 @@
     <t>Total Record(s): 364</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Sep 14, 2026 23:08</t>
+    <t xml:space="preserve">Generated on  Sep 15, 2026 03:51</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -1762,9 +1762,13 @@
       <c t="s" r="J7" s="7">
         <v>19</v>
       </c>
-      <c r="K7" s="7"/>
+      <c t="s" r="K7" s="7">
+        <v>20</v>
+      </c>
       <c r="L7" s="7"/>
-      <c r="M7" s="7"/>
+      <c t="s" r="M7" s="7">
+        <v>21</v>
+      </c>
     </row>
     <row r="8" ht="14.25" customHeight="1">
       <c t="s" r="A8" s="6">
@@ -1787,13 +1791,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H8" s="8">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c t="s" r="I8" s="7">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c t="s" r="J8" s="7">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K8" s="7"/>
       <c r="L8" s="7"/>
@@ -1817,16 +1821,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G9" s="8">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c t="s" r="H9" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I9" s="7">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c t="s" r="J9" s="7">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K9" s="7"/>
       <c r="L9" s="7"/>
@@ -1834,7 +1838,7 @@
     </row>
     <row r="10" ht="15" customHeight="1">
       <c t="s" r="A10" s="6">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B10" s="7">
         <v>918</v>
@@ -1856,10 +1860,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I10" s="7">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c t="s" r="J10" s="7">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K10" s="7"/>
       <c r="L10" s="7"/>
@@ -1892,22 +1896,22 @@
       </c>
       <c r="D12" s="7"/>
       <c t="s" r="E12" s="7">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F12" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G12" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="H12" s="8">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c t="s" r="I12" s="7">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c t="s" r="J12" s="7">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K12" s="7"/>
       <c r="L12" s="7"/>
@@ -1925,22 +1929,22 @@
       </c>
       <c r="D13" s="7"/>
       <c t="s" r="E13" s="7">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F13" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G13" s="8">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c t="s" r="H13" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="I13" s="7">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c t="s" r="J13" s="7">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K13" s="7"/>
       <c r="L13" s="7"/>
@@ -1948,7 +1952,7 @@
     </row>
     <row r="14" ht="14.25" customHeight="1">
       <c t="s" r="A14" s="6">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B14" s="7">
         <v>938</v>
@@ -1958,22 +1962,22 @@
       </c>
       <c r="D14" s="7"/>
       <c t="s" r="E14" s="7">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F14" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G14" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="H14" s="8">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c t="s" r="I14" s="7">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c t="s" r="J14" s="7">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K14" s="7"/>
       <c r="L14" s="7"/>
@@ -2006,22 +2010,22 @@
       </c>
       <c r="D16" s="7"/>
       <c t="s" r="E16" s="7">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F16" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G16" s="8">
+        <v>41</v>
+      </c>
+      <c t="s" r="H16" s="8">
+        <v>42</v>
+      </c>
+      <c t="s" r="I16" s="7">
+        <v>43</v>
+      </c>
+      <c t="s" r="J16" s="7">
         <v>39</v>
-      </c>
-      <c t="s" r="H16" s="8">
-        <v>40</v>
-      </c>
-      <c t="s" r="I16" s="7">
-        <v>41</v>
-      </c>
-      <c t="s" r="J16" s="7">
-        <v>37</v>
       </c>
       <c r="K16" s="7"/>
       <c r="L16" s="7"/>
@@ -2039,22 +2043,22 @@
       </c>
       <c r="D17" s="7"/>
       <c t="s" r="E17" s="7">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F17" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G17" s="8">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c t="s" r="H17" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="I17" s="7">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c t="s" r="J17" s="7">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K17" s="7"/>
       <c r="L17" s="7"/>
@@ -2072,22 +2076,22 @@
       </c>
       <c r="D18" s="7"/>
       <c t="s" r="E18" s="7">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F18" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G18" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="H18" s="8">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c t="s" r="I18" s="7">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c t="s" r="J18" s="7">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K18" s="7"/>
       <c r="L18" s="7"/>
@@ -2105,22 +2109,22 @@
       </c>
       <c r="D19" s="7"/>
       <c t="s" r="E19" s="7">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F19" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G19" s="8">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c t="s" r="H19" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="I19" s="7">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c t="s" r="J19" s="7">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="K19" s="7"/>
       <c r="L19" s="7"/>
@@ -2138,22 +2142,22 @@
       </c>
       <c r="D20" s="7"/>
       <c t="s" r="E20" s="7">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F20" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G20" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="H20" s="8">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c t="s" r="I20" s="7">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c t="s" r="J20" s="7">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="K20" s="7"/>
       <c r="L20" s="7"/>
@@ -2161,7 +2165,7 @@
     </row>
     <row r="21" ht="14.25" customHeight="1">
       <c t="s" r="A21" s="6">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B21" s="7">
         <v>884</v>
@@ -2171,22 +2175,22 @@
       </c>
       <c r="D21" s="7"/>
       <c t="s" r="E21" s="7">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F21" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G21" s="8">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c t="s" r="H21" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="I21" s="7">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c t="s" r="J21" s="7">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K21" s="7"/>
       <c r="L21" s="7"/>
@@ -2219,7 +2223,7 @@
       </c>
       <c r="D23" s="7"/>
       <c t="s" r="E23" s="7">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F23" s="7">
         <v>321</v>
@@ -2228,13 +2232,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H23" s="8">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c t="s" r="I23" s="7">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c t="s" r="J23" s="7">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="K23" s="7"/>
       <c r="L23" s="7"/>
@@ -2252,22 +2256,22 @@
       </c>
       <c r="D24" s="7"/>
       <c t="s" r="E24" s="7">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F24" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G24" s="8">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c t="s" r="H24" s="8">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c t="s" r="I24" s="7">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c t="s" r="J24" s="7">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K24" s="7"/>
       <c r="L24" s="7"/>
@@ -2285,22 +2289,22 @@
       </c>
       <c r="D25" s="7"/>
       <c t="s" r="E25" s="7">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F25" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G25" s="8">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c t="s" r="H25" s="8">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c t="s" r="I25" s="7">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c t="s" r="J25" s="7">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="K25" s="7"/>
       <c r="L25" s="7"/>
@@ -2318,22 +2322,22 @@
       </c>
       <c r="D26" s="7"/>
       <c t="s" r="E26" s="7">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F26" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G26" s="8">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c t="s" r="H26" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="I26" s="7">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c t="s" r="J26" s="7">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="K26" s="7"/>
       <c r="L26" s="7"/>
@@ -2341,7 +2345,7 @@
     </row>
     <row r="27" ht="14.25" customHeight="1">
       <c t="s" r="A27" s="6">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B27" s="7">
         <v>828</v>
@@ -2351,22 +2355,22 @@
       </c>
       <c r="D27" s="7"/>
       <c t="s" r="E27" s="7">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F27" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G27" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="H27" s="8">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c t="s" r="I27" s="7">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c t="s" r="J27" s="7">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K27" s="7"/>
       <c r="L27" s="7"/>
@@ -2399,22 +2403,22 @@
       </c>
       <c r="D29" s="7"/>
       <c t="s" r="E29" s="7">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F29" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G29" s="8">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c t="s" r="H29" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="I29" s="7">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c t="s" r="J29" s="7">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K29" s="7"/>
       <c r="L29" s="7"/>
@@ -2432,22 +2436,22 @@
       </c>
       <c r="D30" s="7"/>
       <c t="s" r="E30" s="7">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F30" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G30" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="H30" s="8">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c t="s" r="I30" s="7">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c t="s" r="J30" s="7">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="K30" s="7"/>
       <c r="L30" s="7"/>
@@ -2465,22 +2469,22 @@
       </c>
       <c r="D31" s="7"/>
       <c t="s" r="E31" s="7">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F31" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G31" s="8">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c t="s" r="H31" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="I31" s="7">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c t="s" r="J31" s="7">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="K31" s="7"/>
       <c r="L31" s="7"/>
@@ -2513,22 +2517,22 @@
       </c>
       <c r="D33" s="7"/>
       <c t="s" r="E33" s="7">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F33" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G33" s="8">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c t="s" r="H33" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="I33" s="7">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c t="s" r="J33" s="7">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K33" s="7"/>
       <c r="L33" s="7"/>
@@ -2546,22 +2550,22 @@
       </c>
       <c r="D34" s="7"/>
       <c t="s" r="E34" s="7">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F34" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G34" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="H34" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I34" s="7">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c t="s" r="J34" s="7">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="K34" s="7"/>
       <c r="L34" s="7"/>
@@ -2579,7 +2583,7 @@
       </c>
       <c r="D35" s="7"/>
       <c t="s" r="E35" s="7">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F35" s="7">
         <v>321</v>
@@ -2588,13 +2592,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H35" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="I35" s="7">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c t="s" r="J35" s="7">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="K35" s="7"/>
       <c r="L35" s="7"/>
@@ -2612,22 +2616,22 @@
       </c>
       <c r="D36" s="7"/>
       <c t="s" r="E36" s="7">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F36" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G36" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="H36" s="8">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c t="s" r="I36" s="7">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c t="s" r="J36" s="7">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="K36" s="7"/>
       <c r="L36" s="7"/>
@@ -2635,7 +2639,7 @@
     </row>
     <row r="37" ht="14.25" customHeight="1">
       <c t="s" r="A37" s="6">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B37" s="7">
         <v>1926</v>
@@ -2645,22 +2649,22 @@
       </c>
       <c r="D37" s="7"/>
       <c t="s" r="E37" s="7">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F37" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G37" s="8">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c t="s" r="H37" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="I37" s="7">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c t="s" r="J37" s="7">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="K37" s="7"/>
       <c r="L37" s="7"/>
@@ -2693,22 +2697,22 @@
       </c>
       <c r="D39" s="7"/>
       <c t="s" r="E39" s="7">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F39" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G39" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="H39" s="8">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c t="s" r="I39" s="7">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c t="s" r="J39" s="7">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="K39" s="7"/>
       <c r="L39" s="7"/>
@@ -2726,22 +2730,22 @@
       </c>
       <c r="D40" s="7"/>
       <c t="s" r="E40" s="7">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F40" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G40" s="8">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c t="s" r="H40" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="I40" s="7">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c t="s" r="J40" s="7">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="K40" s="7"/>
       <c r="L40" s="7"/>
@@ -2759,22 +2763,22 @@
       </c>
       <c r="D41" s="7"/>
       <c t="s" r="E41" s="7">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F41" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G41" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="H41" s="8">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c t="s" r="I41" s="7">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c t="s" r="J41" s="7">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K41" s="7"/>
       <c r="L41" s="7"/>
@@ -2792,22 +2796,22 @@
       </c>
       <c r="D42" s="7"/>
       <c t="s" r="E42" s="7">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F42" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G42" s="8">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c t="s" r="H42" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="I42" s="7">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c t="s" r="J42" s="7">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="K42" s="7"/>
       <c r="L42" s="7"/>
@@ -2825,22 +2829,22 @@
       </c>
       <c r="D43" s="7"/>
       <c t="s" r="E43" s="7">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F43" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G43" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="H43" s="8">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c t="s" r="I43" s="7">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c t="s" r="J43" s="7">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="K43" s="7"/>
       <c r="L43" s="7"/>
@@ -2858,22 +2862,22 @@
       </c>
       <c r="D44" s="7"/>
       <c t="s" r="E44" s="7">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F44" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G44" s="8">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c t="s" r="H44" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="I44" s="7">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c t="s" r="J44" s="7">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="K44" s="7"/>
       <c r="L44" s="7"/>
@@ -2906,22 +2910,22 @@
       </c>
       <c r="D46" s="7"/>
       <c t="s" r="E46" s="7">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F46" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G46" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="H46" s="8">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c t="s" r="I46" s="7">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c t="s" r="J46" s="7">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="K46" s="7"/>
       <c r="L46" s="7"/>
@@ -2939,22 +2943,22 @@
       </c>
       <c r="D47" s="7"/>
       <c t="s" r="E47" s="7">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F47" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G47" s="8">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c t="s" r="H47" s="8">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c t="s" r="I47" s="7">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c t="s" r="J47" s="7">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="K47" s="7"/>
       <c r="L47" s="7"/>
@@ -2972,22 +2976,22 @@
       </c>
       <c r="D48" s="7"/>
       <c t="s" r="E48" s="7">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F48" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G48" s="8">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c t="s" r="H48" s="8">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c t="s" r="I48" s="7">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c t="s" r="J48" s="7">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="K48" s="7"/>
       <c r="L48" s="7"/>
@@ -3020,22 +3024,22 @@
       </c>
       <c r="D50" s="7"/>
       <c t="s" r="E50" s="7">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F50" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G50" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="H50" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="I50" s="7">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c t="s" r="J50" s="7">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="K50" s="7"/>
       <c r="L50" s="7"/>
@@ -3053,22 +3057,22 @@
       </c>
       <c r="D51" s="7"/>
       <c t="s" r="E51" s="7">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F51" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G51" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="H51" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="I51" s="7">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c t="s" r="J51" s="7">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="K51" s="7"/>
       <c r="L51" s="7"/>
@@ -3086,22 +3090,22 @@
       </c>
       <c r="D52" s="7"/>
       <c t="s" r="E52" s="7">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F52" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G52" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="H52" s="8">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c t="s" r="I52" s="7">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c t="s" r="J52" s="7">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="K52" s="7"/>
       <c r="L52" s="7"/>
@@ -3119,22 +3123,22 @@
       </c>
       <c r="D53" s="7"/>
       <c t="s" r="E53" s="7">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F53" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G53" s="8">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c t="s" r="H53" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="I53" s="7">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c t="s" r="J53" s="7">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="K53" s="7"/>
       <c r="L53" s="7"/>
@@ -3167,22 +3171,22 @@
       </c>
       <c r="D55" s="7"/>
       <c t="s" r="E55" s="7">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="F55" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G55" s="8">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c t="s" r="H55" s="8">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c t="s" r="I55" s="7">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c t="s" r="J55" s="7">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="K55" s="7"/>
       <c r="L55" s="7"/>
@@ -3200,22 +3204,22 @@
       </c>
       <c r="D56" s="7"/>
       <c t="s" r="E56" s="7">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="F56" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G56" s="8">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c t="s" r="H56" s="8">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c t="s" r="I56" s="7">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c t="s" r="J56" s="7">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K56" s="7"/>
       <c r="L56" s="7"/>
@@ -3233,22 +3237,22 @@
       </c>
       <c r="D57" s="7"/>
       <c t="s" r="E57" s="7">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="F57" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G57" s="8">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c t="s" r="H57" s="8">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c t="s" r="I57" s="7">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c t="s" r="J57" s="7">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K57" s="7"/>
       <c r="L57" s="7"/>
@@ -3266,22 +3270,22 @@
       </c>
       <c r="D58" s="7"/>
       <c t="s" r="E58" s="7">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="F58" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G58" s="8">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c t="s" r="H58" s="8">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c t="s" r="I58" s="7">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c t="s" r="J58" s="7">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K58" s="7"/>
       <c r="L58" s="7"/>
@@ -3299,22 +3303,22 @@
       </c>
       <c r="D59" s="7"/>
       <c t="s" r="E59" s="7">
+        <v>111</v>
+      </c>
+      <c r="F59" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G59" s="8">
+        <v>85</v>
+      </c>
+      <c t="s" r="H59" s="8">
+        <v>31</v>
+      </c>
+      <c t="s" r="I59" s="7">
         <v>109</v>
       </c>
-      <c r="F59" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G59" s="8">
-        <v>83</v>
-      </c>
-      <c t="s" r="H59" s="8">
-        <v>29</v>
-      </c>
-      <c t="s" r="I59" s="7">
-        <v>107</v>
-      </c>
       <c t="s" r="J59" s="7">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="K59" s="7"/>
       <c r="L59" s="7"/>
@@ -3332,22 +3336,22 @@
       </c>
       <c r="D60" s="7"/>
       <c t="s" r="E60" s="7">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="F60" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G60" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="H60" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="I60" s="7">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c t="s" r="J60" s="7">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="K60" s="7"/>
       <c r="L60" s="7"/>
@@ -3380,22 +3384,22 @@
       </c>
       <c r="D62" s="7"/>
       <c t="s" r="E62" s="7">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="F62" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G62" s="8">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c t="s" r="H62" s="8">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c t="s" r="I62" s="7">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c t="s" r="J62" s="7">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="K62" s="7"/>
       <c r="L62" s="7"/>
@@ -3409,26 +3413,26 @@
         <v>8520</v>
       </c>
       <c t="s" r="C63" s="7">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D63" s="7"/>
       <c t="s" r="E63" s="7">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="F63" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G63" s="8">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c t="s" r="H63" s="8">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c t="s" r="I63" s="7">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c t="s" r="J63" s="7">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="K63" s="7"/>
       <c r="L63" s="7"/>
@@ -3442,26 +3446,26 @@
         <v>8521</v>
       </c>
       <c t="s" r="C64" s="7">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D64" s="7"/>
       <c t="s" r="E64" s="7">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="F64" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G64" s="8">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c t="s" r="H64" s="8">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c t="s" r="I64" s="7">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c t="s" r="J64" s="7">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="K64" s="7"/>
       <c r="L64" s="7"/>
@@ -3479,22 +3483,22 @@
       </c>
       <c r="D65" s="7"/>
       <c t="s" r="E65" s="7">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="F65" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G65" s="8">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c t="s" r="H65" s="8">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c t="s" r="I65" s="7">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c t="s" r="J65" s="7">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="K65" s="7"/>
       <c r="L65" s="7"/>
@@ -3527,22 +3531,22 @@
       </c>
       <c r="D67" s="7"/>
       <c t="s" r="E67" s="7">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F67" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G67" s="8">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c t="s" r="H67" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="I67" s="7">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c t="s" r="J67" s="7">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="K67" s="7"/>
       <c r="L67" s="7"/>
@@ -3560,22 +3564,22 @@
       </c>
       <c r="D68" s="7"/>
       <c t="s" r="E68" s="7">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F68" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G68" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="H68" s="8">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c t="s" r="I68" s="7">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c t="s" r="J68" s="7">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="K68" s="7"/>
       <c r="L68" s="7"/>
@@ -3593,22 +3597,22 @@
       </c>
       <c r="D69" s="7"/>
       <c t="s" r="E69" s="7">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F69" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G69" s="8">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c t="s" r="H69" s="8">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c t="s" r="I69" s="7">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c t="s" r="J69" s="7">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="K69" s="7"/>
       <c r="L69" s="7"/>
@@ -3626,22 +3630,22 @@
       </c>
       <c r="D70" s="7"/>
       <c t="s" r="E70" s="7">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F70" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G70" s="8">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c t="s" r="H70" s="8">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c t="s" r="I70" s="7">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c t="s" r="J70" s="7">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="K70" s="7"/>
       <c r="L70" s="7"/>
@@ -3659,22 +3663,22 @@
       </c>
       <c r="D71" s="7"/>
       <c t="s" r="E71" s="7">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F71" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G71" s="8">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c t="s" r="H71" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="I71" s="7">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c t="s" r="J71" s="7">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="K71" s="7"/>
       <c r="L71" s="7"/>
@@ -3692,22 +3696,22 @@
       </c>
       <c r="D72" s="7"/>
       <c t="s" r="E72" s="7">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F72" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G72" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="H72" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="I72" s="7">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c t="s" r="J72" s="7">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="K72" s="7"/>
       <c r="L72" s="7"/>
@@ -3725,22 +3729,22 @@
       </c>
       <c r="D73" s="7"/>
       <c t="s" r="E73" s="7">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F73" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G73" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="H73" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="I73" s="7">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c t="s" r="J73" s="7">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="K73" s="7"/>
       <c r="L73" s="7"/>
@@ -3773,22 +3777,22 @@
       </c>
       <c r="D75" s="7"/>
       <c t="s" r="E75" s="7">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="F75" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G75" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="H75" s="8">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c t="s" r="I75" s="7">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c t="s" r="J75" s="7">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="K75" s="7"/>
       <c r="L75" s="7"/>
@@ -3806,22 +3810,22 @@
       </c>
       <c r="D76" s="7"/>
       <c t="s" r="E76" s="7">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="F76" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G76" s="8">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c t="s" r="H76" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="I76" s="7">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c t="s" r="J76" s="7">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="K76" s="7"/>
       <c r="L76" s="7"/>
@@ -3839,22 +3843,22 @@
       </c>
       <c r="D77" s="7"/>
       <c t="s" r="E77" s="7">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="F77" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G77" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="H77" s="8">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c t="s" r="I77" s="7">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c t="s" r="J77" s="7">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="K77" s="7"/>
       <c r="L77" s="7"/>
@@ -3872,22 +3876,22 @@
       </c>
       <c r="D78" s="7"/>
       <c t="s" r="E78" s="7">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="F78" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G78" s="8">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c t="s" r="H78" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="I78" s="7">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c t="s" r="J78" s="7">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="K78" s="7"/>
       <c r="L78" s="7"/>
@@ -3905,22 +3909,22 @@
       </c>
       <c r="D79" s="7"/>
       <c t="s" r="E79" s="7">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="F79" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G79" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="H79" s="8">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c t="s" r="I79" s="7">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c t="s" r="J79" s="7">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="K79" s="7"/>
       <c r="L79" s="7"/>
@@ -3938,22 +3942,22 @@
       </c>
       <c r="D80" s="7"/>
       <c t="s" r="E80" s="7">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="F80" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G80" s="8">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c t="s" r="H80" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="I80" s="7">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c t="s" r="J80" s="7">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="K80" s="7"/>
       <c r="L80" s="7"/>
@@ -3961,7 +3965,7 @@
     </row>
     <row r="81" ht="14.25" customHeight="1">
       <c t="s" r="A81" s="6">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B81" s="7">
         <v>960</v>
@@ -3971,22 +3975,22 @@
       </c>
       <c r="D81" s="7"/>
       <c t="s" r="E81" s="7">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="F81" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G81" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="H81" s="8">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c t="s" r="I81" s="7">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c t="s" r="J81" s="7">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="K81" s="7"/>
       <c r="L81" s="7"/>
@@ -4019,7 +4023,7 @@
       </c>
       <c r="D83" s="7"/>
       <c t="s" r="E83" s="7">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F83" s="7">
         <v>321</v>
@@ -4028,20 +4032,20 @@
         <v>16</v>
       </c>
       <c t="s" r="H83" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="I83" s="7">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c t="s" r="J83" s="7">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c t="s" r="K83" s="7">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="L83" s="7"/>
       <c t="s" r="M83" s="7">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="84" ht="14.25" customHeight="1">
@@ -4056,22 +4060,22 @@
       </c>
       <c r="D84" s="7"/>
       <c t="s" r="E84" s="7">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F84" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G84" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="H84" s="8">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c t="s" r="I84" s="7">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c t="s" r="J84" s="7">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="K84" s="7"/>
       <c r="L84" s="7"/>
@@ -4089,22 +4093,22 @@
       </c>
       <c r="D85" s="7"/>
       <c t="s" r="E85" s="7">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F85" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G85" s="8">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c t="s" r="H85" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="I85" s="7">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c t="s" r="J85" s="7">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="K85" s="7"/>
       <c r="L85" s="7"/>
@@ -4137,22 +4141,22 @@
       </c>
       <c r="D87" s="7"/>
       <c t="s" r="E87" s="7">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F87" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G87" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="H87" s="8">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c t="s" r="I87" s="7">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c t="s" r="J87" s="7">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="K87" s="7"/>
       <c r="L87" s="7"/>
@@ -4170,22 +4174,22 @@
       </c>
       <c r="D88" s="7"/>
       <c t="s" r="E88" s="7">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F88" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G88" s="8">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c t="s" r="H88" s="8">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c t="s" r="I88" s="7">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c t="s" r="J88" s="7">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="K88" s="7"/>
       <c r="L88" s="7"/>
@@ -4203,22 +4207,22 @@
       </c>
       <c r="D89" s="7"/>
       <c t="s" r="E89" s="7">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F89" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G89" s="8">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c t="s" r="H89" s="8">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c t="s" r="I89" s="7">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c t="s" r="J89" s="7">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="K89" s="7"/>
       <c r="L89" s="7"/>
@@ -4236,22 +4240,22 @@
       </c>
       <c r="D90" s="7"/>
       <c t="s" r="E90" s="7">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F90" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G90" s="8">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c t="s" r="H90" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="I90" s="7">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c t="s" r="J90" s="7">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K90" s="7"/>
       <c r="L90" s="7"/>
@@ -4269,22 +4273,22 @@
       </c>
       <c r="D91" s="7"/>
       <c t="s" r="E91" s="7">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F91" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G91" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="H91" s="8">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c t="s" r="I91" s="7">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c t="s" r="J91" s="7">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="K91" s="7"/>
       <c r="L91" s="7"/>
@@ -4302,22 +4306,22 @@
       </c>
       <c r="D92" s="7"/>
       <c t="s" r="E92" s="7">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F92" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G92" s="8">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c t="s" r="H92" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="I92" s="7">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c t="s" r="J92" s="7">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="K92" s="7"/>
       <c r="L92" s="7"/>
@@ -4335,22 +4339,22 @@
       </c>
       <c r="D93" s="7"/>
       <c t="s" r="E93" s="7">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F93" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G93" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="H93" s="8">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c t="s" r="I93" s="7">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c t="s" r="J93" s="7">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="K93" s="7"/>
       <c r="L93" s="7"/>
@@ -4368,22 +4372,22 @@
       </c>
       <c r="D94" s="7"/>
       <c t="s" r="E94" s="7">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F94" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G94" s="8">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c t="s" r="H94" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="I94" s="7">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c t="s" r="J94" s="7">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="K94" s="7"/>
       <c r="L94" s="7"/>
@@ -4416,22 +4420,22 @@
       </c>
       <c r="D96" s="7"/>
       <c t="s" r="E96" s="7">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F96" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G96" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="H96" s="8">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c t="s" r="I96" s="7">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c t="s" r="J96" s="7">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="K96" s="7"/>
       <c r="L96" s="7"/>
@@ -4449,22 +4453,22 @@
       </c>
       <c r="D97" s="7"/>
       <c t="s" r="E97" s="7">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F97" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G97" s="8">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c t="s" r="H97" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="I97" s="7">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c t="s" r="J97" s="7">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="K97" s="7"/>
       <c r="L97" s="7"/>
@@ -4482,22 +4486,22 @@
       </c>
       <c r="D98" s="7"/>
       <c t="s" r="E98" s="7">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F98" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G98" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="H98" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="I98" s="7">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c t="s" r="J98" s="7">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="K98" s="7"/>
       <c r="L98" s="7"/>
@@ -4515,22 +4519,22 @@
       </c>
       <c r="D99" s="7"/>
       <c t="s" r="E99" s="7">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F99" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G99" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="H99" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="I99" s="7">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c t="s" r="J99" s="7">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="K99" s="7"/>
       <c r="L99" s="7"/>
@@ -4563,19 +4567,19 @@
       </c>
       <c r="D101" s="7"/>
       <c t="s" r="E101" s="7">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="F101" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G101" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="H101" s="8">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c t="s" r="I101" s="7">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c t="s" r="J101" s="7">
         <v>18</v>
@@ -4596,22 +4600,22 @@
       </c>
       <c r="D102" s="7"/>
       <c t="s" r="E102" s="7">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="F102" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G102" s="8">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c t="s" r="H102" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="I102" s="7">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c t="s" r="J102" s="7">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="K102" s="7"/>
       <c r="L102" s="7"/>
@@ -4629,22 +4633,22 @@
       </c>
       <c r="D103" s="7"/>
       <c t="s" r="E103" s="7">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="F103" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G103" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="H103" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="I103" s="7">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c t="s" r="J103" s="7">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="K103" s="7"/>
       <c r="L103" s="7"/>
@@ -4677,22 +4681,22 @@
       </c>
       <c r="D105" s="7"/>
       <c t="s" r="E105" s="7">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F105" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G105" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="H105" s="8">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c t="s" r="I105" s="7">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c t="s" r="J105" s="7">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K105" s="7"/>
       <c r="L105" s="7"/>
@@ -4710,22 +4714,22 @@
       </c>
       <c r="D106" s="7"/>
       <c t="s" r="E106" s="7">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F106" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G106" s="8">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c t="s" r="H106" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="I106" s="7">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c t="s" r="J106" s="7">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="K106" s="7"/>
       <c r="L106" s="7"/>
@@ -4743,22 +4747,22 @@
       </c>
       <c r="D107" s="7"/>
       <c t="s" r="E107" s="7">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F107" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G107" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="H107" s="8">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c t="s" r="I107" s="7">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c t="s" r="J107" s="7">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="K107" s="7"/>
       <c r="L107" s="7"/>
@@ -4776,22 +4780,22 @@
       </c>
       <c r="D108" s="7"/>
       <c t="s" r="E108" s="7">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F108" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G108" s="8">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c t="s" r="H108" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="I108" s="7">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c t="s" r="J108" s="7">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="K108" s="7"/>
       <c r="L108" s="7"/>
@@ -4809,22 +4813,22 @@
       </c>
       <c r="D109" s="7"/>
       <c t="s" r="E109" s="7">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F109" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G109" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="H109" s="8">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c t="s" r="I109" s="7">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c t="s" r="J109" s="7">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="K109" s="7"/>
       <c r="L109" s="7"/>
@@ -4842,22 +4846,22 @@
       </c>
       <c r="D110" s="7"/>
       <c t="s" r="E110" s="7">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F110" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G110" s="8">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c t="s" r="H110" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="I110" s="7">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c t="s" r="J110" s="7">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="K110" s="7"/>
       <c r="L110" s="7"/>
@@ -4890,22 +4894,22 @@
       </c>
       <c r="D112" s="7"/>
       <c t="s" r="E112" s="7">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F112" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G112" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="H112" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="I112" s="7">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c t="s" r="J112" s="7">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="K112" s="7"/>
       <c r="L112" s="7"/>
@@ -4923,22 +4927,22 @@
       </c>
       <c r="D113" s="7"/>
       <c t="s" r="E113" s="7">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F113" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G113" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="H113" s="8">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c t="s" r="I113" s="7">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c t="s" r="J113" s="7">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="K113" s="7"/>
       <c r="L113" s="7"/>
@@ -4956,22 +4960,22 @@
       </c>
       <c r="D114" s="7"/>
       <c t="s" r="E114" s="7">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F114" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G114" s="8">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c t="s" r="H114" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="I114" s="7">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c t="s" r="J114" s="7">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="K114" s="7"/>
       <c r="L114" s="7"/>
@@ -4989,22 +4993,22 @@
       </c>
       <c r="D115" s="7"/>
       <c t="s" r="E115" s="7">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F115" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G115" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="H115" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="I115" s="7">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c t="s" r="J115" s="7">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="K115" s="7"/>
       <c r="L115" s="7"/>
@@ -5022,22 +5026,22 @@
       </c>
       <c r="D116" s="7"/>
       <c t="s" r="E116" s="7">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F116" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G116" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="H116" s="8">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c t="s" r="I116" s="7">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c t="s" r="J116" s="7">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="K116" s="7"/>
       <c r="L116" s="7"/>
@@ -5055,22 +5059,22 @@
       </c>
       <c r="D117" s="7"/>
       <c t="s" r="E117" s="7">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F117" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G117" s="8">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c t="s" r="H117" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="I117" s="7">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c t="s" r="J117" s="7">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K117" s="7"/>
       <c r="L117" s="7"/>
@@ -5088,22 +5092,22 @@
       </c>
       <c r="D118" s="7"/>
       <c t="s" r="E118" s="7">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F118" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G118" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="H118" s="8">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c t="s" r="I118" s="7">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c t="s" r="J118" s="7">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="K118" s="7"/>
       <c r="L118" s="7"/>
@@ -5121,22 +5125,22 @@
       </c>
       <c r="D119" s="7"/>
       <c t="s" r="E119" s="7">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F119" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G119" s="8">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c t="s" r="H119" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="I119" s="7">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c t="s" r="J119" s="7">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="K119" s="7"/>
       <c r="L119" s="7"/>
@@ -5169,22 +5173,22 @@
       </c>
       <c r="D121" s="7"/>
       <c t="s" r="E121" s="7">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F121" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G121" s="8">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c t="s" r="H121" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="I121" s="7">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c t="s" r="J121" s="7">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="K121" s="7"/>
       <c r="L121" s="7"/>
@@ -5202,22 +5206,22 @@
       </c>
       <c r="D122" s="7"/>
       <c t="s" r="E122" s="7">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F122" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G122" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="H122" s="8">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c t="s" r="I122" s="7">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c t="s" r="J122" s="7">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="K122" s="7"/>
       <c r="L122" s="7"/>
@@ -5235,22 +5239,22 @@
       </c>
       <c r="D123" s="7"/>
       <c t="s" r="E123" s="7">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F123" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G123" s="8">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c t="s" r="H123" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="I123" s="7">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c t="s" r="J123" s="7">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="K123" s="7"/>
       <c r="L123" s="7"/>
@@ -5258,7 +5262,7 @@
     </row>
     <row r="124" ht="14.25" customHeight="1">
       <c t="s" r="A124" s="6">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B124" s="7">
         <v>920</v>
@@ -5268,22 +5272,22 @@
       </c>
       <c r="D124" s="7"/>
       <c t="s" r="E124" s="7">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F124" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G124" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="H124" s="8">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c t="s" r="I124" s="7">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c t="s" r="J124" s="7">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="K124" s="7"/>
       <c r="L124" s="7"/>
@@ -5316,22 +5320,22 @@
       </c>
       <c r="D126" s="7"/>
       <c t="s" r="E126" s="7">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="F126" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G126" s="8">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c t="s" r="H126" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="I126" s="7">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c t="s" r="J126" s="7">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K126" s="7"/>
       <c r="L126" s="7"/>
@@ -5349,22 +5353,22 @@
       </c>
       <c r="D127" s="7"/>
       <c t="s" r="E127" s="7">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="F127" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G127" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="H127" s="8">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c t="s" r="I127" s="7">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c t="s" r="J127" s="7">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="K127" s="7"/>
       <c r="L127" s="7"/>
@@ -5382,22 +5386,22 @@
       </c>
       <c r="D128" s="7"/>
       <c t="s" r="E128" s="7">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="F128" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G128" s="8">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c t="s" r="H128" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="I128" s="7">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c t="s" r="J128" s="7">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="K128" s="7"/>
       <c r="L128" s="7"/>
@@ -5415,22 +5419,22 @@
       </c>
       <c r="D129" s="7"/>
       <c t="s" r="E129" s="7">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="F129" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G129" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="H129" s="8">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c t="s" r="I129" s="7">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c t="s" r="J129" s="7">
-        <v>205</v>
+        <v>21</v>
       </c>
       <c r="K129" s="7"/>
       <c r="L129" s="7"/>
@@ -5448,22 +5452,22 @@
       </c>
       <c r="D130" s="7"/>
       <c t="s" r="E130" s="7">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="F130" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G130" s="8">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c t="s" r="H130" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="I130" s="7">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c t="s" r="J130" s="7">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K130" s="7"/>
       <c r="L130" s="7"/>
@@ -5496,22 +5500,22 @@
       </c>
       <c r="D132" s="7"/>
       <c t="s" r="E132" s="7">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F132" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G132" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="H132" s="8">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c t="s" r="I132" s="7">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c t="s" r="J132" s="7">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K132" s="7"/>
       <c r="L132" s="7"/>
@@ -5529,22 +5533,22 @@
       </c>
       <c r="D133" s="7"/>
       <c t="s" r="E133" s="7">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F133" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G133" s="8">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c t="s" r="H133" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="I133" s="7">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c t="s" r="J133" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="K133" s="7"/>
       <c r="L133" s="7"/>
@@ -5562,22 +5566,22 @@
       </c>
       <c r="D134" s="7"/>
       <c t="s" r="E134" s="7">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F134" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G134" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="H134" s="8">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c t="s" r="I134" s="7">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c t="s" r="J134" s="7">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="K134" s="7"/>
       <c r="L134" s="7"/>
@@ -5585,7 +5589,7 @@
     </row>
     <row r="135" ht="15" customHeight="1">
       <c t="s" r="A135" s="6">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B135" s="7">
         <v>972</v>
@@ -5595,22 +5599,22 @@
       </c>
       <c r="D135" s="7"/>
       <c t="s" r="E135" s="7">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F135" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G135" s="8">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c t="s" r="H135" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="I135" s="7">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c t="s" r="J135" s="7">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="K135" s="7"/>
       <c r="L135" s="7"/>
@@ -5643,22 +5647,22 @@
       </c>
       <c r="D137" s="7"/>
       <c t="s" r="E137" s="7">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F137" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G137" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="H137" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="I137" s="7">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c t="s" r="J137" s="7">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="K137" s="7"/>
       <c r="L137" s="7"/>
@@ -5676,19 +5680,19 @@
       </c>
       <c r="D138" s="7"/>
       <c t="s" r="E138" s="7">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F138" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G138" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="H138" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="I138" s="7">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c t="s" r="J138" s="7">
         <v>19</v>
@@ -5709,22 +5713,22 @@
       </c>
       <c r="D139" s="7"/>
       <c t="s" r="E139" s="7">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F139" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G139" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="H139" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I139" s="7">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c t="s" r="J139" s="7">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K139" s="7"/>
       <c r="L139" s="7"/>
@@ -5738,11 +5742,11 @@
         <v>7706</v>
       </c>
       <c t="s" r="C140" s="7">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D140" s="7"/>
       <c t="s" r="E140" s="7">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F140" s="7">
         <v>321</v>
@@ -5751,13 +5755,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H140" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="I140" s="7">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c t="s" r="J140" s="7">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="K140" s="7"/>
       <c r="L140" s="7"/>
@@ -5765,32 +5769,32 @@
     </row>
     <row r="141" ht="14.25" customHeight="1">
       <c t="s" r="A141" s="6">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B141" s="7">
         <v>7706</v>
       </c>
       <c t="s" r="C141" s="7">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D141" s="7"/>
       <c t="s" r="E141" s="7">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F141" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G141" s="8">
+        <v>31</v>
+      </c>
+      <c t="s" r="H141" s="8">
+        <v>219</v>
+      </c>
+      <c t="s" r="I141" s="7">
+        <v>220</v>
+      </c>
+      <c t="s" r="J141" s="7">
         <v>29</v>
-      </c>
-      <c t="s" r="H141" s="8">
-        <v>218</v>
-      </c>
-      <c t="s" r="I141" s="7">
-        <v>219</v>
-      </c>
-      <c t="s" r="J141" s="7">
-        <v>27</v>
       </c>
       <c r="K141" s="7"/>
       <c r="L141" s="7"/>
@@ -5823,22 +5827,22 @@
       </c>
       <c r="D143" s="7"/>
       <c t="s" r="E143" s="7">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F143" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G143" s="8">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c t="s" r="H143" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="I143" s="7">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c t="s" r="J143" s="7">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="K143" s="7"/>
       <c r="L143" s="7"/>
@@ -5856,22 +5860,22 @@
       </c>
       <c r="D144" s="7"/>
       <c t="s" r="E144" s="7">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F144" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G144" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="H144" s="8">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c t="s" r="I144" s="7">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c t="s" r="J144" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="K144" s="7"/>
       <c r="L144" s="7"/>
@@ -5889,22 +5893,22 @@
       </c>
       <c r="D145" s="7"/>
       <c t="s" r="E145" s="7">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F145" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G145" s="8">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c t="s" r="H145" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="I145" s="7">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c t="s" r="J145" s="7">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="K145" s="7"/>
       <c r="L145" s="7"/>
@@ -5912,7 +5916,7 @@
     </row>
     <row r="146" ht="14.25" customHeight="1">
       <c t="s" r="A146" s="6">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B146" s="7">
         <v>932</v>
@@ -5922,22 +5926,22 @@
       </c>
       <c r="D146" s="7"/>
       <c t="s" r="E146" s="7">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F146" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G146" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="H146" s="8">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c t="s" r="I146" s="7">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c t="s" r="J146" s="7">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="K146" s="7"/>
       <c r="L146" s="7"/>
@@ -5970,22 +5974,22 @@
       </c>
       <c r="D148" s="7"/>
       <c t="s" r="E148" s="7">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F148" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G148" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="H148" s="8">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c t="s" r="I148" s="7">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c t="s" r="J148" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="K148" s="7"/>
       <c r="L148" s="7"/>
@@ -6003,22 +6007,22 @@
       </c>
       <c r="D149" s="7"/>
       <c t="s" r="E149" s="7">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F149" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G149" s="8">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c t="s" r="H149" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="I149" s="7">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c t="s" r="J149" s="7">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K149" s="7"/>
       <c r="L149" s="7"/>
@@ -6036,22 +6040,22 @@
       </c>
       <c r="D150" s="7"/>
       <c t="s" r="E150" s="7">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F150" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G150" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="H150" s="8">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c t="s" r="I150" s="7">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c t="s" r="J150" s="7">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K150" s="7"/>
       <c r="L150" s="7"/>
@@ -6069,22 +6073,22 @@
       </c>
       <c r="D151" s="7"/>
       <c t="s" r="E151" s="7">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F151" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G151" s="8">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c t="s" r="H151" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="I151" s="7">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c t="s" r="J151" s="7">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K151" s="7"/>
       <c r="L151" s="7"/>
@@ -6092,7 +6096,7 @@
     </row>
     <row r="152" ht="14.25" customHeight="1">
       <c t="s" r="A152" s="6">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B152" s="7">
         <v>862</v>
@@ -6102,22 +6106,22 @@
       </c>
       <c r="D152" s="7"/>
       <c t="s" r="E152" s="7">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F152" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G152" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="H152" s="8">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c t="s" r="I152" s="7">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c t="s" r="J152" s="7">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="K152" s="7"/>
       <c r="L152" s="7"/>
@@ -6150,22 +6154,22 @@
       </c>
       <c r="D154" s="7"/>
       <c t="s" r="E154" s="7">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F154" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G154" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="H154" s="8">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c t="s" r="I154" s="7">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c t="s" r="J154" s="7">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K154" s="7"/>
       <c r="L154" s="7"/>
@@ -6183,22 +6187,22 @@
       </c>
       <c r="D155" s="7"/>
       <c t="s" r="E155" s="7">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F155" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G155" s="8">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c t="s" r="H155" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="I155" s="7">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c t="s" r="J155" s="7">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K155" s="7"/>
       <c r="L155" s="7"/>
@@ -6216,22 +6220,22 @@
       </c>
       <c r="D156" s="7"/>
       <c t="s" r="E156" s="7">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F156" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G156" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="H156" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I156" s="7">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c t="s" r="J156" s="7">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="K156" s="7"/>
       <c r="L156" s="7"/>
@@ -6249,7 +6253,7 @@
       </c>
       <c r="D157" s="7"/>
       <c t="s" r="E157" s="7">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F157" s="7">
         <v>321</v>
@@ -6258,13 +6262,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H157" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="I157" s="7">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c t="s" r="J157" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="K157" s="7"/>
       <c r="L157" s="7"/>
@@ -6282,22 +6286,22 @@
       </c>
       <c r="D158" s="7"/>
       <c t="s" r="E158" s="7">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F158" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G158" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="H158" s="8">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c t="s" r="I158" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c t="s" r="J158" s="7">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="K158" s="7"/>
       <c r="L158" s="7"/>
@@ -6315,22 +6319,22 @@
       </c>
       <c r="D159" s="7"/>
       <c t="s" r="E159" s="7">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F159" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G159" s="8">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c t="s" r="H159" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="I159" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c t="s" r="J159" s="7">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K159" s="7"/>
       <c r="L159" s="7"/>
@@ -6363,22 +6367,22 @@
       </c>
       <c r="D161" s="7"/>
       <c t="s" r="E161" s="7">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F161" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G161" s="8">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c t="s" r="H161" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I161" s="7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c t="s" r="J161" s="7">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="K161" s="7"/>
       <c r="L161" s="7"/>
@@ -6392,11 +6396,11 @@
         <v>5068</v>
       </c>
       <c t="s" r="C162" s="7">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D162" s="7"/>
       <c t="s" r="E162" s="7">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F162" s="7">
         <v>321</v>
@@ -6405,13 +6409,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H162" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="I162" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c t="s" r="J162" s="7">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="K162" s="7"/>
       <c r="L162" s="7"/>
@@ -6425,26 +6429,26 @@
         <v>5068</v>
       </c>
       <c t="s" r="C163" s="7">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D163" s="7"/>
       <c t="s" r="E163" s="7">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F163" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G163" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="H163" s="8">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c t="s" r="I163" s="7">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c t="s" r="J163" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="K163" s="7"/>
       <c r="L163" s="7"/>
@@ -6452,32 +6456,32 @@
     </row>
     <row r="164" ht="14.25" customHeight="1">
       <c t="s" r="A164" s="6">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B164" s="7">
         <v>5069</v>
       </c>
       <c t="s" r="C164" s="7">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D164" s="7"/>
       <c t="s" r="E164" s="7">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F164" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G164" s="8">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c t="s" r="H164" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="I164" s="7">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c t="s" r="J164" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="K164" s="7"/>
       <c r="L164" s="7"/>
@@ -6510,22 +6514,22 @@
       </c>
       <c r="D166" s="7"/>
       <c t="s" r="E166" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F166" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G166" s="8">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c t="s" r="H166" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="I166" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c t="s" r="J166" s="7">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="K166" s="7"/>
       <c r="L166" s="7"/>
@@ -6543,22 +6547,22 @@
       </c>
       <c r="D167" s="7"/>
       <c t="s" r="E167" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F167" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G167" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="H167" s="8">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c t="s" r="I167" s="7">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c t="s" r="J167" s="7">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="K167" s="7"/>
       <c r="L167" s="7"/>
@@ -6591,22 +6595,22 @@
       </c>
       <c r="D169" s="7"/>
       <c t="s" r="E169" s="7">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F169" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G169" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="H169" s="8">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c t="s" r="I169" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c t="s" r="J169" s="7">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K169" s="7"/>
       <c r="L169" s="7"/>
@@ -6624,22 +6628,22 @@
       </c>
       <c r="D170" s="7"/>
       <c t="s" r="E170" s="7">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F170" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G170" s="8">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c t="s" r="H170" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="I170" s="7">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c t="s" r="J170" s="7">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="K170" s="7"/>
       <c r="L170" s="7"/>
@@ -6672,22 +6676,22 @@
       </c>
       <c r="D172" s="7"/>
       <c t="s" r="E172" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F172" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G172" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="H172" s="8">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c t="s" r="I172" s="7">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c t="s" r="J172" s="7">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K172" s="7"/>
       <c r="L172" s="7"/>
@@ -6705,22 +6709,22 @@
       </c>
       <c r="D173" s="7"/>
       <c t="s" r="E173" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F173" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G173" s="8">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c t="s" r="H173" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="I173" s="7">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c t="s" r="J173" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="K173" s="7"/>
       <c r="L173" s="7"/>
@@ -6738,22 +6742,22 @@
       </c>
       <c r="D174" s="7"/>
       <c t="s" r="E174" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F174" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G174" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="H174" s="8">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c t="s" r="I174" s="7">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c t="s" r="J174" s="7">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="K174" s="7"/>
       <c r="L174" s="7"/>
@@ -6771,22 +6775,22 @@
       </c>
       <c r="D175" s="7"/>
       <c t="s" r="E175" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F175" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G175" s="8">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c t="s" r="H175" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="I175" s="7">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c t="s" r="J175" s="7">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="K175" s="7"/>
       <c r="L175" s="7"/>
@@ -6819,22 +6823,22 @@
       </c>
       <c r="D177" s="7"/>
       <c t="s" r="E177" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F177" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G177" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="H177" s="8">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c t="s" r="I177" s="7">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c t="s" r="J177" s="7">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="K177" s="7"/>
       <c r="L177" s="7"/>
@@ -6852,22 +6856,22 @@
       </c>
       <c r="D178" s="7"/>
       <c t="s" r="E178" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F178" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G178" s="8">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c t="s" r="H178" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="I178" s="7">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c t="s" r="J178" s="7">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="K178" s="7"/>
       <c r="L178" s="7"/>
@@ -6885,22 +6889,22 @@
       </c>
       <c r="D179" s="7"/>
       <c t="s" r="E179" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F179" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G179" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="H179" s="8">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c t="s" r="I179" s="7">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c t="s" r="J179" s="7">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="K179" s="7"/>
       <c r="L179" s="7"/>
@@ -6918,22 +6922,22 @@
       </c>
       <c r="D180" s="7"/>
       <c t="s" r="E180" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F180" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G180" s="8">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c t="s" r="H180" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="I180" s="7">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c t="s" r="J180" s="7">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="K180" s="7"/>
       <c r="L180" s="7"/>
@@ -6951,22 +6955,22 @@
       </c>
       <c r="D181" s="7"/>
       <c t="s" r="E181" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F181" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G181" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="H181" s="8">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c t="s" r="I181" s="7">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c t="s" r="J181" s="7">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="K181" s="7"/>
       <c r="L181" s="7"/>
@@ -6984,22 +6988,22 @@
       </c>
       <c r="D182" s="7"/>
       <c t="s" r="E182" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F182" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G182" s="8">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c t="s" r="H182" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="I182" s="7">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c t="s" r="J182" s="7">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="K182" s="7"/>
       <c r="L182" s="7"/>
@@ -7017,22 +7021,22 @@
       </c>
       <c r="D183" s="7"/>
       <c t="s" r="E183" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F183" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G183" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="H183" s="8">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c t="s" r="I183" s="7">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c t="s" r="J183" s="7">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="K183" s="7"/>
       <c r="L183" s="7"/>
@@ -7040,7 +7044,7 @@
     </row>
     <row r="184" ht="14.25" customHeight="1">
       <c t="s" r="A184" s="6">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B184" s="7">
         <v>7527</v>
@@ -7050,22 +7054,22 @@
       </c>
       <c r="D184" s="7"/>
       <c t="s" r="E184" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F184" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G184" s="8">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c t="s" r="H184" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="I184" s="7">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c t="s" r="J184" s="7">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="K184" s="7"/>
       <c r="L184" s="7"/>
@@ -7098,22 +7102,22 @@
       </c>
       <c r="D186" s="7"/>
       <c t="s" r="E186" s="7">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F186" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G186" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="H186" s="8">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c t="s" r="I186" s="7">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c t="s" r="J186" s="7">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="K186" s="7"/>
       <c r="L186" s="7"/>
@@ -7131,22 +7135,22 @@
       </c>
       <c r="D187" s="7"/>
       <c t="s" r="E187" s="7">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F187" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G187" s="8">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c t="s" r="H187" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="I187" s="7">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c t="s" r="J187" s="7">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="K187" s="7"/>
       <c r="L187" s="7"/>
@@ -7164,22 +7168,22 @@
       </c>
       <c r="D188" s="7"/>
       <c t="s" r="E188" s="7">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F188" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G188" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="H188" s="8">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c t="s" r="I188" s="7">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c t="s" r="J188" s="7">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K188" s="7"/>
       <c r="L188" s="7"/>
@@ -7197,22 +7201,22 @@
       </c>
       <c r="D189" s="7"/>
       <c t="s" r="E189" s="7">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F189" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G189" s="8">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c t="s" r="H189" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="I189" s="7">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c t="s" r="J189" s="7">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="K189" s="7"/>
       <c r="L189" s="7"/>
@@ -7230,22 +7234,22 @@
       </c>
       <c r="D190" s="7"/>
       <c t="s" r="E190" s="7">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F190" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G190" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="H190" s="8">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c t="s" r="I190" s="7">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c t="s" r="J190" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="K190" s="7"/>
       <c r="L190" s="7"/>
@@ -7263,22 +7267,22 @@
       </c>
       <c r="D191" s="7"/>
       <c t="s" r="E191" s="7">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F191" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G191" s="8">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c t="s" r="H191" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="I191" s="7">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c t="s" r="J191" s="7">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="K191" s="7"/>
       <c r="L191" s="7"/>
@@ -7296,22 +7300,22 @@
       </c>
       <c r="D192" s="7"/>
       <c t="s" r="E192" s="7">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F192" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G192" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="H192" s="8">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c t="s" r="I192" s="7">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c t="s" r="J192" s="7">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="K192" s="7"/>
       <c r="L192" s="7"/>
@@ -7319,7 +7323,7 @@
     </row>
     <row r="193" ht="14.25" customHeight="1">
       <c t="s" r="A193" s="6">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B193" s="7">
         <v>3909</v>
@@ -7329,22 +7333,22 @@
       </c>
       <c r="D193" s="7"/>
       <c t="s" r="E193" s="7">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F193" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G193" s="8">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c t="s" r="H193" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="I193" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c t="s" r="J193" s="7">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="K193" s="7"/>
       <c r="L193" s="7"/>
@@ -7377,22 +7381,22 @@
       </c>
       <c r="D195" s="7"/>
       <c t="s" r="E195" s="7">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F195" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G195" s="8">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c t="s" r="H195" s="8">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c t="s" r="I195" s="7">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c t="s" r="J195" s="7">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="K195" s="7"/>
       <c r="L195" s="7"/>
@@ -7410,22 +7414,22 @@
       </c>
       <c r="D196" s="7"/>
       <c t="s" r="E196" s="7">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F196" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G196" s="8">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c t="s" r="H196" s="8">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c t="s" r="I196" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c t="s" r="J196" s="7">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K196" s="7"/>
       <c r="L196" s="7"/>
@@ -7443,22 +7447,22 @@
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G197" s="8">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c t="s" r="H197" s="8">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c t="s" r="I197" s="7">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c t="s" r="J197" s="7">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="K197" s="7"/>
       <c r="L197" s="7"/>
@@ -7476,22 +7480,22 @@
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F198" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G198" s="8">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c t="s" r="H198" s="8">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c t="s" r="I198" s="7">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c t="s" r="J198" s="7">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K198" s="7"/>
       <c r="L198" s="7"/>
@@ -7524,22 +7528,22 @@
       </c>
       <c r="D200" s="7"/>
       <c t="s" r="E200" s="7">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F200" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G200" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="H200" s="8">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c t="s" r="I200" s="7">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c t="s" r="J200" s="7">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="K200" s="7"/>
       <c r="L200" s="7"/>
@@ -7557,22 +7561,22 @@
       </c>
       <c r="D201" s="7"/>
       <c t="s" r="E201" s="7">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F201" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G201" s="8">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c t="s" r="H201" s="8">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c t="s" r="I201" s="7">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c t="s" r="J201" s="7">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="K201" s="7"/>
       <c r="L201" s="7"/>
@@ -7590,22 +7594,22 @@
       </c>
       <c r="D202" s="7"/>
       <c t="s" r="E202" s="7">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F202" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G202" s="8">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c t="s" r="H202" s="8">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c t="s" r="I202" s="7">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c t="s" r="J202" s="7">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="K202" s="7"/>
       <c r="L202" s="7"/>
@@ -7623,22 +7627,22 @@
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F203" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G203" s="8">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c t="s" r="H203" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="I203" s="7">
         <v>19</v>
       </c>
       <c t="s" r="J203" s="7">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="K203" s="7"/>
       <c r="L203" s="7"/>
@@ -7656,22 +7660,22 @@
       </c>
       <c r="D204" s="7"/>
       <c t="s" r="E204" s="7">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F204" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G204" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="H204" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I204" s="7">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c t="s" r="J204" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="K204" s="7"/>
       <c r="L204" s="7"/>
@@ -7689,7 +7693,7 @@
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
@@ -7698,13 +7702,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H205" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="I205" s="7">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c t="s" r="J205" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="K205" s="7"/>
       <c r="L205" s="7"/>
@@ -7737,7 +7741,7 @@
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F207" s="7">
         <v>321</v>
@@ -7746,13 +7750,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H207" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="I207" s="7">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c t="s" r="J207" s="7">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="K207" s="7"/>
       <c r="L207" s="7"/>
@@ -7770,22 +7774,22 @@
       </c>
       <c r="D208" s="7"/>
       <c t="s" r="E208" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F208" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G208" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="H208" s="8">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c t="s" r="I208" s="7">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c t="s" r="J208" s="7">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="K208" s="7"/>
       <c r="L208" s="7"/>
@@ -7803,22 +7807,22 @@
       </c>
       <c r="D209" s="7"/>
       <c t="s" r="E209" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F209" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G209" s="8">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c t="s" r="H209" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="I209" s="7">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c t="s" r="J209" s="7">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="K209" s="7"/>
       <c r="L209" s="7"/>
@@ -7836,22 +7840,22 @@
       </c>
       <c r="D210" s="7"/>
       <c t="s" r="E210" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F210" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G210" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="H210" s="8">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c t="s" r="I210" s="7">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c t="s" r="J210" s="7">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K210" s="7"/>
       <c r="L210" s="7"/>
@@ -7869,22 +7873,22 @@
       </c>
       <c r="D211" s="7"/>
       <c t="s" r="E211" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F211" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G211" s="8">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c t="s" r="H211" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="I211" s="7">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c t="s" r="J211" s="7">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="K211" s="7"/>
       <c r="L211" s="7"/>
@@ -7902,22 +7906,22 @@
       </c>
       <c r="D212" s="7"/>
       <c t="s" r="E212" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F212" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G212" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="H212" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="I212" s="7">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c t="s" r="J212" s="7">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="K212" s="7"/>
       <c r="L212" s="7"/>
@@ -7950,22 +7954,22 @@
       </c>
       <c r="D214" s="7"/>
       <c t="s" r="E214" s="7">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F214" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G214" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="H214" s="8">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c t="s" r="I214" s="7">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c t="s" r="J214" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="K214" s="7"/>
       <c r="L214" s="7"/>
@@ -7983,22 +7987,22 @@
       </c>
       <c r="D215" s="7"/>
       <c t="s" r="E215" s="7">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F215" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G215" s="8">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c t="s" r="H215" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="I215" s="7">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c t="s" r="J215" s="7">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K215" s="7"/>
       <c r="L215" s="7"/>
@@ -8016,22 +8020,22 @@
       </c>
       <c r="D216" s="7"/>
       <c t="s" r="E216" s="7">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F216" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G216" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="H216" s="8">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c t="s" r="I216" s="7">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c t="s" r="J216" s="7">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="K216" s="7"/>
       <c r="L216" s="7"/>
@@ -8049,19 +8053,19 @@
       </c>
       <c r="D217" s="7"/>
       <c t="s" r="E217" s="7">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F217" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G217" s="8">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c t="s" r="H217" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="I217" s="7">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c t="s" r="J217" s="7">
         <v>19</v>
@@ -8082,22 +8086,22 @@
       </c>
       <c r="D218" s="7"/>
       <c t="s" r="E218" s="7">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F218" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G218" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="H218" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="I218" s="7">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c t="s" r="J218" s="7">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="K218" s="7"/>
       <c r="L218" s="7"/>
@@ -8115,22 +8119,22 @@
       </c>
       <c r="D219" s="7"/>
       <c t="s" r="E219" s="7">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F219" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G219" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="H219" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="I219" s="7">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c t="s" r="J219" s="7">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="K219" s="7"/>
       <c r="L219" s="7"/>
@@ -8163,22 +8167,22 @@
       </c>
       <c r="D221" s="7"/>
       <c t="s" r="E221" s="7">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F221" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G221" s="8">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c t="s" r="H221" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="I221" s="7">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c t="s" r="J221" s="7">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="K221" s="7"/>
       <c r="L221" s="7"/>
@@ -8196,22 +8200,22 @@
       </c>
       <c r="D222" s="7"/>
       <c t="s" r="E222" s="7">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F222" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G222" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="H222" s="8">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c t="s" r="I222" s="7">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c t="s" r="J222" s="7">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="K222" s="7"/>
       <c r="L222" s="7"/>
@@ -8229,22 +8233,22 @@
       </c>
       <c r="D223" s="7"/>
       <c t="s" r="E223" s="7">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F223" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G223" s="8">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c t="s" r="H223" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="I223" s="7">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c t="s" r="J223" s="7">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="K223" s="7"/>
       <c r="L223" s="7"/>
@@ -8262,22 +8266,22 @@
       </c>
       <c r="D224" s="7"/>
       <c t="s" r="E224" s="7">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F224" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G224" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="H224" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I224" s="7">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c t="s" r="J224" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="K224" s="7"/>
       <c r="L224" s="7"/>
@@ -8295,7 +8299,7 @@
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
@@ -8304,13 +8308,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H225" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="I225" s="7">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c t="s" r="J225" s="7">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="K225" s="7"/>
       <c r="L225" s="7"/>
@@ -8318,7 +8322,7 @@
     </row>
     <row r="226" ht="14.25" customHeight="1">
       <c t="s" r="A226" s="6">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B226" s="7">
         <v>982</v>
@@ -8328,22 +8332,22 @@
       </c>
       <c r="D226" s="7"/>
       <c t="s" r="E226" s="7">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F226" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G226" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="H226" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I226" s="7">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c t="s" r="J226" s="7">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="K226" s="7"/>
       <c r="L226" s="7"/>
@@ -8376,22 +8380,22 @@
       </c>
       <c r="D228" s="7"/>
       <c t="s" r="E228" s="7">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F228" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G228" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="H228" s="8">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c t="s" r="I228" s="7">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c t="s" r="J228" s="7">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="K228" s="7"/>
       <c r="L228" s="7"/>
@@ -8409,22 +8413,22 @@
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G229" s="8">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c t="s" r="H229" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="I229" s="7">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c t="s" r="J229" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="K229" s="7"/>
       <c r="L229" s="7"/>
@@ -8442,22 +8446,22 @@
       </c>
       <c r="D230" s="7"/>
       <c t="s" r="E230" s="7">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F230" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G230" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="H230" s="8">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c t="s" r="I230" s="7">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c t="s" r="J230" s="7">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="K230" s="7"/>
       <c r="L230" s="7"/>
@@ -8475,22 +8479,22 @@
       </c>
       <c r="D231" s="7"/>
       <c t="s" r="E231" s="7">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F231" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G231" s="8">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c t="s" r="H231" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="I231" s="7">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c t="s" r="J231" s="7">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="K231" s="7"/>
       <c r="L231" s="7"/>
@@ -8508,22 +8512,22 @@
       </c>
       <c r="D232" s="7"/>
       <c t="s" r="E232" s="7">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F232" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G232" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="H232" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="I232" s="7">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c t="s" r="J232" s="7">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="K232" s="7"/>
       <c r="L232" s="7"/>
@@ -8556,22 +8560,22 @@
       </c>
       <c r="D234" s="7"/>
       <c t="s" r="E234" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F234" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G234" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="H234" s="8">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c t="s" r="I234" s="7">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c t="s" r="J234" s="7">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="K234" s="7"/>
       <c r="L234" s="7"/>
@@ -8589,22 +8593,22 @@
       </c>
       <c r="D235" s="7"/>
       <c t="s" r="E235" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F235" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G235" s="8">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c t="s" r="H235" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="I235" s="7">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c t="s" r="J235" s="7">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="K235" s="7"/>
       <c r="L235" s="7"/>
@@ -8637,22 +8641,22 @@
       </c>
       <c r="D237" s="7"/>
       <c t="s" r="E237" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F237" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G237" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="H237" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="I237" s="7">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c t="s" r="J237" s="7">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="K237" s="7"/>
       <c r="L237" s="7"/>
@@ -8670,22 +8674,22 @@
       </c>
       <c r="D238" s="7"/>
       <c t="s" r="E238" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F238" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G238" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="H238" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="I238" s="7">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c t="s" r="J238" s="7">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="K238" s="7"/>
       <c r="L238" s="7"/>
@@ -8703,22 +8707,22 @@
       </c>
       <c r="D239" s="7"/>
       <c t="s" r="E239" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F239" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G239" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="H239" s="8">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c t="s" r="I239" s="7">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c t="s" r="J239" s="7">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K239" s="7"/>
       <c r="L239" s="7"/>
@@ -8736,22 +8740,22 @@
       </c>
       <c r="D240" s="7"/>
       <c t="s" r="E240" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F240" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G240" s="8">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c t="s" r="H240" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="I240" s="7">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c t="s" r="J240" s="7">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="K240" s="7"/>
       <c r="L240" s="7"/>
@@ -8769,22 +8773,22 @@
       </c>
       <c r="D241" s="7"/>
       <c t="s" r="E241" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F241" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G241" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="H241" s="8">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c t="s" r="I241" s="7">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c t="s" r="J241" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="K241" s="7"/>
       <c r="L241" s="7"/>
@@ -8802,22 +8806,22 @@
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F242" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G242" s="8">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c t="s" r="H242" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="I242" s="7">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c t="s" r="J242" s="7">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="K242" s="7"/>
       <c r="L242" s="7"/>
@@ -8850,29 +8854,29 @@
       </c>
       <c r="D244" s="7"/>
       <c t="s" r="E244" s="7">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F244" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G244" s="8">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c t="s" r="H244" s="8">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c t="s" r="I244" s="7">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c t="s" r="J244" s="7">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c t="s" r="K244" s="7">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="L244" s="7"/>
       <c t="s" r="M244" s="7">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="245" ht="15" customHeight="1">
@@ -8887,29 +8891,29 @@
       </c>
       <c r="D245" s="7"/>
       <c t="s" r="E245" s="7">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F245" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G245" s="8">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c t="s" r="H245" s="8">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c t="s" r="I245" s="7">
         <v>18</v>
       </c>
       <c t="s" r="J245" s="7">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c t="s" r="K245" s="7">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="L245" s="7"/>
       <c t="s" r="M245" s="7">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="246" ht="14.25" customHeight="1">
@@ -8924,29 +8928,29 @@
       </c>
       <c r="D246" s="7"/>
       <c t="s" r="E246" s="7">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F246" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G246" s="8">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c t="s" r="H246" s="8">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c t="s" r="I246" s="7">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c t="s" r="J246" s="7">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c t="s" r="K246" s="7">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="L246" s="7"/>
       <c t="s" r="M246" s="7">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="247" ht="14.25" customHeight="1">
@@ -8961,29 +8965,29 @@
       </c>
       <c r="D247" s="7"/>
       <c t="s" r="E247" s="7">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F247" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G247" s="8">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c t="s" r="H247" s="8">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c t="s" r="I247" s="7">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c t="s" r="J247" s="7">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c t="s" r="K247" s="7">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="L247" s="7"/>
       <c t="s" r="M247" s="7">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="248" ht="14.25" customHeight="1">
@@ -8998,29 +9002,29 @@
       </c>
       <c r="D248" s="7"/>
       <c t="s" r="E248" s="7">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F248" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G248" s="8">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c t="s" r="H248" s="8">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c t="s" r="I248" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c t="s" r="J248" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c t="s" r="K248" s="7">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L248" s="7"/>
       <c t="s" r="M248" s="7">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="249" ht="14.25" customHeight="1">
@@ -9035,22 +9039,22 @@
       </c>
       <c r="D249" s="7"/>
       <c t="s" r="E249" s="7">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F249" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G249" s="8">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c t="s" r="H249" s="8">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c t="s" r="I249" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c t="s" r="J249" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="K249" s="7"/>
       <c r="L249" s="7"/>
@@ -9083,22 +9087,22 @@
       </c>
       <c r="D251" s="7"/>
       <c t="s" r="E251" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F251" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G251" s="8">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c t="s" r="H251" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="I251" s="7">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c t="s" r="J251" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="K251" s="7"/>
       <c r="L251" s="7"/>
@@ -9116,22 +9120,22 @@
       </c>
       <c r="D252" s="7"/>
       <c t="s" r="E252" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F252" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G252" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="H252" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="I252" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c t="s" r="J252" s="7">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K252" s="7"/>
       <c r="L252" s="7"/>
@@ -9149,22 +9153,22 @@
       </c>
       <c r="D253" s="7"/>
       <c t="s" r="E253" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F253" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G253" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="H253" s="8">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c t="s" r="I253" s="7">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c t="s" r="J253" s="7">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="K253" s="7"/>
       <c r="L253" s="7"/>
@@ -9182,22 +9186,22 @@
       </c>
       <c r="D254" s="7"/>
       <c t="s" r="E254" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F254" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G254" s="8">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c t="s" r="H254" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="I254" s="7">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c t="s" r="J254" s="7">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K254" s="7"/>
       <c r="L254" s="7"/>
@@ -9215,22 +9219,22 @@
       </c>
       <c r="D255" s="7"/>
       <c t="s" r="E255" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F255" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G255" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="H255" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="I255" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c t="s" r="J255" s="7">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="K255" s="7"/>
       <c r="L255" s="7"/>
@@ -9248,22 +9252,22 @@
       </c>
       <c r="D256" s="7"/>
       <c t="s" r="E256" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F256" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G256" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="H256" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="I256" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c t="s" r="J256" s="7">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K256" s="7"/>
       <c r="L256" s="7"/>
@@ -9296,22 +9300,22 @@
       </c>
       <c r="D258" s="7"/>
       <c t="s" r="E258" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F258" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G258" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="H258" s="8">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c t="s" r="I258" s="7">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c t="s" r="J258" s="7">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="K258" s="7"/>
       <c r="L258" s="7"/>
@@ -9329,22 +9333,22 @@
       </c>
       <c r="D259" s="7"/>
       <c t="s" r="E259" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F259" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G259" s="8">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c t="s" r="H259" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="I259" s="7">
         <v>19</v>
       </c>
       <c t="s" r="J259" s="7">
-        <v>205</v>
+        <v>21</v>
       </c>
       <c r="K259" s="7"/>
       <c r="L259" s="7"/>
@@ -9362,22 +9366,22 @@
       </c>
       <c r="D260" s="7"/>
       <c t="s" r="E260" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F260" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G260" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="H260" s="8">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c t="s" r="I260" s="7">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c t="s" r="J260" s="7">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K260" s="7"/>
       <c r="L260" s="7"/>
@@ -9385,7 +9389,7 @@
     </row>
     <row r="261" ht="14.25" customHeight="1">
       <c t="s" r="A261" s="6">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B261" s="7">
         <v>821</v>
@@ -9395,22 +9399,22 @@
       </c>
       <c r="D261" s="7"/>
       <c t="s" r="E261" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F261" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G261" s="8">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c t="s" r="H261" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="I261" s="7">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c t="s" r="J261" s="7">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="K261" s="7"/>
       <c r="L261" s="7"/>
@@ -9443,22 +9447,22 @@
       </c>
       <c r="D263" s="7"/>
       <c t="s" r="E263" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F263" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G263" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="H263" s="8">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c t="s" r="I263" s="7">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c t="s" r="J263" s="7">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="K263" s="7"/>
       <c r="L263" s="7"/>
@@ -9476,22 +9480,22 @@
       </c>
       <c r="D264" s="7"/>
       <c t="s" r="E264" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F264" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G264" s="8">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c t="s" r="H264" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="I264" s="7">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c t="s" r="J264" s="7">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="K264" s="7"/>
       <c r="L264" s="7"/>
@@ -9509,22 +9513,22 @@
       </c>
       <c r="D265" s="7"/>
       <c t="s" r="E265" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F265" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G265" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="H265" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="I265" s="7">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c t="s" r="J265" s="7">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="K265" s="7"/>
       <c r="L265" s="7"/>
@@ -9542,22 +9546,22 @@
       </c>
       <c r="D266" s="7"/>
       <c t="s" r="E266" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F266" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G266" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="H266" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="I266" s="7">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c t="s" r="J266" s="7">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="K266" s="7"/>
       <c r="L266" s="7"/>
@@ -9590,22 +9594,22 @@
       </c>
       <c r="D268" s="7"/>
       <c t="s" r="E268" s="7">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F268" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G268" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="H268" s="8">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c t="s" r="I268" s="7">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c t="s" r="J268" s="7">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="K268" s="7"/>
       <c r="L268" s="7"/>
@@ -9623,22 +9627,22 @@
       </c>
       <c r="D269" s="7"/>
       <c t="s" r="E269" s="7">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F269" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G269" s="8">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c t="s" r="H269" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="I269" s="7">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c t="s" r="J269" s="7">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K269" s="7"/>
       <c r="L269" s="7"/>
@@ -9656,22 +9660,22 @@
       </c>
       <c r="D270" s="7"/>
       <c t="s" r="E270" s="7">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F270" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G270" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="H270" s="8">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c t="s" r="I270" s="7">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c t="s" r="J270" s="7">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K270" s="7"/>
       <c r="L270" s="7"/>
@@ -9689,22 +9693,22 @@
       </c>
       <c r="D271" s="7"/>
       <c t="s" r="E271" s="7">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F271" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G271" s="8">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c t="s" r="H271" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="I271" s="7">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c t="s" r="J271" s="7">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="K271" s="7"/>
       <c r="L271" s="7"/>
@@ -9722,22 +9726,22 @@
       </c>
       <c r="D272" s="7"/>
       <c t="s" r="E272" s="7">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F272" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G272" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="H272" s="8">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c t="s" r="I272" s="7">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c t="s" r="J272" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="K272" s="7"/>
       <c r="L272" s="7"/>
@@ -9755,22 +9759,22 @@
       </c>
       <c r="D273" s="7"/>
       <c t="s" r="E273" s="7">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F273" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G273" s="8">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c t="s" r="H273" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="I273" s="7">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c t="s" r="J273" s="7">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="K273" s="7"/>
       <c r="L273" s="7"/>
@@ -9803,22 +9807,22 @@
       </c>
       <c r="D275" s="7"/>
       <c t="s" r="E275" s="7">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F275" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G275" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="H275" s="8">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c t="s" r="I275" s="7">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c t="s" r="J275" s="7">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="K275" s="7"/>
       <c r="L275" s="7"/>
@@ -9836,22 +9840,22 @@
       </c>
       <c r="D276" s="7"/>
       <c t="s" r="E276" s="7">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F276" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G276" s="8">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c t="s" r="H276" s="8">
+        <v>31</v>
+      </c>
+      <c t="s" r="I276" s="7">
+        <v>154</v>
+      </c>
+      <c t="s" r="J276" s="7">
         <v>29</v>
-      </c>
-      <c t="s" r="I276" s="7">
-        <v>152</v>
-      </c>
-      <c t="s" r="J276" s="7">
-        <v>27</v>
       </c>
       <c r="K276" s="7"/>
       <c r="L276" s="7"/>
@@ -9869,22 +9873,22 @@
       </c>
       <c r="D277" s="7"/>
       <c t="s" r="E277" s="7">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F277" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G277" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="H277" s="8">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c t="s" r="I277" s="7">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c t="s" r="J277" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="K277" s="7"/>
       <c r="L277" s="7"/>
@@ -9902,22 +9906,22 @@
       </c>
       <c r="D278" s="7"/>
       <c t="s" r="E278" s="7">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F278" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G278" s="8">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c t="s" r="H278" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="I278" s="7">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c t="s" r="J278" s="7">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="K278" s="7"/>
       <c r="L278" s="7"/>
@@ -9935,22 +9939,22 @@
       </c>
       <c r="D279" s="7"/>
       <c t="s" r="E279" s="7">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F279" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G279" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="H279" s="8">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c t="s" r="I279" s="7">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c t="s" r="J279" s="7">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K279" s="7"/>
       <c r="L279" s="7"/>
@@ -9968,22 +9972,22 @@
       </c>
       <c r="D280" s="7"/>
       <c t="s" r="E280" s="7">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F280" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G280" s="8">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c t="s" r="H280" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="I280" s="7">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c t="s" r="J280" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="K280" s="7"/>
       <c r="L280" s="7"/>
@@ -10001,22 +10005,22 @@
       </c>
       <c r="D281" s="7"/>
       <c t="s" r="E281" s="7">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F281" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G281" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="H281" s="8">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c t="s" r="I281" s="7">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c t="s" r="J281" s="7">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K281" s="7"/>
       <c r="L281" s="7"/>
@@ -10034,22 +10038,22 @@
       </c>
       <c r="D282" s="7"/>
       <c t="s" r="E282" s="7">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F282" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G282" s="8">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c t="s" r="H282" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="I282" s="7">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c t="s" r="J282" s="7">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K282" s="7"/>
       <c r="L282" s="7"/>
@@ -10082,22 +10086,22 @@
       </c>
       <c r="D284" s="7"/>
       <c t="s" r="E284" s="7">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F284" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G284" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="H284" s="8">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c t="s" r="I284" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c t="s" r="J284" s="7">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="K284" s="7"/>
       <c r="L284" s="7"/>
@@ -10115,22 +10119,22 @@
       </c>
       <c r="D285" s="7"/>
       <c t="s" r="E285" s="7">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F285" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G285" s="8">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c t="s" r="H285" s="8">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c t="s" r="I285" s="7">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c t="s" r="J285" s="7">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="K285" s="7"/>
       <c r="L285" s="7"/>
@@ -10148,22 +10152,22 @@
       </c>
       <c r="D286" s="7"/>
       <c t="s" r="E286" s="7">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F286" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G286" s="8">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c t="s" r="H286" s="8">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c t="s" r="I286" s="7">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c t="s" r="J286" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="K286" s="7"/>
       <c r="L286" s="7"/>
@@ -10181,22 +10185,22 @@
       </c>
       <c r="D287" s="7"/>
       <c t="s" r="E287" s="7">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F287" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G287" s="8">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c t="s" r="H287" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="I287" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="J287" s="7">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="K287" s="7"/>
       <c r="L287" s="7"/>
@@ -10229,19 +10233,19 @@
       </c>
       <c r="D289" s="7"/>
       <c t="s" r="E289" s="7">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F289" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G289" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="H289" s="8">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c t="s" r="I289" s="7">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c t="s" r="J289" s="7">
         <v>19</v>
@@ -10262,22 +10266,22 @@
       </c>
       <c r="D290" s="7"/>
       <c t="s" r="E290" s="7">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F290" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G290" s="8">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c t="s" r="H290" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="I290" s="7">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c t="s" r="J290" s="7">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="K290" s="7"/>
       <c r="L290" s="7"/>
@@ -10310,22 +10314,22 @@
       </c>
       <c r="D292" s="7"/>
       <c t="s" r="E292" s="7">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F292" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G292" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="H292" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="I292" s="7">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c t="s" r="J292" s="7">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="K292" s="7"/>
       <c r="L292" s="7"/>
@@ -10343,22 +10347,22 @@
       </c>
       <c r="D293" s="7"/>
       <c t="s" r="E293" s="7">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F293" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G293" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="H293" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="I293" s="7">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c t="s" r="J293" s="7">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="K293" s="7"/>
       <c r="L293" s="7"/>
@@ -10376,22 +10380,22 @@
       </c>
       <c r="D294" s="7"/>
       <c t="s" r="E294" s="7">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F294" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G294" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="H294" s="8">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c t="s" r="I294" s="7">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c t="s" r="J294" s="7">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="K294" s="7"/>
       <c r="L294" s="7"/>
@@ -10409,22 +10413,22 @@
       </c>
       <c r="D295" s="7"/>
       <c t="s" r="E295" s="7">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F295" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G295" s="8">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c t="s" r="H295" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="I295" s="7">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c t="s" r="J295" s="7">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="K295" s="7"/>
       <c r="L295" s="7"/>
@@ -10457,22 +10461,22 @@
       </c>
       <c r="D297" s="7"/>
       <c t="s" r="E297" s="7">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F297" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G297" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="H297" s="8">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c t="s" r="I297" s="7">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c t="s" r="J297" s="7">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="K297" s="7"/>
       <c r="L297" s="7"/>
@@ -10490,22 +10494,22 @@
       </c>
       <c r="D298" s="7"/>
       <c t="s" r="E298" s="7">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F298" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G298" s="8">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c t="s" r="H298" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="I298" s="7">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c t="s" r="J298" s="7">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="K298" s="7"/>
       <c r="L298" s="7"/>
@@ -10523,22 +10527,22 @@
       </c>
       <c r="D299" s="7"/>
       <c t="s" r="E299" s="7">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F299" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G299" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="H299" s="8">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c t="s" r="I299" s="7">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c t="s" r="J299" s="7">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="K299" s="7"/>
       <c r="L299" s="7"/>
@@ -10556,22 +10560,22 @@
       </c>
       <c r="D300" s="7"/>
       <c t="s" r="E300" s="7">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F300" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G300" s="8">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c t="s" r="H300" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="I300" s="7">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c t="s" r="J300" s="7">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="K300" s="7"/>
       <c r="L300" s="7"/>
@@ -10589,22 +10593,22 @@
       </c>
       <c r="D301" s="7"/>
       <c t="s" r="E301" s="7">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F301" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G301" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="H301" s="8">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c t="s" r="I301" s="7">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c t="s" r="J301" s="7">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="K301" s="7"/>
       <c r="L301" s="7"/>
@@ -10622,22 +10626,22 @@
       </c>
       <c r="D302" s="7"/>
       <c t="s" r="E302" s="7">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F302" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G302" s="8">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c t="s" r="H302" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="I302" s="7">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c t="s" r="J302" s="7">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="K302" s="7"/>
       <c r="L302" s="7"/>
@@ -10670,22 +10674,22 @@
       </c>
       <c r="D304" s="7"/>
       <c t="s" r="E304" s="7">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F304" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G304" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="H304" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="I304" s="7">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c t="s" r="J304" s="7">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="K304" s="7"/>
       <c r="L304" s="7"/>
@@ -10703,22 +10707,22 @@
       </c>
       <c r="D305" s="7"/>
       <c t="s" r="E305" s="7">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F305" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G305" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="H305" s="8">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c t="s" r="I305" s="7">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c t="s" r="J305" s="7">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="K305" s="7"/>
       <c r="L305" s="7"/>
@@ -10736,22 +10740,22 @@
       </c>
       <c r="D306" s="7"/>
       <c t="s" r="E306" s="7">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F306" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G306" s="8">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c t="s" r="H306" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="I306" s="7">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c t="s" r="J306" s="7">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="K306" s="7"/>
       <c r="L306" s="7"/>
@@ -10769,22 +10773,22 @@
       </c>
       <c r="D307" s="7"/>
       <c t="s" r="E307" s="7">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F307" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G307" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="H307" s="8">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c t="s" r="I307" s="7">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c t="s" r="J307" s="7">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="K307" s="7"/>
       <c r="L307" s="7"/>
@@ -10802,22 +10806,22 @@
       </c>
       <c r="D308" s="7"/>
       <c t="s" r="E308" s="7">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F308" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G308" s="8">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c t="s" r="H308" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="I308" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c t="s" r="J308" s="7">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="K308" s="7"/>
       <c r="L308" s="7"/>
@@ -10850,22 +10854,22 @@
       </c>
       <c r="D310" s="7"/>
       <c t="s" r="E310" s="7">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F310" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G310" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="H310" s="8">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c t="s" r="I310" s="7">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c t="s" r="J310" s="7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="K310" s="7"/>
       <c r="L310" s="7"/>
@@ -10883,22 +10887,22 @@
       </c>
       <c r="D311" s="7"/>
       <c t="s" r="E311" s="7">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F311" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G311" s="8">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c t="s" r="H311" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="I311" s="7">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c t="s" r="J311" s="7">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K311" s="7"/>
       <c r="L311" s="7"/>
@@ -10916,22 +10920,22 @@
       </c>
       <c r="D312" s="7"/>
       <c t="s" r="E312" s="7">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F312" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G312" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="H312" s="8">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c t="s" r="I312" s="7">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c t="s" r="J312" s="7">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="K312" s="7"/>
       <c r="L312" s="7"/>
@@ -10949,22 +10953,22 @@
       </c>
       <c r="D313" s="7"/>
       <c t="s" r="E313" s="7">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F313" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G313" s="8">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c t="s" r="H313" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="I313" s="7">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c t="s" r="J313" s="7">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K313" s="7"/>
       <c r="L313" s="7"/>
@@ -10982,22 +10986,22 @@
       </c>
       <c r="D314" s="7"/>
       <c t="s" r="E314" s="7">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F314" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G314" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="H314" s="8">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c t="s" r="I314" s="7">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c t="s" r="J314" s="7">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="K314" s="7"/>
       <c r="L314" s="7"/>
@@ -11015,22 +11019,22 @@
       </c>
       <c r="D315" s="7"/>
       <c t="s" r="E315" s="7">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F315" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G315" s="8">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c t="s" r="H315" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="I315" s="7">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c t="s" r="J315" s="7">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="K315" s="7"/>
       <c r="L315" s="7"/>
@@ -11048,22 +11052,22 @@
       </c>
       <c r="D316" s="7"/>
       <c t="s" r="E316" s="7">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F316" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G316" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="H316" s="8">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c t="s" r="I316" s="7">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c t="s" r="J316" s="7">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="K316" s="7"/>
       <c r="L316" s="7"/>
@@ -11071,7 +11075,7 @@
     </row>
     <row r="317" ht="14.25" customHeight="1">
       <c t="s" r="A317" s="6">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B317" s="7">
         <v>3949</v>
@@ -11081,22 +11085,22 @@
       </c>
       <c r="D317" s="7"/>
       <c t="s" r="E317" s="7">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F317" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G317" s="8">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c t="s" r="H317" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="I317" s="7">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c t="s" r="J317" s="7">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="K317" s="7"/>
       <c r="L317" s="7"/>
@@ -11129,22 +11133,22 @@
       </c>
       <c r="D319" s="7"/>
       <c t="s" r="E319" s="7">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F319" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G319" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="H319" s="8">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c t="s" r="I319" s="7">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c t="s" r="J319" s="7">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="K319" s="7"/>
       <c r="L319" s="7"/>
@@ -11162,22 +11166,22 @@
       </c>
       <c r="D320" s="7"/>
       <c t="s" r="E320" s="7">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F320" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G320" s="8">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c t="s" r="H320" s="8">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c t="s" r="I320" s="7">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c t="s" r="J320" s="7">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="K320" s="7"/>
       <c r="L320" s="7"/>
@@ -11195,22 +11199,22 @@
       </c>
       <c r="D321" s="7"/>
       <c t="s" r="E321" s="7">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F321" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G321" s="8">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c t="s" r="H321" s="8">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c t="s" r="I321" s="7">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c t="s" r="J321" s="7">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="K321" s="7"/>
       <c r="L321" s="7"/>
@@ -11228,22 +11232,22 @@
       </c>
       <c r="D322" s="7"/>
       <c t="s" r="E322" s="7">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F322" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G322" s="8">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c t="s" r="H322" s="8">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c t="s" r="I322" s="7">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c t="s" r="J322" s="7">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K322" s="7"/>
       <c r="L322" s="7"/>
@@ -11276,22 +11280,22 @@
       </c>
       <c r="D324" s="7"/>
       <c t="s" r="E324" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F324" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G324" s="8">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c t="s" r="H324" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="I324" s="7">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c t="s" r="J324" s="7">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K324" s="7"/>
       <c r="L324" s="7"/>
@@ -11309,22 +11313,22 @@
       </c>
       <c r="D325" s="7"/>
       <c t="s" r="E325" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F325" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G325" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="H325" s="8">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c t="s" r="I325" s="7">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c t="s" r="J325" s="7">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="K325" s="7"/>
       <c r="L325" s="7"/>
@@ -11342,22 +11346,22 @@
       </c>
       <c r="D326" s="7"/>
       <c t="s" r="E326" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F326" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G326" s="8">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c t="s" r="H326" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="I326" s="7">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c t="s" r="J326" s="7">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="K326" s="7"/>
       <c r="L326" s="7"/>
@@ -11390,22 +11394,22 @@
       </c>
       <c r="D328" s="7"/>
       <c t="s" r="E328" s="7">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="F328" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G328" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="H328" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="I328" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c t="s" r="J328" s="7">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="K328" s="7"/>
       <c r="L328" s="7"/>
@@ -11423,22 +11427,22 @@
       </c>
       <c r="D329" s="7"/>
       <c t="s" r="E329" s="7">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="F329" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G329" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="H329" s="8">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c t="s" r="I329" s="7">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c t="s" r="J329" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="K329" s="7"/>
       <c r="L329" s="7"/>
@@ -11456,22 +11460,22 @@
       </c>
       <c r="D330" s="7"/>
       <c t="s" r="E330" s="7">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="F330" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G330" s="8">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c t="s" r="H330" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="I330" s="7">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c t="s" r="J330" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="K330" s="7"/>
       <c r="L330" s="7"/>
@@ -11489,22 +11493,22 @@
       </c>
       <c r="D331" s="7"/>
       <c t="s" r="E331" s="7">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="F331" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G331" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="H331" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="I331" s="7">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c t="s" r="J331" s="7">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="K331" s="7"/>
       <c r="L331" s="7"/>
@@ -11537,22 +11541,22 @@
       </c>
       <c r="D333" s="7"/>
       <c t="s" r="E333" s="7">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F333" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G333" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="H333" s="8">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c t="s" r="I333" s="7">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c t="s" r="J333" s="7">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="K333" s="7"/>
       <c r="L333" s="7"/>
@@ -11570,22 +11574,22 @@
       </c>
       <c r="D334" s="7"/>
       <c t="s" r="E334" s="7">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F334" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G334" s="8">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c t="s" r="H334" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="I334" s="7">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c t="s" r="J334" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="K334" s="7"/>
       <c r="L334" s="7"/>
@@ -11603,22 +11607,22 @@
       </c>
       <c r="D335" s="7"/>
       <c t="s" r="E335" s="7">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F335" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G335" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="H335" s="8">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c t="s" r="I335" s="7">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c t="s" r="J335" s="7">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K335" s="7"/>
       <c r="L335" s="7"/>
@@ -11636,22 +11640,22 @@
       </c>
       <c r="D336" s="7"/>
       <c t="s" r="E336" s="7">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F336" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G336" s="8">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c t="s" r="H336" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="I336" s="7">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c t="s" r="J336" s="7">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="K336" s="7"/>
       <c r="L336" s="7"/>
@@ -11669,22 +11673,22 @@
       </c>
       <c r="D337" s="7"/>
       <c t="s" r="E337" s="7">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F337" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G337" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="H337" s="8">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c t="s" r="I337" s="7">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c t="s" r="J337" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="K337" s="7"/>
       <c r="L337" s="7"/>
@@ -11702,22 +11706,22 @@
       </c>
       <c r="D338" s="7"/>
       <c t="s" r="E338" s="7">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F338" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G338" s="8">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c t="s" r="H338" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="I338" s="7">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c t="s" r="J338" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="K338" s="7"/>
       <c r="L338" s="7"/>
@@ -11735,22 +11739,22 @@
       </c>
       <c r="D339" s="7"/>
       <c t="s" r="E339" s="7">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F339" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G339" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="H339" s="8">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c t="s" r="I339" s="7">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c t="s" r="J339" s="7">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K339" s="7"/>
       <c r="L339" s="7"/>
@@ -11764,26 +11768,26 @@
         <v>8020</v>
       </c>
       <c t="s" r="C340" s="7">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D340" s="7"/>
       <c t="s" r="E340" s="7">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F340" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G340" s="8">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c t="s" r="H340" s="8">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c t="s" r="I340" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c t="s" r="J340" s="7">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="K340" s="7"/>
       <c r="L340" s="7"/>
@@ -11791,32 +11795,32 @@
     </row>
     <row r="341" ht="14.25" customHeight="1">
       <c t="s" r="A341" s="6">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B341" s="7">
         <v>8021</v>
       </c>
       <c t="s" r="C341" s="7">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D341" s="7"/>
       <c t="s" r="E341" s="7">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F341" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G341" s="8">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c t="s" r="H341" s="8">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c t="s" r="I341" s="7">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c t="s" r="J341" s="7">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="K341" s="7"/>
       <c r="L341" s="7"/>
@@ -11849,22 +11853,22 @@
       </c>
       <c r="D343" s="7"/>
       <c t="s" r="E343" s="7">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F343" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G343" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="H343" s="8">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c t="s" r="I343" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c t="s" r="J343" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="K343" s="7"/>
       <c r="L343" s="7"/>
@@ -11882,22 +11886,22 @@
       </c>
       <c r="D344" s="7"/>
       <c t="s" r="E344" s="7">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F344" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G344" s="8">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c t="s" r="H344" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="I344" s="7">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c t="s" r="J344" s="7">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="K344" s="7"/>
       <c r="L344" s="7"/>
@@ -11930,22 +11934,22 @@
       </c>
       <c r="D346" s="7"/>
       <c t="s" r="E346" s="7">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F346" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G346" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="H346" s="8">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c t="s" r="I346" s="7">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c t="s" r="J346" s="7">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K346" s="7"/>
       <c r="L346" s="7"/>
@@ -11963,22 +11967,22 @@
       </c>
       <c r="D347" s="7"/>
       <c t="s" r="E347" s="7">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F347" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G347" s="8">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c t="s" r="H347" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="I347" s="7">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c t="s" r="J347" s="7">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K347" s="7"/>
       <c r="L347" s="7"/>
@@ -11996,22 +12000,22 @@
       </c>
       <c r="D348" s="7"/>
       <c t="s" r="E348" s="7">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F348" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G348" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="H348" s="8">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c t="s" r="I348" s="7">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c t="s" r="J348" s="7">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="K348" s="7"/>
       <c r="L348" s="7"/>
@@ -12029,22 +12033,22 @@
       </c>
       <c r="D349" s="7"/>
       <c t="s" r="E349" s="7">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F349" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G349" s="8">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c t="s" r="H349" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="I349" s="7">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c t="s" r="J349" s="7">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="K349" s="7"/>
       <c r="L349" s="7"/>
@@ -12062,22 +12066,22 @@
       </c>
       <c r="D350" s="7"/>
       <c t="s" r="E350" s="7">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F350" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G350" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="H350" s="8">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c t="s" r="I350" s="7">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c t="s" r="J350" s="7">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="K350" s="7"/>
       <c r="L350" s="7"/>
@@ -12095,22 +12099,22 @@
       </c>
       <c r="D351" s="7"/>
       <c t="s" r="E351" s="7">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F351" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G351" s="8">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c t="s" r="H351" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="I351" s="7">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c t="s" r="J351" s="7">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K351" s="7"/>
       <c r="L351" s="7"/>
@@ -12143,7 +12147,7 @@
       </c>
       <c r="D353" s="7"/>
       <c t="s" r="E353" s="7">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F353" s="7">
         <v>321</v>
@@ -12152,13 +12156,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H353" s="8">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c t="s" r="I353" s="7">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c t="s" r="J353" s="7">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="K353" s="7"/>
       <c r="L353" s="7"/>
@@ -12176,22 +12180,22 @@
       </c>
       <c r="D354" s="7"/>
       <c t="s" r="E354" s="7">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F354" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G354" s="8">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c t="s" r="H354" s="8">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c t="s" r="I354" s="7">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c t="s" r="J354" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="K354" s="7"/>
       <c r="L354" s="7"/>
@@ -12209,22 +12213,22 @@
       </c>
       <c r="D355" s="7"/>
       <c t="s" r="E355" s="7">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F355" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G355" s="8">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c t="s" r="H355" s="8">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c t="s" r="I355" s="7">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c t="s" r="J355" s="7">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="K355" s="7"/>
       <c r="L355" s="7"/>
@@ -12242,22 +12246,22 @@
       </c>
       <c r="D356" s="7"/>
       <c t="s" r="E356" s="7">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F356" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G356" s="8">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c t="s" r="H356" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I356" s="7">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c t="s" r="J356" s="7">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="K356" s="7"/>
       <c r="L356" s="7"/>
@@ -12275,7 +12279,7 @@
       </c>
       <c r="D357" s="7"/>
       <c t="s" r="E357" s="7">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F357" s="7">
         <v>321</v>
@@ -12284,13 +12288,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H357" s="8">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c t="s" r="I357" s="7">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c t="s" r="J357" s="7">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="K357" s="7"/>
       <c r="L357" s="7"/>
@@ -12323,22 +12327,22 @@
       </c>
       <c r="D359" s="7"/>
       <c t="s" r="E359" s="7">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F359" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G359" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="H359" s="8">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c t="s" r="I359" s="7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c t="s" r="J359" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="K359" s="7"/>
       <c r="L359" s="7"/>
@@ -12356,22 +12360,22 @@
       </c>
       <c r="D360" s="7"/>
       <c t="s" r="E360" s="7">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F360" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G360" s="8">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c t="s" r="H360" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="I360" s="7">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c t="s" r="J360" s="7">
-        <v>352</v>
+        <v>20</v>
       </c>
       <c r="K360" s="7"/>
       <c r="L360" s="7"/>
@@ -12389,22 +12393,22 @@
       </c>
       <c r="D361" s="7"/>
       <c t="s" r="E361" s="7">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F361" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G361" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="H361" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="I361" s="7">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c t="s" r="J361" s="7">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="K361" s="7"/>
       <c r="L361" s="7"/>
@@ -12422,22 +12426,22 @@
       </c>
       <c r="D362" s="7"/>
       <c t="s" r="E362" s="7">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F362" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G362" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="H362" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="I362" s="7">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c t="s" r="J362" s="7">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="K362" s="7"/>
       <c r="L362" s="7"/>
@@ -12476,16 +12480,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G364" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="H364" s="8">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c t="s" r="I364" s="7">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c t="s" r="J364" s="7">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="K364" s="7"/>
       <c r="L364" s="7"/>
@@ -12509,16 +12513,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G365" s="8">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c t="s" r="H365" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="I365" s="7">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c t="s" r="J365" s="7">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="K365" s="7"/>
       <c r="L365" s="7"/>
@@ -12542,16 +12546,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G366" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="H366" s="8">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c t="s" r="I366" s="7">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c t="s" r="J366" s="7">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K366" s="7"/>
       <c r="L366" s="7"/>
@@ -12575,16 +12579,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G367" s="8">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c t="s" r="H367" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="I367" s="7">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c t="s" r="J367" s="7">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K367" s="7"/>
       <c r="L367" s="7"/>
@@ -12608,16 +12612,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G368" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="H368" s="8">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c t="s" r="I368" s="7">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c t="s" r="J368" s="7">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="K368" s="7"/>
       <c r="L368" s="7"/>
@@ -12641,13 +12645,13 @@
         <v>320</v>
       </c>
       <c t="s" r="G369" s="8">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c t="s" r="H369" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="I369" s="7">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c t="s" r="J369" s="7">
         <v>354</v>
@@ -12689,16 +12693,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G371" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="H371" s="8">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c t="s" r="I371" s="7">
         <v>356</v>
       </c>
       <c t="s" r="J371" s="7">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="K371" s="7"/>
       <c r="L371" s="7"/>
@@ -12722,16 +12726,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G372" s="8">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c t="s" r="H372" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="I372" s="7">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c t="s" r="J372" s="7">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K372" s="7"/>
       <c r="L372" s="7"/>
@@ -12755,16 +12759,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G373" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="H373" s="8">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c t="s" r="I373" s="7">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c t="s" r="J373" s="7">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="K373" s="7"/>
       <c r="L373" s="7"/>
@@ -12788,16 +12792,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G374" s="8">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c t="s" r="H374" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="I374" s="7">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c t="s" r="J374" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="K374" s="7"/>
       <c r="L374" s="7"/>
@@ -12821,16 +12825,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G375" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="H375" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="I375" s="7">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c t="s" r="J375" s="7">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K375" s="7"/>
       <c r="L375" s="7"/>
@@ -12854,16 +12858,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G376" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="H376" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="I376" s="7">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c t="s" r="J376" s="7">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="K376" s="7"/>
       <c r="L376" s="7"/>
@@ -12902,13 +12906,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G378" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="H378" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="I378" s="7">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c t="s" r="J378" s="7">
         <v>358</v>
@@ -12935,16 +12939,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G379" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="H379" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="I379" s="7">
         <v>359</v>
       </c>
       <c t="s" r="J379" s="7">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="K379" s="7"/>
       <c r="L379" s="7"/>
@@ -12968,16 +12972,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G380" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="H380" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="I380" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c t="s" r="J380" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="K380" s="7"/>
       <c r="L380" s="7"/>
@@ -13001,16 +13005,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G381" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="H381" s="8">
         <v>360</v>
       </c>
       <c t="s" r="I381" s="7">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c t="s" r="J381" s="7">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="K381" s="7"/>
       <c r="L381" s="7"/>
@@ -13037,13 +13041,13 @@
         <v>360</v>
       </c>
       <c t="s" r="H382" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="I382" s="7">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c t="s" r="J382" s="7">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="K382" s="7"/>
       <c r="L382" s="7"/>
@@ -13067,13 +13071,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G383" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="H383" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="I383" s="7">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c t="s" r="J383" s="7">
         <v>361</v>
@@ -13115,16 +13119,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G385" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="H385" s="8">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c t="s" r="I385" s="7">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c t="s" r="J385" s="7">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="K385" s="7"/>
       <c r="L385" s="7"/>
@@ -13148,16 +13152,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G386" s="8">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c t="s" r="H386" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="I386" s="7">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c t="s" r="J386" s="7">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="K386" s="7"/>
       <c r="L386" s="7"/>
@@ -13196,13 +13200,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G388" s="8">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c t="s" r="H388" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="I388" s="7">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c t="s" r="J388" s="7">
         <v>19</v>
@@ -13229,16 +13233,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G389" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="H389" s="8">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c t="s" r="I389" s="7">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c t="s" r="J389" s="7">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="K389" s="7"/>
       <c r="L389" s="7"/>
@@ -13262,16 +13266,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G390" s="8">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c t="s" r="H390" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="I390" s="7">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c t="s" r="J390" s="7">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="K390" s="7"/>
       <c r="L390" s="7"/>
@@ -13295,16 +13299,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G391" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="H391" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="I391" s="7">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c t="s" r="J391" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="K391" s="7"/>
       <c r="L391" s="7"/>
@@ -13343,16 +13347,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G393" s="8">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c t="s" r="H393" s="8">
+        <v>57</v>
+      </c>
+      <c t="s" r="I393" s="7">
         <v>55</v>
       </c>
-      <c t="s" r="I393" s="7">
-        <v>53</v>
-      </c>
       <c t="s" r="J393" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="K393" s="7"/>
       <c r="L393" s="7"/>
@@ -13376,16 +13380,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G394" s="8">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c t="s" r="H394" s="8">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c t="s" r="I394" s="7">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c t="s" r="J394" s="7">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="K394" s="7"/>
       <c r="L394" s="7"/>
@@ -13409,16 +13413,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G395" s="8">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c t="s" r="H395" s="8">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c t="s" r="I395" s="7">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c t="s" r="J395" s="7">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="K395" s="7"/>
       <c r="L395" s="7"/>
@@ -13442,16 +13446,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G396" s="8">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c t="s" r="H396" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="I396" s="7">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c t="s" r="J396" s="7">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="K396" s="7"/>
       <c r="L396" s="7"/>
@@ -13475,16 +13479,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G397" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="H397" s="8">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c t="s" r="I397" s="7">
         <v>365</v>
       </c>
       <c t="s" r="J397" s="7">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K397" s="7"/>
       <c r="L397" s="7"/>
@@ -13492,7 +13496,7 @@
     </row>
     <row r="398" ht="14.25" customHeight="1">
       <c t="s" r="A398" s="6">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B398" s="7">
         <v>859</v>
@@ -13508,10 +13512,10 @@
         <v>321</v>
       </c>
       <c t="s" r="G398" s="8">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c t="s" r="H398" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="I398" s="7">
         <v>366</v>
@@ -13556,16 +13560,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G400" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="H400" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="I400" s="7">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c t="s" r="J400" s="7">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="K400" s="7"/>
       <c r="L400" s="7"/>
@@ -13589,16 +13593,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G401" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="H401" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="I401" s="7">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c t="s" r="J401" s="7">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="K401" s="7"/>
       <c r="L401" s="7"/>
@@ -13622,16 +13626,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G402" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="H402" s="8">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c t="s" r="I402" s="7">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c t="s" r="J402" s="7">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="K402" s="7"/>
       <c r="L402" s="7"/>
@@ -13655,16 +13659,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G403" s="8">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c t="s" r="H403" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="I403" s="7">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c t="s" r="J403" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="K403" s="7"/>
       <c r="L403" s="7"/>
@@ -13688,16 +13692,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G404" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="H404" s="8">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c t="s" r="I404" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c t="s" r="J404" s="7">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="K404" s="7"/>
       <c r="L404" s="7"/>
@@ -13721,16 +13725,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G405" s="8">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c t="s" r="H405" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="I405" s="7">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c t="s" r="J405" s="7">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K405" s="7"/>
       <c r="L405" s="7"/>
@@ -13754,16 +13758,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G406" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="H406" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="I406" s="7">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c t="s" r="J406" s="7">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="K406" s="7"/>
       <c r="L406" s="7"/>
@@ -13802,7 +13806,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G408" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="H408" s="8">
         <v>17</v>
@@ -13811,7 +13815,7 @@
         <v>370</v>
       </c>
       <c t="s" r="J408" s="7">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="K408" s="7"/>
       <c r="L408" s="7"/>
@@ -13838,13 +13842,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H409" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="I409" s="7">
         <v>371</v>
       </c>
       <c t="s" r="J409" s="7">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="K409" s="7"/>
       <c r="L409" s="7"/>
@@ -13868,16 +13872,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G410" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="H410" s="8">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c t="s" r="I410" s="7">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c t="s" r="J410" s="7">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="K410" s="7"/>
       <c r="L410" s="7"/>
@@ -13901,16 +13905,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G411" s="8">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c t="s" r="H411" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="I411" s="7">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c t="s" r="J411" s="7">
-        <v>205</v>
+        <v>21</v>
       </c>
       <c r="K411" s="7"/>
       <c r="L411" s="7"/>
@@ -13934,16 +13938,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G412" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="H412" s="8">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c t="s" r="I412" s="7">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c t="s" r="J412" s="7">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K412" s="7"/>
       <c r="L412" s="7"/>
@@ -13967,16 +13971,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G413" s="8">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c t="s" r="H413" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="I413" s="7">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c t="s" r="J413" s="7">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="K413" s="7"/>
       <c r="L413" s="7"/>
@@ -14015,20 +14019,22 @@
         <v>321</v>
       </c>
       <c t="s" r="G415" s="8">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c t="s" r="H415" s="8">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c t="s" r="I415" s="7">
         <v>373</v>
       </c>
       <c t="s" r="J415" s="7">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="K415" s="7"/>
       <c r="L415" s="7"/>
-      <c r="M415" s="7"/>
+      <c t="s" r="M415" s="7">
+        <v>202</v>
+      </c>
     </row>
     <row r="416" ht="14.25" customHeight="1">
       <c t="s" r="A416" s="6">
@@ -14048,16 +14054,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G416" s="8">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c t="s" r="H416" s="8">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c t="s" r="I416" s="7">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c t="s" r="J416" s="7">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K416" s="7"/>
       <c r="L416" s="7"/>
@@ -14081,16 +14087,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G417" s="8">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c t="s" r="H417" s="8">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c t="s" r="I417" s="7">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c t="s" r="J417" s="7">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="K417" s="7"/>
       <c r="L417" s="7"/>
@@ -14114,13 +14120,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G418" s="8">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c t="s" r="H418" s="8">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c t="s" r="I418" s="7">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c t="s" r="J418" s="7">
         <v>374</v>
@@ -14162,16 +14168,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G420" s="8">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c t="s" r="H420" s="8">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c t="s" r="I420" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c t="s" r="J420" s="7">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="K420" s="7"/>
       <c r="L420" s="7"/>
@@ -14195,16 +14201,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G421" s="8">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c t="s" r="H421" s="8">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c t="s" r="I421" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c t="s" r="J421" s="7">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="K421" s="7"/>
       <c r="L421" s="7"/>
@@ -14212,7 +14218,7 @@
     </row>
     <row r="422" ht="14.25" customHeight="1">
       <c t="s" r="A422" s="6">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B422" s="7">
         <v>988</v>
@@ -14228,16 +14234,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G422" s="8">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c t="s" r="H422" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I422" s="7">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c t="s" r="J422" s="7">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="K422" s="7"/>
       <c r="L422" s="7"/>
@@ -14276,16 +14282,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G424" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="H424" s="8">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c t="s" r="I424" s="7">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c t="s" r="J424" s="7">
-        <v>352</v>
+        <v>20</v>
       </c>
       <c r="K424" s="7"/>
       <c r="L424" s="7"/>
@@ -14309,16 +14315,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G425" s="8">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c t="s" r="H425" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="I425" s="7">
         <v>377</v>
       </c>
       <c t="s" r="J425" s="7">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="K425" s="7"/>
       <c r="L425" s="7"/>
@@ -14342,16 +14348,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G426" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="H426" s="8">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c t="s" r="I426" s="7">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c t="s" r="J426" s="7">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="K426" s="7"/>
       <c r="L426" s="7"/>
@@ -14375,16 +14381,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G427" s="8">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c t="s" r="H427" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="I427" s="7">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c t="s" r="J427" s="7">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K427" s="7"/>
       <c r="L427" s="7"/>
@@ -14426,13 +14432,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H429" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="I429" s="7">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c t="s" r="J429" s="7">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K429" s="7"/>
       <c r="L429" s="7"/>
@@ -14456,16 +14462,16 @@
         <v>330</v>
       </c>
       <c t="s" r="G430" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="H430" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="I430" s="7">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c t="s" r="J430" s="7">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="K430" s="7"/>
       <c r="L430" s="7"/>
@@ -14489,16 +14495,16 @@
         <v>330</v>
       </c>
       <c t="s" r="G431" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c t="s" r="H431" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="I431" s="7">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c t="s" r="J431" s="7">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="K431" s="7"/>
       <c r="L431" s="7"/>
@@ -14537,16 +14543,16 @@
         <v>330</v>
       </c>
       <c t="s" r="G433" s="8">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c t="s" r="H433" s="8">
         <v>380</v>
       </c>
       <c t="s" r="I433" s="7">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c t="s" r="J433" s="7">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="K433" s="7"/>
       <c r="L433" s="7"/>
@@ -14573,13 +14579,13 @@
         <v>380</v>
       </c>
       <c t="s" r="H434" s="8">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c t="s" r="I434" s="7">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c t="s" r="J434" s="7">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="K434" s="7"/>
       <c r="L434" s="7"/>
@@ -14618,16 +14624,16 @@
         <v>330</v>
       </c>
       <c t="s" r="G436" s="8">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c t="s" r="H436" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="I436" s="7">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c t="s" r="J436" s="7">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="K436" s="7"/>
       <c r="L436" s="7"/>
@@ -14651,16 +14657,16 @@
         <v>330</v>
       </c>
       <c t="s" r="G437" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="H437" s="8">
         <v>382</v>
       </c>
       <c t="s" r="I437" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c t="s" r="J437" s="7">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="K437" s="7"/>
       <c r="L437" s="7"/>
@@ -14705,7 +14711,7 @@
         <v>384</v>
       </c>
       <c t="s" r="I439" s="7">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c t="s" r="J439" s="7">
         <v>385</v>
@@ -14716,7 +14722,7 @@
     </row>
     <row r="440" ht="15" customHeight="1">
       <c t="s" r="A440" s="6">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B440" s="7">
         <v>5063</v>
@@ -14738,10 +14744,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I440" s="7">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c t="s" r="J440" s="7">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="K440" s="7"/>
       <c r="L440" s="7"/>
@@ -14786,7 +14792,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I442" s="7">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c t="s" r="J442" s="7">
         <v>377</v>
@@ -14819,10 +14825,10 @@
         <v>387</v>
       </c>
       <c t="s" r="I443" s="7">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c t="s" r="J443" s="7">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="K443" s="7"/>
       <c r="L443" s="7"/>
@@ -14861,16 +14867,16 @@
         <v>330</v>
       </c>
       <c t="s" r="G445" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="H445" s="8">
         <v>389</v>
       </c>
       <c t="s" r="I445" s="7">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c t="s" r="J445" s="7">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="K445" s="7"/>
       <c r="L445" s="7"/>
@@ -14878,7 +14884,7 @@
     </row>
     <row r="446" ht="14.25" customHeight="1">
       <c t="s" r="A446" s="6">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B446" s="7">
         <v>82</v>
@@ -14897,13 +14903,13 @@
         <v>389</v>
       </c>
       <c t="s" r="H446" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="I446" s="7">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c t="s" r="J446" s="7">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="K446" s="7"/>
       <c r="L446" s="7"/>

--- a/Data/FlightPlan/FPL_15SEP26.xlsx
+++ b/Data/FlightPlan/FPL_15SEP26.xlsx
@@ -191,6 +191,9 @@
     <t>11:10</t>
   </si>
   <si>
+    <t>10:52</t>
+  </si>
+  <si>
     <t>HKG</t>
   </si>
   <si>
@@ -275,6 +278,9 @@
     <t>06:25</t>
   </si>
   <si>
+    <t>06:16</t>
+  </si>
+  <si>
     <t>06:55</t>
   </si>
   <si>
@@ -332,6 +338,9 @@
     <t>06:05</t>
   </si>
   <si>
+    <t>07:55</t>
+  </si>
+  <si>
     <t>11:00</t>
   </si>
   <si>
@@ -380,6 +389,9 @@
     <t>09:40</t>
   </si>
   <si>
+    <t>09:58</t>
+  </si>
+  <si>
     <t>C</t>
   </si>
   <si>
@@ -404,6 +416,9 @@
     <t>VN-A534</t>
   </si>
   <si>
+    <t>06:44</t>
+  </si>
+  <si>
     <t>07:30</t>
   </si>
   <si>
@@ -440,6 +455,9 @@
     <t>05:40</t>
   </si>
   <si>
+    <t>07:12</t>
+  </si>
+  <si>
     <t>HUI</t>
   </si>
   <si>
@@ -467,9 +485,6 @@
     <t>01:40</t>
   </si>
   <si>
-    <t>07:55</t>
-  </si>
-  <si>
     <t>VN-A536</t>
   </si>
   <si>
@@ -503,6 +518,9 @@
     <t>06:50</t>
   </si>
   <si>
+    <t>06:32</t>
+  </si>
+  <si>
     <t>BMV</t>
   </si>
   <si>
@@ -581,6 +599,9 @@
     <t>VN-A547</t>
   </si>
   <si>
+    <t>07:57</t>
+  </si>
+  <si>
     <t>09:55</t>
   </si>
   <si>
@@ -854,6 +875,9 @@
     <t>VN-A636</t>
   </si>
   <si>
+    <t>10:48</t>
+  </si>
+  <si>
     <t>16:45</t>
   </si>
   <si>
@@ -866,9 +890,18 @@
     <t>06:10</t>
   </si>
   <si>
+    <t>07:40</t>
+  </si>
+  <si>
     <t>07:35</t>
   </si>
   <si>
+    <t>09:10</t>
+  </si>
+  <si>
+    <t>KUL</t>
+  </si>
+  <si>
     <t>VN-A640</t>
   </si>
   <si>
@@ -887,12 +920,12 @@
     <t>VN-A642</t>
   </si>
   <si>
-    <t>KUL</t>
-  </si>
-  <si>
     <t>VN-A643</t>
   </si>
   <si>
+    <t>07:03</t>
+  </si>
+  <si>
     <t>17:55</t>
   </si>
   <si>
@@ -902,66 +935,63 @@
     <t>VN-A644</t>
   </si>
   <si>
+    <t>14:45</t>
+  </si>
+  <si>
+    <t>17:20</t>
+  </si>
+  <si>
+    <t>19:55</t>
+  </si>
+  <si>
+    <t>23:55</t>
+  </si>
+  <si>
+    <t>06:15</t>
+  </si>
+  <si>
+    <t>VN-A645</t>
+  </si>
+  <si>
+    <t>22:20</t>
+  </si>
+  <si>
+    <t>VN-A646</t>
+  </si>
+  <si>
+    <t>HND</t>
+  </si>
+  <si>
+    <t>02:00</t>
+  </si>
+  <si>
+    <t>VN-A648</t>
+  </si>
+  <si>
+    <t>SIN</t>
+  </si>
+  <si>
+    <t>13:55</t>
+  </si>
+  <si>
+    <t>14:55</t>
+  </si>
+  <si>
+    <t>22:15</t>
+  </si>
+  <si>
+    <t>00:25</t>
+  </si>
+  <si>
+    <t>VN-A649</t>
+  </si>
+  <si>
     <t>10:35</t>
   </si>
   <si>
-    <t>14:45</t>
-  </si>
-  <si>
-    <t>17:20</t>
-  </si>
-  <si>
-    <t>19:55</t>
-  </si>
-  <si>
-    <t>23:55</t>
-  </si>
-  <si>
-    <t>06:15</t>
-  </si>
-  <si>
-    <t>VN-A645</t>
-  </si>
-  <si>
-    <t>22:20</t>
-  </si>
-  <si>
-    <t>VN-A646</t>
-  </si>
-  <si>
-    <t>HND</t>
-  </si>
-  <si>
-    <t>02:00</t>
-  </si>
-  <si>
-    <t>VN-A648</t>
-  </si>
-  <si>
-    <t>SIN</t>
-  </si>
-  <si>
-    <t>13:55</t>
-  </si>
-  <si>
-    <t>14:55</t>
-  </si>
-  <si>
-    <t>22:15</t>
-  </si>
-  <si>
-    <t>00:25</t>
-  </si>
-  <si>
-    <t>VN-A649</t>
-  </si>
-  <si>
     <t>VN-A650</t>
   </si>
   <si>
-    <t>07:40</t>
-  </si>
-  <si>
     <t>17:10</t>
   </si>
   <si>
@@ -1004,12 +1034,18 @@
     <t>05:30</t>
   </si>
   <si>
+    <t>07:32</t>
+  </si>
+  <si>
     <t>22:10</t>
   </si>
   <si>
     <t>VN-A658</t>
   </si>
   <si>
+    <t>07:09</t>
+  </si>
+  <si>
     <t>VCL</t>
   </si>
   <si>
@@ -1037,6 +1073,9 @@
     <t>VN-A670</t>
   </si>
   <si>
+    <t>07:52</t>
+  </si>
+  <si>
     <t>MNL</t>
   </si>
   <si>
@@ -1085,9 +1124,6 @@
     <t>VN-A677</t>
   </si>
   <si>
-    <t>09:10</t>
-  </si>
-  <si>
     <t>09:45</t>
   </si>
   <si>
@@ -1124,6 +1160,9 @@
     <t>05:45</t>
   </si>
   <si>
+    <t>07:37</t>
+  </si>
+  <si>
     <t>08:05</t>
   </si>
   <si>
@@ -1175,6 +1214,9 @@
     <t>OVB</t>
   </si>
   <si>
+    <t>12:46</t>
+  </si>
+  <si>
     <t>VN-A817</t>
   </si>
   <si>
@@ -1184,7 +1226,7 @@
     <t>Total Record(s): 364</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Sep 15, 2026 03:51</t>
+    <t xml:space="preserve">Generated on  Sep 15, 2026 06:03</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -2242,7 +2284,9 @@
       </c>
       <c r="K23" s="7"/>
       <c r="L23" s="7"/>
-      <c r="M23" s="7"/>
+      <c t="s" r="M23" s="7">
+        <v>60</v>
+      </c>
     </row>
     <row r="24" ht="14.25" customHeight="1">
       <c t="s" r="A24" s="6">
@@ -2265,10 +2309,10 @@
         <v>57</v>
       </c>
       <c t="s" r="H24" s="8">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c t="s" r="I24" s="7">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c t="s" r="J24" s="7">
         <v>23</v>
@@ -2295,16 +2339,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G25" s="8">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c t="s" r="H25" s="8">
         <v>57</v>
       </c>
       <c t="s" r="I25" s="7">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c t="s" r="J25" s="7">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K25" s="7"/>
       <c r="L25" s="7"/>
@@ -2334,10 +2378,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I26" s="7">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c t="s" r="J26" s="7">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K26" s="7"/>
       <c r="L26" s="7"/>
@@ -2367,10 +2411,10 @@
         <v>37</v>
       </c>
       <c t="s" r="I27" s="7">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c t="s" r="J27" s="7">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K27" s="7"/>
       <c r="L27" s="7"/>
@@ -2403,7 +2447,7 @@
       </c>
       <c r="D29" s="7"/>
       <c t="s" r="E29" s="7">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F29" s="7">
         <v>321</v>
@@ -2436,7 +2480,7 @@
       </c>
       <c r="D30" s="7"/>
       <c t="s" r="E30" s="7">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F30" s="7">
         <v>321</v>
@@ -2445,13 +2489,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H30" s="8">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c t="s" r="I30" s="7">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c t="s" r="J30" s="7">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K30" s="7"/>
       <c r="L30" s="7"/>
@@ -2469,22 +2513,22 @@
       </c>
       <c r="D31" s="7"/>
       <c t="s" r="E31" s="7">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F31" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G31" s="8">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c t="s" r="H31" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I31" s="7">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c t="s" r="J31" s="7">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K31" s="7"/>
       <c r="L31" s="7"/>
@@ -2517,7 +2561,7 @@
       </c>
       <c r="D33" s="7"/>
       <c t="s" r="E33" s="7">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F33" s="7">
         <v>321</v>
@@ -2529,10 +2573,10 @@
         <v>31</v>
       </c>
       <c t="s" r="I33" s="7">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c t="s" r="J33" s="7">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K33" s="7"/>
       <c r="L33" s="7"/>
@@ -2550,7 +2594,7 @@
       </c>
       <c r="D34" s="7"/>
       <c t="s" r="E34" s="7">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F34" s="7">
         <v>321</v>
@@ -2562,10 +2606,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I34" s="7">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c t="s" r="J34" s="7">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K34" s="7"/>
       <c r="L34" s="7"/>
@@ -2583,7 +2627,7 @@
       </c>
       <c r="D35" s="7"/>
       <c t="s" r="E35" s="7">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F35" s="7">
         <v>321</v>
@@ -2595,10 +2639,10 @@
         <v>31</v>
       </c>
       <c t="s" r="I35" s="7">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c t="s" r="J35" s="7">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K35" s="7"/>
       <c r="L35" s="7"/>
@@ -2616,7 +2660,7 @@
       </c>
       <c r="D36" s="7"/>
       <c t="s" r="E36" s="7">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F36" s="7">
         <v>321</v>
@@ -2625,13 +2669,13 @@
         <v>31</v>
       </c>
       <c t="s" r="H36" s="8">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c t="s" r="I36" s="7">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c t="s" r="J36" s="7">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K36" s="7"/>
       <c r="L36" s="7"/>
@@ -2649,13 +2693,13 @@
       </c>
       <c r="D37" s="7"/>
       <c t="s" r="E37" s="7">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F37" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G37" s="8">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c t="s" r="H37" s="8">
         <v>31</v>
@@ -2664,7 +2708,7 @@
         <v>26</v>
       </c>
       <c t="s" r="J37" s="7">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K37" s="7"/>
       <c r="L37" s="7"/>
@@ -2697,7 +2741,7 @@
       </c>
       <c r="D39" s="7"/>
       <c t="s" r="E39" s="7">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F39" s="7">
         <v>321</v>
@@ -2706,17 +2750,19 @@
         <v>41</v>
       </c>
       <c t="s" r="H39" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="I39" s="7">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c t="s" r="J39" s="7">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K39" s="7"/>
       <c r="L39" s="7"/>
-      <c r="M39" s="7"/>
+      <c t="s" r="M39" s="7">
+        <v>89</v>
+      </c>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c t="s" r="A40" s="6">
@@ -2730,22 +2776,22 @@
       </c>
       <c r="D40" s="7"/>
       <c t="s" r="E40" s="7">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F40" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G40" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="H40" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I40" s="7">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c t="s" r="J40" s="7">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="K40" s="7"/>
       <c r="L40" s="7"/>
@@ -2763,7 +2809,7 @@
       </c>
       <c r="D41" s="7"/>
       <c t="s" r="E41" s="7">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F41" s="7">
         <v>321</v>
@@ -2772,13 +2818,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H41" s="8">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c t="s" r="I41" s="7">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c t="s" r="J41" s="7">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="K41" s="7"/>
       <c r="L41" s="7"/>
@@ -2796,22 +2842,22 @@
       </c>
       <c r="D42" s="7"/>
       <c t="s" r="E42" s="7">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F42" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G42" s="8">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c t="s" r="H42" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I42" s="7">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c t="s" r="J42" s="7">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="K42" s="7"/>
       <c r="L42" s="7"/>
@@ -2829,7 +2875,7 @@
       </c>
       <c r="D43" s="7"/>
       <c t="s" r="E43" s="7">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F43" s="7">
         <v>321</v>
@@ -2838,13 +2884,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H43" s="8">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c t="s" r="I43" s="7">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c t="s" r="J43" s="7">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="K43" s="7"/>
       <c r="L43" s="7"/>
@@ -2862,13 +2908,13 @@
       </c>
       <c r="D44" s="7"/>
       <c t="s" r="E44" s="7">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F44" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G44" s="8">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c t="s" r="H44" s="8">
         <v>41</v>
@@ -2877,7 +2923,7 @@
         <v>36</v>
       </c>
       <c t="s" r="J44" s="7">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="K44" s="7"/>
       <c r="L44" s="7"/>
@@ -2910,7 +2956,7 @@
       </c>
       <c r="D46" s="7"/>
       <c t="s" r="E46" s="7">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F46" s="7">
         <v>321</v>
@@ -2919,13 +2965,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H46" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="I46" s="7">
         <v>47</v>
       </c>
       <c t="s" r="J46" s="7">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="K46" s="7"/>
       <c r="L46" s="7"/>
@@ -2943,22 +2989,22 @@
       </c>
       <c r="D47" s="7"/>
       <c t="s" r="E47" s="7">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F47" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G47" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="H47" s="8">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c t="s" r="I47" s="7">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c t="s" r="J47" s="7">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="K47" s="7"/>
       <c r="L47" s="7"/>
@@ -2976,22 +3022,22 @@
       </c>
       <c r="D48" s="7"/>
       <c t="s" r="E48" s="7">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F48" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G48" s="8">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c t="s" r="H48" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="I48" s="7">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c t="s" r="J48" s="7">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="K48" s="7"/>
       <c r="L48" s="7"/>
@@ -3024,7 +3070,7 @@
       </c>
       <c r="D50" s="7"/>
       <c t="s" r="E50" s="7">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F50" s="7">
         <v>321</v>
@@ -3036,14 +3082,16 @@
         <v>31</v>
       </c>
       <c t="s" r="I50" s="7">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c t="s" r="J50" s="7">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="K50" s="7"/>
       <c r="L50" s="7"/>
-      <c r="M50" s="7"/>
+      <c t="s" r="M50" s="7">
+        <v>109</v>
+      </c>
     </row>
     <row r="51" ht="14.25" customHeight="1">
       <c t="s" r="A51" s="6">
@@ -3057,7 +3105,7 @@
       </c>
       <c r="D51" s="7"/>
       <c t="s" r="E51" s="7">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F51" s="7">
         <v>321</v>
@@ -3069,10 +3117,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I51" s="7">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c t="s" r="J51" s="7">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="K51" s="7"/>
       <c r="L51" s="7"/>
@@ -3090,7 +3138,7 @@
       </c>
       <c r="D52" s="7"/>
       <c t="s" r="E52" s="7">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F52" s="7">
         <v>321</v>
@@ -3099,13 +3147,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H52" s="8">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c t="s" r="I52" s="7">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c t="s" r="J52" s="7">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K52" s="7"/>
       <c r="L52" s="7"/>
@@ -3123,22 +3171,22 @@
       </c>
       <c r="D53" s="7"/>
       <c t="s" r="E53" s="7">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F53" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G53" s="8">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c t="s" r="H53" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I53" s="7">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c t="s" r="J53" s="7">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="K53" s="7"/>
       <c r="L53" s="7"/>
@@ -3171,22 +3219,22 @@
       </c>
       <c r="D55" s="7"/>
       <c t="s" r="E55" s="7">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="F55" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G55" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="H55" s="8">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c t="s" r="I55" s="7">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c t="s" r="J55" s="7">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="K55" s="7"/>
       <c r="L55" s="7"/>
@@ -3204,19 +3252,19 @@
       </c>
       <c r="D56" s="7"/>
       <c t="s" r="E56" s="7">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="F56" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G56" s="8">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c t="s" r="H56" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="I56" s="7">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c t="s" r="J56" s="7">
         <v>34</v>
@@ -3237,19 +3285,19 @@
       </c>
       <c r="D57" s="7"/>
       <c t="s" r="E57" s="7">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="F57" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G57" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="H57" s="8">
         <v>57</v>
       </c>
       <c t="s" r="I57" s="7">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c t="s" r="J57" s="7">
         <v>23</v>
@@ -3270,7 +3318,7 @@
       </c>
       <c r="D58" s="7"/>
       <c t="s" r="E58" s="7">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="F58" s="7">
         <v>321</v>
@@ -3279,10 +3327,10 @@
         <v>57</v>
       </c>
       <c t="s" r="H58" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="I58" s="7">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c t="s" r="J58" s="7">
         <v>36</v>
@@ -3303,22 +3351,22 @@
       </c>
       <c r="D59" s="7"/>
       <c t="s" r="E59" s="7">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="F59" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G59" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="H59" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I59" s="7">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c t="s" r="J59" s="7">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K59" s="7"/>
       <c r="L59" s="7"/>
@@ -3336,7 +3384,7 @@
       </c>
       <c r="D60" s="7"/>
       <c t="s" r="E60" s="7">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="F60" s="7">
         <v>321</v>
@@ -3348,10 +3396,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I60" s="7">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c t="s" r="J60" s="7">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="K60" s="7"/>
       <c r="L60" s="7"/>
@@ -3384,26 +3432,28 @@
       </c>
       <c r="D62" s="7"/>
       <c t="s" r="E62" s="7">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F62" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G62" s="8">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c t="s" r="H62" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="I62" s="7">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c t="s" r="J62" s="7">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="K62" s="7"/>
       <c r="L62" s="7"/>
-      <c r="M62" s="7"/>
+      <c t="s" r="M62" s="7">
+        <v>126</v>
+      </c>
     </row>
     <row r="63" ht="14.25" customHeight="1">
       <c t="s" r="A63" s="6">
@@ -3413,23 +3463,23 @@
         <v>8520</v>
       </c>
       <c t="s" r="C63" s="7">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="D63" s="7"/>
       <c t="s" r="E63" s="7">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F63" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G63" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="H63" s="8">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c t="s" r="I63" s="7">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c t="s" r="J63" s="7">
         <v>50</v>
@@ -3446,26 +3496,26 @@
         <v>8521</v>
       </c>
       <c t="s" r="C64" s="7">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="D64" s="7"/>
       <c t="s" r="E64" s="7">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F64" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G64" s="8">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c t="s" r="H64" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="I64" s="7">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c t="s" r="J64" s="7">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="K64" s="7"/>
       <c r="L64" s="7"/>
@@ -3483,22 +3533,22 @@
       </c>
       <c r="D65" s="7"/>
       <c t="s" r="E65" s="7">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F65" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G65" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="H65" s="8">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c t="s" r="I65" s="7">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c t="s" r="J65" s="7">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="K65" s="7"/>
       <c r="L65" s="7"/>
@@ -3531,26 +3581,28 @@
       </c>
       <c r="D67" s="7"/>
       <c t="s" r="E67" s="7">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="F67" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G67" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="H67" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I67" s="7">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c t="s" r="J67" s="7">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="K67" s="7"/>
       <c r="L67" s="7"/>
-      <c r="M67" s="7"/>
+      <c t="s" r="M67" s="7">
+        <v>135</v>
+      </c>
     </row>
     <row r="68" ht="14.25" customHeight="1">
       <c t="s" r="A68" s="6">
@@ -3564,7 +3616,7 @@
       </c>
       <c r="D68" s="7"/>
       <c t="s" r="E68" s="7">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="F68" s="7">
         <v>321</v>
@@ -3573,13 +3625,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H68" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="I68" s="7">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c t="s" r="J68" s="7">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K68" s="7"/>
       <c r="L68" s="7"/>
@@ -3597,22 +3649,22 @@
       </c>
       <c r="D69" s="7"/>
       <c t="s" r="E69" s="7">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="F69" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G69" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="H69" s="8">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c t="s" r="I69" s="7">
         <v>45</v>
       </c>
       <c t="s" r="J69" s="7">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="K69" s="7"/>
       <c r="L69" s="7"/>
@@ -3630,22 +3682,22 @@
       </c>
       <c r="D70" s="7"/>
       <c t="s" r="E70" s="7">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="F70" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G70" s="8">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c t="s" r="H70" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="I70" s="7">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c t="s" r="J70" s="7">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="K70" s="7"/>
       <c r="L70" s="7"/>
@@ -3663,22 +3715,22 @@
       </c>
       <c r="D71" s="7"/>
       <c t="s" r="E71" s="7">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="F71" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G71" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="H71" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I71" s="7">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c t="s" r="J71" s="7">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="K71" s="7"/>
       <c r="L71" s="7"/>
@@ -3696,7 +3748,7 @@
       </c>
       <c r="D72" s="7"/>
       <c t="s" r="E72" s="7">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="F72" s="7">
         <v>321</v>
@@ -3708,10 +3760,10 @@
         <v>31</v>
       </c>
       <c t="s" r="I72" s="7">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c t="s" r="J72" s="7">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="K72" s="7"/>
       <c r="L72" s="7"/>
@@ -3729,7 +3781,7 @@
       </c>
       <c r="D73" s="7"/>
       <c t="s" r="E73" s="7">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="F73" s="7">
         <v>321</v>
@@ -3741,10 +3793,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I73" s="7">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c t="s" r="J73" s="7">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="K73" s="7"/>
       <c r="L73" s="7"/>
@@ -3777,7 +3829,7 @@
       </c>
       <c r="D75" s="7"/>
       <c t="s" r="E75" s="7">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="F75" s="7">
         <v>321</v>
@@ -3786,17 +3838,19 @@
         <v>31</v>
       </c>
       <c t="s" r="H75" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="I75" s="7">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c t="s" r="J75" s="7">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="K75" s="7"/>
       <c r="L75" s="7"/>
-      <c r="M75" s="7"/>
+      <c t="s" r="M75" s="7">
+        <v>148</v>
+      </c>
     </row>
     <row r="76" ht="14.25" customHeight="1">
       <c t="s" r="A76" s="6">
@@ -3810,22 +3864,22 @@
       </c>
       <c r="D76" s="7"/>
       <c t="s" r="E76" s="7">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="F76" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G76" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="H76" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I76" s="7">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c t="s" r="J76" s="7">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K76" s="7"/>
       <c r="L76" s="7"/>
@@ -3843,7 +3897,7 @@
       </c>
       <c r="D77" s="7"/>
       <c t="s" r="E77" s="7">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="F77" s="7">
         <v>321</v>
@@ -3852,13 +3906,13 @@
         <v>31</v>
       </c>
       <c t="s" r="H77" s="8">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c t="s" r="I77" s="7">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c t="s" r="J77" s="7">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="K77" s="7"/>
       <c r="L77" s="7"/>
@@ -3876,13 +3930,13 @@
       </c>
       <c r="D78" s="7"/>
       <c t="s" r="E78" s="7">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="F78" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G78" s="8">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c t="s" r="H78" s="8">
         <v>31</v>
@@ -3891,7 +3945,7 @@
         <v>59</v>
       </c>
       <c t="s" r="J78" s="7">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="K78" s="7"/>
       <c r="L78" s="7"/>
@@ -3909,7 +3963,7 @@
       </c>
       <c r="D79" s="7"/>
       <c t="s" r="E79" s="7">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="F79" s="7">
         <v>321</v>
@@ -3918,13 +3972,13 @@
         <v>31</v>
       </c>
       <c t="s" r="H79" s="8">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c t="s" r="I79" s="7">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c t="s" r="J79" s="7">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="K79" s="7"/>
       <c r="L79" s="7"/>
@@ -3942,22 +3996,22 @@
       </c>
       <c r="D80" s="7"/>
       <c t="s" r="E80" s="7">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="F80" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G80" s="8">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c t="s" r="H80" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I80" s="7">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c t="s" r="J80" s="7">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="K80" s="7"/>
       <c r="L80" s="7"/>
@@ -3975,7 +4029,7 @@
       </c>
       <c r="D81" s="7"/>
       <c t="s" r="E81" s="7">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="F81" s="7">
         <v>321</v>
@@ -3984,13 +4038,13 @@
         <v>31</v>
       </c>
       <c t="s" r="H81" s="8">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c t="s" r="I81" s="7">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c t="s" r="J81" s="7">
-        <v>152</v>
+        <v>109</v>
       </c>
       <c r="K81" s="7"/>
       <c r="L81" s="7"/>
@@ -4023,7 +4077,7 @@
       </c>
       <c r="D83" s="7"/>
       <c t="s" r="E83" s="7">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="F83" s="7">
         <v>321</v>
@@ -4035,17 +4089,17 @@
         <v>41</v>
       </c>
       <c t="s" r="I83" s="7">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c t="s" r="J83" s="7">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c t="s" r="K83" s="7">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="L83" s="7"/>
       <c t="s" r="M83" s="7">
-        <v>156</v>
+        <v>161</v>
       </c>
     </row>
     <row r="84" ht="14.25" customHeight="1">
@@ -4060,7 +4114,7 @@
       </c>
       <c r="D84" s="7"/>
       <c t="s" r="E84" s="7">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="F84" s="7">
         <v>321</v>
@@ -4069,13 +4123,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H84" s="8">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c t="s" r="I84" s="7">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c t="s" r="J84" s="7">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="K84" s="7"/>
       <c r="L84" s="7"/>
@@ -4093,22 +4147,22 @@
       </c>
       <c r="D85" s="7"/>
       <c t="s" r="E85" s="7">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="F85" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G85" s="8">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c t="s" r="H85" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I85" s="7">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c t="s" r="J85" s="7">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="K85" s="7"/>
       <c r="L85" s="7"/>
@@ -4141,7 +4195,7 @@
       </c>
       <c r="D87" s="7"/>
       <c t="s" r="E87" s="7">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="F87" s="7">
         <v>321</v>
@@ -4150,17 +4204,19 @@
         <v>41</v>
       </c>
       <c t="s" r="H87" s="8">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c t="s" r="I87" s="7">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c t="s" r="J87" s="7">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="K87" s="7"/>
       <c r="L87" s="7"/>
-      <c r="M87" s="7"/>
+      <c t="s" r="M87" s="7">
+        <v>169</v>
+      </c>
     </row>
     <row r="88" ht="14.25" customHeight="1">
       <c t="s" r="A88" s="6">
@@ -4174,22 +4230,22 @@
       </c>
       <c r="D88" s="7"/>
       <c t="s" r="E88" s="7">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="F88" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G88" s="8">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c t="s" r="H88" s="8">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c t="s" r="I88" s="7">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c t="s" r="J88" s="7">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="K88" s="7"/>
       <c r="L88" s="7"/>
@@ -4207,22 +4263,22 @@
       </c>
       <c r="D89" s="7"/>
       <c t="s" r="E89" s="7">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="F89" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G89" s="8">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c t="s" r="H89" s="8">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c t="s" r="I89" s="7">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c t="s" r="J89" s="7">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="K89" s="7"/>
       <c r="L89" s="7"/>
@@ -4240,13 +4296,13 @@
       </c>
       <c r="D90" s="7"/>
       <c t="s" r="E90" s="7">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="F90" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G90" s="8">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c t="s" r="H90" s="8">
         <v>41</v>
@@ -4273,7 +4329,7 @@
       </c>
       <c r="D91" s="7"/>
       <c t="s" r="E91" s="7">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="F91" s="7">
         <v>321</v>
@@ -4285,10 +4341,10 @@
         <v>46</v>
       </c>
       <c t="s" r="I91" s="7">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c t="s" r="J91" s="7">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K91" s="7"/>
       <c r="L91" s="7"/>
@@ -4306,7 +4362,7 @@
       </c>
       <c r="D92" s="7"/>
       <c t="s" r="E92" s="7">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="F92" s="7">
         <v>321</v>
@@ -4318,10 +4374,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I92" s="7">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c t="s" r="J92" s="7">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="K92" s="7"/>
       <c r="L92" s="7"/>
@@ -4339,7 +4395,7 @@
       </c>
       <c r="D93" s="7"/>
       <c t="s" r="E93" s="7">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="F93" s="7">
         <v>321</v>
@@ -4348,13 +4404,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H93" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="I93" s="7">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c t="s" r="J93" s="7">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="K93" s="7"/>
       <c r="L93" s="7"/>
@@ -4372,22 +4428,22 @@
       </c>
       <c r="D94" s="7"/>
       <c t="s" r="E94" s="7">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="F94" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G94" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="H94" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I94" s="7">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c t="s" r="J94" s="7">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="K94" s="7"/>
       <c r="L94" s="7"/>
@@ -4420,7 +4476,7 @@
       </c>
       <c r="D96" s="7"/>
       <c t="s" r="E96" s="7">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="F96" s="7">
         <v>321</v>
@@ -4429,13 +4485,13 @@
         <v>31</v>
       </c>
       <c t="s" r="H96" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="I96" s="7">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c t="s" r="J96" s="7">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="K96" s="7"/>
       <c r="L96" s="7"/>
@@ -4453,22 +4509,22 @@
       </c>
       <c r="D97" s="7"/>
       <c t="s" r="E97" s="7">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="F97" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G97" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="H97" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I97" s="7">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c t="s" r="J97" s="7">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="K97" s="7"/>
       <c r="L97" s="7"/>
@@ -4486,7 +4542,7 @@
       </c>
       <c r="D98" s="7"/>
       <c t="s" r="E98" s="7">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="F98" s="7">
         <v>321</v>
@@ -4498,10 +4554,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I98" s="7">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c t="s" r="J98" s="7">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="K98" s="7"/>
       <c r="L98" s="7"/>
@@ -4519,7 +4575,7 @@
       </c>
       <c r="D99" s="7"/>
       <c t="s" r="E99" s="7">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="F99" s="7">
         <v>321</v>
@@ -4531,10 +4587,10 @@
         <v>31</v>
       </c>
       <c t="s" r="I99" s="7">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c t="s" r="J99" s="7">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K99" s="7"/>
       <c r="L99" s="7"/>
@@ -4567,7 +4623,7 @@
       </c>
       <c r="D101" s="7"/>
       <c t="s" r="E101" s="7">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="F101" s="7">
         <v>321</v>
@@ -4576,10 +4632,10 @@
         <v>41</v>
       </c>
       <c t="s" r="H101" s="8">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c t="s" r="I101" s="7">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c t="s" r="J101" s="7">
         <v>18</v>
@@ -4600,22 +4656,22 @@
       </c>
       <c r="D102" s="7"/>
       <c t="s" r="E102" s="7">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="F102" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G102" s="8">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c t="s" r="H102" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I102" s="7">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c t="s" r="J102" s="7">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="K102" s="7"/>
       <c r="L102" s="7"/>
@@ -4633,7 +4689,7 @@
       </c>
       <c r="D103" s="7"/>
       <c t="s" r="E103" s="7">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="F103" s="7">
         <v>321</v>
@@ -4648,7 +4704,7 @@
         <v>23</v>
       </c>
       <c t="s" r="J103" s="7">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="K103" s="7"/>
       <c r="L103" s="7"/>
@@ -4681,7 +4737,7 @@
       </c>
       <c r="D105" s="7"/>
       <c t="s" r="E105" s="7">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="F105" s="7">
         <v>321</v>
@@ -4690,10 +4746,10 @@
         <v>41</v>
       </c>
       <c t="s" r="H105" s="8">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c t="s" r="I105" s="7">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c t="s" r="J105" s="7">
         <v>45</v>
@@ -4714,22 +4770,22 @@
       </c>
       <c r="D106" s="7"/>
       <c t="s" r="E106" s="7">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="F106" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G106" s="8">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c t="s" r="H106" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I106" s="7">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c t="s" r="J106" s="7">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="K106" s="7"/>
       <c r="L106" s="7"/>
@@ -4747,7 +4803,7 @@
       </c>
       <c r="D107" s="7"/>
       <c t="s" r="E107" s="7">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="F107" s="7">
         <v>321</v>
@@ -4756,13 +4812,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H107" s="8">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c t="s" r="I107" s="7">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c t="s" r="J107" s="7">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K107" s="7"/>
       <c r="L107" s="7"/>
@@ -4780,22 +4836,22 @@
       </c>
       <c r="D108" s="7"/>
       <c t="s" r="E108" s="7">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="F108" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G108" s="8">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c t="s" r="H108" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I108" s="7">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c t="s" r="J108" s="7">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="K108" s="7"/>
       <c r="L108" s="7"/>
@@ -4813,7 +4869,7 @@
       </c>
       <c r="D109" s="7"/>
       <c t="s" r="E109" s="7">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="F109" s="7">
         <v>321</v>
@@ -4822,13 +4878,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H109" s="8">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c t="s" r="I109" s="7">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c t="s" r="J109" s="7">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="K109" s="7"/>
       <c r="L109" s="7"/>
@@ -4846,22 +4902,22 @@
       </c>
       <c r="D110" s="7"/>
       <c t="s" r="E110" s="7">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="F110" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G110" s="8">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c t="s" r="H110" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I110" s="7">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c t="s" r="J110" s="7">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="K110" s="7"/>
       <c r="L110" s="7"/>
@@ -4894,7 +4950,7 @@
       </c>
       <c r="D112" s="7"/>
       <c t="s" r="E112" s="7">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="F112" s="7">
         <v>321</v>
@@ -4906,14 +4962,16 @@
         <v>41</v>
       </c>
       <c t="s" r="I112" s="7">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c t="s" r="J112" s="7">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="K112" s="7"/>
       <c r="L112" s="7"/>
-      <c r="M112" s="7"/>
+      <c t="s" r="M112" s="7">
+        <v>196</v>
+      </c>
     </row>
     <row r="113" ht="14.25" customHeight="1">
       <c t="s" r="A113" s="6">
@@ -4927,7 +4985,7 @@
       </c>
       <c r="D113" s="7"/>
       <c t="s" r="E113" s="7">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="F113" s="7">
         <v>321</v>
@@ -4939,10 +4997,10 @@
         <v>57</v>
       </c>
       <c t="s" r="I113" s="7">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c t="s" r="J113" s="7">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="K113" s="7"/>
       <c r="L113" s="7"/>
@@ -4960,7 +5018,7 @@
       </c>
       <c r="D114" s="7"/>
       <c t="s" r="E114" s="7">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="F114" s="7">
         <v>321</v>
@@ -4972,10 +5030,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I114" s="7">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c t="s" r="J114" s="7">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="K114" s="7"/>
       <c r="L114" s="7"/>
@@ -4993,7 +5051,7 @@
       </c>
       <c r="D115" s="7"/>
       <c t="s" r="E115" s="7">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="F115" s="7">
         <v>321</v>
@@ -5005,10 +5063,10 @@
         <v>31</v>
       </c>
       <c t="s" r="I115" s="7">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c t="s" r="J115" s="7">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="K115" s="7"/>
       <c r="L115" s="7"/>
@@ -5026,7 +5084,7 @@
       </c>
       <c r="D116" s="7"/>
       <c t="s" r="E116" s="7">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="F116" s="7">
         <v>321</v>
@@ -5035,13 +5093,13 @@
         <v>31</v>
       </c>
       <c t="s" r="H116" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="I116" s="7">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c t="s" r="J116" s="7">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="K116" s="7"/>
       <c r="L116" s="7"/>
@@ -5059,19 +5117,19 @@
       </c>
       <c r="D117" s="7"/>
       <c t="s" r="E117" s="7">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="F117" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G117" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="H117" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I117" s="7">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c t="s" r="J117" s="7">
         <v>36</v>
@@ -5092,7 +5150,7 @@
       </c>
       <c r="D118" s="7"/>
       <c t="s" r="E118" s="7">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="F118" s="7">
         <v>321</v>
@@ -5101,13 +5159,13 @@
         <v>31</v>
       </c>
       <c t="s" r="H118" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="I118" s="7">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c t="s" r="J118" s="7">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="K118" s="7"/>
       <c r="L118" s="7"/>
@@ -5125,19 +5183,19 @@
       </c>
       <c r="D119" s="7"/>
       <c t="s" r="E119" s="7">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="F119" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G119" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="H119" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I119" s="7">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c t="s" r="J119" s="7">
         <v>53</v>
@@ -5173,13 +5231,13 @@
       </c>
       <c r="D121" s="7"/>
       <c t="s" r="E121" s="7">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="F121" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G121" s="8">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c t="s" r="H121" s="8">
         <v>31</v>
@@ -5188,7 +5246,7 @@
         <v>45</v>
       </c>
       <c t="s" r="J121" s="7">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="K121" s="7"/>
       <c r="L121" s="7"/>
@@ -5206,7 +5264,7 @@
       </c>
       <c r="D122" s="7"/>
       <c t="s" r="E122" s="7">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="F122" s="7">
         <v>321</v>
@@ -5215,13 +5273,13 @@
         <v>31</v>
       </c>
       <c t="s" r="H122" s="8">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c t="s" r="I122" s="7">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c t="s" r="J122" s="7">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="K122" s="7"/>
       <c r="L122" s="7"/>
@@ -5239,22 +5297,22 @@
       </c>
       <c r="D123" s="7"/>
       <c t="s" r="E123" s="7">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="F123" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G123" s="8">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c t="s" r="H123" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I123" s="7">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c t="s" r="J123" s="7">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="K123" s="7"/>
       <c r="L123" s="7"/>
@@ -5272,7 +5330,7 @@
       </c>
       <c r="D124" s="7"/>
       <c t="s" r="E124" s="7">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="F124" s="7">
         <v>321</v>
@@ -5281,13 +5339,13 @@
         <v>31</v>
       </c>
       <c t="s" r="H124" s="8">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c t="s" r="I124" s="7">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c t="s" r="J124" s="7">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="K124" s="7"/>
       <c r="L124" s="7"/>
@@ -5320,22 +5378,22 @@
       </c>
       <c r="D126" s="7"/>
       <c t="s" r="E126" s="7">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="F126" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G126" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="H126" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I126" s="7">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c t="s" r="J126" s="7">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K126" s="7"/>
       <c r="L126" s="7"/>
@@ -5353,7 +5411,7 @@
       </c>
       <c r="D127" s="7"/>
       <c t="s" r="E127" s="7">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="F127" s="7">
         <v>321</v>
@@ -5362,13 +5420,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H127" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="I127" s="7">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c t="s" r="J127" s="7">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="K127" s="7"/>
       <c r="L127" s="7"/>
@@ -5386,22 +5444,22 @@
       </c>
       <c r="D128" s="7"/>
       <c t="s" r="E128" s="7">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="F128" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G128" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="H128" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I128" s="7">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c t="s" r="J128" s="7">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="K128" s="7"/>
       <c r="L128" s="7"/>
@@ -5419,7 +5477,7 @@
       </c>
       <c r="D129" s="7"/>
       <c t="s" r="E129" s="7">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="F129" s="7">
         <v>321</v>
@@ -5428,7 +5486,7 @@
         <v>41</v>
       </c>
       <c t="s" r="H129" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="I129" s="7">
         <v>34</v>
@@ -5452,22 +5510,22 @@
       </c>
       <c r="D130" s="7"/>
       <c t="s" r="E130" s="7">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="F130" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G130" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="H130" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I130" s="7">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c t="s" r="J130" s="7">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="K130" s="7"/>
       <c r="L130" s="7"/>
@@ -5500,7 +5558,7 @@
       </c>
       <c r="D132" s="7"/>
       <c t="s" r="E132" s="7">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="F132" s="7">
         <v>321</v>
@@ -5512,10 +5570,10 @@
         <v>37</v>
       </c>
       <c t="s" r="I132" s="7">
-        <v>152</v>
+        <v>109</v>
       </c>
       <c t="s" r="J132" s="7">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="K132" s="7"/>
       <c r="L132" s="7"/>
@@ -5533,7 +5591,7 @@
       </c>
       <c r="D133" s="7"/>
       <c t="s" r="E133" s="7">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="F133" s="7">
         <v>321</v>
@@ -5545,10 +5603,10 @@
         <v>31</v>
       </c>
       <c t="s" r="I133" s="7">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c t="s" r="J133" s="7">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="K133" s="7"/>
       <c r="L133" s="7"/>
@@ -5566,7 +5624,7 @@
       </c>
       <c r="D134" s="7"/>
       <c t="s" r="E134" s="7">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="F134" s="7">
         <v>321</v>
@@ -5575,13 +5633,13 @@
         <v>31</v>
       </c>
       <c t="s" r="H134" s="8">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c t="s" r="I134" s="7">
         <v>52</v>
       </c>
       <c t="s" r="J134" s="7">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="K134" s="7"/>
       <c r="L134" s="7"/>
@@ -5599,22 +5657,22 @@
       </c>
       <c r="D135" s="7"/>
       <c t="s" r="E135" s="7">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="F135" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G135" s="8">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c t="s" r="H135" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I135" s="7">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c t="s" r="J135" s="7">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="K135" s="7"/>
       <c r="L135" s="7"/>
@@ -5647,7 +5705,7 @@
       </c>
       <c r="D137" s="7"/>
       <c t="s" r="E137" s="7">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="F137" s="7">
         <v>321</v>
@@ -5659,10 +5717,10 @@
         <v>31</v>
       </c>
       <c t="s" r="I137" s="7">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c t="s" r="J137" s="7">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="K137" s="7"/>
       <c r="L137" s="7"/>
@@ -5680,7 +5738,7 @@
       </c>
       <c r="D138" s="7"/>
       <c t="s" r="E138" s="7">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="F138" s="7">
         <v>321</v>
@@ -5692,7 +5750,7 @@
         <v>41</v>
       </c>
       <c t="s" r="I138" s="7">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c t="s" r="J138" s="7">
         <v>19</v>
@@ -5713,7 +5771,7 @@
       </c>
       <c r="D139" s="7"/>
       <c t="s" r="E139" s="7">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="F139" s="7">
         <v>321</v>
@@ -5725,10 +5783,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I139" s="7">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c t="s" r="J139" s="7">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="K139" s="7"/>
       <c r="L139" s="7"/>
@@ -5742,11 +5800,11 @@
         <v>7706</v>
       </c>
       <c t="s" r="C140" s="7">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="D140" s="7"/>
       <c t="s" r="E140" s="7">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="F140" s="7">
         <v>321</v>
@@ -5758,10 +5816,10 @@
         <v>31</v>
       </c>
       <c t="s" r="I140" s="7">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c t="s" r="J140" s="7">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="K140" s="7"/>
       <c r="L140" s="7"/>
@@ -5775,11 +5833,11 @@
         <v>7706</v>
       </c>
       <c t="s" r="C141" s="7">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="D141" s="7"/>
       <c t="s" r="E141" s="7">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="F141" s="7">
         <v>321</v>
@@ -5788,10 +5846,10 @@
         <v>31</v>
       </c>
       <c t="s" r="H141" s="8">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c t="s" r="I141" s="7">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c t="s" r="J141" s="7">
         <v>29</v>
@@ -5827,22 +5885,22 @@
       </c>
       <c r="D143" s="7"/>
       <c t="s" r="E143" s="7">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="F143" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G143" s="8">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c t="s" r="H143" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I143" s="7">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c t="s" r="J143" s="7">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="K143" s="7"/>
       <c r="L143" s="7"/>
@@ -5860,7 +5918,7 @@
       </c>
       <c r="D144" s="7"/>
       <c t="s" r="E144" s="7">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="F144" s="7">
         <v>321</v>
@@ -5869,13 +5927,13 @@
         <v>31</v>
       </c>
       <c t="s" r="H144" s="8">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c t="s" r="I144" s="7">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c t="s" r="J144" s="7">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="K144" s="7"/>
       <c r="L144" s="7"/>
@@ -5893,22 +5951,22 @@
       </c>
       <c r="D145" s="7"/>
       <c t="s" r="E145" s="7">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="F145" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G145" s="8">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c t="s" r="H145" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I145" s="7">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c t="s" r="J145" s="7">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="K145" s="7"/>
       <c r="L145" s="7"/>
@@ -5926,7 +5984,7 @@
       </c>
       <c r="D146" s="7"/>
       <c t="s" r="E146" s="7">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="F146" s="7">
         <v>321</v>
@@ -5935,13 +5993,13 @@
         <v>31</v>
       </c>
       <c t="s" r="H146" s="8">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c t="s" r="I146" s="7">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c t="s" r="J146" s="7">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="K146" s="7"/>
       <c r="L146" s="7"/>
@@ -5974,7 +6032,7 @@
       </c>
       <c r="D148" s="7"/>
       <c t="s" r="E148" s="7">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="F148" s="7">
         <v>321</v>
@@ -5986,10 +6044,10 @@
         <v>32</v>
       </c>
       <c t="s" r="I148" s="7">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c t="s" r="J148" s="7">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="K148" s="7"/>
       <c r="L148" s="7"/>
@@ -6007,7 +6065,7 @@
       </c>
       <c r="D149" s="7"/>
       <c t="s" r="E149" s="7">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="F149" s="7">
         <v>321</v>
@@ -6019,10 +6077,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I149" s="7">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c t="s" r="J149" s="7">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K149" s="7"/>
       <c r="L149" s="7"/>
@@ -6040,7 +6098,7 @@
       </c>
       <c r="D150" s="7"/>
       <c t="s" r="E150" s="7">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="F150" s="7">
         <v>321</v>
@@ -6049,13 +6107,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H150" s="8">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c t="s" r="I150" s="7">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c t="s" r="J150" s="7">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="K150" s="7"/>
       <c r="L150" s="7"/>
@@ -6073,22 +6131,22 @@
       </c>
       <c r="D151" s="7"/>
       <c t="s" r="E151" s="7">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="F151" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G151" s="8">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c t="s" r="H151" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I151" s="7">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c t="s" r="J151" s="7">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="K151" s="7"/>
       <c r="L151" s="7"/>
@@ -6106,7 +6164,7 @@
       </c>
       <c r="D152" s="7"/>
       <c t="s" r="E152" s="7">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="F152" s="7">
         <v>321</v>
@@ -6115,13 +6173,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H152" s="8">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c t="s" r="I152" s="7">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c t="s" r="J152" s="7">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="K152" s="7"/>
       <c r="L152" s="7"/>
@@ -6154,7 +6212,7 @@
       </c>
       <c r="D154" s="7"/>
       <c t="s" r="E154" s="7">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="F154" s="7">
         <v>321</v>
@@ -6163,10 +6221,10 @@
         <v>41</v>
       </c>
       <c t="s" r="H154" s="8">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c t="s" r="I154" s="7">
-        <v>152</v>
+        <v>109</v>
       </c>
       <c t="s" r="J154" s="7">
         <v>29</v>
@@ -6187,22 +6245,22 @@
       </c>
       <c r="D155" s="7"/>
       <c t="s" r="E155" s="7">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="F155" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G155" s="8">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c t="s" r="H155" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I155" s="7">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c t="s" r="J155" s="7">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K155" s="7"/>
       <c r="L155" s="7"/>
@@ -6220,7 +6278,7 @@
       </c>
       <c r="D156" s="7"/>
       <c t="s" r="E156" s="7">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="F156" s="7">
         <v>321</v>
@@ -6232,10 +6290,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I156" s="7">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c t="s" r="J156" s="7">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="K156" s="7"/>
       <c r="L156" s="7"/>
@@ -6253,7 +6311,7 @@
       </c>
       <c r="D157" s="7"/>
       <c t="s" r="E157" s="7">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="F157" s="7">
         <v>321</v>
@@ -6265,10 +6323,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I157" s="7">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c t="s" r="J157" s="7">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="K157" s="7"/>
       <c r="L157" s="7"/>
@@ -6286,7 +6344,7 @@
       </c>
       <c r="D158" s="7"/>
       <c t="s" r="E158" s="7">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="F158" s="7">
         <v>321</v>
@@ -6295,13 +6353,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H158" s="8">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c t="s" r="I158" s="7">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c t="s" r="J158" s="7">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K158" s="7"/>
       <c r="L158" s="7"/>
@@ -6319,19 +6377,19 @@
       </c>
       <c r="D159" s="7"/>
       <c t="s" r="E159" s="7">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="F159" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G159" s="8">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c t="s" r="H159" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I159" s="7">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c t="s" r="J159" s="7">
         <v>25</v>
@@ -6367,26 +6425,28 @@
       </c>
       <c r="D161" s="7"/>
       <c t="s" r="E161" s="7">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="F161" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G161" s="8">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c t="s" r="H161" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I161" s="7">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c t="s" r="J161" s="7">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="K161" s="7"/>
       <c r="L161" s="7"/>
-      <c r="M161" s="7"/>
+      <c t="s" r="M161" s="7">
+        <v>116</v>
+      </c>
     </row>
     <row r="162" ht="14.25" customHeight="1">
       <c t="s" r="A162" s="6">
@@ -6396,11 +6456,11 @@
         <v>5068</v>
       </c>
       <c t="s" r="C162" s="7">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="D162" s="7"/>
       <c t="s" r="E162" s="7">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="F162" s="7">
         <v>321</v>
@@ -6412,10 +6472,10 @@
         <v>31</v>
       </c>
       <c t="s" r="I162" s="7">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c t="s" r="J162" s="7">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="K162" s="7"/>
       <c r="L162" s="7"/>
@@ -6429,11 +6489,11 @@
         <v>5068</v>
       </c>
       <c t="s" r="C163" s="7">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="D163" s="7"/>
       <c t="s" r="E163" s="7">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="F163" s="7">
         <v>321</v>
@@ -6442,13 +6502,13 @@
         <v>31</v>
       </c>
       <c t="s" r="H163" s="8">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c t="s" r="I163" s="7">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c t="s" r="J163" s="7">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="K163" s="7"/>
       <c r="L163" s="7"/>
@@ -6462,26 +6522,26 @@
         <v>5069</v>
       </c>
       <c t="s" r="C164" s="7">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="D164" s="7"/>
       <c t="s" r="E164" s="7">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="F164" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G164" s="8">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c t="s" r="H164" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I164" s="7">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c t="s" r="J164" s="7">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="K164" s="7"/>
       <c r="L164" s="7"/>
@@ -6514,22 +6574,22 @@
       </c>
       <c r="D166" s="7"/>
       <c t="s" r="E166" s="7">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="F166" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G166" s="8">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c t="s" r="H166" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I166" s="7">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c t="s" r="J166" s="7">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="K166" s="7"/>
       <c r="L166" s="7"/>
@@ -6547,7 +6607,7 @@
       </c>
       <c r="D167" s="7"/>
       <c t="s" r="E167" s="7">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="F167" s="7">
         <v>321</v>
@@ -6556,13 +6616,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H167" s="8">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c t="s" r="I167" s="7">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c t="s" r="J167" s="7">
-        <v>152</v>
+        <v>109</v>
       </c>
       <c r="K167" s="7"/>
       <c r="L167" s="7"/>
@@ -6595,7 +6655,7 @@
       </c>
       <c r="D169" s="7"/>
       <c t="s" r="E169" s="7">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="F169" s="7">
         <v>321</v>
@@ -6604,13 +6664,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H169" s="8">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c t="s" r="I169" s="7">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c t="s" r="J169" s="7">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="K169" s="7"/>
       <c r="L169" s="7"/>
@@ -6628,22 +6688,22 @@
       </c>
       <c r="D170" s="7"/>
       <c t="s" r="E170" s="7">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="F170" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G170" s="8">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c t="s" r="H170" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I170" s="7">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c t="s" r="J170" s="7">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="K170" s="7"/>
       <c r="L170" s="7"/>
@@ -6676,7 +6736,7 @@
       </c>
       <c r="D172" s="7"/>
       <c t="s" r="E172" s="7">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="F172" s="7">
         <v>321</v>
@@ -6685,7 +6745,7 @@
         <v>31</v>
       </c>
       <c t="s" r="H172" s="8">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c t="s" r="I172" s="7">
         <v>59</v>
@@ -6709,13 +6769,13 @@
       </c>
       <c r="D173" s="7"/>
       <c t="s" r="E173" s="7">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="F173" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G173" s="8">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c t="s" r="H173" s="8">
         <v>31</v>
@@ -6724,7 +6784,7 @@
         <v>35</v>
       </c>
       <c t="s" r="J173" s="7">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="K173" s="7"/>
       <c r="L173" s="7"/>
@@ -6742,7 +6802,7 @@
       </c>
       <c r="D174" s="7"/>
       <c t="s" r="E174" s="7">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="F174" s="7">
         <v>321</v>
@@ -6751,13 +6811,13 @@
         <v>31</v>
       </c>
       <c t="s" r="H174" s="8">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c t="s" r="I174" s="7">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c t="s" r="J174" s="7">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="K174" s="7"/>
       <c r="L174" s="7"/>
@@ -6775,13 +6835,13 @@
       </c>
       <c r="D175" s="7"/>
       <c t="s" r="E175" s="7">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="F175" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G175" s="8">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c t="s" r="H175" s="8">
         <v>31</v>
@@ -6790,7 +6850,7 @@
         <v>52</v>
       </c>
       <c t="s" r="J175" s="7">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="K175" s="7"/>
       <c r="L175" s="7"/>
@@ -6823,7 +6883,7 @@
       </c>
       <c r="D177" s="7"/>
       <c t="s" r="E177" s="7">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="F177" s="7">
         <v>321</v>
@@ -6832,13 +6892,13 @@
         <v>31</v>
       </c>
       <c t="s" r="H177" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="I177" s="7">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c t="s" r="J177" s="7">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K177" s="7"/>
       <c r="L177" s="7"/>
@@ -6856,22 +6916,22 @@
       </c>
       <c r="D178" s="7"/>
       <c t="s" r="E178" s="7">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="F178" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G178" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="H178" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I178" s="7">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c t="s" r="J178" s="7">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="K178" s="7"/>
       <c r="L178" s="7"/>
@@ -6889,7 +6949,7 @@
       </c>
       <c r="D179" s="7"/>
       <c t="s" r="E179" s="7">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="F179" s="7">
         <v>321</v>
@@ -6898,13 +6958,13 @@
         <v>31</v>
       </c>
       <c t="s" r="H179" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="I179" s="7">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c t="s" r="J179" s="7">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="K179" s="7"/>
       <c r="L179" s="7"/>
@@ -6922,13 +6982,13 @@
       </c>
       <c r="D180" s="7"/>
       <c t="s" r="E180" s="7">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="F180" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G180" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="H180" s="8">
         <v>31</v>
@@ -6937,7 +6997,7 @@
         <v>49</v>
       </c>
       <c t="s" r="J180" s="7">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="K180" s="7"/>
       <c r="L180" s="7"/>
@@ -6955,7 +7015,7 @@
       </c>
       <c r="D181" s="7"/>
       <c t="s" r="E181" s="7">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="F181" s="7">
         <v>321</v>
@@ -6964,13 +7024,13 @@
         <v>31</v>
       </c>
       <c t="s" r="H181" s="8">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c t="s" r="I181" s="7">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c t="s" r="J181" s="7">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="K181" s="7"/>
       <c r="L181" s="7"/>
@@ -6988,22 +7048,22 @@
       </c>
       <c r="D182" s="7"/>
       <c t="s" r="E182" s="7">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="F182" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G182" s="8">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c t="s" r="H182" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I182" s="7">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c t="s" r="J182" s="7">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="K182" s="7"/>
       <c r="L182" s="7"/>
@@ -7021,7 +7081,7 @@
       </c>
       <c r="D183" s="7"/>
       <c t="s" r="E183" s="7">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="F183" s="7">
         <v>321</v>
@@ -7030,13 +7090,13 @@
         <v>31</v>
       </c>
       <c t="s" r="H183" s="8">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c t="s" r="I183" s="7">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c t="s" r="J183" s="7">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="K183" s="7"/>
       <c r="L183" s="7"/>
@@ -7054,22 +7114,22 @@
       </c>
       <c r="D184" s="7"/>
       <c t="s" r="E184" s="7">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="F184" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G184" s="8">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c t="s" r="H184" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I184" s="7">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c t="s" r="J184" s="7">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="K184" s="7"/>
       <c r="L184" s="7"/>
@@ -7102,7 +7162,7 @@
       </c>
       <c r="D186" s="7"/>
       <c t="s" r="E186" s="7">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="F186" s="7">
         <v>321</v>
@@ -7111,13 +7171,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H186" s="8">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c t="s" r="I186" s="7">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c t="s" r="J186" s="7">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="K186" s="7"/>
       <c r="L186" s="7"/>
@@ -7135,13 +7195,13 @@
       </c>
       <c r="D187" s="7"/>
       <c t="s" r="E187" s="7">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="F187" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G187" s="8">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c t="s" r="H187" s="8">
         <v>41</v>
@@ -7150,7 +7210,7 @@
         <v>33</v>
       </c>
       <c t="s" r="J187" s="7">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="K187" s="7"/>
       <c r="L187" s="7"/>
@@ -7168,7 +7228,7 @@
       </c>
       <c r="D188" s="7"/>
       <c t="s" r="E188" s="7">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="F188" s="7">
         <v>321</v>
@@ -7180,10 +7240,10 @@
         <v>57</v>
       </c>
       <c t="s" r="I188" s="7">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c t="s" r="J188" s="7">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K188" s="7"/>
       <c r="L188" s="7"/>
@@ -7201,7 +7261,7 @@
       </c>
       <c r="D189" s="7"/>
       <c t="s" r="E189" s="7">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="F189" s="7">
         <v>321</v>
@@ -7216,7 +7276,7 @@
         <v>34</v>
       </c>
       <c t="s" r="J189" s="7">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="K189" s="7"/>
       <c r="L189" s="7"/>
@@ -7234,7 +7294,7 @@
       </c>
       <c r="D190" s="7"/>
       <c t="s" r="E190" s="7">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="F190" s="7">
         <v>321</v>
@@ -7243,13 +7303,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H190" s="8">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c t="s" r="I190" s="7">
         <v>50</v>
       </c>
       <c t="s" r="J190" s="7">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="K190" s="7"/>
       <c r="L190" s="7"/>
@@ -7267,22 +7327,22 @@
       </c>
       <c r="D191" s="7"/>
       <c t="s" r="E191" s="7">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="F191" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G191" s="8">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c t="s" r="H191" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I191" s="7">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c t="s" r="J191" s="7">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K191" s="7"/>
       <c r="L191" s="7"/>
@@ -7300,7 +7360,7 @@
       </c>
       <c r="D192" s="7"/>
       <c t="s" r="E192" s="7">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="F192" s="7">
         <v>321</v>
@@ -7309,13 +7369,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H192" s="8">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c t="s" r="I192" s="7">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c t="s" r="J192" s="7">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="K192" s="7"/>
       <c r="L192" s="7"/>
@@ -7333,22 +7393,22 @@
       </c>
       <c r="D193" s="7"/>
       <c t="s" r="E193" s="7">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="F193" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G193" s="8">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c t="s" r="H193" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I193" s="7">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c t="s" r="J193" s="7">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="K193" s="7"/>
       <c r="L193" s="7"/>
@@ -7381,22 +7441,22 @@
       </c>
       <c r="D195" s="7"/>
       <c t="s" r="E195" s="7">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="F195" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G195" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="H195" s="8">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c t="s" r="I195" s="7">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c t="s" r="J195" s="7">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="K195" s="7"/>
       <c r="L195" s="7"/>
@@ -7414,22 +7474,22 @@
       </c>
       <c r="D196" s="7"/>
       <c t="s" r="E196" s="7">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="F196" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G196" s="8">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c t="s" r="H196" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="I196" s="7">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c t="s" r="J196" s="7">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="K196" s="7"/>
       <c r="L196" s="7"/>
@@ -7447,22 +7507,22 @@
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G197" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="H197" s="8">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c t="s" r="I197" s="7">
         <v>36</v>
       </c>
       <c t="s" r="J197" s="7">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="K197" s="7"/>
       <c r="L197" s="7"/>
@@ -7480,22 +7540,22 @@
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="F198" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G198" s="8">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c t="s" r="H198" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="I198" s="7">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c t="s" r="J198" s="7">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="K198" s="7"/>
       <c r="L198" s="7"/>
@@ -7528,7 +7588,7 @@
       </c>
       <c r="D200" s="7"/>
       <c t="s" r="E200" s="7">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="F200" s="7">
         <v>321</v>
@@ -7537,13 +7597,13 @@
         <v>31</v>
       </c>
       <c t="s" r="H200" s="8">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c t="s" r="I200" s="7">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c t="s" r="J200" s="7">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K200" s="7"/>
       <c r="L200" s="7"/>
@@ -7561,22 +7621,22 @@
       </c>
       <c r="D201" s="7"/>
       <c t="s" r="E201" s="7">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="F201" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G201" s="8">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c t="s" r="H201" s="8">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c t="s" r="I201" s="7">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c t="s" r="J201" s="7">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="K201" s="7"/>
       <c r="L201" s="7"/>
@@ -7594,22 +7654,22 @@
       </c>
       <c r="D202" s="7"/>
       <c t="s" r="E202" s="7">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="F202" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G202" s="8">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c t="s" r="H202" s="8">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c t="s" r="I202" s="7">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c t="s" r="J202" s="7">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="K202" s="7"/>
       <c r="L202" s="7"/>
@@ -7627,13 +7687,13 @@
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="F203" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G203" s="8">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c t="s" r="H203" s="8">
         <v>31</v>
@@ -7642,7 +7702,7 @@
         <v>19</v>
       </c>
       <c t="s" r="J203" s="7">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="K203" s="7"/>
       <c r="L203" s="7"/>
@@ -7660,7 +7720,7 @@
       </c>
       <c r="D204" s="7"/>
       <c t="s" r="E204" s="7">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="F204" s="7">
         <v>321</v>
@@ -7672,10 +7732,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I204" s="7">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c t="s" r="J204" s="7">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="K204" s="7"/>
       <c r="L204" s="7"/>
@@ -7693,7 +7753,7 @@
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
@@ -7705,10 +7765,10 @@
         <v>31</v>
       </c>
       <c t="s" r="I205" s="7">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c t="s" r="J205" s="7">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="K205" s="7"/>
       <c r="L205" s="7"/>
@@ -7741,7 +7801,7 @@
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="F207" s="7">
         <v>321</v>
@@ -7753,14 +7813,16 @@
         <v>31</v>
       </c>
       <c t="s" r="I207" s="7">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c t="s" r="J207" s="7">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="K207" s="7"/>
       <c r="L207" s="7"/>
-      <c r="M207" s="7"/>
+      <c t="s" r="M207" s="7">
+        <v>288</v>
+      </c>
     </row>
     <row r="208" ht="14.25" customHeight="1">
       <c t="s" r="A208" s="6">
@@ -7774,7 +7836,7 @@
       </c>
       <c r="D208" s="7"/>
       <c t="s" r="E208" s="7">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="F208" s="7">
         <v>321</v>
@@ -7783,13 +7845,13 @@
         <v>31</v>
       </c>
       <c t="s" r="H208" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="I208" s="7">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c t="s" r="J208" s="7">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="K208" s="7"/>
       <c r="L208" s="7"/>
@@ -7807,22 +7869,22 @@
       </c>
       <c r="D209" s="7"/>
       <c t="s" r="E209" s="7">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="F209" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G209" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="H209" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I209" s="7">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c t="s" r="J209" s="7">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="K209" s="7"/>
       <c r="L209" s="7"/>
@@ -7840,7 +7902,7 @@
       </c>
       <c r="D210" s="7"/>
       <c t="s" r="E210" s="7">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="F210" s="7">
         <v>321</v>
@@ -7852,10 +7914,10 @@
         <v>57</v>
       </c>
       <c t="s" r="I210" s="7">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c t="s" r="J210" s="7">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="K210" s="7"/>
       <c r="L210" s="7"/>
@@ -7873,7 +7935,7 @@
       </c>
       <c r="D211" s="7"/>
       <c t="s" r="E211" s="7">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="F211" s="7">
         <v>321</v>
@@ -7885,10 +7947,10 @@
         <v>31</v>
       </c>
       <c t="s" r="I211" s="7">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c t="s" r="J211" s="7">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="K211" s="7"/>
       <c r="L211" s="7"/>
@@ -7906,7 +7968,7 @@
       </c>
       <c r="D212" s="7"/>
       <c t="s" r="E212" s="7">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="F212" s="7">
         <v>321</v>
@@ -7918,10 +7980,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I212" s="7">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c t="s" r="J212" s="7">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="K212" s="7"/>
       <c r="L212" s="7"/>
@@ -7954,7 +8016,7 @@
       </c>
       <c r="D214" s="7"/>
       <c t="s" r="E214" s="7">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="F214" s="7">
         <v>321</v>
@@ -7963,17 +8025,21 @@
         <v>41</v>
       </c>
       <c t="s" r="H214" s="8">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c t="s" r="I214" s="7">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c t="s" r="J214" s="7">
-        <v>244</v>
-      </c>
-      <c r="K214" s="7"/>
+        <v>251</v>
+      </c>
+      <c t="s" r="K214" s="7">
+        <v>168</v>
+      </c>
       <c r="L214" s="7"/>
-      <c r="M214" s="7"/>
+      <c t="s" r="M214" s="7">
+        <v>293</v>
+      </c>
     </row>
     <row r="215" ht="15" customHeight="1">
       <c t="s" r="A215" s="6">
@@ -7987,40 +8053,44 @@
       </c>
       <c r="D215" s="7"/>
       <c t="s" r="E215" s="7">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="F215" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G215" s="8">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c t="s" r="H215" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I215" s="7">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c t="s" r="J215" s="7">
-        <v>67</v>
-      </c>
-      <c r="K215" s="7"/>
+        <v>68</v>
+      </c>
+      <c t="s" r="K215" s="7">
+        <v>44</v>
+      </c>
       <c r="L215" s="7"/>
-      <c r="M215" s="7"/>
+      <c t="s" r="M215" s="7">
+        <v>295</v>
+      </c>
     </row>
     <row r="216" ht="14.25" customHeight="1">
       <c t="s" r="A216" s="6">
         <v>13</v>
       </c>
       <c r="B216" s="7">
-        <v>272</v>
+        <v>1813</v>
       </c>
       <c t="s" r="C216" s="7">
         <v>14</v>
       </c>
       <c r="D216" s="7"/>
       <c t="s" r="E216" s="7">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="F216" s="7">
         <v>321</v>
@@ -8029,13 +8099,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H216" s="8">
-        <v>132</v>
+        <v>296</v>
       </c>
       <c t="s" r="I216" s="7">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c t="s" r="J216" s="7">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="K216" s="7"/>
       <c r="L216" s="7"/>
@@ -8046,29 +8116,29 @@
         <v>13</v>
       </c>
       <c r="B217" s="7">
-        <v>273</v>
+        <v>1814</v>
       </c>
       <c t="s" r="C217" s="7">
         <v>14</v>
       </c>
       <c r="D217" s="7"/>
       <c t="s" r="E217" s="7">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="F217" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G217" s="8">
-        <v>132</v>
+        <v>296</v>
       </c>
       <c t="s" r="H217" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I217" s="7">
-        <v>94</v>
+        <v>217</v>
       </c>
       <c t="s" r="J217" s="7">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="K217" s="7"/>
       <c r="L217" s="7"/>
@@ -8086,7 +8156,7 @@
       </c>
       <c r="D218" s="7"/>
       <c t="s" r="E218" s="7">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="F218" s="7">
         <v>321</v>
@@ -8098,10 +8168,10 @@
         <v>31</v>
       </c>
       <c t="s" r="I218" s="7">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c t="s" r="J218" s="7">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K218" s="7"/>
       <c r="L218" s="7"/>
@@ -8119,7 +8189,7 @@
       </c>
       <c r="D219" s="7"/>
       <c t="s" r="E219" s="7">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="F219" s="7">
         <v>321</v>
@@ -8131,10 +8201,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I219" s="7">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c t="s" r="J219" s="7">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="K219" s="7"/>
       <c r="L219" s="7"/>
@@ -8167,22 +8237,22 @@
       </c>
       <c r="D221" s="7"/>
       <c t="s" r="E221" s="7">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="F221" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G221" s="8">
-        <v>287</v>
+        <v>298</v>
       </c>
       <c t="s" r="H221" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I221" s="7">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c t="s" r="J221" s="7">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="K221" s="7"/>
       <c r="L221" s="7"/>
@@ -8200,7 +8270,7 @@
       </c>
       <c r="D222" s="7"/>
       <c t="s" r="E222" s="7">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="F222" s="7">
         <v>321</v>
@@ -8215,7 +8285,7 @@
         <v>34</v>
       </c>
       <c t="s" r="J222" s="7">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="K222" s="7"/>
       <c r="L222" s="7"/>
@@ -8233,7 +8303,7 @@
       </c>
       <c r="D223" s="7"/>
       <c t="s" r="E223" s="7">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="F223" s="7">
         <v>321</v>
@@ -8245,10 +8315,10 @@
         <v>31</v>
       </c>
       <c t="s" r="I223" s="7">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c t="s" r="J223" s="7">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="K223" s="7"/>
       <c r="L223" s="7"/>
@@ -8266,7 +8336,7 @@
       </c>
       <c r="D224" s="7"/>
       <c t="s" r="E224" s="7">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="F224" s="7">
         <v>321</v>
@@ -8278,10 +8348,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I224" s="7">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c t="s" r="J224" s="7">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="K224" s="7"/>
       <c r="L224" s="7"/>
@@ -8299,7 +8369,7 @@
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
@@ -8311,10 +8381,10 @@
         <v>31</v>
       </c>
       <c t="s" r="I225" s="7">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c t="s" r="J225" s="7">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="K225" s="7"/>
       <c r="L225" s="7"/>
@@ -8332,7 +8402,7 @@
       </c>
       <c r="D226" s="7"/>
       <c t="s" r="E226" s="7">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="F226" s="7">
         <v>321</v>
@@ -8344,10 +8414,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I226" s="7">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c t="s" r="J226" s="7">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="K226" s="7"/>
       <c r="L226" s="7"/>
@@ -8380,7 +8450,7 @@
       </c>
       <c r="D228" s="7"/>
       <c t="s" r="E228" s="7">
-        <v>288</v>
+        <v>299</v>
       </c>
       <c r="F228" s="7">
         <v>321</v>
@@ -8389,13 +8459,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H228" s="8">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c t="s" r="I228" s="7">
-        <v>289</v>
+        <v>300</v>
       </c>
       <c t="s" r="J228" s="7">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="K228" s="7"/>
       <c r="L228" s="7"/>
@@ -8413,22 +8483,22 @@
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>288</v>
+        <v>299</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G229" s="8">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c t="s" r="H229" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I229" s="7">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c t="s" r="J229" s="7">
-        <v>290</v>
+        <v>301</v>
       </c>
       <c r="K229" s="7"/>
       <c r="L229" s="7"/>
@@ -8446,7 +8516,7 @@
       </c>
       <c r="D230" s="7"/>
       <c t="s" r="E230" s="7">
-        <v>288</v>
+        <v>299</v>
       </c>
       <c r="F230" s="7">
         <v>321</v>
@@ -8455,13 +8525,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H230" s="8">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c t="s" r="I230" s="7">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c t="s" r="J230" s="7">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="K230" s="7"/>
       <c r="L230" s="7"/>
@@ -8479,22 +8549,22 @@
       </c>
       <c r="D231" s="7"/>
       <c t="s" r="E231" s="7">
-        <v>288</v>
+        <v>299</v>
       </c>
       <c r="F231" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G231" s="8">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c t="s" r="H231" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I231" s="7">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c t="s" r="J231" s="7">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="K231" s="7"/>
       <c r="L231" s="7"/>
@@ -8512,7 +8582,7 @@
       </c>
       <c r="D232" s="7"/>
       <c t="s" r="E232" s="7">
-        <v>288</v>
+        <v>299</v>
       </c>
       <c r="F232" s="7">
         <v>321</v>
@@ -8524,10 +8594,10 @@
         <v>31</v>
       </c>
       <c t="s" r="I232" s="7">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c t="s" r="J232" s="7">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="K232" s="7"/>
       <c r="L232" s="7"/>
@@ -8553,14 +8623,14 @@
         <v>13</v>
       </c>
       <c r="B234" s="7">
-        <v>1813</v>
+        <v>272</v>
       </c>
       <c t="s" r="C234" s="7">
         <v>14</v>
       </c>
       <c r="D234" s="7"/>
       <c t="s" r="E234" s="7">
-        <v>291</v>
+        <v>302</v>
       </c>
       <c r="F234" s="7">
         <v>321</v>
@@ -8569,13 +8639,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H234" s="8">
-        <v>292</v>
+        <v>137</v>
       </c>
       <c t="s" r="I234" s="7">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c t="s" r="J234" s="7">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="K234" s="7"/>
       <c r="L234" s="7"/>
@@ -8586,29 +8656,29 @@
         <v>13</v>
       </c>
       <c r="B235" s="7">
-        <v>1814</v>
+        <v>273</v>
       </c>
       <c t="s" r="C235" s="7">
         <v>14</v>
       </c>
       <c r="D235" s="7"/>
       <c t="s" r="E235" s="7">
-        <v>291</v>
+        <v>302</v>
       </c>
       <c r="F235" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G235" s="8">
-        <v>292</v>
+        <v>137</v>
       </c>
       <c t="s" r="H235" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I235" s="7">
-        <v>210</v>
+        <v>96</v>
       </c>
       <c t="s" r="J235" s="7">
-        <v>50</v>
+        <v>19</v>
       </c>
       <c r="K235" s="7"/>
       <c r="L235" s="7"/>
@@ -8641,7 +8711,7 @@
       </c>
       <c r="D237" s="7"/>
       <c t="s" r="E237" s="7">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="F237" s="7">
         <v>321</v>
@@ -8653,14 +8723,16 @@
         <v>31</v>
       </c>
       <c t="s" r="I237" s="7">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c t="s" r="J237" s="7">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="K237" s="7"/>
       <c r="L237" s="7"/>
-      <c r="M237" s="7"/>
+      <c t="s" r="M237" s="7">
+        <v>304</v>
+      </c>
     </row>
     <row r="238" ht="14.25" customHeight="1">
       <c t="s" r="A238" s="6">
@@ -8674,7 +8746,7 @@
       </c>
       <c r="D238" s="7"/>
       <c t="s" r="E238" s="7">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="F238" s="7">
         <v>321</v>
@@ -8686,10 +8758,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I238" s="7">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c t="s" r="J238" s="7">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="K238" s="7"/>
       <c r="L238" s="7"/>
@@ -8707,7 +8779,7 @@
       </c>
       <c r="D239" s="7"/>
       <c t="s" r="E239" s="7">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="F239" s="7">
         <v>321</v>
@@ -8716,10 +8788,10 @@
         <v>41</v>
       </c>
       <c t="s" r="H239" s="8">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c t="s" r="I239" s="7">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c t="s" r="J239" s="7">
         <v>48</v>
@@ -8740,22 +8812,22 @@
       </c>
       <c r="D240" s="7"/>
       <c t="s" r="E240" s="7">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="F240" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G240" s="8">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c t="s" r="H240" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I240" s="7">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c t="s" r="J240" s="7">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="K240" s="7"/>
       <c r="L240" s="7"/>
@@ -8773,7 +8845,7 @@
       </c>
       <c r="D241" s="7"/>
       <c t="s" r="E241" s="7">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="F241" s="7">
         <v>321</v>
@@ -8782,13 +8854,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H241" s="8">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c t="s" r="I241" s="7">
-        <v>294</v>
+        <v>305</v>
       </c>
       <c t="s" r="J241" s="7">
-        <v>295</v>
+        <v>306</v>
       </c>
       <c r="K241" s="7"/>
       <c r="L241" s="7"/>
@@ -8806,22 +8878,22 @@
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="F242" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G242" s="8">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c t="s" r="H242" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I242" s="7">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c t="s" r="J242" s="7">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K242" s="7"/>
       <c r="L242" s="7"/>
@@ -8854,29 +8926,29 @@
       </c>
       <c r="D244" s="7"/>
       <c t="s" r="E244" s="7">
-        <v>296</v>
+        <v>307</v>
       </c>
       <c r="F244" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G244" s="8">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c t="s" r="H244" s="8">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c t="s" r="I244" s="7">
         <v>55</v>
       </c>
       <c t="s" r="J244" s="7">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c t="s" r="K244" s="7">
-        <v>152</v>
+        <v>109</v>
       </c>
       <c r="L244" s="7"/>
       <c t="s" r="M244" s="7">
-        <v>297</v>
+        <v>94</v>
       </c>
     </row>
     <row r="245" ht="15" customHeight="1">
@@ -8891,25 +8963,25 @@
       </c>
       <c r="D245" s="7"/>
       <c t="s" r="E245" s="7">
-        <v>296</v>
+        <v>307</v>
       </c>
       <c r="F245" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G245" s="8">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c t="s" r="H245" s="8">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c t="s" r="I245" s="7">
         <v>18</v>
       </c>
       <c t="s" r="J245" s="7">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c t="s" r="K245" s="7">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="L245" s="7"/>
       <c t="s" r="M245" s="7">
@@ -8928,29 +9000,29 @@
       </c>
       <c r="D246" s="7"/>
       <c t="s" r="E246" s="7">
-        <v>296</v>
+        <v>307</v>
       </c>
       <c r="F246" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G246" s="8">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c t="s" r="H246" s="8">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c t="s" r="I246" s="7">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c t="s" r="J246" s="7">
-        <v>298</v>
+        <v>308</v>
       </c>
       <c t="s" r="K246" s="7">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="L246" s="7"/>
       <c t="s" r="M246" s="7">
-        <v>176</v>
+        <v>182</v>
       </c>
     </row>
     <row r="247" ht="14.25" customHeight="1">
@@ -8965,25 +9037,25 @@
       </c>
       <c r="D247" s="7"/>
       <c t="s" r="E247" s="7">
-        <v>296</v>
+        <v>307</v>
       </c>
       <c r="F247" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G247" s="8">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c t="s" r="H247" s="8">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c t="s" r="I247" s="7">
         <v>50</v>
       </c>
       <c t="s" r="J247" s="7">
-        <v>299</v>
+        <v>309</v>
       </c>
       <c t="s" r="K247" s="7">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="L247" s="7"/>
       <c t="s" r="M247" s="7">
@@ -9002,29 +9074,29 @@
       </c>
       <c r="D248" s="7"/>
       <c t="s" r="E248" s="7">
-        <v>296</v>
+        <v>307</v>
       </c>
       <c r="F248" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G248" s="8">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c t="s" r="H248" s="8">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c t="s" r="I248" s="7">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c t="s" r="J248" s="7">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c t="s" r="K248" s="7">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="L248" s="7"/>
       <c t="s" r="M248" s="7">
-        <v>138</v>
+        <v>143</v>
       </c>
     </row>
     <row r="249" ht="14.25" customHeight="1">
@@ -9039,22 +9111,22 @@
       </c>
       <c r="D249" s="7"/>
       <c t="s" r="E249" s="7">
-        <v>296</v>
+        <v>307</v>
       </c>
       <c r="F249" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G249" s="8">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c t="s" r="H249" s="8">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c t="s" r="I249" s="7">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c t="s" r="J249" s="7">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="K249" s="7"/>
       <c r="L249" s="7"/>
@@ -9087,26 +9159,28 @@
       </c>
       <c r="D251" s="7"/>
       <c t="s" r="E251" s="7">
-        <v>303</v>
+        <v>313</v>
       </c>
       <c r="F251" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G251" s="8">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c t="s" r="H251" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I251" s="7">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c t="s" r="J251" s="7">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="K251" s="7"/>
       <c r="L251" s="7"/>
-      <c r="M251" s="7"/>
+      <c t="s" r="M251" s="7">
+        <v>295</v>
+      </c>
     </row>
     <row r="252" ht="14.25" customHeight="1">
       <c t="s" r="A252" s="6">
@@ -9120,7 +9194,7 @@
       </c>
       <c r="D252" s="7"/>
       <c t="s" r="E252" s="7">
-        <v>303</v>
+        <v>313</v>
       </c>
       <c r="F252" s="7">
         <v>321</v>
@@ -9132,10 +9206,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I252" s="7">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c t="s" r="J252" s="7">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K252" s="7"/>
       <c r="L252" s="7"/>
@@ -9153,7 +9227,7 @@
       </c>
       <c r="D253" s="7"/>
       <c t="s" r="E253" s="7">
-        <v>303</v>
+        <v>313</v>
       </c>
       <c r="F253" s="7">
         <v>321</v>
@@ -9162,13 +9236,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H253" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="I253" s="7">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c t="s" r="J253" s="7">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="K253" s="7"/>
       <c r="L253" s="7"/>
@@ -9186,22 +9260,22 @@
       </c>
       <c r="D254" s="7"/>
       <c t="s" r="E254" s="7">
-        <v>303</v>
+        <v>313</v>
       </c>
       <c r="F254" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G254" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="H254" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I254" s="7">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c t="s" r="J254" s="7">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K254" s="7"/>
       <c r="L254" s="7"/>
@@ -9219,7 +9293,7 @@
       </c>
       <c r="D255" s="7"/>
       <c t="s" r="E255" s="7">
-        <v>303</v>
+        <v>313</v>
       </c>
       <c r="F255" s="7">
         <v>321</v>
@@ -9231,10 +9305,10 @@
         <v>31</v>
       </c>
       <c t="s" r="I255" s="7">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c t="s" r="J255" s="7">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K255" s="7"/>
       <c r="L255" s="7"/>
@@ -9252,7 +9326,7 @@
       </c>
       <c r="D256" s="7"/>
       <c t="s" r="E256" s="7">
-        <v>303</v>
+        <v>313</v>
       </c>
       <c r="F256" s="7">
         <v>321</v>
@@ -9264,10 +9338,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I256" s="7">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c t="s" r="J256" s="7">
-        <v>304</v>
+        <v>314</v>
       </c>
       <c r="K256" s="7"/>
       <c r="L256" s="7"/>
@@ -9300,7 +9374,7 @@
       </c>
       <c r="D258" s="7"/>
       <c t="s" r="E258" s="7">
-        <v>305</v>
+        <v>315</v>
       </c>
       <c r="F258" s="7">
         <v>321</v>
@@ -9309,13 +9383,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H258" s="8">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c t="s" r="I258" s="7">
         <v>45</v>
       </c>
       <c t="s" r="J258" s="7">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="K258" s="7"/>
       <c r="L258" s="7"/>
@@ -9333,13 +9407,13 @@
       </c>
       <c r="D259" s="7"/>
       <c t="s" r="E259" s="7">
-        <v>305</v>
+        <v>315</v>
       </c>
       <c r="F259" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G259" s="8">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c t="s" r="H259" s="8">
         <v>41</v>
@@ -9366,7 +9440,7 @@
       </c>
       <c r="D260" s="7"/>
       <c t="s" r="E260" s="7">
-        <v>305</v>
+        <v>315</v>
       </c>
       <c r="F260" s="7">
         <v>321</v>
@@ -9375,13 +9449,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H260" s="8">
-        <v>306</v>
+        <v>316</v>
       </c>
       <c t="s" r="I260" s="7">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c t="s" r="J260" s="7">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K260" s="7"/>
       <c r="L260" s="7"/>
@@ -9399,22 +9473,22 @@
       </c>
       <c r="D261" s="7"/>
       <c t="s" r="E261" s="7">
-        <v>305</v>
+        <v>315</v>
       </c>
       <c r="F261" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G261" s="8">
-        <v>306</v>
+        <v>316</v>
       </c>
       <c t="s" r="H261" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I261" s="7">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c t="s" r="J261" s="7">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="K261" s="7"/>
       <c r="L261" s="7"/>
@@ -9447,7 +9521,7 @@
       </c>
       <c r="D263" s="7"/>
       <c t="s" r="E263" s="7">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="F263" s="7">
         <v>321</v>
@@ -9456,13 +9530,13 @@
         <v>31</v>
       </c>
       <c t="s" r="H263" s="8">
-        <v>309</v>
+        <v>319</v>
       </c>
       <c t="s" r="I263" s="7">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c t="s" r="J263" s="7">
-        <v>310</v>
+        <v>320</v>
       </c>
       <c r="K263" s="7"/>
       <c r="L263" s="7"/>
@@ -9480,22 +9554,22 @@
       </c>
       <c r="D264" s="7"/>
       <c t="s" r="E264" s="7">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="F264" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G264" s="8">
-        <v>309</v>
+        <v>319</v>
       </c>
       <c t="s" r="H264" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I264" s="7">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c t="s" r="J264" s="7">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="K264" s="7"/>
       <c r="L264" s="7"/>
@@ -9513,7 +9587,7 @@
       </c>
       <c r="D265" s="7"/>
       <c t="s" r="E265" s="7">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="F265" s="7">
         <v>321</v>
@@ -9525,10 +9599,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I265" s="7">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c t="s" r="J265" s="7">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="K265" s="7"/>
       <c r="L265" s="7"/>
@@ -9546,7 +9620,7 @@
       </c>
       <c r="D266" s="7"/>
       <c t="s" r="E266" s="7">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="F266" s="7">
         <v>321</v>
@@ -9558,10 +9632,10 @@
         <v>31</v>
       </c>
       <c t="s" r="I266" s="7">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c t="s" r="J266" s="7">
-        <v>313</v>
+        <v>323</v>
       </c>
       <c r="K266" s="7"/>
       <c r="L266" s="7"/>
@@ -9594,7 +9668,7 @@
       </c>
       <c r="D268" s="7"/>
       <c t="s" r="E268" s="7">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="F268" s="7">
         <v>321</v>
@@ -9603,17 +9677,19 @@
         <v>31</v>
       </c>
       <c t="s" r="H268" s="8">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c t="s" r="I268" s="7">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c t="s" r="J268" s="7">
         <v>58</v>
       </c>
       <c r="K268" s="7"/>
       <c r="L268" s="7"/>
-      <c r="M268" s="7"/>
+      <c t="s" r="M268" s="7">
+        <v>293</v>
+      </c>
     </row>
     <row r="269" ht="14.25" customHeight="1">
       <c t="s" r="A269" s="6">
@@ -9627,22 +9703,22 @@
       </c>
       <c r="D269" s="7"/>
       <c t="s" r="E269" s="7">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="F269" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G269" s="8">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c t="s" r="H269" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I269" s="7">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c t="s" r="J269" s="7">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="K269" s="7"/>
       <c r="L269" s="7"/>
@@ -9660,7 +9736,7 @@
       </c>
       <c r="D270" s="7"/>
       <c t="s" r="E270" s="7">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="F270" s="7">
         <v>321</v>
@@ -9669,13 +9745,13 @@
         <v>31</v>
       </c>
       <c t="s" r="H270" s="8">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c t="s" r="I270" s="7">
-        <v>297</v>
+        <v>325</v>
       </c>
       <c t="s" r="J270" s="7">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K270" s="7"/>
       <c r="L270" s="7"/>
@@ -9693,22 +9769,22 @@
       </c>
       <c r="D271" s="7"/>
       <c t="s" r="E271" s="7">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="F271" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G271" s="8">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c t="s" r="H271" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I271" s="7">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c t="s" r="J271" s="7">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="K271" s="7"/>
       <c r="L271" s="7"/>
@@ -9726,7 +9802,7 @@
       </c>
       <c r="D272" s="7"/>
       <c t="s" r="E272" s="7">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="F272" s="7">
         <v>321</v>
@@ -9735,13 +9811,13 @@
         <v>31</v>
       </c>
       <c t="s" r="H272" s="8">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c t="s" r="I272" s="7">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c t="s" r="J272" s="7">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="K272" s="7"/>
       <c r="L272" s="7"/>
@@ -9759,22 +9835,22 @@
       </c>
       <c r="D273" s="7"/>
       <c t="s" r="E273" s="7">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="F273" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G273" s="8">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c t="s" r="H273" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I273" s="7">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c t="s" r="J273" s="7">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K273" s="7"/>
       <c r="L273" s="7"/>
@@ -9807,7 +9883,7 @@
       </c>
       <c r="D275" s="7"/>
       <c t="s" r="E275" s="7">
-        <v>315</v>
+        <v>326</v>
       </c>
       <c r="F275" s="7">
         <v>320</v>
@@ -9816,13 +9892,13 @@
         <v>31</v>
       </c>
       <c t="s" r="H275" s="8">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c t="s" r="I275" s="7">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c t="s" r="J275" s="7">
-        <v>316</v>
+        <v>293</v>
       </c>
       <c r="K275" s="7"/>
       <c r="L275" s="7"/>
@@ -9840,19 +9916,19 @@
       </c>
       <c r="D276" s="7"/>
       <c t="s" r="E276" s="7">
-        <v>315</v>
+        <v>326</v>
       </c>
       <c r="F276" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G276" s="8">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c t="s" r="H276" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I276" s="7">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c t="s" r="J276" s="7">
         <v>29</v>
@@ -9873,7 +9949,7 @@
       </c>
       <c r="D277" s="7"/>
       <c t="s" r="E277" s="7">
-        <v>315</v>
+        <v>326</v>
       </c>
       <c r="F277" s="7">
         <v>320</v>
@@ -9882,13 +9958,13 @@
         <v>31</v>
       </c>
       <c t="s" r="H277" s="8">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c t="s" r="I277" s="7">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c t="s" r="J277" s="7">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="K277" s="7"/>
       <c r="L277" s="7"/>
@@ -9906,13 +9982,13 @@
       </c>
       <c r="D278" s="7"/>
       <c t="s" r="E278" s="7">
-        <v>315</v>
+        <v>326</v>
       </c>
       <c r="F278" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G278" s="8">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c t="s" r="H278" s="8">
         <v>31</v>
@@ -9921,7 +9997,7 @@
         <v>34</v>
       </c>
       <c t="s" r="J278" s="7">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K278" s="7"/>
       <c r="L278" s="7"/>
@@ -9939,7 +10015,7 @@
       </c>
       <c r="D279" s="7"/>
       <c t="s" r="E279" s="7">
-        <v>315</v>
+        <v>326</v>
       </c>
       <c r="F279" s="7">
         <v>320</v>
@@ -9948,13 +10024,13 @@
         <v>31</v>
       </c>
       <c t="s" r="H279" s="8">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c t="s" r="I279" s="7">
         <v>23</v>
       </c>
       <c t="s" r="J279" s="7">
-        <v>317</v>
+        <v>327</v>
       </c>
       <c r="K279" s="7"/>
       <c r="L279" s="7"/>
@@ -9972,22 +10048,22 @@
       </c>
       <c r="D280" s="7"/>
       <c t="s" r="E280" s="7">
-        <v>315</v>
+        <v>326</v>
       </c>
       <c r="F280" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G280" s="8">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c t="s" r="H280" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I280" s="7">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c t="s" r="J280" s="7">
-        <v>295</v>
+        <v>306</v>
       </c>
       <c r="K280" s="7"/>
       <c r="L280" s="7"/>
@@ -10005,7 +10081,7 @@
       </c>
       <c r="D281" s="7"/>
       <c t="s" r="E281" s="7">
-        <v>315</v>
+        <v>326</v>
       </c>
       <c r="F281" s="7">
         <v>320</v>
@@ -10014,13 +10090,13 @@
         <v>31</v>
       </c>
       <c t="s" r="H281" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="I281" s="7">
         <v>52</v>
       </c>
       <c t="s" r="J281" s="7">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="K281" s="7"/>
       <c r="L281" s="7"/>
@@ -10038,22 +10114,22 @@
       </c>
       <c r="D282" s="7"/>
       <c t="s" r="E282" s="7">
-        <v>315</v>
+        <v>326</v>
       </c>
       <c r="F282" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G282" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="H282" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I282" s="7">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c t="s" r="J282" s="7">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="K282" s="7"/>
       <c r="L282" s="7"/>
@@ -10086,7 +10162,7 @@
       </c>
       <c r="D284" s="7"/>
       <c t="s" r="E284" s="7">
-        <v>318</v>
+        <v>328</v>
       </c>
       <c r="F284" s="7">
         <v>321</v>
@@ -10095,13 +10171,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H284" s="8">
-        <v>309</v>
+        <v>319</v>
       </c>
       <c t="s" r="I284" s="7">
-        <v>290</v>
+        <v>301</v>
       </c>
       <c t="s" r="J284" s="7">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="K284" s="7"/>
       <c r="L284" s="7"/>
@@ -10119,22 +10195,22 @@
       </c>
       <c r="D285" s="7"/>
       <c t="s" r="E285" s="7">
-        <v>318</v>
+        <v>328</v>
       </c>
       <c r="F285" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G285" s="8">
-        <v>309</v>
+        <v>319</v>
       </c>
       <c t="s" r="H285" s="8">
         <v>57</v>
       </c>
       <c t="s" r="I285" s="7">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c t="s" r="J285" s="7">
-        <v>319</v>
+        <v>329</v>
       </c>
       <c r="K285" s="7"/>
       <c r="L285" s="7"/>
@@ -10152,7 +10228,7 @@
       </c>
       <c r="D286" s="7"/>
       <c t="s" r="E286" s="7">
-        <v>318</v>
+        <v>328</v>
       </c>
       <c r="F286" s="7">
         <v>321</v>
@@ -10161,13 +10237,13 @@
         <v>57</v>
       </c>
       <c t="s" r="H286" s="8">
-        <v>309</v>
+        <v>319</v>
       </c>
       <c t="s" r="I286" s="7">
-        <v>320</v>
+        <v>330</v>
       </c>
       <c t="s" r="J286" s="7">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="K286" s="7"/>
       <c r="L286" s="7"/>
@@ -10185,22 +10261,22 @@
       </c>
       <c r="D287" s="7"/>
       <c t="s" r="E287" s="7">
-        <v>318</v>
+        <v>328</v>
       </c>
       <c r="F287" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G287" s="8">
-        <v>309</v>
+        <v>319</v>
       </c>
       <c t="s" r="H287" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I287" s="7">
-        <v>321</v>
+        <v>331</v>
       </c>
       <c t="s" r="J287" s="7">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="K287" s="7"/>
       <c r="L287" s="7"/>
@@ -10233,7 +10309,7 @@
       </c>
       <c r="D289" s="7"/>
       <c t="s" r="E289" s="7">
-        <v>322</v>
+        <v>332</v>
       </c>
       <c r="F289" s="7">
         <v>321</v>
@@ -10242,10 +10318,10 @@
         <v>41</v>
       </c>
       <c t="s" r="H289" s="8">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c t="s" r="I289" s="7">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c t="s" r="J289" s="7">
         <v>19</v>
@@ -10266,22 +10342,22 @@
       </c>
       <c r="D290" s="7"/>
       <c t="s" r="E290" s="7">
-        <v>322</v>
+        <v>332</v>
       </c>
       <c r="F290" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G290" s="8">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c t="s" r="H290" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I290" s="7">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c t="s" r="J290" s="7">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="K290" s="7"/>
       <c r="L290" s="7"/>
@@ -10314,7 +10390,7 @@
       </c>
       <c r="D292" s="7"/>
       <c t="s" r="E292" s="7">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="F292" s="7">
         <v>320</v>
@@ -10326,10 +10402,10 @@
         <v>31</v>
       </c>
       <c t="s" r="I292" s="7">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c t="s" r="J292" s="7">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="K292" s="7"/>
       <c r="L292" s="7"/>
@@ -10347,7 +10423,7 @@
       </c>
       <c r="D293" s="7"/>
       <c t="s" r="E293" s="7">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="F293" s="7">
         <v>320</v>
@@ -10359,10 +10435,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I293" s="7">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c t="s" r="J293" s="7">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="K293" s="7"/>
       <c r="L293" s="7"/>
@@ -10380,7 +10456,7 @@
       </c>
       <c r="D294" s="7"/>
       <c t="s" r="E294" s="7">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="F294" s="7">
         <v>320</v>
@@ -10389,13 +10465,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H294" s="8">
-        <v>325</v>
+        <v>335</v>
       </c>
       <c t="s" r="I294" s="7">
         <v>36</v>
       </c>
       <c t="s" r="J294" s="7">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="K294" s="7"/>
       <c r="L294" s="7"/>
@@ -10413,22 +10489,22 @@
       </c>
       <c r="D295" s="7"/>
       <c t="s" r="E295" s="7">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="F295" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G295" s="8">
-        <v>325</v>
+        <v>335</v>
       </c>
       <c t="s" r="H295" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I295" s="7">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c t="s" r="J295" s="7">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K295" s="7"/>
       <c r="L295" s="7"/>
@@ -10461,7 +10537,7 @@
       </c>
       <c r="D297" s="7"/>
       <c t="s" r="E297" s="7">
-        <v>327</v>
+        <v>337</v>
       </c>
       <c r="F297" s="7">
         <v>320</v>
@@ -10473,10 +10549,10 @@
         <v>42</v>
       </c>
       <c t="s" r="I297" s="7">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c t="s" r="J297" s="7">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="K297" s="7"/>
       <c r="L297" s="7"/>
@@ -10494,7 +10570,7 @@
       </c>
       <c r="D298" s="7"/>
       <c t="s" r="E298" s="7">
-        <v>327</v>
+        <v>337</v>
       </c>
       <c r="F298" s="7">
         <v>320</v>
@@ -10506,10 +10582,10 @@
         <v>31</v>
       </c>
       <c t="s" r="I298" s="7">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c t="s" r="J298" s="7">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="K298" s="7"/>
       <c r="L298" s="7"/>
@@ -10527,7 +10603,7 @@
       </c>
       <c r="D299" s="7"/>
       <c t="s" r="E299" s="7">
-        <v>327</v>
+        <v>337</v>
       </c>
       <c r="F299" s="7">
         <v>320</v>
@@ -10539,10 +10615,10 @@
         <v>57</v>
       </c>
       <c t="s" r="I299" s="7">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c t="s" r="J299" s="7">
-        <v>310</v>
+        <v>320</v>
       </c>
       <c r="K299" s="7"/>
       <c r="L299" s="7"/>
@@ -10560,7 +10636,7 @@
       </c>
       <c r="D300" s="7"/>
       <c t="s" r="E300" s="7">
-        <v>327</v>
+        <v>337</v>
       </c>
       <c r="F300" s="7">
         <v>320</v>
@@ -10572,10 +10648,10 @@
         <v>31</v>
       </c>
       <c t="s" r="I300" s="7">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c t="s" r="J300" s="7">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="K300" s="7"/>
       <c r="L300" s="7"/>
@@ -10593,7 +10669,7 @@
       </c>
       <c r="D301" s="7"/>
       <c t="s" r="E301" s="7">
-        <v>327</v>
+        <v>337</v>
       </c>
       <c r="F301" s="7">
         <v>320</v>
@@ -10602,13 +10678,13 @@
         <v>31</v>
       </c>
       <c t="s" r="H301" s="8">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c t="s" r="I301" s="7">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c t="s" r="J301" s="7">
-        <v>328</v>
+        <v>338</v>
       </c>
       <c r="K301" s="7"/>
       <c r="L301" s="7"/>
@@ -10626,22 +10702,22 @@
       </c>
       <c r="D302" s="7"/>
       <c t="s" r="E302" s="7">
-        <v>327</v>
+        <v>337</v>
       </c>
       <c r="F302" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G302" s="8">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c t="s" r="H302" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I302" s="7">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c t="s" r="J302" s="7">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="K302" s="7"/>
       <c r="L302" s="7"/>
@@ -10674,7 +10750,7 @@
       </c>
       <c r="D304" s="7"/>
       <c t="s" r="E304" s="7">
-        <v>329</v>
+        <v>339</v>
       </c>
       <c r="F304" s="7">
         <v>321</v>
@@ -10686,14 +10762,16 @@
         <v>41</v>
       </c>
       <c t="s" r="I304" s="7">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c t="s" r="J304" s="7">
-        <v>316</v>
+        <v>293</v>
       </c>
       <c r="K304" s="7"/>
       <c r="L304" s="7"/>
-      <c r="M304" s="7"/>
+      <c t="s" r="M304" s="7">
+        <v>341</v>
+      </c>
     </row>
     <row r="305" ht="15" customHeight="1">
       <c t="s" r="A305" s="6">
@@ -10707,7 +10785,7 @@
       </c>
       <c r="D305" s="7"/>
       <c t="s" r="E305" s="7">
-        <v>329</v>
+        <v>339</v>
       </c>
       <c r="F305" s="7">
         <v>321</v>
@@ -10716,13 +10794,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H305" s="8">
-        <v>309</v>
+        <v>319</v>
       </c>
       <c t="s" r="I305" s="7">
         <v>59</v>
       </c>
       <c t="s" r="J305" s="7">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="K305" s="7"/>
       <c r="L305" s="7"/>
@@ -10740,22 +10818,22 @@
       </c>
       <c r="D306" s="7"/>
       <c t="s" r="E306" s="7">
-        <v>329</v>
+        <v>339</v>
       </c>
       <c r="F306" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G306" s="8">
-        <v>309</v>
+        <v>319</v>
       </c>
       <c t="s" r="H306" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I306" s="7">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c t="s" r="J306" s="7">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="K306" s="7"/>
       <c r="L306" s="7"/>
@@ -10773,7 +10851,7 @@
       </c>
       <c r="D307" s="7"/>
       <c t="s" r="E307" s="7">
-        <v>329</v>
+        <v>339</v>
       </c>
       <c r="F307" s="7">
         <v>321</v>
@@ -10782,10 +10860,10 @@
         <v>41</v>
       </c>
       <c t="s" r="H307" s="8">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c t="s" r="I307" s="7">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c t="s" r="J307" s="7">
         <v>52</v>
@@ -10806,22 +10884,22 @@
       </c>
       <c r="D308" s="7"/>
       <c t="s" r="E308" s="7">
-        <v>329</v>
+        <v>339</v>
       </c>
       <c r="F308" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G308" s="8">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c t="s" r="H308" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I308" s="7">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c t="s" r="J308" s="7">
-        <v>331</v>
+        <v>342</v>
       </c>
       <c r="K308" s="7"/>
       <c r="L308" s="7"/>
@@ -10854,7 +10932,7 @@
       </c>
       <c r="D310" s="7"/>
       <c t="s" r="E310" s="7">
-        <v>332</v>
+        <v>343</v>
       </c>
       <c r="F310" s="7">
         <v>320</v>
@@ -10863,17 +10941,19 @@
         <v>41</v>
       </c>
       <c t="s" r="H310" s="8">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c t="s" r="I310" s="7">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c t="s" r="J310" s="7">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="K310" s="7"/>
       <c r="L310" s="7"/>
-      <c r="M310" s="7"/>
+      <c t="s" r="M310" s="7">
+        <v>344</v>
+      </c>
     </row>
     <row r="311" ht="14.25" customHeight="1">
       <c t="s" r="A311" s="6">
@@ -10887,13 +10967,13 @@
       </c>
       <c r="D311" s="7"/>
       <c t="s" r="E311" s="7">
-        <v>332</v>
+        <v>343</v>
       </c>
       <c r="F311" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G311" s="8">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c t="s" r="H311" s="8">
         <v>41</v>
@@ -10920,7 +11000,7 @@
       </c>
       <c r="D312" s="7"/>
       <c t="s" r="E312" s="7">
-        <v>332</v>
+        <v>343</v>
       </c>
       <c r="F312" s="7">
         <v>320</v>
@@ -10929,13 +11009,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H312" s="8">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c t="s" r="I312" s="7">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c t="s" r="J312" s="7">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="K312" s="7"/>
       <c r="L312" s="7"/>
@@ -10953,13 +11033,13 @@
       </c>
       <c r="D313" s="7"/>
       <c t="s" r="E313" s="7">
-        <v>332</v>
+        <v>343</v>
       </c>
       <c r="F313" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G313" s="8">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c t="s" r="H313" s="8">
         <v>41</v>
@@ -10968,7 +11048,7 @@
         <v>47</v>
       </c>
       <c t="s" r="J313" s="7">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K313" s="7"/>
       <c r="L313" s="7"/>
@@ -10986,7 +11066,7 @@
       </c>
       <c r="D314" s="7"/>
       <c t="s" r="E314" s="7">
-        <v>332</v>
+        <v>343</v>
       </c>
       <c r="F314" s="7">
         <v>320</v>
@@ -10995,13 +11075,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H314" s="8">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c t="s" r="I314" s="7">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c t="s" r="J314" s="7">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="K314" s="7"/>
       <c r="L314" s="7"/>
@@ -11019,22 +11099,22 @@
       </c>
       <c r="D315" s="7"/>
       <c t="s" r="E315" s="7">
-        <v>332</v>
+        <v>343</v>
       </c>
       <c r="F315" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G315" s="8">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c t="s" r="H315" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I315" s="7">
-        <v>298</v>
+        <v>308</v>
       </c>
       <c t="s" r="J315" s="7">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="K315" s="7"/>
       <c r="L315" s="7"/>
@@ -11052,7 +11132,7 @@
       </c>
       <c r="D316" s="7"/>
       <c t="s" r="E316" s="7">
-        <v>332</v>
+        <v>343</v>
       </c>
       <c r="F316" s="7">
         <v>320</v>
@@ -11061,13 +11141,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H316" s="8">
-        <v>334</v>
+        <v>346</v>
       </c>
       <c t="s" r="I316" s="7">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c t="s" r="J316" s="7">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="K316" s="7"/>
       <c r="L316" s="7"/>
@@ -11085,22 +11165,22 @@
       </c>
       <c r="D317" s="7"/>
       <c t="s" r="E317" s="7">
-        <v>332</v>
+        <v>343</v>
       </c>
       <c r="F317" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G317" s="8">
-        <v>334</v>
+        <v>346</v>
       </c>
       <c t="s" r="H317" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I317" s="7">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c t="s" r="J317" s="7">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="K317" s="7"/>
       <c r="L317" s="7"/>
@@ -11133,7 +11213,7 @@
       </c>
       <c r="D319" s="7"/>
       <c t="s" r="E319" s="7">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="F319" s="7">
         <v>321</v>
@@ -11142,13 +11222,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H319" s="8">
-        <v>309</v>
+        <v>319</v>
       </c>
       <c t="s" r="I319" s="7">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c t="s" r="J319" s="7">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="K319" s="7"/>
       <c r="L319" s="7"/>
@@ -11166,22 +11246,22 @@
       </c>
       <c r="D320" s="7"/>
       <c t="s" r="E320" s="7">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="F320" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G320" s="8">
-        <v>309</v>
+        <v>319</v>
       </c>
       <c t="s" r="H320" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="I320" s="7">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c t="s" r="J320" s="7">
-        <v>336</v>
+        <v>348</v>
       </c>
       <c r="K320" s="7"/>
       <c r="L320" s="7"/>
@@ -11199,22 +11279,22 @@
       </c>
       <c r="D321" s="7"/>
       <c t="s" r="E321" s="7">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="F321" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G321" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="H321" s="8">
-        <v>309</v>
+        <v>319</v>
       </c>
       <c t="s" r="I321" s="7">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c t="s" r="J321" s="7">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="K321" s="7"/>
       <c r="L321" s="7"/>
@@ -11232,22 +11312,22 @@
       </c>
       <c r="D322" s="7"/>
       <c t="s" r="E322" s="7">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="F322" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G322" s="8">
-        <v>309</v>
+        <v>319</v>
       </c>
       <c t="s" r="H322" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="I322" s="7">
-        <v>328</v>
+        <v>338</v>
       </c>
       <c t="s" r="J322" s="7">
-        <v>337</v>
+        <v>349</v>
       </c>
       <c r="K322" s="7"/>
       <c r="L322" s="7"/>
@@ -11280,19 +11360,19 @@
       </c>
       <c r="D324" s="7"/>
       <c t="s" r="E324" s="7">
-        <v>338</v>
+        <v>350</v>
       </c>
       <c r="F324" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G324" s="8">
-        <v>339</v>
+        <v>351</v>
       </c>
       <c t="s" r="H324" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I324" s="7">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c t="s" r="J324" s="7">
         <v>35</v>
@@ -11313,7 +11393,7 @@
       </c>
       <c r="D325" s="7"/>
       <c t="s" r="E325" s="7">
-        <v>338</v>
+        <v>350</v>
       </c>
       <c r="F325" s="7">
         <v>320</v>
@@ -11322,13 +11402,13 @@
         <v>31</v>
       </c>
       <c t="s" r="H325" s="8">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c t="s" r="I325" s="7">
-        <v>320</v>
+        <v>330</v>
       </c>
       <c t="s" r="J325" s="7">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="K325" s="7"/>
       <c r="L325" s="7"/>
@@ -11346,22 +11426,22 @@
       </c>
       <c r="D326" s="7"/>
       <c t="s" r="E326" s="7">
-        <v>338</v>
+        <v>350</v>
       </c>
       <c r="F326" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G326" s="8">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c t="s" r="H326" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I326" s="7">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c t="s" r="J326" s="7">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K326" s="7"/>
       <c r="L326" s="7"/>
@@ -11394,7 +11474,7 @@
       </c>
       <c r="D328" s="7"/>
       <c t="s" r="E328" s="7">
-        <v>340</v>
+        <v>352</v>
       </c>
       <c r="F328" s="7">
         <v>320</v>
@@ -11406,10 +11486,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I328" s="7">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c t="s" r="J328" s="7">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="K328" s="7"/>
       <c r="L328" s="7"/>
@@ -11427,7 +11507,7 @@
       </c>
       <c r="D329" s="7"/>
       <c t="s" r="E329" s="7">
-        <v>340</v>
+        <v>352</v>
       </c>
       <c r="F329" s="7">
         <v>320</v>
@@ -11439,10 +11519,10 @@
         <v>57</v>
       </c>
       <c t="s" r="I329" s="7">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c t="s" r="J329" s="7">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="K329" s="7"/>
       <c r="L329" s="7"/>
@@ -11460,7 +11540,7 @@
       </c>
       <c r="D330" s="7"/>
       <c t="s" r="E330" s="7">
-        <v>340</v>
+        <v>352</v>
       </c>
       <c r="F330" s="7">
         <v>320</v>
@@ -11472,10 +11552,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I330" s="7">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c t="s" r="J330" s="7">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="K330" s="7"/>
       <c r="L330" s="7"/>
@@ -11493,7 +11573,7 @@
       </c>
       <c r="D331" s="7"/>
       <c t="s" r="E331" s="7">
-        <v>340</v>
+        <v>352</v>
       </c>
       <c r="F331" s="7">
         <v>320</v>
@@ -11505,10 +11585,10 @@
         <v>31</v>
       </c>
       <c t="s" r="I331" s="7">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c t="s" r="J331" s="7">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="K331" s="7"/>
       <c r="L331" s="7"/>
@@ -11541,7 +11621,7 @@
       </c>
       <c r="D333" s="7"/>
       <c t="s" r="E333" s="7">
-        <v>341</v>
+        <v>353</v>
       </c>
       <c r="F333" s="7">
         <v>321</v>
@@ -11553,14 +11633,16 @@
         <v>46</v>
       </c>
       <c t="s" r="I333" s="7">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c t="s" r="J333" s="7">
-        <v>316</v>
+        <v>293</v>
       </c>
       <c r="K333" s="7"/>
       <c r="L333" s="7"/>
-      <c r="M333" s="7"/>
+      <c t="s" r="M333" s="7">
+        <v>354</v>
+      </c>
     </row>
     <row r="334" ht="14.25" customHeight="1">
       <c t="s" r="A334" s="6">
@@ -11574,7 +11656,7 @@
       </c>
       <c r="D334" s="7"/>
       <c t="s" r="E334" s="7">
-        <v>341</v>
+        <v>353</v>
       </c>
       <c r="F334" s="7">
         <v>321</v>
@@ -11586,10 +11668,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I334" s="7">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c t="s" r="J334" s="7">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="K334" s="7"/>
       <c r="L334" s="7"/>
@@ -11607,7 +11689,7 @@
       </c>
       <c r="D335" s="7"/>
       <c t="s" r="E335" s="7">
-        <v>341</v>
+        <v>353</v>
       </c>
       <c r="F335" s="7">
         <v>321</v>
@@ -11616,10 +11698,10 @@
         <v>41</v>
       </c>
       <c t="s" r="H335" s="8">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c t="s" r="I335" s="7">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c t="s" r="J335" s="7">
         <v>49</v>
@@ -11640,22 +11722,22 @@
       </c>
       <c r="D336" s="7"/>
       <c t="s" r="E336" s="7">
-        <v>341</v>
+        <v>353</v>
       </c>
       <c r="F336" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G336" s="8">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c t="s" r="H336" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I336" s="7">
-        <v>319</v>
+        <v>329</v>
       </c>
       <c t="s" r="J336" s="7">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="K336" s="7"/>
       <c r="L336" s="7"/>
@@ -11673,7 +11755,7 @@
       </c>
       <c r="D337" s="7"/>
       <c t="s" r="E337" s="7">
-        <v>341</v>
+        <v>353</v>
       </c>
       <c r="F337" s="7">
         <v>321</v>
@@ -11685,10 +11767,10 @@
         <v>42</v>
       </c>
       <c t="s" r="I337" s="7">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c t="s" r="J337" s="7">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="K337" s="7"/>
       <c r="L337" s="7"/>
@@ -11706,7 +11788,7 @@
       </c>
       <c r="D338" s="7"/>
       <c t="s" r="E338" s="7">
-        <v>341</v>
+        <v>353</v>
       </c>
       <c r="F338" s="7">
         <v>321</v>
@@ -11718,10 +11800,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I338" s="7">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c t="s" r="J338" s="7">
-        <v>321</v>
+        <v>331</v>
       </c>
       <c r="K338" s="7"/>
       <c r="L338" s="7"/>
@@ -11739,7 +11821,7 @@
       </c>
       <c r="D339" s="7"/>
       <c t="s" r="E339" s="7">
-        <v>341</v>
+        <v>353</v>
       </c>
       <c r="F339" s="7">
         <v>321</v>
@@ -11748,13 +11830,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H339" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="I339" s="7">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c t="s" r="J339" s="7">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="K339" s="7"/>
       <c r="L339" s="7"/>
@@ -11768,26 +11850,26 @@
         <v>8020</v>
       </c>
       <c t="s" r="C340" s="7">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="D340" s="7"/>
       <c t="s" r="E340" s="7">
-        <v>341</v>
+        <v>353</v>
       </c>
       <c r="F340" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G340" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="H340" s="8">
-        <v>342</v>
+        <v>355</v>
       </c>
       <c t="s" r="I340" s="7">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c t="s" r="J340" s="7">
-        <v>343</v>
+        <v>356</v>
       </c>
       <c r="K340" s="7"/>
       <c r="L340" s="7"/>
@@ -11801,26 +11883,26 @@
         <v>8021</v>
       </c>
       <c t="s" r="C341" s="7">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="D341" s="7"/>
       <c t="s" r="E341" s="7">
-        <v>341</v>
+        <v>353</v>
       </c>
       <c r="F341" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G341" s="8">
-        <v>342</v>
+        <v>355</v>
       </c>
       <c t="s" r="H341" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="I341" s="7">
-        <v>344</v>
+        <v>357</v>
       </c>
       <c t="s" r="J341" s="7">
-        <v>345</v>
+        <v>358</v>
       </c>
       <c r="K341" s="7"/>
       <c r="L341" s="7"/>
@@ -11853,7 +11935,7 @@
       </c>
       <c r="D343" s="7"/>
       <c t="s" r="E343" s="7">
-        <v>346</v>
+        <v>359</v>
       </c>
       <c r="F343" s="7">
         <v>320</v>
@@ -11862,13 +11944,13 @@
         <v>31</v>
       </c>
       <c t="s" r="H343" s="8">
-        <v>347</v>
+        <v>360</v>
       </c>
       <c t="s" r="I343" s="7">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c t="s" r="J343" s="7">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="K343" s="7"/>
       <c r="L343" s="7"/>
@@ -11886,22 +11968,22 @@
       </c>
       <c r="D344" s="7"/>
       <c t="s" r="E344" s="7">
-        <v>346</v>
+        <v>359</v>
       </c>
       <c r="F344" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G344" s="8">
-        <v>347</v>
+        <v>360</v>
       </c>
       <c t="s" r="H344" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I344" s="7">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c t="s" r="J344" s="7">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="K344" s="7"/>
       <c r="L344" s="7"/>
@@ -11934,7 +12016,7 @@
       </c>
       <c r="D346" s="7"/>
       <c t="s" r="E346" s="7">
-        <v>348</v>
+        <v>361</v>
       </c>
       <c r="F346" s="7">
         <v>320</v>
@@ -11943,13 +12025,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H346" s="8">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c t="s" r="I346" s="7">
-        <v>349</v>
+        <v>362</v>
       </c>
       <c t="s" r="J346" s="7">
-        <v>350</v>
+        <v>363</v>
       </c>
       <c r="K346" s="7"/>
       <c r="L346" s="7"/>
@@ -11967,19 +12049,19 @@
       </c>
       <c r="D347" s="7"/>
       <c t="s" r="E347" s="7">
-        <v>348</v>
+        <v>361</v>
       </c>
       <c r="F347" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G347" s="8">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c t="s" r="H347" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I347" s="7">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c t="s" r="J347" s="7">
         <v>34</v>
@@ -12000,7 +12082,7 @@
       </c>
       <c r="D348" s="7"/>
       <c t="s" r="E348" s="7">
-        <v>348</v>
+        <v>361</v>
       </c>
       <c r="F348" s="7">
         <v>320</v>
@@ -12009,13 +12091,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H348" s="8">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c t="s" r="I348" s="7">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c t="s" r="J348" s="7">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="K348" s="7"/>
       <c r="L348" s="7"/>
@@ -12033,22 +12115,22 @@
       </c>
       <c r="D349" s="7"/>
       <c t="s" r="E349" s="7">
-        <v>348</v>
+        <v>361</v>
       </c>
       <c r="F349" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G349" s="8">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c t="s" r="H349" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I349" s="7">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c t="s" r="J349" s="7">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="K349" s="7"/>
       <c r="L349" s="7"/>
@@ -12066,7 +12148,7 @@
       </c>
       <c r="D350" s="7"/>
       <c t="s" r="E350" s="7">
-        <v>348</v>
+        <v>361</v>
       </c>
       <c r="F350" s="7">
         <v>320</v>
@@ -12075,13 +12157,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H350" s="8">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c t="s" r="I350" s="7">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c t="s" r="J350" s="7">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K350" s="7"/>
       <c r="L350" s="7"/>
@@ -12099,19 +12181,19 @@
       </c>
       <c r="D351" s="7"/>
       <c t="s" r="E351" s="7">
-        <v>348</v>
+        <v>361</v>
       </c>
       <c r="F351" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G351" s="8">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c t="s" r="H351" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I351" s="7">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c t="s" r="J351" s="7">
         <v>25</v>
@@ -12147,7 +12229,7 @@
       </c>
       <c r="D353" s="7"/>
       <c t="s" r="E353" s="7">
-        <v>351</v>
+        <v>364</v>
       </c>
       <c r="F353" s="7">
         <v>321</v>
@@ -12156,13 +12238,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H353" s="8">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c t="s" r="I353" s="7">
-        <v>297</v>
+        <v>325</v>
       </c>
       <c t="s" r="J353" s="7">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="K353" s="7"/>
       <c r="L353" s="7"/>
@@ -12180,22 +12262,22 @@
       </c>
       <c r="D354" s="7"/>
       <c t="s" r="E354" s="7">
-        <v>351</v>
+        <v>364</v>
       </c>
       <c r="F354" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G354" s="8">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c t="s" r="H354" s="8">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c t="s" r="I354" s="7">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c t="s" r="J354" s="7">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="K354" s="7"/>
       <c r="L354" s="7"/>
@@ -12213,22 +12295,22 @@
       </c>
       <c r="D355" s="7"/>
       <c t="s" r="E355" s="7">
-        <v>351</v>
+        <v>364</v>
       </c>
       <c r="F355" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G355" s="8">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c t="s" r="H355" s="8">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c t="s" r="I355" s="7">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c t="s" r="J355" s="7">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="K355" s="7"/>
       <c r="L355" s="7"/>
@@ -12246,22 +12328,22 @@
       </c>
       <c r="D356" s="7"/>
       <c t="s" r="E356" s="7">
-        <v>351</v>
+        <v>364</v>
       </c>
       <c r="F356" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G356" s="8">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c t="s" r="H356" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I356" s="7">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c t="s" r="J356" s="7">
-        <v>328</v>
+        <v>338</v>
       </c>
       <c r="K356" s="7"/>
       <c r="L356" s="7"/>
@@ -12279,7 +12361,7 @@
       </c>
       <c r="D357" s="7"/>
       <c t="s" r="E357" s="7">
-        <v>351</v>
+        <v>364</v>
       </c>
       <c r="F357" s="7">
         <v>321</v>
@@ -12288,13 +12370,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H357" s="8">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c t="s" r="I357" s="7">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c t="s" r="J357" s="7">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K357" s="7"/>
       <c r="L357" s="7"/>
@@ -12327,7 +12409,7 @@
       </c>
       <c r="D359" s="7"/>
       <c t="s" r="E359" s="7">
-        <v>352</v>
+        <v>365</v>
       </c>
       <c r="F359" s="7">
         <v>321</v>
@@ -12336,13 +12418,13 @@
         <v>31</v>
       </c>
       <c t="s" r="H359" s="8">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c t="s" r="I359" s="7">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c t="s" r="J359" s="7">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="K359" s="7"/>
       <c r="L359" s="7"/>
@@ -12360,13 +12442,13 @@
       </c>
       <c r="D360" s="7"/>
       <c t="s" r="E360" s="7">
-        <v>352</v>
+        <v>365</v>
       </c>
       <c r="F360" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G360" s="8">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c t="s" r="H360" s="8">
         <v>31</v>
@@ -12393,7 +12475,7 @@
       </c>
       <c r="D361" s="7"/>
       <c t="s" r="E361" s="7">
-        <v>352</v>
+        <v>365</v>
       </c>
       <c r="F361" s="7">
         <v>321</v>
@@ -12405,10 +12487,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I361" s="7">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c t="s" r="J361" s="7">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="K361" s="7"/>
       <c r="L361" s="7"/>
@@ -12426,7 +12508,7 @@
       </c>
       <c r="D362" s="7"/>
       <c t="s" r="E362" s="7">
-        <v>352</v>
+        <v>365</v>
       </c>
       <c r="F362" s="7">
         <v>321</v>
@@ -12438,10 +12520,10 @@
         <v>31</v>
       </c>
       <c t="s" r="I362" s="7">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c t="s" r="J362" s="7">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="K362" s="7"/>
       <c r="L362" s="7"/>
@@ -12474,7 +12556,7 @@
       </c>
       <c r="D364" s="7"/>
       <c t="s" r="E364" s="7">
-        <v>353</v>
+        <v>366</v>
       </c>
       <c r="F364" s="7">
         <v>320</v>
@@ -12486,10 +12568,10 @@
         <v>57</v>
       </c>
       <c t="s" r="I364" s="7">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c t="s" r="J364" s="7">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="K364" s="7"/>
       <c r="L364" s="7"/>
@@ -12507,7 +12589,7 @@
       </c>
       <c r="D365" s="7"/>
       <c t="s" r="E365" s="7">
-        <v>353</v>
+        <v>366</v>
       </c>
       <c r="F365" s="7">
         <v>320</v>
@@ -12519,10 +12601,10 @@
         <v>31</v>
       </c>
       <c t="s" r="I365" s="7">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c t="s" r="J365" s="7">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="K365" s="7"/>
       <c r="L365" s="7"/>
@@ -12540,7 +12622,7 @@
       </c>
       <c r="D366" s="7"/>
       <c t="s" r="E366" s="7">
-        <v>353</v>
+        <v>366</v>
       </c>
       <c r="F366" s="7">
         <v>320</v>
@@ -12549,10 +12631,10 @@
         <v>31</v>
       </c>
       <c t="s" r="H366" s="8">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c t="s" r="I366" s="7">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c t="s" r="J366" s="7">
         <v>23</v>
@@ -12573,19 +12655,19 @@
       </c>
       <c r="D367" s="7"/>
       <c t="s" r="E367" s="7">
-        <v>353</v>
+        <v>366</v>
       </c>
       <c r="F367" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G367" s="8">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c t="s" r="H367" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I367" s="7">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c t="s" r="J367" s="7">
         <v>36</v>
@@ -12606,7 +12688,7 @@
       </c>
       <c r="D368" s="7"/>
       <c t="s" r="E368" s="7">
-        <v>353</v>
+        <v>366</v>
       </c>
       <c r="F368" s="7">
         <v>320</v>
@@ -12615,13 +12697,13 @@
         <v>31</v>
       </c>
       <c t="s" r="H368" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="I368" s="7">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c t="s" r="J368" s="7">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="K368" s="7"/>
       <c r="L368" s="7"/>
@@ -12639,22 +12721,22 @@
       </c>
       <c r="D369" s="7"/>
       <c t="s" r="E369" s="7">
-        <v>353</v>
+        <v>366</v>
       </c>
       <c r="F369" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G369" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="H369" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I369" s="7">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c t="s" r="J369" s="7">
-        <v>354</v>
+        <v>367</v>
       </c>
       <c r="K369" s="7"/>
       <c r="L369" s="7"/>
@@ -12687,7 +12769,7 @@
       </c>
       <c r="D371" s="7"/>
       <c t="s" r="E371" s="7">
-        <v>355</v>
+        <v>368</v>
       </c>
       <c r="F371" s="7">
         <v>320</v>
@@ -12696,17 +12778,19 @@
         <v>41</v>
       </c>
       <c t="s" r="H371" s="8">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c t="s" r="I371" s="7">
-        <v>356</v>
+        <v>369</v>
       </c>
       <c t="s" r="J371" s="7">
         <v>43</v>
       </c>
       <c r="K371" s="7"/>
       <c r="L371" s="7"/>
-      <c r="M371" s="7"/>
+      <c t="s" r="M371" s="7">
+        <v>43</v>
+      </c>
     </row>
     <row r="372" ht="14.25" customHeight="1">
       <c t="s" r="A372" s="6">
@@ -12720,22 +12804,22 @@
       </c>
       <c r="D372" s="7"/>
       <c t="s" r="E372" s="7">
-        <v>355</v>
+        <v>368</v>
       </c>
       <c r="F372" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G372" s="8">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c t="s" r="H372" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I372" s="7">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c t="s" r="J372" s="7">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K372" s="7"/>
       <c r="L372" s="7"/>
@@ -12753,7 +12837,7 @@
       </c>
       <c r="D373" s="7"/>
       <c t="s" r="E373" s="7">
-        <v>355</v>
+        <v>368</v>
       </c>
       <c r="F373" s="7">
         <v>320</v>
@@ -12762,13 +12846,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H373" s="8">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c t="s" r="I373" s="7">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c t="s" r="J373" s="7">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="K373" s="7"/>
       <c r="L373" s="7"/>
@@ -12786,13 +12870,13 @@
       </c>
       <c r="D374" s="7"/>
       <c t="s" r="E374" s="7">
-        <v>355</v>
+        <v>368</v>
       </c>
       <c r="F374" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G374" s="8">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c t="s" r="H374" s="8">
         <v>41</v>
@@ -12801,7 +12885,7 @@
         <v>59</v>
       </c>
       <c t="s" r="J374" s="7">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="K374" s="7"/>
       <c r="L374" s="7"/>
@@ -12819,7 +12903,7 @@
       </c>
       <c r="D375" s="7"/>
       <c t="s" r="E375" s="7">
-        <v>355</v>
+        <v>368</v>
       </c>
       <c r="F375" s="7">
         <v>320</v>
@@ -12831,10 +12915,10 @@
         <v>31</v>
       </c>
       <c t="s" r="I375" s="7">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c t="s" r="J375" s="7">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="K375" s="7"/>
       <c r="L375" s="7"/>
@@ -12852,7 +12936,7 @@
       </c>
       <c r="D376" s="7"/>
       <c t="s" r="E376" s="7">
-        <v>355</v>
+        <v>368</v>
       </c>
       <c r="F376" s="7">
         <v>320</v>
@@ -12864,10 +12948,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I376" s="7">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c t="s" r="J376" s="7">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="K376" s="7"/>
       <c r="L376" s="7"/>
@@ -12900,7 +12984,7 @@
       </c>
       <c r="D378" s="7"/>
       <c t="s" r="E378" s="7">
-        <v>357</v>
+        <v>370</v>
       </c>
       <c r="F378" s="7">
         <v>321</v>
@@ -12912,10 +12996,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I378" s="7">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c t="s" r="J378" s="7">
-        <v>358</v>
+        <v>295</v>
       </c>
       <c r="K378" s="7"/>
       <c r="L378" s="7"/>
@@ -12933,7 +13017,7 @@
       </c>
       <c r="D379" s="7"/>
       <c t="s" r="E379" s="7">
-        <v>357</v>
+        <v>370</v>
       </c>
       <c r="F379" s="7">
         <v>321</v>
@@ -12945,10 +13029,10 @@
         <v>31</v>
       </c>
       <c t="s" r="I379" s="7">
-        <v>359</v>
+        <v>371</v>
       </c>
       <c t="s" r="J379" s="7">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="K379" s="7"/>
       <c r="L379" s="7"/>
@@ -12966,7 +13050,7 @@
       </c>
       <c r="D380" s="7"/>
       <c t="s" r="E380" s="7">
-        <v>357</v>
+        <v>370</v>
       </c>
       <c r="F380" s="7">
         <v>321</v>
@@ -12978,10 +13062,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I380" s="7">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c t="s" r="J380" s="7">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="K380" s="7"/>
       <c r="L380" s="7"/>
@@ -12999,7 +13083,7 @@
       </c>
       <c r="D381" s="7"/>
       <c t="s" r="E381" s="7">
-        <v>357</v>
+        <v>370</v>
       </c>
       <c r="F381" s="7">
         <v>321</v>
@@ -13008,13 +13092,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H381" s="8">
-        <v>360</v>
+        <v>372</v>
       </c>
       <c t="s" r="I381" s="7">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c t="s" r="J381" s="7">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K381" s="7"/>
       <c r="L381" s="7"/>
@@ -13032,22 +13116,22 @@
       </c>
       <c r="D382" s="7"/>
       <c t="s" r="E382" s="7">
-        <v>357</v>
+        <v>370</v>
       </c>
       <c r="F382" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G382" s="8">
-        <v>360</v>
+        <v>372</v>
       </c>
       <c t="s" r="H382" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I382" s="7">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c t="s" r="J382" s="7">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="K382" s="7"/>
       <c r="L382" s="7"/>
@@ -13065,7 +13149,7 @@
       </c>
       <c r="D383" s="7"/>
       <c t="s" r="E383" s="7">
-        <v>357</v>
+        <v>370</v>
       </c>
       <c r="F383" s="7">
         <v>321</v>
@@ -13077,10 +13161,10 @@
         <v>31</v>
       </c>
       <c t="s" r="I383" s="7">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c t="s" r="J383" s="7">
-        <v>361</v>
+        <v>373</v>
       </c>
       <c r="K383" s="7"/>
       <c r="L383" s="7"/>
@@ -13113,7 +13197,7 @@
       </c>
       <c r="D385" s="7"/>
       <c t="s" r="E385" s="7">
-        <v>362</v>
+        <v>374</v>
       </c>
       <c r="F385" s="7">
         <v>321</v>
@@ -13122,13 +13206,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H385" s="8">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c t="s" r="I385" s="7">
-        <v>152</v>
+        <v>109</v>
       </c>
       <c t="s" r="J385" s="7">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="K385" s="7"/>
       <c r="L385" s="7"/>
@@ -13146,13 +13230,13 @@
       </c>
       <c r="D386" s="7"/>
       <c t="s" r="E386" s="7">
-        <v>362</v>
+        <v>374</v>
       </c>
       <c r="F386" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G386" s="8">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c t="s" r="H386" s="8">
         <v>41</v>
@@ -13161,7 +13245,7 @@
         <v>35</v>
       </c>
       <c t="s" r="J386" s="7">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="K386" s="7"/>
       <c r="L386" s="7"/>
@@ -13194,19 +13278,19 @@
       </c>
       <c r="D388" s="7"/>
       <c t="s" r="E388" s="7">
-        <v>363</v>
+        <v>375</v>
       </c>
       <c r="F388" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G388" s="8">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c t="s" r="H388" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I388" s="7">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c t="s" r="J388" s="7">
         <v>19</v>
@@ -13227,7 +13311,7 @@
       </c>
       <c r="D389" s="7"/>
       <c t="s" r="E389" s="7">
-        <v>363</v>
+        <v>375</v>
       </c>
       <c r="F389" s="7">
         <v>321</v>
@@ -13236,13 +13320,13 @@
         <v>31</v>
       </c>
       <c t="s" r="H389" s="8">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c t="s" r="I389" s="7">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c t="s" r="J389" s="7">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K389" s="7"/>
       <c r="L389" s="7"/>
@@ -13260,22 +13344,22 @@
       </c>
       <c r="D390" s="7"/>
       <c t="s" r="E390" s="7">
-        <v>363</v>
+        <v>375</v>
       </c>
       <c r="F390" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G390" s="8">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c t="s" r="H390" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I390" s="7">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c t="s" r="J390" s="7">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="K390" s="7"/>
       <c r="L390" s="7"/>
@@ -13293,7 +13377,7 @@
       </c>
       <c r="D391" s="7"/>
       <c t="s" r="E391" s="7">
-        <v>363</v>
+        <v>375</v>
       </c>
       <c r="F391" s="7">
         <v>321</v>
@@ -13305,10 +13389,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I391" s="7">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c t="s" r="J391" s="7">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="K391" s="7"/>
       <c r="L391" s="7"/>
@@ -13341,13 +13425,13 @@
       </c>
       <c r="D393" s="7"/>
       <c t="s" r="E393" s="7">
-        <v>364</v>
+        <v>376</v>
       </c>
       <c r="F393" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G393" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="H393" s="8">
         <v>57</v>
@@ -13356,7 +13440,7 @@
         <v>55</v>
       </c>
       <c t="s" r="J393" s="7">
-        <v>290</v>
+        <v>301</v>
       </c>
       <c r="K393" s="7"/>
       <c r="L393" s="7"/>
@@ -13374,7 +13458,7 @@
       </c>
       <c r="D394" s="7"/>
       <c t="s" r="E394" s="7">
-        <v>364</v>
+        <v>376</v>
       </c>
       <c r="F394" s="7">
         <v>321</v>
@@ -13383,13 +13467,13 @@
         <v>57</v>
       </c>
       <c t="s" r="H394" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="I394" s="7">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c t="s" r="J394" s="7">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="K394" s="7"/>
       <c r="L394" s="7"/>
@@ -13407,22 +13491,22 @@
       </c>
       <c r="D395" s="7"/>
       <c t="s" r="E395" s="7">
-        <v>364</v>
+        <v>376</v>
       </c>
       <c r="F395" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G395" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="H395" s="8">
-        <v>309</v>
+        <v>319</v>
       </c>
       <c t="s" r="I395" s="7">
-        <v>336</v>
+        <v>348</v>
       </c>
       <c t="s" r="J395" s="7">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="K395" s="7"/>
       <c r="L395" s="7"/>
@@ -13440,22 +13524,22 @@
       </c>
       <c r="D396" s="7"/>
       <c t="s" r="E396" s="7">
-        <v>364</v>
+        <v>376</v>
       </c>
       <c r="F396" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G396" s="8">
-        <v>309</v>
+        <v>319</v>
       </c>
       <c t="s" r="H396" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I396" s="7">
-        <v>294</v>
+        <v>305</v>
       </c>
       <c t="s" r="J396" s="7">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="K396" s="7"/>
       <c r="L396" s="7"/>
@@ -13473,7 +13557,7 @@
       </c>
       <c r="D397" s="7"/>
       <c t="s" r="E397" s="7">
-        <v>364</v>
+        <v>376</v>
       </c>
       <c r="F397" s="7">
         <v>321</v>
@@ -13482,13 +13566,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H397" s="8">
-        <v>342</v>
+        <v>355</v>
       </c>
       <c t="s" r="I397" s="7">
-        <v>365</v>
+        <v>377</v>
       </c>
       <c t="s" r="J397" s="7">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="K397" s="7"/>
       <c r="L397" s="7"/>
@@ -13506,22 +13590,22 @@
       </c>
       <c r="D398" s="7"/>
       <c t="s" r="E398" s="7">
-        <v>364</v>
+        <v>376</v>
       </c>
       <c r="F398" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G398" s="8">
-        <v>342</v>
+        <v>355</v>
       </c>
       <c t="s" r="H398" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I398" s="7">
-        <v>366</v>
+        <v>378</v>
       </c>
       <c t="s" r="J398" s="7">
-        <v>367</v>
+        <v>379</v>
       </c>
       <c r="K398" s="7"/>
       <c r="L398" s="7"/>
@@ -13554,7 +13638,7 @@
       </c>
       <c r="D400" s="7"/>
       <c t="s" r="E400" s="7">
-        <v>368</v>
+        <v>380</v>
       </c>
       <c r="F400" s="7">
         <v>321</v>
@@ -13566,10 +13650,10 @@
         <v>31</v>
       </c>
       <c t="s" r="I400" s="7">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c t="s" r="J400" s="7">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="K400" s="7"/>
       <c r="L400" s="7"/>
@@ -13587,7 +13671,7 @@
       </c>
       <c r="D401" s="7"/>
       <c t="s" r="E401" s="7">
-        <v>368</v>
+        <v>380</v>
       </c>
       <c r="F401" s="7">
         <v>321</v>
@@ -13599,10 +13683,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I401" s="7">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c t="s" r="J401" s="7">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="K401" s="7"/>
       <c r="L401" s="7"/>
@@ -13620,7 +13704,7 @@
       </c>
       <c r="D402" s="7"/>
       <c t="s" r="E402" s="7">
-        <v>368</v>
+        <v>380</v>
       </c>
       <c r="F402" s="7">
         <v>321</v>
@@ -13629,13 +13713,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H402" s="8">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c t="s" r="I402" s="7">
         <v>49</v>
       </c>
       <c t="s" r="J402" s="7">
-        <v>298</v>
+        <v>308</v>
       </c>
       <c r="K402" s="7"/>
       <c r="L402" s="7"/>
@@ -13653,22 +13737,22 @@
       </c>
       <c r="D403" s="7"/>
       <c t="s" r="E403" s="7">
-        <v>368</v>
+        <v>380</v>
       </c>
       <c r="F403" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G403" s="8">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c t="s" r="H403" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I403" s="7">
-        <v>320</v>
+        <v>330</v>
       </c>
       <c t="s" r="J403" s="7">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="K403" s="7"/>
       <c r="L403" s="7"/>
@@ -13686,7 +13770,7 @@
       </c>
       <c r="D404" s="7"/>
       <c t="s" r="E404" s="7">
-        <v>368</v>
+        <v>380</v>
       </c>
       <c r="F404" s="7">
         <v>321</v>
@@ -13695,13 +13779,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H404" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="I404" s="7">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c t="s" r="J404" s="7">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="K404" s="7"/>
       <c r="L404" s="7"/>
@@ -13719,22 +13803,22 @@
       </c>
       <c r="D405" s="7"/>
       <c t="s" r="E405" s="7">
-        <v>368</v>
+        <v>380</v>
       </c>
       <c r="F405" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G405" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="H405" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I405" s="7">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c t="s" r="J405" s="7">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="K405" s="7"/>
       <c r="L405" s="7"/>
@@ -13752,7 +13836,7 @@
       </c>
       <c r="D406" s="7"/>
       <c t="s" r="E406" s="7">
-        <v>368</v>
+        <v>380</v>
       </c>
       <c r="F406" s="7">
         <v>321</v>
@@ -13764,10 +13848,10 @@
         <v>31</v>
       </c>
       <c t="s" r="I406" s="7">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c t="s" r="J406" s="7">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="K406" s="7"/>
       <c r="L406" s="7"/>
@@ -13800,7 +13884,7 @@
       </c>
       <c r="D408" s="7"/>
       <c t="s" r="E408" s="7">
-        <v>369</v>
+        <v>381</v>
       </c>
       <c r="F408" s="7">
         <v>320</v>
@@ -13812,14 +13896,16 @@
         <v>17</v>
       </c>
       <c t="s" r="I408" s="7">
-        <v>370</v>
+        <v>382</v>
       </c>
       <c t="s" r="J408" s="7">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="K408" s="7"/>
       <c r="L408" s="7"/>
-      <c r="M408" s="7"/>
+      <c t="s" r="M408" s="7">
+        <v>383</v>
+      </c>
     </row>
     <row r="409" ht="14.25" customHeight="1">
       <c t="s" r="A409" s="6">
@@ -13833,7 +13919,7 @@
       </c>
       <c r="D409" s="7"/>
       <c t="s" r="E409" s="7">
-        <v>369</v>
+        <v>381</v>
       </c>
       <c r="F409" s="7">
         <v>320</v>
@@ -13845,10 +13931,10 @@
         <v>31</v>
       </c>
       <c t="s" r="I409" s="7">
-        <v>371</v>
+        <v>384</v>
       </c>
       <c t="s" r="J409" s="7">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="K409" s="7"/>
       <c r="L409" s="7"/>
@@ -13866,7 +13952,7 @@
       </c>
       <c r="D410" s="7"/>
       <c t="s" r="E410" s="7">
-        <v>369</v>
+        <v>381</v>
       </c>
       <c r="F410" s="7">
         <v>320</v>
@@ -13875,13 +13961,13 @@
         <v>31</v>
       </c>
       <c t="s" r="H410" s="8">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c t="s" r="I410" s="7">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c t="s" r="J410" s="7">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="K410" s="7"/>
       <c r="L410" s="7"/>
@@ -13899,13 +13985,13 @@
       </c>
       <c r="D411" s="7"/>
       <c t="s" r="E411" s="7">
-        <v>369</v>
+        <v>381</v>
       </c>
       <c r="F411" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G411" s="8">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c t="s" r="H411" s="8">
         <v>31</v>
@@ -13932,7 +14018,7 @@
       </c>
       <c r="D412" s="7"/>
       <c t="s" r="E412" s="7">
-        <v>369</v>
+        <v>381</v>
       </c>
       <c r="F412" s="7">
         <v>320</v>
@@ -13944,10 +14030,10 @@
         <v>42</v>
       </c>
       <c t="s" r="I412" s="7">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c t="s" r="J412" s="7">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K412" s="7"/>
       <c r="L412" s="7"/>
@@ -13965,7 +14051,7 @@
       </c>
       <c r="D413" s="7"/>
       <c t="s" r="E413" s="7">
-        <v>369</v>
+        <v>381</v>
       </c>
       <c r="F413" s="7">
         <v>320</v>
@@ -13977,10 +14063,10 @@
         <v>31</v>
       </c>
       <c t="s" r="I413" s="7">
-        <v>317</v>
+        <v>327</v>
       </c>
       <c t="s" r="J413" s="7">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="K413" s="7"/>
       <c r="L413" s="7"/>
@@ -14013,27 +14099,27 @@
       </c>
       <c r="D415" s="7"/>
       <c t="s" r="E415" s="7">
-        <v>372</v>
+        <v>385</v>
       </c>
       <c r="F415" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G415" s="8">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c t="s" r="H415" s="8">
         <v>57</v>
       </c>
       <c t="s" r="I415" s="7">
-        <v>373</v>
+        <v>386</v>
       </c>
       <c t="s" r="J415" s="7">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="K415" s="7"/>
       <c r="L415" s="7"/>
       <c t="s" r="M415" s="7">
-        <v>202</v>
+        <v>209</v>
       </c>
     </row>
     <row r="416" ht="14.25" customHeight="1">
@@ -14048,7 +14134,7 @@
       </c>
       <c r="D416" s="7"/>
       <c t="s" r="E416" s="7">
-        <v>372</v>
+        <v>385</v>
       </c>
       <c r="F416" s="7">
         <v>321</v>
@@ -14057,10 +14143,10 @@
         <v>57</v>
       </c>
       <c t="s" r="H416" s="8">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c t="s" r="I416" s="7">
-        <v>349</v>
+        <v>362</v>
       </c>
       <c t="s" r="J416" s="7">
         <v>49</v>
@@ -14081,22 +14167,22 @@
       </c>
       <c r="D417" s="7"/>
       <c t="s" r="E417" s="7">
-        <v>372</v>
+        <v>385</v>
       </c>
       <c r="F417" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G417" s="8">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c t="s" r="H417" s="8">
         <v>57</v>
       </c>
       <c t="s" r="I417" s="7">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c t="s" r="J417" s="7">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="K417" s="7"/>
       <c r="L417" s="7"/>
@@ -14114,7 +14200,7 @@
       </c>
       <c r="D418" s="7"/>
       <c t="s" r="E418" s="7">
-        <v>372</v>
+        <v>385</v>
       </c>
       <c r="F418" s="7">
         <v>321</v>
@@ -14123,13 +14209,13 @@
         <v>57</v>
       </c>
       <c t="s" r="H418" s="8">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c t="s" r="I418" s="7">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c t="s" r="J418" s="7">
-        <v>374</v>
+        <v>387</v>
       </c>
       <c r="K418" s="7"/>
       <c r="L418" s="7"/>
@@ -14162,22 +14248,22 @@
       </c>
       <c r="D420" s="7"/>
       <c t="s" r="E420" s="7">
-        <v>375</v>
+        <v>388</v>
       </c>
       <c r="F420" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G420" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="H420" s="8">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c t="s" r="I420" s="7">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c t="s" r="J420" s="7">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="K420" s="7"/>
       <c r="L420" s="7"/>
@@ -14195,22 +14281,22 @@
       </c>
       <c r="D421" s="7"/>
       <c t="s" r="E421" s="7">
-        <v>375</v>
+        <v>388</v>
       </c>
       <c r="F421" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G421" s="8">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c t="s" r="H421" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="I421" s="7">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c t="s" r="J421" s="7">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="K421" s="7"/>
       <c r="L421" s="7"/>
@@ -14228,19 +14314,19 @@
       </c>
       <c r="D422" s="7"/>
       <c t="s" r="E422" s="7">
-        <v>375</v>
+        <v>388</v>
       </c>
       <c r="F422" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G422" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="H422" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I422" s="7">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c t="s" r="J422" s="7">
         <v>43</v>
@@ -14276,7 +14362,7 @@
       </c>
       <c r="D424" s="7"/>
       <c t="s" r="E424" s="7">
-        <v>376</v>
+        <v>389</v>
       </c>
       <c r="F424" s="7">
         <v>321</v>
@@ -14285,10 +14371,10 @@
         <v>41</v>
       </c>
       <c t="s" r="H424" s="8">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c t="s" r="I424" s="7">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c t="s" r="J424" s="7">
         <v>20</v>
@@ -14309,22 +14395,22 @@
       </c>
       <c r="D425" s="7"/>
       <c t="s" r="E425" s="7">
-        <v>376</v>
+        <v>389</v>
       </c>
       <c r="F425" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G425" s="8">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c t="s" r="H425" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I425" s="7">
-        <v>377</v>
+        <v>390</v>
       </c>
       <c t="s" r="J425" s="7">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="K425" s="7"/>
       <c r="L425" s="7"/>
@@ -14342,7 +14428,7 @@
       </c>
       <c r="D426" s="7"/>
       <c t="s" r="E426" s="7">
-        <v>376</v>
+        <v>389</v>
       </c>
       <c r="F426" s="7">
         <v>321</v>
@@ -14357,7 +14443,7 @@
         <v>36</v>
       </c>
       <c t="s" r="J426" s="7">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="K426" s="7"/>
       <c r="L426" s="7"/>
@@ -14375,7 +14461,7 @@
       </c>
       <c r="D427" s="7"/>
       <c t="s" r="E427" s="7">
-        <v>376</v>
+        <v>389</v>
       </c>
       <c r="F427" s="7">
         <v>321</v>
@@ -14387,10 +14473,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I427" s="7">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c t="s" r="J427" s="7">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="K427" s="7"/>
       <c r="L427" s="7"/>
@@ -14423,7 +14509,7 @@
       </c>
       <c r="D429" s="7"/>
       <c t="s" r="E429" s="7">
-        <v>378</v>
+        <v>391</v>
       </c>
       <c r="F429" s="7">
         <v>330</v>
@@ -14438,7 +14524,7 @@
         <v>45</v>
       </c>
       <c t="s" r="J429" s="7">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K429" s="7"/>
       <c r="L429" s="7"/>
@@ -14456,7 +14542,7 @@
       </c>
       <c r="D430" s="7"/>
       <c t="s" r="E430" s="7">
-        <v>378</v>
+        <v>391</v>
       </c>
       <c r="F430" s="7">
         <v>330</v>
@@ -14468,7 +14554,7 @@
         <v>31</v>
       </c>
       <c t="s" r="I430" s="7">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c t="s" r="J430" s="7">
         <v>50</v>
@@ -14489,7 +14575,7 @@
       </c>
       <c r="D431" s="7"/>
       <c t="s" r="E431" s="7">
-        <v>378</v>
+        <v>391</v>
       </c>
       <c r="F431" s="7">
         <v>330</v>
@@ -14501,10 +14587,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I431" s="7">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c t="s" r="J431" s="7">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K431" s="7"/>
       <c r="L431" s="7"/>
@@ -14537,22 +14623,22 @@
       </c>
       <c r="D433" s="7"/>
       <c t="s" r="E433" s="7">
-        <v>379</v>
+        <v>392</v>
       </c>
       <c r="F433" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G433" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="H433" s="8">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c t="s" r="I433" s="7">
         <v>43</v>
       </c>
       <c t="s" r="J433" s="7">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="K433" s="7"/>
       <c r="L433" s="7"/>
@@ -14570,22 +14656,22 @@
       </c>
       <c r="D434" s="7"/>
       <c t="s" r="E434" s="7">
-        <v>379</v>
+        <v>392</v>
       </c>
       <c r="F434" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G434" s="8">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c t="s" r="H434" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="I434" s="7">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c t="s" r="J434" s="7">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="K434" s="7"/>
       <c r="L434" s="7"/>
@@ -14618,22 +14704,22 @@
       </c>
       <c r="D436" s="7"/>
       <c t="s" r="E436" s="7">
-        <v>381</v>
+        <v>394</v>
       </c>
       <c r="F436" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G436" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="H436" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I436" s="7">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c t="s" r="J436" s="7">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="K436" s="7"/>
       <c r="L436" s="7"/>
@@ -14651,7 +14737,7 @@
       </c>
       <c r="D437" s="7"/>
       <c t="s" r="E437" s="7">
-        <v>381</v>
+        <v>394</v>
       </c>
       <c r="F437" s="7">
         <v>330</v>
@@ -14660,13 +14746,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H437" s="8">
-        <v>382</v>
+        <v>395</v>
       </c>
       <c t="s" r="I437" s="7">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c t="s" r="J437" s="7">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="K437" s="7"/>
       <c r="L437" s="7"/>
@@ -14699,7 +14785,7 @@
       </c>
       <c r="D439" s="7"/>
       <c t="s" r="E439" s="7">
-        <v>383</v>
+        <v>396</v>
       </c>
       <c r="F439" s="7">
         <v>330</v>
@@ -14708,13 +14794,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H439" s="8">
-        <v>384</v>
+        <v>397</v>
       </c>
       <c t="s" r="I439" s="7">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c t="s" r="J439" s="7">
-        <v>385</v>
+        <v>398</v>
       </c>
       <c r="K439" s="7"/>
       <c r="L439" s="7"/>
@@ -14732,22 +14818,22 @@
       </c>
       <c r="D440" s="7"/>
       <c t="s" r="E440" s="7">
-        <v>383</v>
+        <v>396</v>
       </c>
       <c r="F440" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G440" s="8">
-        <v>384</v>
+        <v>397</v>
       </c>
       <c t="s" r="H440" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I440" s="7">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c t="s" r="J440" s="7">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="K440" s="7"/>
       <c r="L440" s="7"/>
@@ -14780,26 +14866,28 @@
       </c>
       <c r="D442" s="7"/>
       <c t="s" r="E442" s="7">
-        <v>386</v>
+        <v>399</v>
       </c>
       <c r="F442" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G442" s="8">
-        <v>387</v>
+        <v>400</v>
       </c>
       <c t="s" r="H442" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I442" s="7">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c t="s" r="J442" s="7">
-        <v>377</v>
+        <v>390</v>
       </c>
       <c r="K442" s="7"/>
       <c r="L442" s="7"/>
-      <c r="M442" s="7"/>
+      <c t="s" r="M442" s="7">
+        <v>401</v>
+      </c>
     </row>
     <row r="443" ht="14.25" customHeight="1">
       <c t="s" r="A443" s="6">
@@ -14813,7 +14901,7 @@
       </c>
       <c r="D443" s="7"/>
       <c t="s" r="E443" s="7">
-        <v>386</v>
+        <v>399</v>
       </c>
       <c r="F443" s="7">
         <v>330</v>
@@ -14822,13 +14910,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H443" s="8">
-        <v>387</v>
+        <v>400</v>
       </c>
       <c t="s" r="I443" s="7">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c t="s" r="J443" s="7">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="K443" s="7"/>
       <c r="L443" s="7"/>
@@ -14861,7 +14949,7 @@
       </c>
       <c r="D445" s="7"/>
       <c t="s" r="E445" s="7">
-        <v>388</v>
+        <v>402</v>
       </c>
       <c r="F445" s="7">
         <v>330</v>
@@ -14870,13 +14958,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H445" s="8">
-        <v>389</v>
+        <v>403</v>
       </c>
       <c t="s" r="I445" s="7">
         <v>59</v>
       </c>
       <c t="s" r="J445" s="7">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K445" s="7"/>
       <c r="L445" s="7"/>
@@ -14894,22 +14982,22 @@
       </c>
       <c r="D446" s="7"/>
       <c t="s" r="E446" s="7">
-        <v>388</v>
+        <v>402</v>
       </c>
       <c r="F446" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G446" s="8">
-        <v>389</v>
+        <v>403</v>
       </c>
       <c t="s" r="H446" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I446" s="7">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c t="s" r="J446" s="7">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="K446" s="7"/>
       <c r="L446" s="7"/>
@@ -14917,7 +15005,7 @@
     </row>
     <row r="447" ht="15.75" customHeight="1">
       <c t="s" r="A447" s="9">
-        <v>390</v>
+        <v>404</v>
       </c>
       <c r="B447" s="9"/>
       <c r="C447" s="9"/>
@@ -14937,7 +15025,7 @@
     <row r="448" ht="65.25" customHeight="1"/>
     <row r="449" ht="16.5" customHeight="1">
       <c t="s" r="A449" s="10">
-        <v>391</v>
+        <v>405</v>
       </c>
       <c r="B449" s="10"/>
       <c r="C449" s="10"/>
@@ -14950,7 +15038,7 @@
       <c r="J449" s="10"/>
       <c r="K449" s="10"/>
       <c t="s" r="L449" s="11">
-        <v>392</v>
+        <v>406</v>
       </c>
       <c r="M449" s="11"/>
       <c r="N449" s="11"/>

--- a/Data/FlightPlan/FPL_15SEP26.xlsx
+++ b/Data/FlightPlan/FPL_15SEP26.xlsx
@@ -401,6 +401,9 @@
     <t>11:25</t>
   </si>
   <si>
+    <t>11:42</t>
+  </si>
+  <si>
     <t>11:55</t>
   </si>
   <si>
@@ -533,210 +536,228 @@
     <t>11:05</t>
   </si>
   <si>
+    <t>14:35</t>
+  </si>
+  <si>
+    <t>15:35</t>
+  </si>
+  <si>
+    <t>17:15</t>
+  </si>
+  <si>
+    <t>VDH</t>
+  </si>
+  <si>
+    <t>17:50</t>
+  </si>
+  <si>
+    <t>20:00</t>
+  </si>
+  <si>
+    <t>VN-A539</t>
+  </si>
+  <si>
+    <t>VII</t>
+  </si>
+  <si>
+    <t>05:00</t>
+  </si>
+  <si>
+    <t>06:50</t>
+  </si>
+  <si>
+    <t>06:32</t>
+  </si>
+  <si>
+    <t>BMV</t>
+  </si>
+  <si>
+    <t>07:20</t>
+  </si>
+  <si>
+    <t>08:45</t>
+  </si>
+  <si>
+    <t>08:41</t>
+  </si>
+  <si>
+    <t>09:15</t>
+  </si>
+  <si>
+    <t>13:40</t>
+  </si>
+  <si>
+    <t>18:10</t>
+  </si>
+  <si>
+    <t>20:40</t>
+  </si>
+  <si>
+    <t>21:10</t>
+  </si>
+  <si>
+    <t>22:30</t>
+  </si>
+  <si>
+    <t>VN-A542</t>
+  </si>
+  <si>
+    <t>10:35</t>
+  </si>
+  <si>
+    <t>12:19</t>
+  </si>
+  <si>
+    <t>12:50</t>
+  </si>
+  <si>
+    <t>VN-A543</t>
+  </si>
+  <si>
+    <t>HKT</t>
+  </si>
+  <si>
+    <t>11:19</t>
+  </si>
+  <si>
+    <t>13:50</t>
+  </si>
+  <si>
+    <t>18:05</t>
+  </si>
+  <si>
+    <t>VN-A544</t>
+  </si>
+  <si>
+    <t>09:42</t>
+  </si>
+  <si>
+    <t>12:16</t>
+  </si>
+  <si>
+    <t>14:15</t>
+  </si>
+  <si>
+    <t>17:35</t>
+  </si>
+  <si>
+    <t>19:35</t>
+  </si>
+  <si>
+    <t>20:05</t>
+  </si>
+  <si>
+    <t>VN-A547</t>
+  </si>
+  <si>
+    <t>08:00</t>
+  </si>
+  <si>
+    <t>09:55</t>
+  </si>
+  <si>
+    <t>10:03</t>
+  </si>
+  <si>
+    <t>11:30</t>
+  </si>
+  <si>
+    <t>11:44</t>
+  </si>
+  <si>
+    <t>15:05</t>
+  </si>
+  <si>
+    <t>16:25</t>
+  </si>
+  <si>
+    <t>16:55</t>
+  </si>
+  <si>
+    <t>20:45</t>
+  </si>
+  <si>
+    <t>21:50</t>
+  </si>
+  <si>
+    <t>VN-A549</t>
+  </si>
+  <si>
+    <t>NRT</t>
+  </si>
+  <si>
+    <t>13:05</t>
+  </si>
+  <si>
+    <t>TPE</t>
+  </si>
+  <si>
+    <t>14:25</t>
+  </si>
+  <si>
+    <t>19:00</t>
+  </si>
+  <si>
+    <t>NGO</t>
+  </si>
+  <si>
+    <t>VN-A551</t>
+  </si>
+  <si>
+    <t>07:10</t>
+  </si>
+  <si>
+    <t>09:05</t>
+  </si>
+  <si>
+    <t>10:25</t>
+  </si>
+  <si>
+    <t>14:20</t>
+  </si>
+  <si>
+    <t>15:00</t>
+  </si>
+  <si>
+    <t>16:20</t>
+  </si>
+  <si>
+    <t>VN-A552</t>
+  </si>
+  <si>
+    <t>14:05</t>
+  </si>
+  <si>
+    <t>18:30</t>
+  </si>
+  <si>
+    <t>DEL</t>
+  </si>
+  <si>
+    <t>22:55</t>
+  </si>
+  <si>
+    <t>00:05</t>
+  </si>
+  <si>
+    <t>VN-A553</t>
+  </si>
+  <si>
+    <t>10:33</t>
+  </si>
+  <si>
+    <t>21:00</t>
+  </si>
+  <si>
+    <t>22:00</t>
+  </si>
+  <si>
+    <t>22:45</t>
+  </si>
+  <si>
     <t>00:30</t>
   </si>
   <si>
-    <t>VN-A539</t>
-  </si>
-  <si>
-    <t>VII</t>
-  </si>
-  <si>
-    <t>05:00</t>
-  </si>
-  <si>
-    <t>06:50</t>
-  </si>
-  <si>
-    <t>06:32</t>
-  </si>
-  <si>
-    <t>BMV</t>
-  </si>
-  <si>
-    <t>07:20</t>
-  </si>
-  <si>
-    <t>08:45</t>
-  </si>
-  <si>
-    <t>08:41</t>
-  </si>
-  <si>
-    <t>09:15</t>
-  </si>
-  <si>
-    <t>13:40</t>
-  </si>
-  <si>
-    <t>18:10</t>
-  </si>
-  <si>
-    <t>20:40</t>
-  </si>
-  <si>
-    <t>21:10</t>
-  </si>
-  <si>
-    <t>22:30</t>
-  </si>
-  <si>
-    <t>VN-A542</t>
-  </si>
-  <si>
-    <t>10:35</t>
-  </si>
-  <si>
-    <t>12:50</t>
-  </si>
-  <si>
-    <t>14:35</t>
-  </si>
-  <si>
-    <t>17:15</t>
-  </si>
-  <si>
-    <t>VN-A543</t>
-  </si>
-  <si>
-    <t>HKT</t>
-  </si>
-  <si>
-    <t>11:19</t>
-  </si>
-  <si>
-    <t>13:50</t>
-  </si>
-  <si>
-    <t>18:05</t>
-  </si>
-  <si>
-    <t>VN-A544</t>
-  </si>
-  <si>
-    <t>09:42</t>
-  </si>
-  <si>
-    <t>12:16</t>
-  </si>
-  <si>
-    <t>14:15</t>
-  </si>
-  <si>
-    <t>17:35</t>
-  </si>
-  <si>
-    <t>19:35</t>
-  </si>
-  <si>
-    <t>20:05</t>
-  </si>
-  <si>
-    <t>VN-A547</t>
-  </si>
-  <si>
-    <t>08:00</t>
-  </si>
-  <si>
-    <t>09:55</t>
-  </si>
-  <si>
-    <t>10:03</t>
-  </si>
-  <si>
-    <t>11:30</t>
-  </si>
-  <si>
-    <t>15:05</t>
-  </si>
-  <si>
-    <t>16:25</t>
-  </si>
-  <si>
-    <t>16:55</t>
-  </si>
-  <si>
-    <t>20:45</t>
-  </si>
-  <si>
-    <t>21:50</t>
-  </si>
-  <si>
-    <t>VN-A549</t>
-  </si>
-  <si>
-    <t>NRT</t>
-  </si>
-  <si>
-    <t>13:05</t>
-  </si>
-  <si>
-    <t>TPE</t>
-  </si>
-  <si>
-    <t>14:25</t>
-  </si>
-  <si>
-    <t>19:00</t>
-  </si>
-  <si>
-    <t>NGO</t>
-  </si>
-  <si>
-    <t>VN-A551</t>
-  </si>
-  <si>
-    <t>07:10</t>
-  </si>
-  <si>
-    <t>09:05</t>
-  </si>
-  <si>
-    <t>10:25</t>
-  </si>
-  <si>
-    <t>14:20</t>
-  </si>
-  <si>
-    <t>15:00</t>
-  </si>
-  <si>
-    <t>16:20</t>
-  </si>
-  <si>
-    <t>VN-A552</t>
-  </si>
-  <si>
-    <t>14:05</t>
-  </si>
-  <si>
-    <t>18:30</t>
-  </si>
-  <si>
-    <t>DEL</t>
-  </si>
-  <si>
-    <t>22:55</t>
-  </si>
-  <si>
-    <t>00:05</t>
-  </si>
-  <si>
-    <t>VN-A553</t>
-  </si>
-  <si>
-    <t>10:33</t>
-  </si>
-  <si>
-    <t>21:00</t>
-  </si>
-  <si>
-    <t>22:00</t>
-  </si>
-  <si>
-    <t>22:45</t>
-  </si>
-  <si>
     <t>KHV</t>
   </si>
   <si>
@@ -746,9 +767,6 @@
     <t>VN-A554</t>
   </si>
   <si>
-    <t>17:50</t>
-  </si>
-  <si>
     <t>18:50</t>
   </si>
   <si>
@@ -785,18 +803,6 @@
     <t>09:31</t>
   </si>
   <si>
-    <t>11:42</t>
-  </si>
-  <si>
-    <t>15:35</t>
-  </si>
-  <si>
-    <t>VDH</t>
-  </si>
-  <si>
-    <t>20:00</t>
-  </si>
-  <si>
     <t>VN-A580</t>
   </si>
   <si>
@@ -986,7 +992,7 @@
     <t>09:32</t>
   </si>
   <si>
-    <t>11:33</t>
+    <t>11:39</t>
   </si>
   <si>
     <t>VN-A642</t>
@@ -1379,7 +1385,7 @@
     <t>Total Record(s): 364</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Sep 15, 2026 10:24</t>
+    <t xml:space="preserve">Generated on  Sep 15, 2026 10:38</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -3415,7 +3421,9 @@
       </c>
       <c r="K55" s="7"/>
       <c r="L55" s="7"/>
-      <c r="M55" s="7"/>
+      <c t="s" r="M55" s="7">
+        <v>130</v>
+      </c>
     </row>
     <row r="56" ht="14.25" customHeight="1">
       <c t="s" r="A56" s="6">
@@ -3441,7 +3449,7 @@
         <v>89</v>
       </c>
       <c t="s" r="I56" s="7">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c t="s" r="J56" s="7">
         <v>34</v>
@@ -3474,7 +3482,7 @@
         <v>58</v>
       </c>
       <c t="s" r="I57" s="7">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c t="s" r="J57" s="7">
         <v>23</v>
@@ -3507,7 +3515,7 @@
         <v>89</v>
       </c>
       <c t="s" r="I58" s="7">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c t="s" r="J58" s="7">
         <v>36</v>
@@ -3540,7 +3548,7 @@
         <v>31</v>
       </c>
       <c t="s" r="I59" s="7">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c t="s" r="J59" s="7">
         <v>74</v>
@@ -3573,10 +3581,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I60" s="7">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="J60" s="7">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="K60" s="7"/>
       <c r="L60" s="7"/>
@@ -3609,27 +3617,27 @@
       </c>
       <c r="D62" s="7"/>
       <c t="s" r="E62" s="7">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F62" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G62" s="8">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c t="s" r="H62" s="8">
         <v>89</v>
       </c>
       <c t="s" r="I62" s="7">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c t="s" r="J62" s="7">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="K62" s="7"/>
       <c r="L62" s="7"/>
       <c t="s" r="M62" s="7">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="63" ht="14.25" customHeight="1">
@@ -3640,11 +3648,11 @@
         <v>8520</v>
       </c>
       <c t="s" r="C63" s="7">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D63" s="7"/>
       <c t="s" r="E63" s="7">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F63" s="7">
         <v>321</v>
@@ -3653,10 +3661,10 @@
         <v>89</v>
       </c>
       <c t="s" r="H63" s="8">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c t="s" r="I63" s="7">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c t="s" r="J63" s="7">
         <v>51</v>
@@ -3673,26 +3681,26 @@
         <v>8521</v>
       </c>
       <c t="s" r="C64" s="7">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D64" s="7"/>
       <c t="s" r="E64" s="7">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F64" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G64" s="8">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c t="s" r="H64" s="8">
         <v>89</v>
       </c>
       <c t="s" r="I64" s="7">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c t="s" r="J64" s="7">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="K64" s="7"/>
       <c r="L64" s="7"/>
@@ -3710,7 +3718,7 @@
       </c>
       <c r="D65" s="7"/>
       <c t="s" r="E65" s="7">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F65" s="7">
         <v>321</v>
@@ -3719,13 +3727,13 @@
         <v>89</v>
       </c>
       <c t="s" r="H65" s="8">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c t="s" r="I65" s="7">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c t="s" r="J65" s="7">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="K65" s="7"/>
       <c r="L65" s="7"/>
@@ -3758,7 +3766,7 @@
       </c>
       <c r="D67" s="7"/>
       <c t="s" r="E67" s="7">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F67" s="7">
         <v>321</v>
@@ -3773,12 +3781,12 @@
         <v>76</v>
       </c>
       <c t="s" r="J67" s="7">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="K67" s="7"/>
       <c r="L67" s="7"/>
       <c t="s" r="M67" s="7">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="68" ht="14.25" customHeight="1">
@@ -3793,7 +3801,7 @@
       </c>
       <c r="D68" s="7"/>
       <c t="s" r="E68" s="7">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F68" s="7">
         <v>321</v>
@@ -3805,7 +3813,7 @@
         <v>89</v>
       </c>
       <c t="s" r="I68" s="7">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c t="s" r="J68" s="7">
         <v>97</v>
@@ -3813,7 +3821,7 @@
       <c r="K68" s="7"/>
       <c r="L68" s="7"/>
       <c t="s" r="M68" s="7">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="69" ht="14.25" customHeight="1">
@@ -3828,7 +3836,7 @@
       </c>
       <c r="D69" s="7"/>
       <c t="s" r="E69" s="7">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F69" s="7">
         <v>321</v>
@@ -3837,18 +3845,18 @@
         <v>89</v>
       </c>
       <c t="s" r="H69" s="8">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c t="s" r="I69" s="7">
         <v>45</v>
       </c>
       <c t="s" r="J69" s="7">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="K69" s="7"/>
       <c r="L69" s="7"/>
       <c t="s" r="M69" s="7">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="70" ht="15" customHeight="1">
@@ -3863,19 +3871,19 @@
       </c>
       <c r="D70" s="7"/>
       <c t="s" r="E70" s="7">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F70" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G70" s="8">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c t="s" r="H70" s="8">
         <v>89</v>
       </c>
       <c t="s" r="I70" s="7">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c t="s" r="J70" s="7">
         <v>80</v>
@@ -3896,7 +3904,7 @@
       </c>
       <c r="D71" s="7"/>
       <c t="s" r="E71" s="7">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F71" s="7">
         <v>321</v>
@@ -3929,7 +3937,7 @@
       </c>
       <c r="D72" s="7"/>
       <c t="s" r="E72" s="7">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F72" s="7">
         <v>321</v>
@@ -3941,10 +3949,10 @@
         <v>31</v>
       </c>
       <c t="s" r="I72" s="7">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c t="s" r="J72" s="7">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="K72" s="7"/>
       <c r="L72" s="7"/>
@@ -3962,7 +3970,7 @@
       </c>
       <c r="D73" s="7"/>
       <c t="s" r="E73" s="7">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F73" s="7">
         <v>321</v>
@@ -3974,10 +3982,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I73" s="7">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c t="s" r="J73" s="7">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="K73" s="7"/>
       <c r="L73" s="7"/>
@@ -4010,7 +4018,7 @@
       </c>
       <c r="D75" s="7"/>
       <c t="s" r="E75" s="7">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F75" s="7">
         <v>321</v>
@@ -4022,15 +4030,15 @@
         <v>89</v>
       </c>
       <c t="s" r="I75" s="7">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c t="s" r="J75" s="7">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="K75" s="7"/>
       <c r="L75" s="7"/>
       <c t="s" r="M75" s="7">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="76" ht="14.25" customHeight="1">
@@ -4045,7 +4053,7 @@
       </c>
       <c r="D76" s="7"/>
       <c t="s" r="E76" s="7">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F76" s="7">
         <v>321</v>
@@ -4057,7 +4065,7 @@
         <v>31</v>
       </c>
       <c t="s" r="I76" s="7">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c t="s" r="J76" s="7">
         <v>97</v>
@@ -4065,7 +4073,7 @@
       <c r="K76" s="7"/>
       <c r="L76" s="7"/>
       <c t="s" r="M76" s="7">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="77" ht="14.25" customHeight="1">
@@ -4080,7 +4088,7 @@
       </c>
       <c r="D77" s="7"/>
       <c t="s" r="E77" s="7">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F77" s="7">
         <v>321</v>
@@ -4089,13 +4097,13 @@
         <v>31</v>
       </c>
       <c t="s" r="H77" s="8">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c t="s" r="I77" s="7">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c t="s" r="J77" s="7">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="K77" s="7"/>
       <c r="L77" s="7"/>
@@ -4115,13 +4123,13 @@
       </c>
       <c r="D78" s="7"/>
       <c t="s" r="E78" s="7">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F78" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G78" s="8">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c t="s" r="H78" s="8">
         <v>31</v>
@@ -4130,7 +4138,7 @@
         <v>60</v>
       </c>
       <c t="s" r="J78" s="7">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="K78" s="7"/>
       <c r="L78" s="7"/>
@@ -4148,7 +4156,7 @@
       </c>
       <c r="D79" s="7"/>
       <c t="s" r="E79" s="7">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F79" s="7">
         <v>321</v>
@@ -4160,7 +4168,7 @@
         <v>117</v>
       </c>
       <c t="s" r="I79" s="7">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c t="s" r="J79" s="7">
         <v>124</v>
@@ -4181,7 +4189,7 @@
       </c>
       <c r="D80" s="7"/>
       <c t="s" r="E80" s="7">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F80" s="7">
         <v>321</v>
@@ -4196,7 +4204,7 @@
         <v>123</v>
       </c>
       <c t="s" r="J80" s="7">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="K80" s="7"/>
       <c r="L80" s="7"/>
@@ -4214,7 +4222,7 @@
       </c>
       <c r="D81" s="7"/>
       <c t="s" r="E81" s="7">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F81" s="7">
         <v>321</v>
@@ -4223,13 +4231,13 @@
         <v>31</v>
       </c>
       <c t="s" r="H81" s="8">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c t="s" r="I81" s="7">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c t="s" r="J81" s="7">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="K81" s="7"/>
       <c r="L81" s="7"/>
@@ -4262,7 +4270,7 @@
       </c>
       <c r="D83" s="7"/>
       <c t="s" r="E83" s="7">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F83" s="7">
         <v>321</v>
@@ -4274,10 +4282,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I83" s="7">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c t="s" r="J83" s="7">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c t="s" r="K83" s="7">
         <v>97</v>
@@ -4292,14 +4300,14 @@
         <v>13</v>
       </c>
       <c r="B84" s="7">
-        <v>860</v>
+        <v>600</v>
       </c>
       <c t="s" r="C84" s="7">
         <v>14</v>
       </c>
       <c r="D84" s="7"/>
       <c t="s" r="E84" s="7">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F84" s="7">
         <v>321</v>
@@ -4308,13 +4316,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H84" s="8">
-        <v>137</v>
+        <v>17</v>
       </c>
       <c t="s" r="I84" s="7">
-        <v>79</v>
+        <v>175</v>
       </c>
       <c t="s" r="J84" s="7">
-        <v>66</v>
+        <v>176</v>
       </c>
       <c r="K84" s="7"/>
       <c r="L84" s="7"/>
@@ -4325,45 +4333,63 @@
         <v>13</v>
       </c>
       <c r="B85" s="7">
-        <v>861</v>
+        <v>601</v>
       </c>
       <c t="s" r="C85" s="7">
         <v>14</v>
       </c>
       <c r="D85" s="7"/>
       <c t="s" r="E85" s="7">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F85" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G85" s="8">
-        <v>137</v>
+        <v>17</v>
       </c>
       <c t="s" r="H85" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I85" s="7">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c t="s" r="J85" s="7">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="K85" s="7"/>
       <c r="L85" s="7"/>
       <c r="M85" s="7"/>
     </row>
     <row r="86" ht="14.25" customHeight="1">
-      <c r="A86" s="6"/>
-      <c r="B86" s="7"/>
-      <c r="C86" s="7"/>
+      <c t="s" r="A86" s="6">
+        <v>13</v>
+      </c>
+      <c r="B86" s="7">
+        <v>262</v>
+      </c>
+      <c t="s" r="C86" s="7">
+        <v>14</v>
+      </c>
       <c r="D86" s="7"/>
-      <c r="E86" s="7"/>
-      <c r="F86" s="7"/>
-      <c r="G86" s="8"/>
-      <c r="H86" s="8"/>
-      <c r="I86" s="7"/>
-      <c r="J86" s="7"/>
+      <c t="s" r="E86" s="7">
+        <v>172</v>
+      </c>
+      <c r="F86" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G86" s="8">
+        <v>41</v>
+      </c>
+      <c t="s" r="H86" s="8">
+        <v>178</v>
+      </c>
+      <c t="s" r="I86" s="7">
+        <v>179</v>
+      </c>
+      <c t="s" r="J86" s="7">
+        <v>66</v>
+      </c>
       <c r="K86" s="7"/>
       <c r="L86" s="7"/>
       <c r="M86" s="7"/>
@@ -4373,104 +4399,82 @@
         <v>13</v>
       </c>
       <c r="B87" s="7">
-        <v>224</v>
+        <v>263</v>
       </c>
       <c t="s" r="C87" s="7">
         <v>14</v>
       </c>
       <c r="D87" s="7"/>
       <c t="s" r="E87" s="7">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="F87" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G87" s="8">
-        <v>41</v>
+        <v>178</v>
       </c>
       <c t="s" r="H87" s="8">
-        <v>176</v>
+        <v>41</v>
       </c>
       <c t="s" r="I87" s="7">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c t="s" r="J87" s="7">
-        <v>178</v>
+        <v>25</v>
       </c>
       <c r="K87" s="7"/>
       <c r="L87" s="7"/>
-      <c t="s" r="M87" s="7">
-        <v>179</v>
-      </c>
+      <c r="M87" s="7"/>
     </row>
     <row r="88" ht="14.25" customHeight="1">
-      <c t="s" r="A88" s="6">
-        <v>13</v>
-      </c>
-      <c r="B88" s="7">
-        <v>741</v>
-      </c>
-      <c t="s" r="C88" s="7">
-        <v>14</v>
-      </c>
+      <c r="A88" s="6"/>
+      <c r="B88" s="7"/>
+      <c r="C88" s="7"/>
       <c r="D88" s="7"/>
-      <c t="s" r="E88" s="7">
-        <v>175</v>
-      </c>
-      <c r="F88" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G88" s="8">
-        <v>176</v>
-      </c>
-      <c t="s" r="H88" s="8">
-        <v>180</v>
-      </c>
-      <c t="s" r="I88" s="7">
-        <v>181</v>
-      </c>
-      <c t="s" r="J88" s="7">
-        <v>182</v>
-      </c>
+      <c r="E88" s="7"/>
+      <c r="F88" s="7"/>
+      <c r="G88" s="8"/>
+      <c r="H88" s="8"/>
+      <c r="I88" s="7"/>
+      <c r="J88" s="7"/>
       <c r="K88" s="7"/>
       <c r="L88" s="7"/>
-      <c t="s" r="M88" s="7">
-        <v>183</v>
-      </c>
+      <c r="M88" s="7"/>
     </row>
     <row r="89" ht="14.25" customHeight="1">
       <c t="s" r="A89" s="6">
         <v>13</v>
       </c>
       <c r="B89" s="7">
-        <v>740</v>
+        <v>224</v>
       </c>
       <c t="s" r="C89" s="7">
         <v>14</v>
       </c>
       <c r="D89" s="7"/>
       <c t="s" r="E89" s="7">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="F89" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G89" s="8">
-        <v>180</v>
+        <v>41</v>
       </c>
       <c t="s" r="H89" s="8">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c t="s" r="I89" s="7">
+        <v>183</v>
+      </c>
+      <c t="s" r="J89" s="7">
         <v>184</v>
-      </c>
-      <c t="s" r="J89" s="7">
-        <v>165</v>
       </c>
       <c r="K89" s="7"/>
       <c r="L89" s="7"/>
       <c t="s" r="M89" s="7">
-        <v>165</v>
+        <v>185</v>
       </c>
     </row>
     <row r="90" ht="15" customHeight="1">
@@ -4478,95 +4482,99 @@
         <v>13</v>
       </c>
       <c r="B90" s="7">
-        <v>227</v>
+        <v>741</v>
       </c>
       <c t="s" r="C90" s="7">
         <v>14</v>
       </c>
       <c r="D90" s="7"/>
       <c t="s" r="E90" s="7">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="F90" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G90" s="8">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c t="s" r="H90" s="8">
-        <v>41</v>
+        <v>186</v>
       </c>
       <c t="s" r="I90" s="7">
-        <v>60</v>
+        <v>187</v>
       </c>
       <c t="s" r="J90" s="7">
-        <v>34</v>
+        <v>188</v>
       </c>
       <c r="K90" s="7"/>
       <c r="L90" s="7"/>
-      <c r="M90" s="7"/>
+      <c t="s" r="M90" s="7">
+        <v>189</v>
+      </c>
     </row>
     <row r="91" ht="14.25" customHeight="1">
       <c t="s" r="A91" s="6">
         <v>13</v>
       </c>
       <c r="B91" s="7">
-        <v>252</v>
+        <v>740</v>
       </c>
       <c t="s" r="C91" s="7">
         <v>14</v>
       </c>
       <c r="D91" s="7"/>
       <c t="s" r="E91" s="7">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="F91" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G91" s="8">
-        <v>41</v>
+        <v>186</v>
       </c>
       <c t="s" r="H91" s="8">
-        <v>47</v>
+        <v>182</v>
       </c>
       <c t="s" r="I91" s="7">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c t="s" r="J91" s="7">
-        <v>83</v>
+        <v>166</v>
       </c>
       <c r="K91" s="7"/>
       <c r="L91" s="7"/>
-      <c r="M91" s="7"/>
+      <c t="s" r="M91" s="7">
+        <v>166</v>
+      </c>
     </row>
     <row r="92" ht="14.25" customHeight="1">
       <c t="s" r="A92" s="6">
         <v>13</v>
       </c>
       <c r="B92" s="7">
-        <v>253</v>
+        <v>227</v>
       </c>
       <c t="s" r="C92" s="7">
         <v>14</v>
       </c>
       <c r="D92" s="7"/>
       <c t="s" r="E92" s="7">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="F92" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G92" s="8">
-        <v>47</v>
+        <v>182</v>
       </c>
       <c t="s" r="H92" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I92" s="7">
-        <v>121</v>
+        <v>60</v>
       </c>
       <c t="s" r="J92" s="7">
-        <v>186</v>
+        <v>34</v>
       </c>
       <c r="K92" s="7"/>
       <c r="L92" s="7"/>
@@ -4577,14 +4585,14 @@
         <v>13</v>
       </c>
       <c r="B93" s="7">
-        <v>644</v>
+        <v>252</v>
       </c>
       <c t="s" r="C93" s="7">
         <v>14</v>
       </c>
       <c r="D93" s="7"/>
       <c t="s" r="E93" s="7">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="F93" s="7">
         <v>321</v>
@@ -4593,13 +4601,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H93" s="8">
-        <v>89</v>
+        <v>47</v>
       </c>
       <c t="s" r="I93" s="7">
-        <v>104</v>
+        <v>191</v>
       </c>
       <c t="s" r="J93" s="7">
-        <v>187</v>
+        <v>83</v>
       </c>
       <c r="K93" s="7"/>
       <c r="L93" s="7"/>
@@ -4610,45 +4618,63 @@
         <v>13</v>
       </c>
       <c r="B94" s="7">
-        <v>645</v>
+        <v>253</v>
       </c>
       <c t="s" r="C94" s="7">
         <v>14</v>
       </c>
       <c r="D94" s="7"/>
       <c t="s" r="E94" s="7">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="F94" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G94" s="8">
-        <v>89</v>
+        <v>47</v>
       </c>
       <c t="s" r="H94" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I94" s="7">
-        <v>188</v>
+        <v>121</v>
       </c>
       <c t="s" r="J94" s="7">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="K94" s="7"/>
       <c r="L94" s="7"/>
       <c r="M94" s="7"/>
     </row>
     <row r="95" ht="15" customHeight="1">
-      <c r="A95" s="6"/>
-      <c r="B95" s="7"/>
-      <c r="C95" s="7"/>
+      <c t="s" r="A95" s="6">
+        <v>13</v>
+      </c>
+      <c r="B95" s="7">
+        <v>644</v>
+      </c>
+      <c t="s" r="C95" s="7">
+        <v>14</v>
+      </c>
       <c r="D95" s="7"/>
-      <c r="E95" s="7"/>
-      <c r="F95" s="7"/>
-      <c r="G95" s="8"/>
-      <c r="H95" s="8"/>
-      <c r="I95" s="7"/>
-      <c r="J95" s="7"/>
+      <c t="s" r="E95" s="7">
+        <v>181</v>
+      </c>
+      <c r="F95" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G95" s="8">
+        <v>41</v>
+      </c>
+      <c t="s" r="H95" s="8">
+        <v>89</v>
+      </c>
+      <c t="s" r="I95" s="7">
+        <v>104</v>
+      </c>
+      <c t="s" r="J95" s="7">
+        <v>193</v>
+      </c>
       <c r="K95" s="7"/>
       <c r="L95" s="7"/>
       <c r="M95" s="7"/>
@@ -4658,63 +4684,45 @@
         <v>13</v>
       </c>
       <c r="B96" s="7">
-        <v>1491</v>
+        <v>645</v>
       </c>
       <c t="s" r="C96" s="7">
         <v>14</v>
       </c>
       <c r="D96" s="7"/>
       <c t="s" r="E96" s="7">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="F96" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G96" s="8">
-        <v>31</v>
+        <v>89</v>
       </c>
       <c t="s" r="H96" s="8">
-        <v>180</v>
+        <v>41</v>
       </c>
       <c t="s" r="I96" s="7">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c t="s" r="J96" s="7">
-        <v>79</v>
+        <v>195</v>
       </c>
       <c r="K96" s="7"/>
       <c r="L96" s="7"/>
       <c r="M96" s="7"/>
     </row>
     <row r="97" ht="14.25" customHeight="1">
-      <c t="s" r="A97" s="6">
-        <v>13</v>
-      </c>
-      <c r="B97" s="7">
-        <v>1492</v>
-      </c>
-      <c t="s" r="C97" s="7">
-        <v>14</v>
-      </c>
+      <c r="A97" s="6"/>
+      <c r="B97" s="7"/>
+      <c r="C97" s="7"/>
       <c r="D97" s="7"/>
-      <c t="s" r="E97" s="7">
-        <v>190</v>
-      </c>
-      <c r="F97" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G97" s="8">
-        <v>180</v>
-      </c>
-      <c t="s" r="H97" s="8">
-        <v>31</v>
-      </c>
-      <c t="s" r="I97" s="7">
-        <v>192</v>
-      </c>
-      <c t="s" r="J97" s="7">
-        <v>193</v>
-      </c>
+      <c r="E97" s="7"/>
+      <c r="F97" s="7"/>
+      <c r="G97" s="8"/>
+      <c r="H97" s="8"/>
+      <c r="I97" s="7"/>
+      <c r="J97" s="7"/>
       <c r="K97" s="7"/>
       <c r="L97" s="7"/>
       <c r="M97" s="7"/>
@@ -4724,14 +4732,14 @@
         <v>13</v>
       </c>
       <c r="B98" s="7">
-        <v>439</v>
+        <v>1491</v>
       </c>
       <c t="s" r="C98" s="7">
         <v>14</v>
       </c>
       <c r="D98" s="7"/>
       <c t="s" r="E98" s="7">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="F98" s="7">
         <v>321</v>
@@ -4740,62 +4748,82 @@
         <v>31</v>
       </c>
       <c t="s" r="H98" s="8">
-        <v>96</v>
+        <v>186</v>
       </c>
       <c t="s" r="I98" s="7">
-        <v>83</v>
+        <v>197</v>
       </c>
       <c t="s" r="J98" s="7">
-        <v>194</v>
+        <v>79</v>
       </c>
       <c r="K98" s="7"/>
       <c r="L98" s="7"/>
-      <c r="M98" s="7"/>
+      <c t="s" r="M98" s="7">
+        <v>198</v>
+      </c>
     </row>
     <row r="99" ht="14.25" customHeight="1">
       <c t="s" r="A99" s="6">
         <v>13</v>
       </c>
       <c r="B99" s="7">
-        <v>438</v>
+        <v>1492</v>
       </c>
       <c t="s" r="C99" s="7">
         <v>14</v>
       </c>
       <c r="D99" s="7"/>
       <c t="s" r="E99" s="7">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="F99" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G99" s="8">
-        <v>96</v>
+        <v>186</v>
       </c>
       <c t="s" r="H99" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I99" s="7">
-        <v>103</v>
+        <v>199</v>
       </c>
       <c t="s" r="J99" s="7">
-        <v>66</v>
+        <v>175</v>
       </c>
       <c r="K99" s="7"/>
       <c r="L99" s="7"/>
       <c r="M99" s="7"/>
     </row>
     <row r="100" ht="15" customHeight="1">
-      <c r="A100" s="6"/>
-      <c r="B100" s="7"/>
-      <c r="C100" s="7"/>
+      <c t="s" r="A100" s="6">
+        <v>13</v>
+      </c>
+      <c r="B100" s="7">
+        <v>439</v>
+      </c>
+      <c t="s" r="C100" s="7">
+        <v>14</v>
+      </c>
       <c r="D100" s="7"/>
-      <c r="E100" s="7"/>
-      <c r="F100" s="7"/>
-      <c r="G100" s="8"/>
-      <c r="H100" s="8"/>
-      <c r="I100" s="7"/>
-      <c r="J100" s="7"/>
+      <c t="s" r="E100" s="7">
+        <v>196</v>
+      </c>
+      <c r="F100" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G100" s="8">
+        <v>31</v>
+      </c>
+      <c t="s" r="H100" s="8">
+        <v>96</v>
+      </c>
+      <c t="s" r="I100" s="7">
+        <v>83</v>
+      </c>
+      <c t="s" r="J100" s="7">
+        <v>177</v>
+      </c>
       <c r="K100" s="7"/>
       <c r="L100" s="7"/>
       <c r="M100" s="7"/>
@@ -4805,65 +4833,45 @@
         <v>13</v>
       </c>
       <c r="B101" s="7">
-        <v>809</v>
+        <v>438</v>
       </c>
       <c t="s" r="C101" s="7">
         <v>14</v>
       </c>
       <c r="D101" s="7"/>
       <c t="s" r="E101" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F101" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G101" s="8">
-        <v>41</v>
+        <v>96</v>
       </c>
       <c t="s" r="H101" s="8">
-        <v>196</v>
+        <v>31</v>
       </c>
       <c t="s" r="I101" s="7">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c t="s" r="J101" s="7">
-        <v>18</v>
+        <v>66</v>
       </c>
       <c r="K101" s="7"/>
       <c r="L101" s="7"/>
-      <c t="s" r="M101" s="7">
-        <v>197</v>
-      </c>
+      <c r="M101" s="7"/>
     </row>
     <row r="102" ht="14.25" customHeight="1">
-      <c t="s" r="A102" s="6">
-        <v>13</v>
-      </c>
-      <c r="B102" s="7">
-        <v>808</v>
-      </c>
-      <c t="s" r="C102" s="7">
-        <v>14</v>
-      </c>
+      <c r="A102" s="6"/>
+      <c r="B102" s="7"/>
+      <c r="C102" s="7"/>
       <c r="D102" s="7"/>
-      <c t="s" r="E102" s="7">
-        <v>195</v>
-      </c>
-      <c r="F102" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G102" s="8">
-        <v>196</v>
-      </c>
-      <c t="s" r="H102" s="8">
-        <v>41</v>
-      </c>
-      <c t="s" r="I102" s="7">
-        <v>130</v>
-      </c>
-      <c t="s" r="J102" s="7">
-        <v>198</v>
-      </c>
+      <c r="E102" s="7"/>
+      <c r="F102" s="7"/>
+      <c r="G102" s="8"/>
+      <c r="H102" s="8"/>
+      <c r="I102" s="7"/>
+      <c r="J102" s="7"/>
       <c r="K102" s="7"/>
       <c r="L102" s="7"/>
       <c r="M102" s="7"/>
@@ -4873,14 +4881,14 @@
         <v>13</v>
       </c>
       <c r="B103" s="7">
-        <v>144</v>
+        <v>809</v>
       </c>
       <c t="s" r="C103" s="7">
         <v>14</v>
       </c>
       <c r="D103" s="7"/>
       <c t="s" r="E103" s="7">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="F103" s="7">
         <v>321</v>
@@ -4889,29 +4897,49 @@
         <v>41</v>
       </c>
       <c t="s" r="H103" s="8">
-        <v>31</v>
+        <v>201</v>
       </c>
       <c t="s" r="I103" s="7">
-        <v>23</v>
+        <v>97</v>
       </c>
       <c t="s" r="J103" s="7">
-        <v>199</v>
+        <v>18</v>
       </c>
       <c r="K103" s="7"/>
       <c r="L103" s="7"/>
-      <c r="M103" s="7"/>
+      <c t="s" r="M103" s="7">
+        <v>202</v>
+      </c>
     </row>
     <row r="104" ht="14.25" customHeight="1">
-      <c r="A104" s="6"/>
-      <c r="B104" s="7"/>
-      <c r="C104" s="7"/>
+      <c t="s" r="A104" s="6">
+        <v>13</v>
+      </c>
+      <c r="B104" s="7">
+        <v>808</v>
+      </c>
+      <c t="s" r="C104" s="7">
+        <v>14</v>
+      </c>
       <c r="D104" s="7"/>
-      <c r="E104" s="7"/>
-      <c r="F104" s="7"/>
-      <c r="G104" s="8"/>
-      <c r="H104" s="8"/>
-      <c r="I104" s="7"/>
-      <c r="J104" s="7"/>
+      <c t="s" r="E104" s="7">
+        <v>200</v>
+      </c>
+      <c r="F104" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G104" s="8">
+        <v>201</v>
+      </c>
+      <c t="s" r="H104" s="8">
+        <v>41</v>
+      </c>
+      <c t="s" r="I104" s="7">
+        <v>131</v>
+      </c>
+      <c t="s" r="J104" s="7">
+        <v>203</v>
+      </c>
       <c r="K104" s="7"/>
       <c r="L104" s="7"/>
       <c r="M104" s="7"/>
@@ -4921,7 +4949,7 @@
         <v>13</v>
       </c>
       <c r="B105" s="7">
-        <v>1280</v>
+        <v>144</v>
       </c>
       <c t="s" r="C105" s="7">
         <v>14</v>
@@ -4937,68 +4965,46 @@
         <v>41</v>
       </c>
       <c t="s" r="H105" s="8">
-        <v>152</v>
+        <v>31</v>
       </c>
       <c t="s" r="I105" s="7">
-        <v>150</v>
+        <v>23</v>
       </c>
       <c t="s" r="J105" s="7">
-        <v>45</v>
+        <v>204</v>
       </c>
       <c r="K105" s="7"/>
       <c r="L105" s="7"/>
-      <c t="s" r="M105" s="7">
-        <v>201</v>
-      </c>
+      <c r="M105" s="7"/>
     </row>
     <row r="106" ht="14.25" customHeight="1">
-      <c t="s" r="A106" s="6">
-        <v>13</v>
-      </c>
-      <c r="B106" s="7">
-        <v>1281</v>
-      </c>
-      <c t="s" r="C106" s="7">
-        <v>14</v>
-      </c>
+      <c r="A106" s="6"/>
+      <c r="B106" s="7"/>
+      <c r="C106" s="7"/>
       <c r="D106" s="7"/>
-      <c t="s" r="E106" s="7">
-        <v>200</v>
-      </c>
-      <c r="F106" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G106" s="8">
-        <v>152</v>
-      </c>
-      <c t="s" r="H106" s="8">
-        <v>41</v>
-      </c>
-      <c t="s" r="I106" s="7">
-        <v>98</v>
-      </c>
-      <c t="s" r="J106" s="7">
-        <v>143</v>
-      </c>
+      <c r="E106" s="7"/>
+      <c r="F106" s="7"/>
+      <c r="G106" s="8"/>
+      <c r="H106" s="8"/>
+      <c r="I106" s="7"/>
+      <c r="J106" s="7"/>
       <c r="K106" s="7"/>
       <c r="L106" s="7"/>
-      <c t="s" r="M106" s="7">
-        <v>202</v>
-      </c>
+      <c r="M106" s="7"/>
     </row>
     <row r="107" ht="14.25" customHeight="1">
       <c t="s" r="A107" s="6">
         <v>13</v>
       </c>
       <c r="B107" s="7">
-        <v>308</v>
+        <v>1280</v>
       </c>
       <c t="s" r="C107" s="7">
         <v>14</v>
       </c>
       <c r="D107" s="7"/>
       <c t="s" r="E107" s="7">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="F107" s="7">
         <v>321</v>
@@ -5007,64 +5013,68 @@
         <v>41</v>
       </c>
       <c t="s" r="H107" s="8">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c t="s" r="I107" s="7">
-        <v>203</v>
+        <v>151</v>
       </c>
       <c t="s" r="J107" s="7">
-        <v>83</v>
+        <v>45</v>
       </c>
       <c r="K107" s="7"/>
       <c r="L107" s="7"/>
-      <c r="M107" s="7"/>
+      <c t="s" r="M107" s="7">
+        <v>206</v>
+      </c>
     </row>
     <row r="108" ht="14.25" customHeight="1">
       <c t="s" r="A108" s="6">
         <v>13</v>
       </c>
       <c r="B108" s="7">
-        <v>307</v>
+        <v>1281</v>
       </c>
       <c t="s" r="C108" s="7">
         <v>14</v>
       </c>
       <c r="D108" s="7"/>
       <c t="s" r="E108" s="7">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="F108" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G108" s="8">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c t="s" r="H108" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I108" s="7">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c t="s" r="J108" s="7">
-        <v>204</v>
+        <v>144</v>
       </c>
       <c r="K108" s="7"/>
       <c r="L108" s="7"/>
-      <c r="M108" s="7"/>
+      <c t="s" r="M108" s="7">
+        <v>207</v>
+      </c>
     </row>
     <row r="109" ht="14.25" customHeight="1">
       <c t="s" r="A109" s="6">
         <v>13</v>
       </c>
       <c r="B109" s="7">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c t="s" r="C109" s="7">
         <v>14</v>
       </c>
       <c r="D109" s="7"/>
       <c t="s" r="E109" s="7">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="F109" s="7">
         <v>321</v>
@@ -5073,13 +5083,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H109" s="8">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c t="s" r="I109" s="7">
-        <v>186</v>
+        <v>208</v>
       </c>
       <c t="s" r="J109" s="7">
-        <v>205</v>
+        <v>83</v>
       </c>
       <c r="K109" s="7"/>
       <c r="L109" s="7"/>
@@ -5090,45 +5100,63 @@
         <v>13</v>
       </c>
       <c r="B110" s="7">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c t="s" r="C110" s="7">
         <v>14</v>
       </c>
       <c r="D110" s="7"/>
       <c t="s" r="E110" s="7">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="F110" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G110" s="8">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c t="s" r="H110" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I110" s="7">
-        <v>206</v>
+        <v>121</v>
       </c>
       <c t="s" r="J110" s="7">
-        <v>158</v>
+        <v>209</v>
       </c>
       <c r="K110" s="7"/>
       <c r="L110" s="7"/>
       <c r="M110" s="7"/>
     </row>
     <row r="111" ht="14.25" customHeight="1">
-      <c r="A111" s="6"/>
-      <c r="B111" s="7"/>
-      <c r="C111" s="7"/>
+      <c t="s" r="A111" s="6">
+        <v>13</v>
+      </c>
+      <c r="B111" s="7">
+        <v>312</v>
+      </c>
+      <c t="s" r="C111" s="7">
+        <v>14</v>
+      </c>
       <c r="D111" s="7"/>
-      <c r="E111" s="7"/>
-      <c r="F111" s="7"/>
-      <c r="G111" s="8"/>
-      <c r="H111" s="8"/>
-      <c r="I111" s="7"/>
-      <c r="J111" s="7"/>
+      <c t="s" r="E111" s="7">
+        <v>205</v>
+      </c>
+      <c r="F111" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G111" s="8">
+        <v>41</v>
+      </c>
+      <c t="s" r="H111" s="8">
+        <v>165</v>
+      </c>
+      <c t="s" r="I111" s="7">
+        <v>192</v>
+      </c>
+      <c t="s" r="J111" s="7">
+        <v>210</v>
+      </c>
       <c r="K111" s="7"/>
       <c r="L111" s="7"/>
       <c r="M111" s="7"/>
@@ -5138,117 +5166,97 @@
         <v>13</v>
       </c>
       <c r="B112" s="7">
-        <v>121</v>
+        <v>311</v>
       </c>
       <c t="s" r="C112" s="7">
         <v>14</v>
       </c>
       <c r="D112" s="7"/>
       <c t="s" r="E112" s="7">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="F112" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G112" s="8">
-        <v>31</v>
+        <v>165</v>
       </c>
       <c t="s" r="H112" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I112" s="7">
-        <v>147</v>
+        <v>211</v>
       </c>
       <c t="s" r="J112" s="7">
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="K112" s="7"/>
       <c r="L112" s="7"/>
-      <c t="s" r="M112" s="7">
-        <v>208</v>
-      </c>
+      <c r="M112" s="7"/>
     </row>
     <row r="113" ht="14.25" customHeight="1">
-      <c t="s" r="A113" s="6">
-        <v>13</v>
-      </c>
-      <c r="B113" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="C113" s="7">
-        <v>14</v>
-      </c>
+      <c r="A113" s="6"/>
+      <c r="B113" s="7"/>
+      <c r="C113" s="7"/>
       <c r="D113" s="7"/>
-      <c t="s" r="E113" s="7">
-        <v>207</v>
-      </c>
-      <c r="F113" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G113" s="8">
-        <v>41</v>
-      </c>
-      <c t="s" r="H113" s="8">
-        <v>58</v>
-      </c>
-      <c t="s" r="I113" s="7">
-        <v>97</v>
-      </c>
-      <c t="s" r="J113" s="7">
-        <v>209</v>
-      </c>
+      <c r="E113" s="7"/>
+      <c r="F113" s="7"/>
+      <c r="G113" s="8"/>
+      <c r="H113" s="8"/>
+      <c r="I113" s="7"/>
+      <c r="J113" s="7"/>
       <c r="K113" s="7"/>
       <c r="L113" s="7"/>
-      <c t="s" r="M113" s="7">
-        <v>210</v>
-      </c>
+      <c r="M113" s="7"/>
     </row>
     <row r="114" ht="14.25" customHeight="1">
       <c t="s" r="A114" s="6">
         <v>13</v>
       </c>
       <c r="B114" s="7">
-        <v>330</v>
+        <v>121</v>
       </c>
       <c t="s" r="C114" s="7">
         <v>14</v>
       </c>
       <c r="D114" s="7"/>
       <c t="s" r="E114" s="7">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="F114" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G114" s="8">
-        <v>58</v>
+        <v>31</v>
       </c>
       <c t="s" r="H114" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I114" s="7">
-        <v>100</v>
+        <v>148</v>
       </c>
       <c t="s" r="J114" s="7">
-        <v>211</v>
+        <v>173</v>
       </c>
       <c r="K114" s="7"/>
       <c r="L114" s="7"/>
-      <c r="M114" s="7"/>
+      <c t="s" r="M114" s="7">
+        <v>213</v>
+      </c>
     </row>
     <row r="115" ht="15" customHeight="1">
       <c t="s" r="A115" s="6">
         <v>13</v>
       </c>
       <c r="B115" s="7">
-        <v>136</v>
+        <v>321</v>
       </c>
       <c t="s" r="C115" s="7">
         <v>14</v>
       </c>
       <c r="D115" s="7"/>
       <c t="s" r="E115" s="7">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="F115" s="7">
         <v>321</v>
@@ -5257,79 +5265,83 @@
         <v>41</v>
       </c>
       <c t="s" r="H115" s="8">
-        <v>31</v>
+        <v>58</v>
       </c>
       <c t="s" r="I115" s="7">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c t="s" r="J115" s="7">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="K115" s="7"/>
       <c r="L115" s="7"/>
-      <c r="M115" s="7"/>
+      <c t="s" r="M115" s="7">
+        <v>215</v>
+      </c>
     </row>
     <row r="116" ht="14.25" customHeight="1">
       <c t="s" r="A116" s="6">
         <v>13</v>
       </c>
       <c r="B116" s="7">
-        <v>511</v>
+        <v>330</v>
       </c>
       <c t="s" r="C116" s="7">
         <v>14</v>
       </c>
       <c r="D116" s="7"/>
       <c t="s" r="E116" s="7">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="F116" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G116" s="8">
-        <v>31</v>
+        <v>58</v>
       </c>
       <c t="s" r="H116" s="8">
-        <v>89</v>
+        <v>41</v>
       </c>
       <c t="s" r="I116" s="7">
-        <v>212</v>
+        <v>100</v>
       </c>
       <c t="s" r="J116" s="7">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="K116" s="7"/>
       <c r="L116" s="7"/>
-      <c r="M116" s="7"/>
+      <c t="s" r="M116" s="7">
+        <v>217</v>
+      </c>
     </row>
     <row r="117" ht="14.25" customHeight="1">
       <c t="s" r="A117" s="6">
         <v>13</v>
       </c>
       <c r="B117" s="7">
-        <v>512</v>
+        <v>136</v>
       </c>
       <c t="s" r="C117" s="7">
         <v>14</v>
       </c>
       <c r="D117" s="7"/>
       <c t="s" r="E117" s="7">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="F117" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G117" s="8">
-        <v>89</v>
+        <v>41</v>
       </c>
       <c t="s" r="H117" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I117" s="7">
-        <v>214</v>
+        <v>106</v>
       </c>
       <c t="s" r="J117" s="7">
-        <v>36</v>
+        <v>208</v>
       </c>
       <c r="K117" s="7"/>
       <c r="L117" s="7"/>
@@ -5340,14 +5352,14 @@
         <v>13</v>
       </c>
       <c r="B118" s="7">
-        <v>519</v>
+        <v>511</v>
       </c>
       <c t="s" r="C118" s="7">
         <v>14</v>
       </c>
       <c r="D118" s="7"/>
       <c t="s" r="E118" s="7">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="F118" s="7">
         <v>321</v>
@@ -5359,10 +5371,10 @@
         <v>89</v>
       </c>
       <c t="s" r="I118" s="7">
-        <v>66</v>
+        <v>218</v>
       </c>
       <c t="s" r="J118" s="7">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="K118" s="7"/>
       <c r="L118" s="7"/>
@@ -5373,14 +5385,14 @@
         <v>13</v>
       </c>
       <c r="B119" s="7">
-        <v>647</v>
+        <v>512</v>
       </c>
       <c t="s" r="C119" s="7">
         <v>14</v>
       </c>
       <c r="D119" s="7"/>
       <c t="s" r="E119" s="7">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="F119" s="7">
         <v>321</v>
@@ -5389,29 +5401,47 @@
         <v>89</v>
       </c>
       <c t="s" r="H119" s="8">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c t="s" r="I119" s="7">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c t="s" r="J119" s="7">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="K119" s="7"/>
       <c r="L119" s="7"/>
       <c r="M119" s="7"/>
     </row>
     <row r="120" ht="15" customHeight="1">
-      <c r="A120" s="6"/>
-      <c r="B120" s="7"/>
-      <c r="C120" s="7"/>
+      <c t="s" r="A120" s="6">
+        <v>13</v>
+      </c>
+      <c r="B120" s="7">
+        <v>519</v>
+      </c>
+      <c t="s" r="C120" s="7">
+        <v>14</v>
+      </c>
       <c r="D120" s="7"/>
-      <c r="E120" s="7"/>
-      <c r="F120" s="7"/>
-      <c r="G120" s="8"/>
-      <c r="H120" s="8"/>
-      <c r="I120" s="7"/>
-      <c r="J120" s="7"/>
+      <c t="s" r="E120" s="7">
+        <v>212</v>
+      </c>
+      <c r="F120" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G120" s="8">
+        <v>31</v>
+      </c>
+      <c t="s" r="H120" s="8">
+        <v>89</v>
+      </c>
+      <c t="s" r="I120" s="7">
+        <v>66</v>
+      </c>
+      <c t="s" r="J120" s="7">
+        <v>221</v>
+      </c>
       <c r="K120" s="7"/>
       <c r="L120" s="7"/>
       <c r="M120" s="7"/>
@@ -5421,65 +5451,45 @@
         <v>13</v>
       </c>
       <c r="B121" s="7">
-        <v>933</v>
+        <v>647</v>
       </c>
       <c t="s" r="C121" s="7">
         <v>14</v>
       </c>
       <c r="D121" s="7"/>
       <c t="s" r="E121" s="7">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="F121" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G121" s="8">
-        <v>218</v>
+        <v>89</v>
       </c>
       <c t="s" r="H121" s="8">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c t="s" r="I121" s="7">
-        <v>45</v>
+        <v>222</v>
       </c>
       <c t="s" r="J121" s="7">
-        <v>219</v>
+        <v>54</v>
       </c>
       <c r="K121" s="7"/>
       <c r="L121" s="7"/>
-      <c t="s" r="M121" s="7">
-        <v>50</v>
-      </c>
+      <c r="M121" s="7"/>
     </row>
     <row r="122" ht="14.25" customHeight="1">
-      <c t="s" r="A122" s="6">
-        <v>13</v>
-      </c>
-      <c r="B122" s="7">
-        <v>942</v>
-      </c>
-      <c t="s" r="C122" s="7">
-        <v>14</v>
-      </c>
+      <c r="A122" s="6"/>
+      <c r="B122" s="7"/>
+      <c r="C122" s="7"/>
       <c r="D122" s="7"/>
-      <c t="s" r="E122" s="7">
-        <v>217</v>
-      </c>
-      <c r="F122" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G122" s="8">
-        <v>31</v>
-      </c>
-      <c t="s" r="H122" s="8">
-        <v>220</v>
-      </c>
-      <c t="s" r="I122" s="7">
-        <v>221</v>
-      </c>
-      <c t="s" r="J122" s="7">
-        <v>123</v>
-      </c>
+      <c r="E122" s="7"/>
+      <c r="F122" s="7"/>
+      <c r="G122" s="8"/>
+      <c r="H122" s="8"/>
+      <c r="I122" s="7"/>
+      <c r="J122" s="7"/>
       <c r="K122" s="7"/>
       <c r="L122" s="7"/>
       <c r="M122" s="7"/>
@@ -5489,47 +5499,49 @@
         <v>13</v>
       </c>
       <c r="B123" s="7">
-        <v>943</v>
+        <v>933</v>
       </c>
       <c t="s" r="C123" s="7">
         <v>14</v>
       </c>
       <c r="D123" s="7"/>
       <c t="s" r="E123" s="7">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="F123" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G123" s="8">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c t="s" r="H123" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I123" s="7">
-        <v>222</v>
+        <v>45</v>
       </c>
       <c t="s" r="J123" s="7">
-        <v>157</v>
+        <v>225</v>
       </c>
       <c r="K123" s="7"/>
       <c r="L123" s="7"/>
-      <c r="M123" s="7"/>
+      <c t="s" r="M123" s="7">
+        <v>50</v>
+      </c>
     </row>
     <row r="124" ht="14.25" customHeight="1">
       <c t="s" r="A124" s="6">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="B124" s="7">
-        <v>920</v>
+        <v>942</v>
       </c>
       <c t="s" r="C124" s="7">
         <v>14</v>
       </c>
       <c r="D124" s="7"/>
       <c t="s" r="E124" s="7">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="F124" s="7">
         <v>321</v>
@@ -5538,116 +5550,112 @@
         <v>31</v>
       </c>
       <c t="s" r="H124" s="8">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c t="s" r="I124" s="7">
-        <v>169</v>
+        <v>227</v>
       </c>
       <c t="s" r="J124" s="7">
-        <v>208</v>
+        <v>123</v>
       </c>
       <c r="K124" s="7"/>
       <c r="L124" s="7"/>
       <c r="M124" s="7"/>
     </row>
     <row r="125" ht="15" customHeight="1">
-      <c r="A125" s="6"/>
-      <c r="B125" s="7"/>
-      <c r="C125" s="7"/>
+      <c t="s" r="A125" s="6">
+        <v>13</v>
+      </c>
+      <c r="B125" s="7">
+        <v>943</v>
+      </c>
+      <c t="s" r="C125" s="7">
+        <v>14</v>
+      </c>
       <c r="D125" s="7"/>
-      <c r="E125" s="7"/>
-      <c r="F125" s="7"/>
-      <c r="G125" s="8"/>
-      <c r="H125" s="8"/>
-      <c r="I125" s="7"/>
-      <c r="J125" s="7"/>
+      <c t="s" r="E125" s="7">
+        <v>223</v>
+      </c>
+      <c r="F125" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G125" s="8">
+        <v>226</v>
+      </c>
+      <c t="s" r="H125" s="8">
+        <v>31</v>
+      </c>
+      <c t="s" r="I125" s="7">
+        <v>228</v>
+      </c>
+      <c t="s" r="J125" s="7">
+        <v>158</v>
+      </c>
       <c r="K125" s="7"/>
       <c r="L125" s="7"/>
       <c r="M125" s="7"/>
     </row>
     <row r="126" ht="14.25" customHeight="1">
       <c t="s" r="A126" s="6">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="B126" s="7">
-        <v>625</v>
+        <v>920</v>
       </c>
       <c t="s" r="C126" s="7">
         <v>14</v>
       </c>
       <c r="D126" s="7"/>
       <c t="s" r="E126" s="7">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F126" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G126" s="8">
-        <v>89</v>
+        <v>31</v>
       </c>
       <c t="s" r="H126" s="8">
-        <v>41</v>
+        <v>229</v>
       </c>
       <c t="s" r="I126" s="7">
-        <v>225</v>
+        <v>170</v>
       </c>
       <c t="s" r="J126" s="7">
-        <v>69</v>
+        <v>213</v>
       </c>
       <c r="K126" s="7"/>
       <c r="L126" s="7"/>
-      <c t="s" r="M126" s="7">
-        <v>69</v>
-      </c>
+      <c r="M126" s="7"/>
     </row>
     <row r="127" ht="14.25" customHeight="1">
-      <c t="s" r="A127" s="6">
-        <v>13</v>
-      </c>
-      <c r="B127" s="7">
-        <v>630</v>
-      </c>
-      <c t="s" r="C127" s="7">
-        <v>14</v>
-      </c>
+      <c r="A127" s="6"/>
+      <c r="B127" s="7"/>
+      <c r="C127" s="7"/>
       <c r="D127" s="7"/>
-      <c t="s" r="E127" s="7">
-        <v>224</v>
-      </c>
-      <c r="F127" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G127" s="8">
-        <v>41</v>
-      </c>
-      <c t="s" r="H127" s="8">
-        <v>89</v>
-      </c>
-      <c t="s" r="I127" s="7">
-        <v>226</v>
-      </c>
-      <c t="s" r="J127" s="7">
-        <v>227</v>
-      </c>
+      <c r="E127" s="7"/>
+      <c r="F127" s="7"/>
+      <c r="G127" s="8"/>
+      <c r="H127" s="8"/>
+      <c r="I127" s="7"/>
+      <c r="J127" s="7"/>
       <c r="K127" s="7"/>
       <c r="L127" s="7"/>
-      <c t="s" r="M127" s="7">
-        <v>191</v>
-      </c>
+      <c r="M127" s="7"/>
     </row>
     <row r="128" ht="14.25" customHeight="1">
       <c t="s" r="A128" s="6">
         <v>13</v>
       </c>
       <c r="B128" s="7">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c t="s" r="C128" s="7">
         <v>14</v>
       </c>
       <c r="D128" s="7"/>
       <c t="s" r="E128" s="7">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="F128" s="7">
         <v>321</v>
@@ -5659,28 +5667,30 @@
         <v>41</v>
       </c>
       <c t="s" r="I128" s="7">
-        <v>115</v>
+        <v>231</v>
       </c>
       <c t="s" r="J128" s="7">
-        <v>166</v>
+        <v>69</v>
       </c>
       <c r="K128" s="7"/>
       <c r="L128" s="7"/>
-      <c r="M128" s="7"/>
+      <c t="s" r="M128" s="7">
+        <v>69</v>
+      </c>
     </row>
     <row r="129" ht="14.25" customHeight="1">
       <c t="s" r="A129" s="6">
         <v>13</v>
       </c>
       <c r="B129" s="7">
-        <v>636</v>
+        <v>630</v>
       </c>
       <c t="s" r="C129" s="7">
         <v>14</v>
       </c>
       <c r="D129" s="7"/>
       <c t="s" r="E129" s="7">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="F129" s="7">
         <v>321</v>
@@ -5692,28 +5702,30 @@
         <v>89</v>
       </c>
       <c t="s" r="I129" s="7">
-        <v>34</v>
+        <v>232</v>
       </c>
       <c t="s" r="J129" s="7">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="K129" s="7"/>
       <c r="L129" s="7"/>
-      <c r="M129" s="7"/>
+      <c t="s" r="M129" s="7">
+        <v>197</v>
+      </c>
     </row>
     <row r="130" ht="15" customHeight="1">
       <c t="s" r="A130" s="6">
         <v>13</v>
       </c>
       <c r="B130" s="7">
-        <v>633</v>
+        <v>629</v>
       </c>
       <c t="s" r="C130" s="7">
         <v>14</v>
       </c>
       <c r="D130" s="7"/>
       <c t="s" r="E130" s="7">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="F130" s="7">
         <v>321</v>
@@ -5725,26 +5737,44 @@
         <v>41</v>
       </c>
       <c t="s" r="I130" s="7">
-        <v>229</v>
+        <v>115</v>
       </c>
       <c t="s" r="J130" s="7">
-        <v>230</v>
+        <v>167</v>
       </c>
       <c r="K130" s="7"/>
       <c r="L130" s="7"/>
       <c r="M130" s="7"/>
     </row>
     <row r="131" ht="14.25" customHeight="1">
-      <c r="A131" s="6"/>
-      <c r="B131" s="7"/>
-      <c r="C131" s="7"/>
+      <c t="s" r="A131" s="6">
+        <v>13</v>
+      </c>
+      <c r="B131" s="7">
+        <v>636</v>
+      </c>
+      <c t="s" r="C131" s="7">
+        <v>14</v>
+      </c>
       <c r="D131" s="7"/>
-      <c r="E131" s="7"/>
-      <c r="F131" s="7"/>
-      <c r="G131" s="8"/>
-      <c r="H131" s="8"/>
-      <c r="I131" s="7"/>
-      <c r="J131" s="7"/>
+      <c t="s" r="E131" s="7">
+        <v>230</v>
+      </c>
+      <c r="F131" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G131" s="8">
+        <v>41</v>
+      </c>
+      <c t="s" r="H131" s="8">
+        <v>89</v>
+      </c>
+      <c t="s" r="I131" s="7">
+        <v>34</v>
+      </c>
+      <c t="s" r="J131" s="7">
+        <v>234</v>
+      </c>
       <c r="K131" s="7"/>
       <c r="L131" s="7"/>
       <c r="M131" s="7"/>
@@ -5754,65 +5784,45 @@
         <v>13</v>
       </c>
       <c r="B132" s="7">
-        <v>930</v>
+        <v>633</v>
       </c>
       <c t="s" r="C132" s="7">
         <v>14</v>
       </c>
       <c r="D132" s="7"/>
       <c t="s" r="E132" s="7">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F132" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G132" s="8">
-        <v>31</v>
+        <v>89</v>
       </c>
       <c t="s" r="H132" s="8">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c t="s" r="I132" s="7">
-        <v>170</v>
+        <v>235</v>
       </c>
       <c t="s" r="J132" s="7">
-        <v>119</v>
+        <v>236</v>
       </c>
       <c r="K132" s="7"/>
       <c r="L132" s="7"/>
-      <c t="s" r="M132" s="7">
-        <v>232</v>
-      </c>
+      <c r="M132" s="7"/>
     </row>
     <row r="133" ht="14.25" customHeight="1">
-      <c t="s" r="A133" s="6">
-        <v>13</v>
-      </c>
-      <c r="B133" s="7">
-        <v>931</v>
-      </c>
-      <c t="s" r="C133" s="7">
-        <v>14</v>
-      </c>
+      <c r="A133" s="6"/>
+      <c r="B133" s="7"/>
+      <c r="C133" s="7"/>
       <c r="D133" s="7"/>
-      <c t="s" r="E133" s="7">
-        <v>231</v>
-      </c>
-      <c r="F133" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G133" s="8">
-        <v>37</v>
-      </c>
-      <c t="s" r="H133" s="8">
-        <v>31</v>
-      </c>
-      <c t="s" r="I133" s="7">
-        <v>122</v>
-      </c>
-      <c t="s" r="J133" s="7">
-        <v>233</v>
-      </c>
+      <c r="E133" s="7"/>
+      <c r="F133" s="7"/>
+      <c r="G133" s="8"/>
+      <c r="H133" s="8"/>
+      <c r="I133" s="7"/>
+      <c r="J133" s="7"/>
       <c r="K133" s="7"/>
       <c r="L133" s="7"/>
       <c r="M133" s="7"/>
@@ -5822,14 +5832,14 @@
         <v>13</v>
       </c>
       <c r="B134" s="7">
-        <v>971</v>
+        <v>930</v>
       </c>
       <c t="s" r="C134" s="7">
         <v>14</v>
       </c>
       <c r="D134" s="7"/>
       <c t="s" r="E134" s="7">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="F134" s="7">
         <v>321</v>
@@ -5838,72 +5848,92 @@
         <v>31</v>
       </c>
       <c t="s" r="H134" s="8">
-        <v>234</v>
+        <v>37</v>
       </c>
       <c t="s" r="I134" s="7">
-        <v>53</v>
+        <v>171</v>
       </c>
       <c t="s" r="J134" s="7">
-        <v>235</v>
+        <v>119</v>
       </c>
       <c r="K134" s="7"/>
       <c r="L134" s="7"/>
-      <c r="M134" s="7"/>
+      <c t="s" r="M134" s="7">
+        <v>238</v>
+      </c>
     </row>
     <row r="135" ht="15" customHeight="1">
       <c t="s" r="A135" s="6">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="B135" s="7">
-        <v>972</v>
+        <v>931</v>
       </c>
       <c t="s" r="C135" s="7">
         <v>14</v>
       </c>
       <c r="D135" s="7"/>
       <c t="s" r="E135" s="7">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="F135" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G135" s="8">
-        <v>234</v>
+        <v>37</v>
       </c>
       <c t="s" r="H135" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I135" s="7">
-        <v>236</v>
+        <v>122</v>
       </c>
       <c t="s" r="J135" s="7">
-        <v>161</v>
+        <v>239</v>
       </c>
       <c r="K135" s="7"/>
       <c r="L135" s="7"/>
       <c r="M135" s="7"/>
     </row>
     <row r="136" ht="14.25" customHeight="1">
-      <c r="A136" s="6"/>
-      <c r="B136" s="7"/>
-      <c r="C136" s="7"/>
+      <c t="s" r="A136" s="6">
+        <v>13</v>
+      </c>
+      <c r="B136" s="7">
+        <v>971</v>
+      </c>
+      <c t="s" r="C136" s="7">
+        <v>14</v>
+      </c>
       <c r="D136" s="7"/>
-      <c r="E136" s="7"/>
-      <c r="F136" s="7"/>
-      <c r="G136" s="8"/>
-      <c r="H136" s="8"/>
-      <c r="I136" s="7"/>
-      <c r="J136" s="7"/>
+      <c t="s" r="E136" s="7">
+        <v>237</v>
+      </c>
+      <c r="F136" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G136" s="8">
+        <v>31</v>
+      </c>
+      <c t="s" r="H136" s="8">
+        <v>240</v>
+      </c>
+      <c t="s" r="I136" s="7">
+        <v>53</v>
+      </c>
+      <c t="s" r="J136" s="7">
+        <v>241</v>
+      </c>
       <c r="K136" s="7"/>
       <c r="L136" s="7"/>
       <c r="M136" s="7"/>
     </row>
     <row r="137" ht="14.25" customHeight="1">
       <c t="s" r="A137" s="6">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="B137" s="7">
-        <v>190</v>
+        <v>972</v>
       </c>
       <c t="s" r="C137" s="7">
         <v>14</v>
@@ -5916,52 +5946,32 @@
         <v>321</v>
       </c>
       <c t="s" r="G137" s="8">
-        <v>41</v>
+        <v>240</v>
       </c>
       <c t="s" r="H137" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I137" s="7">
-        <v>94</v>
+        <v>242</v>
       </c>
       <c t="s" r="J137" s="7">
-        <v>227</v>
+        <v>162</v>
       </c>
       <c r="K137" s="7"/>
       <c r="L137" s="7"/>
-      <c t="s" r="M137" s="7">
-        <v>238</v>
-      </c>
+      <c r="M137" s="7"/>
     </row>
     <row r="138" ht="14.25" customHeight="1">
-      <c t="s" r="A138" s="6">
-        <v>13</v>
-      </c>
-      <c r="B138" s="7">
-        <v>195</v>
-      </c>
-      <c t="s" r="C138" s="7">
-        <v>14</v>
-      </c>
+      <c r="A138" s="6"/>
+      <c r="B138" s="7"/>
+      <c r="C138" s="7"/>
       <c r="D138" s="7"/>
-      <c t="s" r="E138" s="7">
-        <v>237</v>
-      </c>
-      <c r="F138" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G138" s="8">
-        <v>31</v>
-      </c>
-      <c t="s" r="H138" s="8">
-        <v>41</v>
-      </c>
-      <c t="s" r="I138" s="7">
-        <v>129</v>
-      </c>
-      <c t="s" r="J138" s="7">
-        <v>19</v>
-      </c>
+      <c r="E138" s="7"/>
+      <c r="F138" s="7"/>
+      <c r="G138" s="8"/>
+      <c r="H138" s="8"/>
+      <c r="I138" s="7"/>
+      <c r="J138" s="7"/>
       <c r="K138" s="7"/>
       <c r="L138" s="7"/>
       <c r="M138" s="7"/>
@@ -5971,14 +5981,14 @@
         <v>13</v>
       </c>
       <c r="B139" s="7">
-        <v>1616</v>
+        <v>190</v>
       </c>
       <c t="s" r="C139" s="7">
         <v>14</v>
       </c>
       <c r="D139" s="7"/>
       <c t="s" r="E139" s="7">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="F139" s="7">
         <v>321</v>
@@ -5987,46 +5997,48 @@
         <v>41</v>
       </c>
       <c t="s" r="H139" s="8">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c t="s" r="I139" s="7">
-        <v>239</v>
+        <v>94</v>
       </c>
       <c t="s" r="J139" s="7">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="K139" s="7"/>
       <c r="L139" s="7"/>
-      <c r="M139" s="7"/>
+      <c t="s" r="M139" s="7">
+        <v>244</v>
+      </c>
     </row>
     <row r="140" ht="15" customHeight="1">
       <c t="s" r="A140" s="6">
         <v>13</v>
       </c>
       <c r="B140" s="7">
-        <v>7706</v>
+        <v>195</v>
       </c>
       <c t="s" r="C140" s="7">
-        <v>141</v>
+        <v>14</v>
       </c>
       <c r="D140" s="7"/>
       <c t="s" r="E140" s="7">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="F140" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G140" s="8">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c t="s" r="H140" s="8">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c t="s" r="I140" s="7">
-        <v>241</v>
+        <v>129</v>
       </c>
       <c t="s" r="J140" s="7">
-        <v>174</v>
+        <v>19</v>
       </c>
       <c r="K140" s="7"/>
       <c r="L140" s="7"/>
@@ -6034,116 +6046,114 @@
     </row>
     <row r="141" ht="14.25" customHeight="1">
       <c t="s" r="A141" s="6">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="B141" s="7">
-        <v>7706</v>
+        <v>1616</v>
       </c>
       <c t="s" r="C141" s="7">
-        <v>141</v>
+        <v>14</v>
       </c>
       <c r="D141" s="7"/>
       <c t="s" r="E141" s="7">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="F141" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G141" s="8">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c t="s" r="H141" s="8">
-        <v>242</v>
+        <v>17</v>
       </c>
       <c t="s" r="I141" s="7">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c t="s" r="J141" s="7">
-        <v>29</v>
+        <v>246</v>
       </c>
       <c r="K141" s="7"/>
       <c r="L141" s="7"/>
       <c r="M141" s="7"/>
     </row>
     <row r="142" ht="14.25" customHeight="1">
-      <c r="A142" s="6"/>
-      <c r="B142" s="7"/>
-      <c r="C142" s="7"/>
+      <c t="s" r="A142" s="6">
+        <v>13</v>
+      </c>
+      <c r="B142" s="7">
+        <v>7706</v>
+      </c>
+      <c t="s" r="C142" s="7">
+        <v>142</v>
+      </c>
       <c r="D142" s="7"/>
-      <c r="E142" s="7"/>
-      <c r="F142" s="7"/>
-      <c r="G142" s="8"/>
-      <c r="H142" s="8"/>
-      <c r="I142" s="7"/>
-      <c r="J142" s="7"/>
+      <c t="s" r="E142" s="7">
+        <v>243</v>
+      </c>
+      <c r="F142" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G142" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H142" s="8">
+        <v>31</v>
+      </c>
+      <c t="s" r="I142" s="7">
+        <v>247</v>
+      </c>
+      <c t="s" r="J142" s="7">
+        <v>248</v>
+      </c>
       <c r="K142" s="7"/>
       <c r="L142" s="7"/>
       <c r="M142" s="7"/>
     </row>
     <row r="143" ht="14.25" customHeight="1">
       <c t="s" r="A143" s="6">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="B143" s="7">
-        <v>921</v>
+        <v>7706</v>
       </c>
       <c t="s" r="C143" s="7">
-        <v>14</v>
+        <v>142</v>
       </c>
       <c r="D143" s="7"/>
       <c t="s" r="E143" s="7">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F143" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G143" s="8">
-        <v>223</v>
+        <v>31</v>
       </c>
       <c t="s" r="H143" s="8">
-        <v>31</v>
+        <v>249</v>
       </c>
       <c t="s" r="I143" s="7">
-        <v>140</v>
+        <v>250</v>
       </c>
       <c t="s" r="J143" s="7">
-        <v>192</v>
+        <v>29</v>
       </c>
       <c r="K143" s="7"/>
       <c r="L143" s="7"/>
-      <c t="s" r="M143" s="7">
-        <v>34</v>
-      </c>
+      <c r="M143" s="7"/>
     </row>
     <row r="144" ht="14.25" customHeight="1">
-      <c t="s" r="A144" s="6">
-        <v>13</v>
-      </c>
-      <c r="B144" s="7">
-        <v>946</v>
-      </c>
-      <c t="s" r="C144" s="7">
-        <v>14</v>
-      </c>
+      <c r="A144" s="6"/>
+      <c r="B144" s="7"/>
+      <c r="C144" s="7"/>
       <c r="D144" s="7"/>
-      <c t="s" r="E144" s="7">
-        <v>244</v>
-      </c>
-      <c r="F144" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G144" s="8">
-        <v>31</v>
-      </c>
-      <c t="s" r="H144" s="8">
-        <v>142</v>
-      </c>
-      <c t="s" r="I144" s="7">
-        <v>193</v>
-      </c>
-      <c t="s" r="J144" s="7">
-        <v>245</v>
-      </c>
+      <c r="E144" s="7"/>
+      <c r="F144" s="7"/>
+      <c r="G144" s="8"/>
+      <c r="H144" s="8"/>
+      <c r="I144" s="7"/>
+      <c r="J144" s="7"/>
       <c r="K144" s="7"/>
       <c r="L144" s="7"/>
       <c r="M144" s="7"/>
@@ -6153,47 +6163,49 @@
         <v>13</v>
       </c>
       <c r="B145" s="7">
-        <v>947</v>
+        <v>921</v>
       </c>
       <c t="s" r="C145" s="7">
         <v>14</v>
       </c>
       <c r="D145" s="7"/>
       <c t="s" r="E145" s="7">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="F145" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G145" s="8">
-        <v>142</v>
+        <v>229</v>
       </c>
       <c t="s" r="H145" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I145" s="7">
-        <v>246</v>
+        <v>141</v>
       </c>
       <c t="s" r="J145" s="7">
-        <v>247</v>
+        <v>199</v>
       </c>
       <c r="K145" s="7"/>
       <c r="L145" s="7"/>
-      <c r="M145" s="7"/>
+      <c t="s" r="M145" s="7">
+        <v>34</v>
+      </c>
     </row>
     <row r="146" ht="14.25" customHeight="1">
       <c t="s" r="A146" s="6">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="B146" s="7">
-        <v>932</v>
+        <v>946</v>
       </c>
       <c t="s" r="C146" s="7">
         <v>14</v>
       </c>
       <c r="D146" s="7"/>
       <c t="s" r="E146" s="7">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="F146" s="7">
         <v>321</v>
@@ -6202,97 +6214,95 @@
         <v>31</v>
       </c>
       <c t="s" r="H146" s="8">
-        <v>218</v>
+        <v>143</v>
       </c>
       <c t="s" r="I146" s="7">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c t="s" r="J146" s="7">
-        <v>208</v>
+        <v>179</v>
       </c>
       <c r="K146" s="7"/>
       <c r="L146" s="7"/>
       <c r="M146" s="7"/>
     </row>
     <row r="147" ht="14.25" customHeight="1">
-      <c r="A147" s="6"/>
-      <c r="B147" s="7"/>
-      <c r="C147" s="7"/>
+      <c t="s" r="A147" s="6">
+        <v>13</v>
+      </c>
+      <c r="B147" s="7">
+        <v>947</v>
+      </c>
+      <c t="s" r="C147" s="7">
+        <v>14</v>
+      </c>
       <c r="D147" s="7"/>
-      <c r="E147" s="7"/>
-      <c r="F147" s="7"/>
-      <c r="G147" s="8"/>
-      <c r="H147" s="8"/>
-      <c r="I147" s="7"/>
-      <c r="J147" s="7"/>
+      <c t="s" r="E147" s="7">
+        <v>251</v>
+      </c>
+      <c r="F147" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G147" s="8">
+        <v>143</v>
+      </c>
+      <c t="s" r="H147" s="8">
+        <v>31</v>
+      </c>
+      <c t="s" r="I147" s="7">
+        <v>252</v>
+      </c>
+      <c t="s" r="J147" s="7">
+        <v>253</v>
+      </c>
       <c r="K147" s="7"/>
       <c r="L147" s="7"/>
       <c r="M147" s="7"/>
     </row>
     <row r="148" ht="14.25" customHeight="1">
       <c t="s" r="A148" s="6">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="B148" s="7">
-        <v>855</v>
+        <v>932</v>
       </c>
       <c t="s" r="C148" s="7">
         <v>14</v>
       </c>
       <c r="D148" s="7"/>
       <c t="s" r="E148" s="7">
+        <v>251</v>
+      </c>
+      <c r="F148" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G148" s="8">
+        <v>31</v>
+      </c>
+      <c t="s" r="H148" s="8">
+        <v>224</v>
+      </c>
+      <c t="s" r="I148" s="7">
         <v>248</v>
       </c>
-      <c r="F148" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G148" s="8">
-        <v>41</v>
-      </c>
-      <c t="s" r="H148" s="8">
-        <v>32</v>
-      </c>
-      <c t="s" r="I148" s="7">
-        <v>249</v>
-      </c>
       <c t="s" r="J148" s="7">
-        <v>250</v>
+        <v>213</v>
       </c>
       <c r="K148" s="7"/>
       <c r="L148" s="7"/>
-      <c t="s" r="M148" s="7">
-        <v>251</v>
-      </c>
+      <c r="M148" s="7"/>
     </row>
     <row r="149" ht="14.25" customHeight="1">
-      <c t="s" r="A149" s="6">
-        <v>13</v>
-      </c>
-      <c r="B149" s="7">
-        <v>854</v>
-      </c>
-      <c t="s" r="C149" s="7">
-        <v>14</v>
-      </c>
+      <c r="A149" s="6"/>
+      <c r="B149" s="7"/>
+      <c r="C149" s="7"/>
       <c r="D149" s="7"/>
-      <c t="s" r="E149" s="7">
-        <v>248</v>
-      </c>
-      <c r="F149" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G149" s="8">
-        <v>32</v>
-      </c>
-      <c t="s" r="H149" s="8">
-        <v>41</v>
-      </c>
-      <c t="s" r="I149" s="7">
-        <v>167</v>
-      </c>
-      <c t="s" r="J149" s="7">
-        <v>64</v>
-      </c>
+      <c r="E149" s="7"/>
+      <c r="F149" s="7"/>
+      <c r="G149" s="8"/>
+      <c r="H149" s="8"/>
+      <c r="I149" s="7"/>
+      <c r="J149" s="7"/>
       <c r="K149" s="7"/>
       <c r="L149" s="7"/>
       <c r="M149" s="7"/>
@@ -6302,14 +6312,14 @@
         <v>13</v>
       </c>
       <c r="B150" s="7">
-        <v>216</v>
+        <v>855</v>
       </c>
       <c t="s" r="C150" s="7">
         <v>14</v>
       </c>
       <c r="D150" s="7"/>
       <c t="s" r="E150" s="7">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="F150" s="7">
         <v>321</v>
@@ -6318,46 +6328,48 @@
         <v>41</v>
       </c>
       <c t="s" r="H150" s="8">
-        <v>176</v>
+        <v>32</v>
       </c>
       <c t="s" r="I150" s="7">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c t="s" r="J150" s="7">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="K150" s="7"/>
       <c r="L150" s="7"/>
-      <c r="M150" s="7"/>
+      <c t="s" r="M150" s="7">
+        <v>257</v>
+      </c>
     </row>
     <row r="151" ht="14.25" customHeight="1">
       <c t="s" r="A151" s="6">
         <v>13</v>
       </c>
       <c r="B151" s="7">
-        <v>217</v>
+        <v>854</v>
       </c>
       <c t="s" r="C151" s="7">
         <v>14</v>
       </c>
       <c r="D151" s="7"/>
       <c t="s" r="E151" s="7">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="F151" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G151" s="8">
-        <v>176</v>
+        <v>32</v>
       </c>
       <c t="s" r="H151" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I151" s="7">
-        <v>239</v>
+        <v>168</v>
       </c>
       <c t="s" r="J151" s="7">
-        <v>254</v>
+        <v>64</v>
       </c>
       <c r="K151" s="7"/>
       <c r="L151" s="7"/>
@@ -6365,17 +6377,17 @@
     </row>
     <row r="152" ht="14.25" customHeight="1">
       <c t="s" r="A152" s="6">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="B152" s="7">
-        <v>862</v>
+        <v>216</v>
       </c>
       <c t="s" r="C152" s="7">
         <v>14</v>
       </c>
       <c r="D152" s="7"/>
       <c t="s" r="E152" s="7">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="F152" s="7">
         <v>321</v>
@@ -6384,46 +6396,64 @@
         <v>41</v>
       </c>
       <c t="s" r="H152" s="8">
-        <v>137</v>
+        <v>182</v>
       </c>
       <c t="s" r="I152" s="7">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c t="s" r="J152" s="7">
-        <v>139</v>
+        <v>259</v>
       </c>
       <c r="K152" s="7"/>
       <c r="L152" s="7"/>
       <c r="M152" s="7"/>
     </row>
     <row r="153" ht="14.25" customHeight="1">
-      <c r="A153" s="6"/>
-      <c r="B153" s="7"/>
-      <c r="C153" s="7"/>
+      <c t="s" r="A153" s="6">
+        <v>13</v>
+      </c>
+      <c r="B153" s="7">
+        <v>217</v>
+      </c>
+      <c t="s" r="C153" s="7">
+        <v>14</v>
+      </c>
       <c r="D153" s="7"/>
-      <c r="E153" s="7"/>
-      <c r="F153" s="7"/>
-      <c r="G153" s="8"/>
-      <c r="H153" s="8"/>
-      <c r="I153" s="7"/>
-      <c r="J153" s="7"/>
+      <c t="s" r="E153" s="7">
+        <v>254</v>
+      </c>
+      <c r="F153" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G153" s="8">
+        <v>182</v>
+      </c>
+      <c t="s" r="H153" s="8">
+        <v>41</v>
+      </c>
+      <c t="s" r="I153" s="7">
+        <v>245</v>
+      </c>
+      <c t="s" r="J153" s="7">
+        <v>260</v>
+      </c>
       <c r="K153" s="7"/>
       <c r="L153" s="7"/>
       <c r="M153" s="7"/>
     </row>
     <row r="154" ht="14.25" customHeight="1">
       <c t="s" r="A154" s="6">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="B154" s="7">
-        <v>212</v>
+        <v>862</v>
       </c>
       <c t="s" r="C154" s="7">
         <v>14</v>
       </c>
       <c r="D154" s="7"/>
       <c t="s" r="E154" s="7">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="F154" s="7">
         <v>321</v>
@@ -6432,68 +6462,46 @@
         <v>41</v>
       </c>
       <c t="s" r="H154" s="8">
-        <v>176</v>
+        <v>138</v>
       </c>
       <c t="s" r="I154" s="7">
-        <v>170</v>
+        <v>261</v>
       </c>
       <c t="s" r="J154" s="7">
-        <v>29</v>
+        <v>140</v>
       </c>
       <c r="K154" s="7"/>
       <c r="L154" s="7"/>
-      <c t="s" r="M154" s="7">
-        <v>257</v>
-      </c>
+      <c r="M154" s="7"/>
     </row>
     <row r="155" ht="15" customHeight="1">
-      <c t="s" r="A155" s="6">
-        <v>13</v>
-      </c>
-      <c r="B155" s="7">
-        <v>215</v>
-      </c>
-      <c t="s" r="C155" s="7">
-        <v>14</v>
-      </c>
+      <c r="A155" s="6"/>
+      <c r="B155" s="7"/>
+      <c r="C155" s="7"/>
       <c r="D155" s="7"/>
-      <c t="s" r="E155" s="7">
-        <v>256</v>
-      </c>
-      <c r="F155" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G155" s="8">
-        <v>176</v>
-      </c>
-      <c t="s" r="H155" s="8">
-        <v>41</v>
-      </c>
-      <c t="s" r="I155" s="7">
-        <v>128</v>
-      </c>
-      <c t="s" r="J155" s="7">
-        <v>63</v>
-      </c>
+      <c r="E155" s="7"/>
+      <c r="F155" s="7"/>
+      <c r="G155" s="8"/>
+      <c r="H155" s="8"/>
+      <c r="I155" s="7"/>
+      <c r="J155" s="7"/>
       <c r="K155" s="7"/>
       <c r="L155" s="7"/>
-      <c t="s" r="M155" s="7">
-        <v>258</v>
-      </c>
+      <c r="M155" s="7"/>
     </row>
     <row r="156" ht="14.25" customHeight="1">
       <c t="s" r="A156" s="6">
         <v>13</v>
       </c>
       <c r="B156" s="7">
-        <v>600</v>
+        <v>212</v>
       </c>
       <c t="s" r="C156" s="7">
         <v>14</v>
       </c>
       <c r="D156" s="7"/>
       <c t="s" r="E156" s="7">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="F156" s="7">
         <v>321</v>
@@ -6502,64 +6510,68 @@
         <v>41</v>
       </c>
       <c t="s" r="H156" s="8">
-        <v>17</v>
+        <v>182</v>
       </c>
       <c t="s" r="I156" s="7">
-        <v>193</v>
+        <v>171</v>
       </c>
       <c t="s" r="J156" s="7">
-        <v>259</v>
+        <v>29</v>
       </c>
       <c r="K156" s="7"/>
       <c r="L156" s="7"/>
-      <c r="M156" s="7"/>
+      <c t="s" r="M156" s="7">
+        <v>263</v>
+      </c>
     </row>
     <row r="157" ht="14.25" customHeight="1">
       <c t="s" r="A157" s="6">
         <v>13</v>
       </c>
       <c r="B157" s="7">
-        <v>601</v>
+        <v>215</v>
       </c>
       <c t="s" r="C157" s="7">
         <v>14</v>
       </c>
       <c r="D157" s="7"/>
       <c t="s" r="E157" s="7">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="F157" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G157" s="8">
-        <v>17</v>
+        <v>182</v>
       </c>
       <c t="s" r="H157" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I157" s="7">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c t="s" r="J157" s="7">
-        <v>194</v>
+        <v>63</v>
       </c>
       <c r="K157" s="7"/>
       <c r="L157" s="7"/>
-      <c r="M157" s="7"/>
+      <c t="s" r="M157" s="7">
+        <v>130</v>
+      </c>
     </row>
     <row r="158" ht="14.25" customHeight="1">
       <c t="s" r="A158" s="6">
         <v>13</v>
       </c>
       <c r="B158" s="7">
-        <v>262</v>
+        <v>860</v>
       </c>
       <c t="s" r="C158" s="7">
         <v>14</v>
       </c>
       <c r="D158" s="7"/>
       <c t="s" r="E158" s="7">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="F158" s="7">
         <v>321</v>
@@ -6568,10 +6580,10 @@
         <v>41</v>
       </c>
       <c t="s" r="H158" s="8">
-        <v>260</v>
+        <v>138</v>
       </c>
       <c t="s" r="I158" s="7">
-        <v>245</v>
+        <v>79</v>
       </c>
       <c t="s" r="J158" s="7">
         <v>66</v>
@@ -6585,29 +6597,29 @@
         <v>13</v>
       </c>
       <c r="B159" s="7">
-        <v>263</v>
+        <v>861</v>
       </c>
       <c t="s" r="C159" s="7">
         <v>14</v>
       </c>
       <c r="D159" s="7"/>
       <c t="s" r="E159" s="7">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="F159" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G159" s="8">
-        <v>260</v>
+        <v>138</v>
       </c>
       <c t="s" r="H159" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I159" s="7">
-        <v>261</v>
+        <v>134</v>
       </c>
       <c t="s" r="J159" s="7">
-        <v>25</v>
+        <v>248</v>
       </c>
       <c r="K159" s="7"/>
       <c r="L159" s="7"/>
@@ -6640,22 +6652,22 @@
       </c>
       <c r="D161" s="7"/>
       <c t="s" r="E161" s="7">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="F161" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G161" s="8">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c t="s" r="H161" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I161" s="7">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c t="s" r="J161" s="7">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="K161" s="7"/>
       <c r="L161" s="7"/>
@@ -6671,11 +6683,11 @@
         <v>5068</v>
       </c>
       <c t="s" r="C162" s="7">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D162" s="7"/>
       <c t="s" r="E162" s="7">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="F162" s="7">
         <v>321</v>
@@ -6687,10 +6699,10 @@
         <v>31</v>
       </c>
       <c t="s" r="I162" s="7">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c t="s" r="J162" s="7">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="K162" s="7"/>
       <c r="L162" s="7"/>
@@ -6704,11 +6716,11 @@
         <v>5068</v>
       </c>
       <c t="s" r="C163" s="7">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D163" s="7"/>
       <c t="s" r="E163" s="7">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="F163" s="7">
         <v>321</v>
@@ -6717,13 +6729,13 @@
         <v>31</v>
       </c>
       <c t="s" r="H163" s="8">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c t="s" r="I163" s="7">
         <v>124</v>
       </c>
       <c t="s" r="J163" s="7">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c t="s" r="K163" s="7">
         <v>84</v>
@@ -6741,26 +6753,26 @@
         <v>5069</v>
       </c>
       <c t="s" r="C164" s="7">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D164" s="7"/>
       <c t="s" r="E164" s="7">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="F164" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G164" s="8">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c t="s" r="H164" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I164" s="7">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c t="s" r="J164" s="7">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="K164" s="7"/>
       <c r="L164" s="7"/>
@@ -6793,27 +6805,27 @@
       </c>
       <c r="D166" s="7"/>
       <c t="s" r="E166" s="7">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="F166" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G166" s="8">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c t="s" r="H166" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I166" s="7">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c t="s" r="J166" s="7">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="K166" s="7"/>
       <c r="L166" s="7"/>
       <c t="s" r="M166" s="7">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="167" ht="14.25" customHeight="1">
@@ -6828,7 +6840,7 @@
       </c>
       <c r="D167" s="7"/>
       <c t="s" r="E167" s="7">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="F167" s="7">
         <v>321</v>
@@ -6837,13 +6849,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H167" s="8">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c t="s" r="I167" s="7">
         <v>75</v>
       </c>
       <c t="s" r="J167" s="7">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="K167" s="7"/>
       <c r="L167" s="7"/>
@@ -6876,7 +6888,7 @@
       </c>
       <c r="D169" s="7"/>
       <c t="s" r="E169" s="7">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="F169" s="7">
         <v>321</v>
@@ -6885,7 +6897,7 @@
         <v>31</v>
       </c>
       <c t="s" r="H169" s="8">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c t="s" r="I169" s="7">
         <v>60</v>
@@ -6909,13 +6921,13 @@
       </c>
       <c r="D170" s="7"/>
       <c t="s" r="E170" s="7">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="F170" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G170" s="8">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c t="s" r="H170" s="8">
         <v>31</v>
@@ -6924,7 +6936,7 @@
         <v>35</v>
       </c>
       <c t="s" r="J170" s="7">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="K170" s="7"/>
       <c r="L170" s="7"/>
@@ -6942,7 +6954,7 @@
       </c>
       <c r="D171" s="7"/>
       <c t="s" r="E171" s="7">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="F171" s="7">
         <v>321</v>
@@ -6957,7 +6969,7 @@
         <v>124</v>
       </c>
       <c t="s" r="J171" s="7">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="K171" s="7"/>
       <c r="L171" s="7"/>
@@ -6975,7 +6987,7 @@
       </c>
       <c r="D172" s="7"/>
       <c t="s" r="E172" s="7">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="F172" s="7">
         <v>321</v>
@@ -6990,7 +7002,7 @@
         <v>53</v>
       </c>
       <c t="s" r="J172" s="7">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="K172" s="7"/>
       <c r="L172" s="7"/>
@@ -7023,7 +7035,7 @@
       </c>
       <c r="D174" s="7"/>
       <c t="s" r="E174" s="7">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="F174" s="7">
         <v>321</v>
@@ -7035,7 +7047,7 @@
         <v>89</v>
       </c>
       <c t="s" r="I174" s="7">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c t="s" r="J174" s="7">
         <v>97</v>
@@ -7043,7 +7055,7 @@
       <c r="K174" s="7"/>
       <c r="L174" s="7"/>
       <c t="s" r="M174" s="7">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="175" ht="15" customHeight="1">
@@ -7058,7 +7070,7 @@
       </c>
       <c r="D175" s="7"/>
       <c t="s" r="E175" s="7">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="F175" s="7">
         <v>321</v>
@@ -7073,7 +7085,7 @@
         <v>78</v>
       </c>
       <c t="s" r="J175" s="7">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="K175" s="7"/>
       <c r="L175" s="7"/>
@@ -7093,7 +7105,7 @@
       </c>
       <c r="D176" s="7"/>
       <c t="s" r="E176" s="7">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="F176" s="7">
         <v>321</v>
@@ -7105,7 +7117,7 @@
         <v>89</v>
       </c>
       <c t="s" r="I176" s="7">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c t="s" r="J176" s="7">
         <v>80</v>
@@ -7130,7 +7142,7 @@
       </c>
       <c r="D177" s="7"/>
       <c t="s" r="E177" s="7">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="F177" s="7">
         <v>321</v>
@@ -7145,14 +7157,14 @@
         <v>50</v>
       </c>
       <c t="s" r="J177" s="7">
-        <v>193</v>
+        <v>175</v>
       </c>
       <c t="s" r="K177" s="7">
         <v>19</v>
       </c>
       <c r="L177" s="7"/>
       <c t="s" r="M177" s="7">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="178" ht="14.25" customHeight="1">
@@ -7167,7 +7179,7 @@
       </c>
       <c r="D178" s="7"/>
       <c t="s" r="E178" s="7">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="F178" s="7">
         <v>321</v>
@@ -7176,13 +7188,13 @@
         <v>31</v>
       </c>
       <c t="s" r="H178" s="8">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c t="s" r="I178" s="7">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c t="s" r="J178" s="7">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="K178" s="7"/>
       <c r="L178" s="7"/>
@@ -7200,22 +7212,22 @@
       </c>
       <c r="D179" s="7"/>
       <c t="s" r="E179" s="7">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="F179" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G179" s="8">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c t="s" r="H179" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I179" s="7">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c t="s" r="J179" s="7">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="K179" s="7"/>
       <c r="L179" s="7"/>
@@ -7233,7 +7245,7 @@
       </c>
       <c r="D180" s="7"/>
       <c t="s" r="E180" s="7">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="F180" s="7">
         <v>321</v>
@@ -7242,13 +7254,13 @@
         <v>31</v>
       </c>
       <c t="s" r="H180" s="8">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c t="s" r="I180" s="7">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c t="s" r="J180" s="7">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="K180" s="7"/>
       <c r="L180" s="7"/>
@@ -7266,22 +7278,22 @@
       </c>
       <c r="D181" s="7"/>
       <c t="s" r="E181" s="7">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="F181" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G181" s="8">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c t="s" r="H181" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I181" s="7">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c t="s" r="J181" s="7">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="K181" s="7"/>
       <c r="L181" s="7"/>
@@ -7314,7 +7326,7 @@
       </c>
       <c r="D183" s="7"/>
       <c t="s" r="E183" s="7">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="F183" s="7">
         <v>321</v>
@@ -7323,18 +7335,18 @@
         <v>41</v>
       </c>
       <c t="s" r="H183" s="8">
-        <v>260</v>
+        <v>178</v>
       </c>
       <c t="s" r="I183" s="7">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c t="s" r="J183" s="7">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K183" s="7"/>
       <c r="L183" s="7"/>
       <c t="s" r="M183" s="7">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="184" ht="14.25" customHeight="1">
@@ -7349,13 +7361,13 @@
       </c>
       <c r="D184" s="7"/>
       <c t="s" r="E184" s="7">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="F184" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G184" s="8">
-        <v>260</v>
+        <v>178</v>
       </c>
       <c t="s" r="H184" s="8">
         <v>41</v>
@@ -7364,12 +7376,12 @@
         <v>33</v>
       </c>
       <c t="s" r="J184" s="7">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="K184" s="7"/>
       <c r="L184" s="7"/>
       <c t="s" r="M184" s="7">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="185" ht="15" customHeight="1">
@@ -7384,7 +7396,7 @@
       </c>
       <c r="D185" s="7"/>
       <c t="s" r="E185" s="7">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="F185" s="7">
         <v>321</v>
@@ -7396,7 +7408,7 @@
         <v>58</v>
       </c>
       <c t="s" r="I185" s="7">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c t="s" r="J185" s="7">
         <v>79</v>
@@ -7417,7 +7429,7 @@
       </c>
       <c r="D186" s="7"/>
       <c t="s" r="E186" s="7">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="F186" s="7">
         <v>321</v>
@@ -7432,7 +7444,7 @@
         <v>34</v>
       </c>
       <c t="s" r="J186" s="7">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="K186" s="7"/>
       <c r="L186" s="7"/>
@@ -7450,7 +7462,7 @@
       </c>
       <c r="D187" s="7"/>
       <c t="s" r="E187" s="7">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="F187" s="7">
         <v>321</v>
@@ -7459,13 +7471,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H187" s="8">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c t="s" r="I187" s="7">
         <v>51</v>
       </c>
       <c t="s" r="J187" s="7">
-        <v>194</v>
+        <v>177</v>
       </c>
       <c r="K187" s="7"/>
       <c r="L187" s="7"/>
@@ -7483,13 +7495,13 @@
       </c>
       <c r="D188" s="7"/>
       <c t="s" r="E188" s="7">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="F188" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G188" s="8">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c t="s" r="H188" s="8">
         <v>41</v>
@@ -7516,7 +7528,7 @@
       </c>
       <c r="D189" s="7"/>
       <c t="s" r="E189" s="7">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="F189" s="7">
         <v>321</v>
@@ -7525,13 +7537,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H189" s="8">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c t="s" r="I189" s="7">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c t="s" r="J189" s="7">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="K189" s="7"/>
       <c r="L189" s="7"/>
@@ -7549,22 +7561,22 @@
       </c>
       <c r="D190" s="7"/>
       <c t="s" r="E190" s="7">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="F190" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G190" s="8">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c t="s" r="H190" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I190" s="7">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c t="s" r="J190" s="7">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="K190" s="7"/>
       <c r="L190" s="7"/>
@@ -7597,7 +7609,7 @@
       </c>
       <c r="D192" s="7"/>
       <c t="s" r="E192" s="7">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="F192" s="7">
         <v>321</v>
@@ -7606,10 +7618,10 @@
         <v>89</v>
       </c>
       <c t="s" r="H192" s="8">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c t="s" r="I192" s="7">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c t="s" r="J192" s="7">
         <v>109</v>
@@ -7630,19 +7642,19 @@
       </c>
       <c r="D193" s="7"/>
       <c t="s" r="E193" s="7">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="F193" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G193" s="8">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c t="s" r="H193" s="8">
         <v>89</v>
       </c>
       <c t="s" r="I193" s="7">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c t="s" r="J193" s="7">
         <v>102</v>
@@ -7663,7 +7675,7 @@
       </c>
       <c r="D194" s="7"/>
       <c t="s" r="E194" s="7">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="F194" s="7">
         <v>321</v>
@@ -7672,13 +7684,13 @@
         <v>89</v>
       </c>
       <c t="s" r="H194" s="8">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c t="s" r="I194" s="7">
         <v>36</v>
       </c>
       <c t="s" r="J194" s="7">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="K194" s="7"/>
       <c r="L194" s="7"/>
@@ -7696,22 +7708,22 @@
       </c>
       <c r="D195" s="7"/>
       <c t="s" r="E195" s="7">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="F195" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G195" s="8">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c t="s" r="H195" s="8">
         <v>89</v>
       </c>
       <c t="s" r="I195" s="7">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c t="s" r="J195" s="7">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="K195" s="7"/>
       <c r="L195" s="7"/>
@@ -7744,7 +7756,7 @@
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
@@ -7756,7 +7768,7 @@
         <v>127</v>
       </c>
       <c t="s" r="I197" s="7">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c t="s" r="J197" s="7">
         <v>97</v>
@@ -7764,7 +7776,7 @@
       <c r="K197" s="7"/>
       <c r="L197" s="7"/>
       <c t="s" r="M197" s="7">
-        <v>184</v>
+        <v>190</v>
       </c>
     </row>
     <row r="198" ht="14.25" customHeight="1">
@@ -7779,7 +7791,7 @@
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="F198" s="7">
         <v>321</v>
@@ -7788,7 +7800,7 @@
         <v>127</v>
       </c>
       <c t="s" r="H198" s="8">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c t="s" r="I198" s="7">
         <v>78</v>
@@ -7799,7 +7811,7 @@
       <c r="K198" s="7"/>
       <c r="L198" s="7"/>
       <c t="s" r="M198" s="7">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="199" ht="14.25" customHeight="1">
@@ -7814,25 +7826,25 @@
       </c>
       <c r="D199" s="7"/>
       <c t="s" r="E199" s="7">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="F199" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G199" s="8">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c t="s" r="H199" s="8">
         <v>127</v>
       </c>
       <c t="s" r="I199" s="7">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c t="s" r="J199" s="7">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c t="s" r="K199" s="7">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="L199" s="7"/>
       <c t="s" r="M199" s="7">
@@ -7851,7 +7863,7 @@
       </c>
       <c r="D200" s="7"/>
       <c t="s" r="E200" s="7">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="F200" s="7">
         <v>321</v>
@@ -7866,14 +7878,14 @@
         <v>19</v>
       </c>
       <c t="s" r="J200" s="7">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c t="s" r="K200" s="7">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L200" s="7"/>
       <c t="s" r="M200" s="7">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="201" ht="14.25" customHeight="1">
@@ -7888,7 +7900,7 @@
       </c>
       <c r="D201" s="7"/>
       <c t="s" r="E201" s="7">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="F201" s="7">
         <v>321</v>
@@ -7900,10 +7912,10 @@
         <v>58</v>
       </c>
       <c t="s" r="I201" s="7">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c t="s" r="J201" s="7">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="K201" s="7"/>
       <c r="L201" s="7"/>
@@ -7921,7 +7933,7 @@
       </c>
       <c r="D202" s="7"/>
       <c t="s" r="E202" s="7">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="F202" s="7">
         <v>321</v>
@@ -7936,7 +7948,7 @@
         <v>104</v>
       </c>
       <c t="s" r="J202" s="7">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="K202" s="7"/>
       <c r="L202" s="7"/>
@@ -7969,7 +7981,7 @@
       </c>
       <c r="D204" s="7"/>
       <c t="s" r="E204" s="7">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="F204" s="7">
         <v>321</v>
@@ -7981,15 +7993,15 @@
         <v>31</v>
       </c>
       <c t="s" r="I204" s="7">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c t="s" r="J204" s="7">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="K204" s="7"/>
       <c r="L204" s="7"/>
       <c t="s" r="M204" s="7">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="205" ht="15" customHeight="1">
@@ -8004,7 +8016,7 @@
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
@@ -8019,7 +8031,7 @@
         <v>63</v>
       </c>
       <c t="s" r="J205" s="7">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="K205" s="7"/>
       <c r="L205" s="7"/>
@@ -8037,7 +8049,7 @@
       </c>
       <c r="D206" s="7"/>
       <c t="s" r="E206" s="7">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="F206" s="7">
         <v>321</v>
@@ -8049,10 +8061,10 @@
         <v>31</v>
       </c>
       <c t="s" r="I206" s="7">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c t="s" r="J206" s="7">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="K206" s="7"/>
       <c r="L206" s="7"/>
@@ -8070,7 +8082,7 @@
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="F207" s="7">
         <v>321</v>
@@ -8082,10 +8094,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I207" s="7">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c t="s" r="J207" s="7">
-        <v>245</v>
+        <v>179</v>
       </c>
       <c r="K207" s="7"/>
       <c r="L207" s="7"/>
@@ -8103,7 +8115,7 @@
       </c>
       <c r="D208" s="7"/>
       <c t="s" r="E208" s="7">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="F208" s="7">
         <v>321</v>
@@ -8115,10 +8127,10 @@
         <v>31</v>
       </c>
       <c t="s" r="I208" s="7">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c t="s" r="J208" s="7">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="K208" s="7"/>
       <c r="L208" s="7"/>
@@ -8136,7 +8148,7 @@
       </c>
       <c r="D209" s="7"/>
       <c t="s" r="E209" s="7">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="F209" s="7">
         <v>321</v>
@@ -8148,10 +8160,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I209" s="7">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c t="s" r="J209" s="7">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="K209" s="7"/>
       <c r="L209" s="7"/>
@@ -8184,7 +8196,7 @@
       </c>
       <c r="D211" s="7"/>
       <c t="s" r="E211" s="7">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="F211" s="7">
         <v>321</v>
@@ -8196,17 +8208,17 @@
         <v>127</v>
       </c>
       <c t="s" r="I211" s="7">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c t="s" r="J211" s="7">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c t="s" r="K211" s="7">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="L211" s="7"/>
       <c t="s" r="M211" s="7">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="212" ht="14.25" customHeight="1">
@@ -8221,7 +8233,7 @@
       </c>
       <c r="D212" s="7"/>
       <c t="s" r="E212" s="7">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="F212" s="7">
         <v>321</v>
@@ -8233,7 +8245,7 @@
         <v>41</v>
       </c>
       <c t="s" r="I212" s="7">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c t="s" r="J212" s="7">
         <v>69</v>
@@ -8243,7 +8255,7 @@
       </c>
       <c r="L212" s="7"/>
       <c t="s" r="M212" s="7">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="213" ht="14.25" customHeight="1">
@@ -8258,7 +8270,7 @@
       </c>
       <c r="D213" s="7"/>
       <c t="s" r="E213" s="7">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="F213" s="7">
         <v>321</v>
@@ -8267,17 +8279,19 @@
         <v>41</v>
       </c>
       <c t="s" r="H213" s="8">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c t="s" r="I213" s="7">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c t="s" r="J213" s="7">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="K213" s="7"/>
       <c r="L213" s="7"/>
-      <c r="M213" s="7"/>
+      <c t="s" r="M213" s="7">
+        <v>19</v>
+      </c>
     </row>
     <row r="214" ht="14.25" customHeight="1">
       <c t="s" r="A214" s="6">
@@ -8291,13 +8305,13 @@
       </c>
       <c r="D214" s="7"/>
       <c t="s" r="E214" s="7">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="F214" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G214" s="8">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c t="s" r="H214" s="8">
         <v>41</v>
@@ -8324,7 +8338,7 @@
       </c>
       <c r="D215" s="7"/>
       <c t="s" r="E215" s="7">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="F215" s="7">
         <v>321</v>
@@ -8336,7 +8350,7 @@
         <v>31</v>
       </c>
       <c t="s" r="I215" s="7">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c t="s" r="J215" s="7">
         <v>65</v>
@@ -8357,7 +8371,7 @@
       </c>
       <c r="D216" s="7"/>
       <c t="s" r="E216" s="7">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="F216" s="7">
         <v>321</v>
@@ -8369,10 +8383,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I216" s="7">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c t="s" r="J216" s="7">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="K216" s="7"/>
       <c r="L216" s="7"/>
@@ -8405,27 +8419,27 @@
       </c>
       <c r="D218" s="7"/>
       <c t="s" r="E218" s="7">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="F218" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G218" s="8">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c t="s" r="H218" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I218" s="7">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c t="s" r="J218" s="7">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="K218" s="7"/>
       <c r="L218" s="7"/>
       <c t="s" r="M218" s="7">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="219" ht="14.25" customHeight="1">
@@ -8440,7 +8454,7 @@
       </c>
       <c r="D219" s="7"/>
       <c t="s" r="E219" s="7">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="F219" s="7">
         <v>321</v>
@@ -8455,7 +8469,7 @@
         <v>34</v>
       </c>
       <c t="s" r="J219" s="7">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="K219" s="7"/>
       <c r="L219" s="7"/>
@@ -8473,7 +8487,7 @@
       </c>
       <c r="D220" s="7"/>
       <c t="s" r="E220" s="7">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="F220" s="7">
         <v>321</v>
@@ -8506,7 +8520,7 @@
       </c>
       <c r="D221" s="7"/>
       <c t="s" r="E221" s="7">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="F221" s="7">
         <v>321</v>
@@ -8518,10 +8532,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I221" s="7">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c t="s" r="J221" s="7">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="K221" s="7"/>
       <c r="L221" s="7"/>
@@ -8539,7 +8553,7 @@
       </c>
       <c r="D222" s="7"/>
       <c t="s" r="E222" s="7">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="F222" s="7">
         <v>321</v>
@@ -8551,10 +8565,10 @@
         <v>31</v>
       </c>
       <c t="s" r="I222" s="7">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c t="s" r="J222" s="7">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="K222" s="7"/>
       <c r="L222" s="7"/>
@@ -8572,7 +8586,7 @@
       </c>
       <c r="D223" s="7"/>
       <c t="s" r="E223" s="7">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="F223" s="7">
         <v>321</v>
@@ -8584,10 +8598,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I223" s="7">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c t="s" r="J223" s="7">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="K223" s="7"/>
       <c r="L223" s="7"/>
@@ -8620,7 +8634,7 @@
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
@@ -8629,18 +8643,18 @@
         <v>41</v>
       </c>
       <c t="s" r="H225" s="8">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c t="s" r="I225" s="7">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c t="s" r="J225" s="7">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="K225" s="7"/>
       <c r="L225" s="7"/>
       <c t="s" r="M225" s="7">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="226" ht="14.25" customHeight="1">
@@ -8655,27 +8669,27 @@
       </c>
       <c r="D226" s="7"/>
       <c t="s" r="E226" s="7">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="F226" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G226" s="8">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c t="s" r="H226" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I226" s="7">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c t="s" r="J226" s="7">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="K226" s="7"/>
       <c r="L226" s="7"/>
       <c t="s" r="M226" s="7">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="227" ht="14.25" customHeight="1">
@@ -8690,7 +8704,7 @@
       </c>
       <c r="D227" s="7"/>
       <c t="s" r="E227" s="7">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="F227" s="7">
         <v>321</v>
@@ -8699,18 +8713,18 @@
         <v>41</v>
       </c>
       <c t="s" r="H227" s="8">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c t="s" r="I227" s="7">
         <v>100</v>
       </c>
       <c t="s" r="J227" s="7">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="K227" s="7"/>
       <c r="L227" s="7"/>
       <c t="s" r="M227" s="7">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="228" ht="14.25" customHeight="1">
@@ -8725,22 +8739,22 @@
       </c>
       <c r="D228" s="7"/>
       <c t="s" r="E228" s="7">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="F228" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G228" s="8">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c t="s" r="H228" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I228" s="7">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c t="s" r="J228" s="7">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="K228" s="7"/>
       <c r="L228" s="7"/>
@@ -8758,7 +8772,7 @@
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
@@ -8770,10 +8784,10 @@
         <v>31</v>
       </c>
       <c t="s" r="I229" s="7">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c t="s" r="J229" s="7">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="K229" s="7"/>
       <c r="L229" s="7"/>
@@ -8806,7 +8820,7 @@
       </c>
       <c r="D231" s="7"/>
       <c t="s" r="E231" s="7">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="F231" s="7">
         <v>321</v>
@@ -8815,18 +8829,18 @@
         <v>41</v>
       </c>
       <c t="s" r="H231" s="8">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c t="s" r="I231" s="7">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c t="s" r="J231" s="7">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="K231" s="7"/>
       <c r="L231" s="7"/>
       <c t="s" r="M231" s="7">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="232" ht="14.25" customHeight="1">
@@ -8841,13 +8855,13 @@
       </c>
       <c r="D232" s="7"/>
       <c t="s" r="E232" s="7">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="F232" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G232" s="8">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c t="s" r="H232" s="8">
         <v>41</v>
@@ -8889,7 +8903,7 @@
       </c>
       <c r="D234" s="7"/>
       <c t="s" r="E234" s="7">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="F234" s="7">
         <v>321</v>
@@ -8901,15 +8915,15 @@
         <v>31</v>
       </c>
       <c t="s" r="I234" s="7">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c t="s" r="J234" s="7">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="K234" s="7"/>
       <c r="L234" s="7"/>
       <c t="s" r="M234" s="7">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="235" ht="15" customHeight="1">
@@ -8924,7 +8938,7 @@
       </c>
       <c r="D235" s="7"/>
       <c t="s" r="E235" s="7">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="F235" s="7">
         <v>321</v>
@@ -8936,7 +8950,7 @@
         <v>41</v>
       </c>
       <c t="s" r="I235" s="7">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c t="s" r="J235" s="7">
         <v>128</v>
@@ -8944,7 +8958,7 @@
       <c r="K235" s="7"/>
       <c r="L235" s="7"/>
       <c t="s" r="M235" s="7">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="236" ht="14.25" customHeight="1">
@@ -8959,7 +8973,7 @@
       </c>
       <c r="D236" s="7"/>
       <c t="s" r="E236" s="7">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="F236" s="7">
         <v>321</v>
@@ -8968,10 +8982,10 @@
         <v>41</v>
       </c>
       <c t="s" r="H236" s="8">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c t="s" r="I236" s="7">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c t="s" r="J236" s="7">
         <v>49</v>
@@ -8992,19 +9006,19 @@
       </c>
       <c r="D237" s="7"/>
       <c t="s" r="E237" s="7">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="F237" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G237" s="8">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c t="s" r="H237" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I237" s="7">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c t="s" r="J237" s="7">
         <v>110</v>
@@ -9025,7 +9039,7 @@
       </c>
       <c r="D238" s="7"/>
       <c t="s" r="E238" s="7">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="F238" s="7">
         <v>321</v>
@@ -9034,13 +9048,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H238" s="8">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c t="s" r="I238" s="7">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c t="s" r="J238" s="7">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="K238" s="7"/>
       <c r="L238" s="7"/>
@@ -9058,13 +9072,13 @@
       </c>
       <c r="D239" s="7"/>
       <c t="s" r="E239" s="7">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="F239" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G239" s="8">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c t="s" r="H239" s="8">
         <v>41</v>
@@ -9106,25 +9120,25 @@
       </c>
       <c r="D241" s="7"/>
       <c t="s" r="E241" s="7">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="F241" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G241" s="8">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c t="s" r="H241" s="8">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c t="s" r="I241" s="7">
         <v>56</v>
       </c>
       <c t="s" r="J241" s="7">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c t="s" r="K241" s="7">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L241" s="7"/>
       <c t="s" r="M241" s="7">
@@ -9143,16 +9157,16 @@
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="F242" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G242" s="8">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c t="s" r="H242" s="8">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c t="s" r="I242" s="7">
         <v>18</v>
@@ -9180,25 +9194,25 @@
       </c>
       <c r="D243" s="7"/>
       <c t="s" r="E243" s="7">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="F243" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G243" s="8">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c t="s" r="H243" s="8">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c t="s" r="I243" s="7">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c t="s" r="J243" s="7">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c t="s" r="K243" s="7">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="L243" s="7"/>
       <c t="s" r="M243" s="7">
@@ -9217,13 +9231,13 @@
       </c>
       <c r="D244" s="7"/>
       <c t="s" r="E244" s="7">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="F244" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G244" s="8">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c t="s" r="H244" s="8">
         <v>107</v>
@@ -9232,7 +9246,7 @@
         <v>51</v>
       </c>
       <c t="s" r="J244" s="7">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c t="s" r="K244" s="7">
         <v>121</v>
@@ -9254,7 +9268,7 @@
       </c>
       <c r="D245" s="7"/>
       <c t="s" r="E245" s="7">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="F245" s="7">
         <v>321</v>
@@ -9263,20 +9277,20 @@
         <v>107</v>
       </c>
       <c t="s" r="H245" s="8">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c t="s" r="I245" s="7">
-        <v>245</v>
+        <v>179</v>
       </c>
       <c t="s" r="J245" s="7">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c t="s" r="K245" s="7">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="L245" s="7"/>
       <c t="s" r="M245" s="7">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="246" ht="14.25" customHeight="1">
@@ -9291,22 +9305,22 @@
       </c>
       <c r="D246" s="7"/>
       <c t="s" r="E246" s="7">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="F246" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G246" s="8">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c t="s" r="H246" s="8">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c t="s" r="I246" s="7">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c t="s" r="J246" s="7">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="K246" s="7"/>
       <c r="L246" s="7"/>
@@ -9339,13 +9353,13 @@
       </c>
       <c r="D248" s="7"/>
       <c t="s" r="E248" s="7">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="F248" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G248" s="8">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c t="s" r="H248" s="8">
         <v>31</v>
@@ -9354,12 +9368,12 @@
         <v>91</v>
       </c>
       <c t="s" r="J248" s="7">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="K248" s="7"/>
       <c r="L248" s="7"/>
       <c t="s" r="M248" s="7">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="249" ht="14.25" customHeight="1">
@@ -9374,7 +9388,7 @@
       </c>
       <c r="D249" s="7"/>
       <c t="s" r="E249" s="7">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="F249" s="7">
         <v>321</v>
@@ -9407,7 +9421,7 @@
       </c>
       <c r="D250" s="7"/>
       <c t="s" r="E250" s="7">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="F250" s="7">
         <v>321</v>
@@ -9419,7 +9433,7 @@
         <v>89</v>
       </c>
       <c t="s" r="I250" s="7">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c t="s" r="J250" s="7">
         <v>109</v>
@@ -9440,7 +9454,7 @@
       </c>
       <c r="D251" s="7"/>
       <c t="s" r="E251" s="7">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="F251" s="7">
         <v>321</v>
@@ -9473,7 +9487,7 @@
       </c>
       <c r="D252" s="7"/>
       <c t="s" r="E252" s="7">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="F252" s="7">
         <v>321</v>
@@ -9485,7 +9499,7 @@
         <v>31</v>
       </c>
       <c t="s" r="I252" s="7">
-        <v>194</v>
+        <v>177</v>
       </c>
       <c t="s" r="J252" s="7">
         <v>66</v>
@@ -9506,7 +9520,7 @@
       </c>
       <c r="D253" s="7"/>
       <c t="s" r="E253" s="7">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="F253" s="7">
         <v>321</v>
@@ -9518,10 +9532,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I253" s="7">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c t="s" r="J253" s="7">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="K253" s="7"/>
       <c r="L253" s="7"/>
@@ -9554,7 +9568,7 @@
       </c>
       <c r="D255" s="7"/>
       <c t="s" r="E255" s="7">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="F255" s="7">
         <v>321</v>
@@ -9563,7 +9577,7 @@
         <v>41</v>
       </c>
       <c t="s" r="H255" s="8">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c t="s" r="I255" s="7">
         <v>45</v>
@@ -9589,13 +9603,13 @@
       </c>
       <c r="D256" s="7"/>
       <c t="s" r="E256" s="7">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="F256" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G256" s="8">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c t="s" r="H256" s="8">
         <v>41</v>
@@ -9604,7 +9618,7 @@
         <v>19</v>
       </c>
       <c t="s" r="J256" s="7">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="K256" s="7"/>
       <c r="L256" s="7"/>
@@ -9622,7 +9636,7 @@
       </c>
       <c r="D257" s="7"/>
       <c t="s" r="E257" s="7">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="F257" s="7">
         <v>321</v>
@@ -9631,10 +9645,10 @@
         <v>41</v>
       </c>
       <c t="s" r="H257" s="8">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c t="s" r="I257" s="7">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c t="s" r="J257" s="7">
         <v>68</v>
@@ -9655,22 +9669,22 @@
       </c>
       <c r="D258" s="7"/>
       <c t="s" r="E258" s="7">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="F258" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G258" s="8">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c t="s" r="H258" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I258" s="7">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c t="s" r="J258" s="7">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K258" s="7"/>
       <c r="L258" s="7"/>
@@ -9703,7 +9717,7 @@
       </c>
       <c r="D260" s="7"/>
       <c t="s" r="E260" s="7">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="F260" s="7">
         <v>321</v>
@@ -9712,18 +9726,18 @@
         <v>31</v>
       </c>
       <c t="s" r="H260" s="8">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c t="s" r="I260" s="7">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c t="s" r="J260" s="7">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="K260" s="7"/>
       <c r="L260" s="7"/>
       <c t="s" r="M260" s="7">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="261" ht="14.25" customHeight="1">
@@ -9738,22 +9752,22 @@
       </c>
       <c r="D261" s="7"/>
       <c t="s" r="E261" s="7">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="F261" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G261" s="8">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c t="s" r="H261" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I261" s="7">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c t="s" r="J261" s="7">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="K261" s="7"/>
       <c r="L261" s="7"/>
@@ -9771,7 +9785,7 @@
       </c>
       <c r="D262" s="7"/>
       <c t="s" r="E262" s="7">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="F262" s="7">
         <v>321</v>
@@ -9786,7 +9800,7 @@
         <v>104</v>
       </c>
       <c t="s" r="J262" s="7">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="K262" s="7"/>
       <c r="L262" s="7"/>
@@ -9804,7 +9818,7 @@
       </c>
       <c r="D263" s="7"/>
       <c t="s" r="E263" s="7">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="F263" s="7">
         <v>321</v>
@@ -9816,10 +9830,10 @@
         <v>31</v>
       </c>
       <c t="s" r="I263" s="7">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c t="s" r="J263" s="7">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="K263" s="7"/>
       <c r="L263" s="7"/>
@@ -9852,7 +9866,7 @@
       </c>
       <c r="D265" s="7"/>
       <c t="s" r="E265" s="7">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="F265" s="7">
         <v>321</v>
@@ -9861,10 +9875,10 @@
         <v>31</v>
       </c>
       <c t="s" r="H265" s="8">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c t="s" r="I265" s="7">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c t="s" r="J265" s="7">
         <v>59</v>
@@ -9872,7 +9886,7 @@
       <c r="K265" s="7"/>
       <c r="L265" s="7"/>
       <c t="s" r="M265" s="7">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="266" ht="14.25" customHeight="1">
@@ -9887,13 +9901,13 @@
       </c>
       <c r="D266" s="7"/>
       <c t="s" r="E266" s="7">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="F266" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G266" s="8">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c t="s" r="H266" s="8">
         <v>31</v>
@@ -9907,7 +9921,7 @@
       <c r="K266" s="7"/>
       <c r="L266" s="7"/>
       <c t="s" r="M266" s="7">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="267" ht="14.25" customHeight="1">
@@ -9922,7 +9936,7 @@
       </c>
       <c r="D267" s="7"/>
       <c t="s" r="E267" s="7">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="F267" s="7">
         <v>321</v>
@@ -9934,7 +9948,7 @@
         <v>89</v>
       </c>
       <c t="s" r="I267" s="7">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c t="s" r="J267" s="7">
         <v>122</v>
@@ -9955,7 +9969,7 @@
       </c>
       <c r="D268" s="7"/>
       <c t="s" r="E268" s="7">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="F268" s="7">
         <v>321</v>
@@ -9967,10 +9981,10 @@
         <v>31</v>
       </c>
       <c t="s" r="I268" s="7">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c t="s" r="J268" s="7">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="K268" s="7"/>
       <c r="L268" s="7"/>
@@ -9988,7 +10002,7 @@
       </c>
       <c r="D269" s="7"/>
       <c t="s" r="E269" s="7">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="F269" s="7">
         <v>321</v>
@@ -10000,10 +10014,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I269" s="7">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c t="s" r="J269" s="7">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K269" s="7"/>
       <c r="L269" s="7"/>
@@ -10021,7 +10035,7 @@
       </c>
       <c r="D270" s="7"/>
       <c t="s" r="E270" s="7">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="F270" s="7">
         <v>321</v>
@@ -10033,7 +10047,7 @@
         <v>31</v>
       </c>
       <c t="s" r="I270" s="7">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c t="s" r="J270" s="7">
         <v>86</v>
@@ -10069,7 +10083,7 @@
       </c>
       <c r="D272" s="7"/>
       <c t="s" r="E272" s="7">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="F272" s="7">
         <v>320</v>
@@ -10084,12 +10098,12 @@
         <v>113</v>
       </c>
       <c t="s" r="J272" s="7">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K272" s="7"/>
       <c r="L272" s="7"/>
       <c t="s" r="M272" s="7">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="273" ht="14.25" customHeight="1">
@@ -10104,7 +10118,7 @@
       </c>
       <c r="D273" s="7"/>
       <c t="s" r="E273" s="7">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="F273" s="7">
         <v>320</v>
@@ -10116,7 +10130,7 @@
         <v>31</v>
       </c>
       <c t="s" r="I273" s="7">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c t="s" r="J273" s="7">
         <v>29</v>
@@ -10124,7 +10138,7 @@
       <c r="K273" s="7"/>
       <c r="L273" s="7"/>
       <c t="s" r="M273" s="7">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="274" ht="14.25" customHeight="1">
@@ -10139,7 +10153,7 @@
       </c>
       <c r="D274" s="7"/>
       <c t="s" r="E274" s="7">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="F274" s="7">
         <v>320</v>
@@ -10154,14 +10168,14 @@
         <v>128</v>
       </c>
       <c t="s" r="J274" s="7">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c t="s" r="K274" s="7">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="L274" s="7"/>
       <c t="s" r="M274" s="7">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="275" ht="15" customHeight="1">
@@ -10176,7 +10190,7 @@
       </c>
       <c r="D275" s="7"/>
       <c t="s" r="E275" s="7">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="F275" s="7">
         <v>320</v>
@@ -10213,7 +10227,7 @@
       </c>
       <c r="D276" s="7"/>
       <c t="s" r="E276" s="7">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="F276" s="7">
         <v>320</v>
@@ -10222,16 +10236,16 @@
         <v>31</v>
       </c>
       <c t="s" r="H276" s="8">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c t="s" r="I276" s="7">
         <v>23</v>
       </c>
       <c t="s" r="J276" s="7">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c t="s" r="K276" s="7">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L276" s="7"/>
       <c t="s" r="M276" s="7">
@@ -10250,29 +10264,29 @@
       </c>
       <c r="D277" s="7"/>
       <c t="s" r="E277" s="7">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="F277" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G277" s="8">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c t="s" r="H277" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I277" s="7">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c t="s" r="J277" s="7">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c t="s" r="K277" s="7">
         <v>123</v>
       </c>
       <c r="L277" s="7"/>
       <c t="s" r="M277" s="7">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="278" ht="14.25" customHeight="1">
@@ -10287,7 +10301,7 @@
       </c>
       <c r="D278" s="7"/>
       <c t="s" r="E278" s="7">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="F278" s="7">
         <v>320</v>
@@ -10302,14 +10316,14 @@
         <v>53</v>
       </c>
       <c t="s" r="J278" s="7">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c t="s" r="K278" s="7">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="L278" s="7"/>
       <c t="s" r="M278" s="7">
-        <v>188</v>
+        <v>194</v>
       </c>
     </row>
     <row r="279" ht="14.25" customHeight="1">
@@ -10324,7 +10338,7 @@
       </c>
       <c r="D279" s="7"/>
       <c t="s" r="E279" s="7">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="F279" s="7">
         <v>320</v>
@@ -10336,17 +10350,17 @@
         <v>31</v>
       </c>
       <c t="s" r="I279" s="7">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c t="s" r="J279" s="7">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c t="s" r="K279" s="7">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="L279" s="7"/>
       <c t="s" r="M279" s="7">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="280" ht="15" customHeight="1">
@@ -10376,7 +10390,7 @@
       </c>
       <c r="D281" s="7"/>
       <c t="s" r="E281" s="7">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="F281" s="7">
         <v>321</v>
@@ -10385,10 +10399,10 @@
         <v>41</v>
       </c>
       <c t="s" r="H281" s="8">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c t="s" r="I281" s="7">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c t="s" r="J281" s="7">
         <v>106</v>
@@ -10396,7 +10410,7 @@
       <c r="K281" s="7"/>
       <c r="L281" s="7"/>
       <c t="s" r="M281" s="7">
-        <v>251</v>
+        <v>257</v>
       </c>
     </row>
     <row r="282" ht="14.25" customHeight="1">
@@ -10411,22 +10425,22 @@
       </c>
       <c r="D282" s="7"/>
       <c t="s" r="E282" s="7">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="F282" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G282" s="8">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c t="s" r="H282" s="8">
         <v>58</v>
       </c>
       <c t="s" r="I282" s="7">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c t="s" r="J282" s="7">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="K282" s="7"/>
       <c r="L282" s="7"/>
@@ -10444,7 +10458,7 @@
       </c>
       <c r="D283" s="7"/>
       <c t="s" r="E283" s="7">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="F283" s="7">
         <v>321</v>
@@ -10453,13 +10467,13 @@
         <v>58</v>
       </c>
       <c t="s" r="H283" s="8">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c t="s" r="I283" s="7">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c t="s" r="J283" s="7">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="K283" s="7"/>
       <c r="L283" s="7"/>
@@ -10477,13 +10491,13 @@
       </c>
       <c r="D284" s="7"/>
       <c t="s" r="E284" s="7">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="F284" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G284" s="8">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c t="s" r="H284" s="8">
         <v>41</v>
@@ -10492,7 +10506,7 @@
         <v>125</v>
       </c>
       <c t="s" r="J284" s="7">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="K284" s="7"/>
       <c r="L284" s="7"/>
@@ -10525,7 +10539,7 @@
       </c>
       <c r="D286" s="7"/>
       <c t="s" r="E286" s="7">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="F286" s="7">
         <v>321</v>
@@ -10534,10 +10548,10 @@
         <v>41</v>
       </c>
       <c t="s" r="H286" s="8">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c t="s" r="I286" s="7">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c t="s" r="J286" s="7">
         <v>19</v>
@@ -10545,7 +10559,7 @@
       <c r="K286" s="7"/>
       <c r="L286" s="7"/>
       <c t="s" r="M286" s="7">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="287" ht="14.25" customHeight="1">
@@ -10560,22 +10574,22 @@
       </c>
       <c r="D287" s="7"/>
       <c t="s" r="E287" s="7">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="F287" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G287" s="8">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c t="s" r="H287" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I287" s="7">
-        <v>193</v>
+        <v>175</v>
       </c>
       <c t="s" r="J287" s="7">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="K287" s="7"/>
       <c r="L287" s="7"/>
@@ -10608,7 +10622,7 @@
       </c>
       <c r="D289" s="7"/>
       <c t="s" r="E289" s="7">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="F289" s="7">
         <v>320</v>
@@ -10623,12 +10637,12 @@
         <v>93</v>
       </c>
       <c t="s" r="J289" s="7">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="K289" s="7"/>
       <c r="L289" s="7"/>
       <c t="s" r="M289" s="7">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="290" ht="15" customHeight="1">
@@ -10643,7 +10657,7 @@
       </c>
       <c r="D290" s="7"/>
       <c t="s" r="E290" s="7">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="F290" s="7">
         <v>320</v>
@@ -10655,10 +10669,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I290" s="7">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c t="s" r="J290" s="7">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="K290" s="7"/>
       <c r="L290" s="7"/>
@@ -10676,7 +10690,7 @@
       </c>
       <c r="D291" s="7"/>
       <c t="s" r="E291" s="7">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="F291" s="7">
         <v>320</v>
@@ -10685,13 +10699,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H291" s="8">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c t="s" r="I291" s="7">
         <v>36</v>
       </c>
       <c t="s" r="J291" s="7">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="K291" s="7"/>
       <c r="L291" s="7"/>
@@ -10709,19 +10723,19 @@
       </c>
       <c r="D292" s="7"/>
       <c t="s" r="E292" s="7">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="F292" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G292" s="8">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c t="s" r="H292" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I292" s="7">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c t="s" r="J292" s="7">
         <v>87</v>
@@ -10757,7 +10771,7 @@
       </c>
       <c r="D294" s="7"/>
       <c t="s" r="E294" s="7">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="F294" s="7">
         <v>320</v>
@@ -10769,15 +10783,15 @@
         <v>42</v>
       </c>
       <c t="s" r="I294" s="7">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c t="s" r="J294" s="7">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="K294" s="7"/>
       <c r="L294" s="7"/>
       <c t="s" r="M294" s="7">
-        <v>226</v>
+        <v>232</v>
       </c>
     </row>
     <row r="295" ht="15" customHeight="1">
@@ -10792,7 +10806,7 @@
       </c>
       <c r="D295" s="7"/>
       <c t="s" r="E295" s="7">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="F295" s="7">
         <v>320</v>
@@ -10804,17 +10818,17 @@
         <v>31</v>
       </c>
       <c t="s" r="I295" s="7">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c t="s" r="J295" s="7">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c t="s" r="K295" s="7">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="L295" s="7"/>
       <c t="s" r="M295" s="7">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="296" ht="14.25" customHeight="1">
@@ -10829,7 +10843,7 @@
       </c>
       <c r="D296" s="7"/>
       <c t="s" r="E296" s="7">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="F296" s="7">
         <v>320</v>
@@ -10841,10 +10855,10 @@
         <v>58</v>
       </c>
       <c t="s" r="I296" s="7">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c t="s" r="J296" s="7">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="K296" s="7"/>
       <c r="L296" s="7"/>
@@ -10862,7 +10876,7 @@
       </c>
       <c r="D297" s="7"/>
       <c t="s" r="E297" s="7">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="F297" s="7">
         <v>320</v>
@@ -10874,10 +10888,10 @@
         <v>31</v>
       </c>
       <c t="s" r="I297" s="7">
-        <v>193</v>
+        <v>175</v>
       </c>
       <c t="s" r="J297" s="7">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="K297" s="7"/>
       <c r="L297" s="7"/>
@@ -10895,7 +10909,7 @@
       </c>
       <c r="D298" s="7"/>
       <c t="s" r="E298" s="7">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="F298" s="7">
         <v>320</v>
@@ -10904,13 +10918,13 @@
         <v>31</v>
       </c>
       <c t="s" r="H298" s="8">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c t="s" r="I298" s="7">
         <v>84</v>
       </c>
       <c t="s" r="J298" s="7">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="K298" s="7"/>
       <c r="L298" s="7"/>
@@ -10928,13 +10942,13 @@
       </c>
       <c r="D299" s="7"/>
       <c t="s" r="E299" s="7">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="F299" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G299" s="8">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c t="s" r="H299" s="8">
         <v>31</v>
@@ -10943,7 +10957,7 @@
         <v>73</v>
       </c>
       <c t="s" r="J299" s="7">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="K299" s="7"/>
       <c r="L299" s="7"/>
@@ -10976,7 +10990,7 @@
       </c>
       <c r="D301" s="7"/>
       <c t="s" r="E301" s="7">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="F301" s="7">
         <v>321</v>
@@ -10988,15 +11002,15 @@
         <v>41</v>
       </c>
       <c t="s" r="I301" s="7">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c t="s" r="J301" s="7">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K301" s="7"/>
       <c r="L301" s="7"/>
       <c t="s" r="M301" s="7">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="302" ht="14.25" customHeight="1">
@@ -11011,7 +11025,7 @@
       </c>
       <c r="D302" s="7"/>
       <c t="s" r="E302" s="7">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="F302" s="7">
         <v>321</v>
@@ -11020,13 +11034,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H302" s="8">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c t="s" r="I302" s="7">
         <v>60</v>
       </c>
       <c t="s" r="J302" s="7">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="K302" s="7"/>
       <c r="L302" s="7"/>
@@ -11044,22 +11058,22 @@
       </c>
       <c r="D303" s="7"/>
       <c t="s" r="E303" s="7">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="F303" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G303" s="8">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c t="s" r="H303" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I303" s="7">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c t="s" r="J303" s="7">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="K303" s="7"/>
       <c r="L303" s="7"/>
@@ -11077,7 +11091,7 @@
       </c>
       <c r="D304" s="7"/>
       <c t="s" r="E304" s="7">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="F304" s="7">
         <v>321</v>
@@ -11086,10 +11100,10 @@
         <v>41</v>
       </c>
       <c t="s" r="H304" s="8">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c t="s" r="I304" s="7">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c t="s" r="J304" s="7">
         <v>53</v>
@@ -11110,22 +11124,22 @@
       </c>
       <c r="D305" s="7"/>
       <c t="s" r="E305" s="7">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="F305" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G305" s="8">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c t="s" r="H305" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I305" s="7">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c t="s" r="J305" s="7">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="K305" s="7"/>
       <c r="L305" s="7"/>
@@ -11158,7 +11172,7 @@
       </c>
       <c r="D307" s="7"/>
       <c t="s" r="E307" s="7">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="F307" s="7">
         <v>320</v>
@@ -11173,12 +11187,12 @@
         <v>76</v>
       </c>
       <c t="s" r="J307" s="7">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="K307" s="7"/>
       <c r="L307" s="7"/>
       <c t="s" r="M307" s="7">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="308" ht="14.25" customHeight="1">
@@ -11193,7 +11207,7 @@
       </c>
       <c r="D308" s="7"/>
       <c t="s" r="E308" s="7">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="F308" s="7">
         <v>320</v>
@@ -11213,7 +11227,7 @@
       <c r="K308" s="7"/>
       <c r="L308" s="7"/>
       <c t="s" r="M308" s="7">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="309" ht="14.25" customHeight="1">
@@ -11243,7 +11257,7 @@
       </c>
       <c r="D310" s="7"/>
       <c t="s" r="E310" s="7">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="F310" s="7">
         <v>321</v>
@@ -11252,18 +11266,18 @@
         <v>41</v>
       </c>
       <c t="s" r="H310" s="8">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c t="s" r="I310" s="7">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c t="s" r="J310" s="7">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="K310" s="7"/>
       <c r="L310" s="7"/>
       <c t="s" r="M310" s="7">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="311" ht="14.25" customHeight="1">
@@ -11278,27 +11292,27 @@
       </c>
       <c r="D311" s="7"/>
       <c t="s" r="E311" s="7">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="F311" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G311" s="8">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c t="s" r="H311" s="8">
         <v>89</v>
       </c>
       <c t="s" r="I311" s="7">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c t="s" r="J311" s="7">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="K311" s="7"/>
       <c r="L311" s="7"/>
       <c t="s" r="M311" s="7">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="312" ht="14.25" customHeight="1">
@@ -11313,7 +11327,7 @@
       </c>
       <c r="D312" s="7"/>
       <c t="s" r="E312" s="7">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="F312" s="7">
         <v>321</v>
@@ -11322,13 +11336,13 @@
         <v>89</v>
       </c>
       <c t="s" r="H312" s="8">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c t="s" r="I312" s="7">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c t="s" r="J312" s="7">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="K312" s="7"/>
       <c r="L312" s="7"/>
@@ -11346,22 +11360,22 @@
       </c>
       <c r="D313" s="7"/>
       <c t="s" r="E313" s="7">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="F313" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G313" s="8">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c t="s" r="H313" s="8">
         <v>89</v>
       </c>
       <c t="s" r="I313" s="7">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c t="s" r="J313" s="7">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="K313" s="7"/>
       <c r="L313" s="7"/>
@@ -11394,13 +11408,13 @@
       </c>
       <c r="D315" s="7"/>
       <c t="s" r="E315" s="7">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="F315" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G315" s="8">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c t="s" r="H315" s="8">
         <v>31</v>
@@ -11414,7 +11428,7 @@
       <c r="K315" s="7"/>
       <c r="L315" s="7"/>
       <c t="s" r="M315" s="7">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="316" ht="14.25" customHeight="1">
@@ -11429,7 +11443,7 @@
       </c>
       <c r="D316" s="7"/>
       <c t="s" r="E316" s="7">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="F316" s="7">
         <v>320</v>
@@ -11438,10 +11452,10 @@
         <v>31</v>
       </c>
       <c t="s" r="H316" s="8">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c t="s" r="I316" s="7">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c t="s" r="J316" s="7">
         <v>103</v>
@@ -11462,19 +11476,19 @@
       </c>
       <c r="D317" s="7"/>
       <c t="s" r="E317" s="7">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="F317" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G317" s="8">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c t="s" r="H317" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I317" s="7">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c t="s" r="J317" s="7">
         <v>67</v>
@@ -11510,7 +11524,7 @@
       </c>
       <c r="D319" s="7"/>
       <c t="s" r="E319" s="7">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="F319" s="7">
         <v>320</v>
@@ -11522,7 +11536,7 @@
         <v>41</v>
       </c>
       <c t="s" r="I319" s="7">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c t="s" r="J319" s="7">
         <v>111</v>
@@ -11543,7 +11557,7 @@
       </c>
       <c r="D320" s="7"/>
       <c t="s" r="E320" s="7">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="F320" s="7">
         <v>320</v>
@@ -11555,10 +11569,10 @@
         <v>58</v>
       </c>
       <c t="s" r="I320" s="7">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c t="s" r="J320" s="7">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="K320" s="7"/>
       <c r="L320" s="7"/>
@@ -11576,7 +11590,7 @@
       </c>
       <c r="D321" s="7"/>
       <c t="s" r="E321" s="7">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="F321" s="7">
         <v>320</v>
@@ -11588,10 +11602,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I321" s="7">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c t="s" r="J321" s="7">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="K321" s="7"/>
       <c r="L321" s="7"/>
@@ -11609,7 +11623,7 @@
       </c>
       <c r="D322" s="7"/>
       <c t="s" r="E322" s="7">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="F322" s="7">
         <v>320</v>
@@ -11621,10 +11635,10 @@
         <v>31</v>
       </c>
       <c t="s" r="I322" s="7">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c t="s" r="J322" s="7">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="K322" s="7"/>
       <c r="L322" s="7"/>
@@ -11657,7 +11671,7 @@
       </c>
       <c r="D324" s="7"/>
       <c t="s" r="E324" s="7">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="F324" s="7">
         <v>320</v>
@@ -11666,10 +11680,10 @@
         <v>41</v>
       </c>
       <c t="s" r="H324" s="8">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c t="s" r="I324" s="7">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c t="s" r="J324" s="7">
         <v>123</v>
@@ -11690,22 +11704,22 @@
       </c>
       <c r="D325" s="7"/>
       <c t="s" r="E325" s="7">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="F325" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G325" s="8">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c t="s" r="H325" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I325" s="7">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c t="s" r="J325" s="7">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="K325" s="7"/>
       <c r="L325" s="7"/>
@@ -11738,7 +11752,7 @@
       </c>
       <c r="D327" s="7"/>
       <c t="s" r="E327" s="7">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="F327" s="7">
         <v>321</v>
@@ -11750,15 +11764,15 @@
         <v>47</v>
       </c>
       <c t="s" r="I327" s="7">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c t="s" r="J327" s="7">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K327" s="7"/>
       <c r="L327" s="7"/>
       <c t="s" r="M327" s="7">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="328" ht="14.25" customHeight="1">
@@ -11773,7 +11787,7 @@
       </c>
       <c r="D328" s="7"/>
       <c t="s" r="E328" s="7">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="F328" s="7">
         <v>321</v>
@@ -11785,7 +11799,7 @@
         <v>41</v>
       </c>
       <c t="s" r="I328" s="7">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c t="s" r="J328" s="7">
         <v>118</v>
@@ -11793,7 +11807,7 @@
       <c r="K328" s="7"/>
       <c r="L328" s="7"/>
       <c t="s" r="M328" s="7">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="329" ht="14.25" customHeight="1">
@@ -11808,7 +11822,7 @@
       </c>
       <c r="D329" s="7"/>
       <c t="s" r="E329" s="7">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="F329" s="7">
         <v>321</v>
@@ -11817,7 +11831,7 @@
         <v>41</v>
       </c>
       <c t="s" r="H329" s="8">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c t="s" r="I329" s="7">
         <v>129</v>
@@ -11841,22 +11855,22 @@
       </c>
       <c r="D330" s="7"/>
       <c t="s" r="E330" s="7">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="F330" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G330" s="8">
+        <v>182</v>
+      </c>
+      <c t="s" r="H330" s="8">
+        <v>41</v>
+      </c>
+      <c t="s" r="I330" s="7">
+        <v>367</v>
+      </c>
+      <c t="s" r="J330" s="7">
         <v>176</v>
-      </c>
-      <c t="s" r="H330" s="8">
-        <v>41</v>
-      </c>
-      <c t="s" r="I330" s="7">
-        <v>365</v>
-      </c>
-      <c t="s" r="J330" s="7">
-        <v>259</v>
       </c>
       <c r="K330" s="7"/>
       <c r="L330" s="7"/>
@@ -11874,7 +11888,7 @@
       </c>
       <c r="D331" s="7"/>
       <c t="s" r="E331" s="7">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="F331" s="7">
         <v>321</v>
@@ -11889,7 +11903,7 @@
         <v>64</v>
       </c>
       <c t="s" r="J331" s="7">
-        <v>245</v>
+        <v>179</v>
       </c>
       <c r="K331" s="7"/>
       <c r="L331" s="7"/>
@@ -11907,7 +11921,7 @@
       </c>
       <c r="D332" s="7"/>
       <c t="s" r="E332" s="7">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="F332" s="7">
         <v>321</v>
@@ -11919,7 +11933,7 @@
         <v>41</v>
       </c>
       <c t="s" r="I332" s="7">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c t="s" r="J332" s="7">
         <v>125</v>
@@ -11940,7 +11954,7 @@
       </c>
       <c r="D333" s="7"/>
       <c t="s" r="E333" s="7">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="F333" s="7">
         <v>321</v>
@@ -11952,10 +11966,10 @@
         <v>89</v>
       </c>
       <c t="s" r="I333" s="7">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c t="s" r="J333" s="7">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="K333" s="7"/>
       <c r="L333" s="7"/>
@@ -11969,11 +11983,11 @@
         <v>8020</v>
       </c>
       <c t="s" r="C334" s="7">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D334" s="7"/>
       <c t="s" r="E334" s="7">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="F334" s="7">
         <v>321</v>
@@ -11982,13 +11996,13 @@
         <v>89</v>
       </c>
       <c t="s" r="H334" s="8">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c t="s" r="I334" s="7">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c t="s" r="J334" s="7">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="K334" s="7"/>
       <c r="L334" s="7"/>
@@ -12002,26 +12016,26 @@
         <v>8021</v>
       </c>
       <c t="s" r="C335" s="7">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D335" s="7"/>
       <c t="s" r="E335" s="7">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="F335" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G335" s="8">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c t="s" r="H335" s="8">
         <v>89</v>
       </c>
       <c t="s" r="I335" s="7">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c t="s" r="J335" s="7">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="K335" s="7"/>
       <c r="L335" s="7"/>
@@ -12054,7 +12068,7 @@
       </c>
       <c r="D337" s="7"/>
       <c t="s" r="E337" s="7">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="F337" s="7">
         <v>320</v>
@@ -12063,18 +12077,18 @@
         <v>31</v>
       </c>
       <c t="s" r="H337" s="8">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c t="s" r="I337" s="7">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c t="s" r="J337" s="7">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="K337" s="7"/>
       <c r="L337" s="7"/>
       <c t="s" r="M337" s="7">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="338" ht="14.25" customHeight="1">
@@ -12089,19 +12103,19 @@
       </c>
       <c r="D338" s="7"/>
       <c t="s" r="E338" s="7">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="F338" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G338" s="8">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c t="s" r="H338" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I338" s="7">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c t="s" r="J338" s="7">
         <v>121</v>
@@ -12137,7 +12151,7 @@
       </c>
       <c r="D340" s="7"/>
       <c t="s" r="E340" s="7">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="F340" s="7">
         <v>320</v>
@@ -12146,18 +12160,18 @@
         <v>41</v>
       </c>
       <c t="s" r="H340" s="8">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c t="s" r="I340" s="7">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c t="s" r="J340" s="7">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="K340" s="7"/>
       <c r="L340" s="7"/>
       <c t="s" r="M340" s="7">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="341" ht="14.25" customHeight="1">
@@ -12172,19 +12186,19 @@
       </c>
       <c r="D341" s="7"/>
       <c t="s" r="E341" s="7">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="F341" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G341" s="8">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c t="s" r="H341" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I341" s="7">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c t="s" r="J341" s="7">
         <v>34</v>
@@ -12205,7 +12219,7 @@
       </c>
       <c r="D342" s="7"/>
       <c t="s" r="E342" s="7">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="F342" s="7">
         <v>320</v>
@@ -12217,7 +12231,7 @@
         <v>127</v>
       </c>
       <c t="s" r="I342" s="7">
-        <v>193</v>
+        <v>175</v>
       </c>
       <c t="s" r="J342" s="7">
         <v>122</v>
@@ -12238,7 +12252,7 @@
       </c>
       <c r="D343" s="7"/>
       <c t="s" r="E343" s="7">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="F343" s="7">
         <v>320</v>
@@ -12250,10 +12264,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I343" s="7">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c t="s" r="J343" s="7">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="K343" s="7"/>
       <c r="L343" s="7"/>
@@ -12271,7 +12285,7 @@
       </c>
       <c r="D344" s="7"/>
       <c t="s" r="E344" s="7">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="F344" s="7">
         <v>320</v>
@@ -12280,7 +12294,7 @@
         <v>41</v>
       </c>
       <c t="s" r="H344" s="8">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c t="s" r="I344" s="7">
         <v>65</v>
@@ -12304,19 +12318,19 @@
       </c>
       <c r="D345" s="7"/>
       <c t="s" r="E345" s="7">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="F345" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G345" s="8">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c t="s" r="H345" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I345" s="7">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c t="s" r="J345" s="7">
         <v>25</v>
@@ -12352,7 +12366,7 @@
       </c>
       <c r="D347" s="7"/>
       <c t="s" r="E347" s="7">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="F347" s="7">
         <v>321</v>
@@ -12361,13 +12375,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H347" s="8">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c t="s" r="I347" s="7">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c t="s" r="J347" s="7">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="K347" s="7"/>
       <c r="L347" s="7"/>
@@ -12385,22 +12399,22 @@
       </c>
       <c r="D348" s="7"/>
       <c t="s" r="E348" s="7">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="F348" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G348" s="8">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c t="s" r="H348" s="8">
         <v>127</v>
       </c>
       <c t="s" r="I348" s="7">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c t="s" r="J348" s="7">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="K348" s="7"/>
       <c r="L348" s="7"/>
@@ -12418,7 +12432,7 @@
       </c>
       <c r="D349" s="7"/>
       <c t="s" r="E349" s="7">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="F349" s="7">
         <v>321</v>
@@ -12427,13 +12441,13 @@
         <v>127</v>
       </c>
       <c t="s" r="H349" s="8">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c t="s" r="I349" s="7">
         <v>82</v>
       </c>
       <c t="s" r="J349" s="7">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="K349" s="7"/>
       <c r="L349" s="7"/>
@@ -12451,22 +12465,22 @@
       </c>
       <c r="D350" s="7"/>
       <c t="s" r="E350" s="7">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="F350" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G350" s="8">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c t="s" r="H350" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I350" s="7">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c t="s" r="J350" s="7">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="K350" s="7"/>
       <c r="L350" s="7"/>
@@ -12484,7 +12498,7 @@
       </c>
       <c r="D351" s="7"/>
       <c t="s" r="E351" s="7">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="F351" s="7">
         <v>321</v>
@@ -12493,10 +12507,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H351" s="8">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c t="s" r="I351" s="7">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c t="s" r="J351" s="7">
         <v>76</v>
@@ -12532,7 +12546,7 @@
       </c>
       <c r="D353" s="7"/>
       <c t="s" r="E353" s="7">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="F353" s="7">
         <v>321</v>
@@ -12544,15 +12558,15 @@
         <v>107</v>
       </c>
       <c t="s" r="I353" s="7">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c t="s" r="J353" s="7">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="K353" s="7"/>
       <c r="L353" s="7"/>
       <c t="s" r="M353" s="7">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="354" ht="14.25" customHeight="1">
@@ -12567,7 +12581,7 @@
       </c>
       <c r="D354" s="7"/>
       <c t="s" r="E354" s="7">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="F354" s="7">
         <v>321</v>
@@ -12587,7 +12601,7 @@
       <c r="K354" s="7"/>
       <c r="L354" s="7"/>
       <c t="s" r="M354" s="7">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="355" ht="15" customHeight="1">
@@ -12602,7 +12616,7 @@
       </c>
       <c r="D355" s="7"/>
       <c t="s" r="E355" s="7">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="F355" s="7">
         <v>321</v>
@@ -12614,10 +12628,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I355" s="7">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c t="s" r="J355" s="7">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="K355" s="7"/>
       <c r="L355" s="7"/>
@@ -12635,7 +12649,7 @@
       </c>
       <c r="D356" s="7"/>
       <c t="s" r="E356" s="7">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="F356" s="7">
         <v>321</v>
@@ -12650,7 +12664,7 @@
         <v>111</v>
       </c>
       <c t="s" r="J356" s="7">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="K356" s="7"/>
       <c r="L356" s="7"/>
@@ -12683,7 +12697,7 @@
       </c>
       <c r="D358" s="7"/>
       <c t="s" r="E358" s="7">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="F358" s="7">
         <v>320</v>
@@ -12695,10 +12709,10 @@
         <v>58</v>
       </c>
       <c t="s" r="I358" s="7">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c t="s" r="J358" s="7">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="K358" s="7"/>
       <c r="L358" s="7"/>
@@ -12718,7 +12732,7 @@
       </c>
       <c r="D359" s="7"/>
       <c t="s" r="E359" s="7">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="F359" s="7">
         <v>320</v>
@@ -12733,7 +12747,7 @@
         <v>129</v>
       </c>
       <c t="s" r="J359" s="7">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="K359" s="7"/>
       <c r="L359" s="7"/>
@@ -12751,7 +12765,7 @@
       </c>
       <c r="D360" s="7"/>
       <c t="s" r="E360" s="7">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="F360" s="7">
         <v>320</v>
@@ -12763,7 +12777,7 @@
         <v>127</v>
       </c>
       <c t="s" r="I360" s="7">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c t="s" r="J360" s="7">
         <v>23</v>
@@ -12784,7 +12798,7 @@
       </c>
       <c r="D361" s="7"/>
       <c t="s" r="E361" s="7">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="F361" s="7">
         <v>320</v>
@@ -12796,7 +12810,7 @@
         <v>31</v>
       </c>
       <c t="s" r="I361" s="7">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c t="s" r="J361" s="7">
         <v>36</v>
@@ -12817,7 +12831,7 @@
       </c>
       <c r="D362" s="7"/>
       <c t="s" r="E362" s="7">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="F362" s="7">
         <v>320</v>
@@ -12829,10 +12843,10 @@
         <v>89</v>
       </c>
       <c t="s" r="I362" s="7">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c t="s" r="J362" s="7">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="K362" s="7"/>
       <c r="L362" s="7"/>
@@ -12850,7 +12864,7 @@
       </c>
       <c r="D363" s="7"/>
       <c t="s" r="E363" s="7">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="F363" s="7">
         <v>320</v>
@@ -12862,10 +12876,10 @@
         <v>31</v>
       </c>
       <c t="s" r="I363" s="7">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c t="s" r="J363" s="7">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="K363" s="7"/>
       <c r="L363" s="7"/>
@@ -12898,7 +12912,7 @@
       </c>
       <c r="D365" s="7"/>
       <c t="s" r="E365" s="7">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="F365" s="7">
         <v>320</v>
@@ -12907,10 +12921,10 @@
         <v>41</v>
       </c>
       <c t="s" r="H365" s="8">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c t="s" r="I365" s="7">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c t="s" r="J365" s="7">
         <v>43</v>
@@ -12933,19 +12947,19 @@
       </c>
       <c r="D366" s="7"/>
       <c t="s" r="E366" s="7">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="F366" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G366" s="8">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c t="s" r="H366" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I366" s="7">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c t="s" r="J366" s="7">
         <v>69</v>
@@ -12953,7 +12967,7 @@
       <c r="K366" s="7"/>
       <c r="L366" s="7"/>
       <c t="s" r="M366" s="7">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="367" ht="14.25" customHeight="1">
@@ -12968,7 +12982,7 @@
       </c>
       <c r="D367" s="7"/>
       <c t="s" r="E367" s="7">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="F367" s="7">
         <v>320</v>
@@ -12977,18 +12991,18 @@
         <v>41</v>
       </c>
       <c t="s" r="H367" s="8">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c t="s" r="I367" s="7">
         <v>97</v>
       </c>
       <c t="s" r="J367" s="7">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="K367" s="7"/>
       <c r="L367" s="7"/>
       <c t="s" r="M367" s="7">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="368" ht="14.25" customHeight="1">
@@ -13003,13 +13017,13 @@
       </c>
       <c r="D368" s="7"/>
       <c t="s" r="E368" s="7">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="F368" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G368" s="8">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c t="s" r="H368" s="8">
         <v>41</v>
@@ -13036,7 +13050,7 @@
       </c>
       <c r="D369" s="7"/>
       <c t="s" r="E369" s="7">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="F369" s="7">
         <v>320</v>
@@ -13045,13 +13059,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H369" s="8">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c t="s" r="I369" s="7">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c t="s" r="J369" s="7">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="K369" s="7"/>
       <c r="L369" s="7"/>
@@ -13069,22 +13083,22 @@
       </c>
       <c r="D370" s="7"/>
       <c t="s" r="E370" s="7">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="F370" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G370" s="8">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c t="s" r="H370" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I370" s="7">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c t="s" r="J370" s="7">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="K370" s="7"/>
       <c r="L370" s="7"/>
@@ -13102,7 +13116,7 @@
       </c>
       <c r="D371" s="7"/>
       <c t="s" r="E371" s="7">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="F371" s="7">
         <v>320</v>
@@ -13111,13 +13125,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H371" s="8">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c t="s" r="I371" s="7">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c t="s" r="J371" s="7">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="K371" s="7"/>
       <c r="L371" s="7"/>
@@ -13135,22 +13149,22 @@
       </c>
       <c r="D372" s="7"/>
       <c t="s" r="E372" s="7">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="F372" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G372" s="8">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c t="s" r="H372" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I372" s="7">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c t="s" r="J372" s="7">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="K372" s="7"/>
       <c r="L372" s="7"/>
@@ -13183,7 +13197,7 @@
       </c>
       <c r="D374" s="7"/>
       <c t="s" r="E374" s="7">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="F374" s="7">
         <v>321</v>
@@ -13195,15 +13209,15 @@
         <v>41</v>
       </c>
       <c t="s" r="I374" s="7">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c t="s" r="J374" s="7">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="K374" s="7"/>
       <c r="L374" s="7"/>
       <c t="s" r="M374" s="7">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="375" ht="15" customHeight="1">
@@ -13218,7 +13232,7 @@
       </c>
       <c r="D375" s="7"/>
       <c t="s" r="E375" s="7">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="F375" s="7">
         <v>321</v>
@@ -13230,15 +13244,15 @@
         <v>31</v>
       </c>
       <c t="s" r="I375" s="7">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c t="s" r="J375" s="7">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="K375" s="7"/>
       <c r="L375" s="7"/>
       <c t="s" r="M375" s="7">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="376" ht="14.25" customHeight="1">
@@ -13253,7 +13267,7 @@
       </c>
       <c r="D376" s="7"/>
       <c t="s" r="E376" s="7">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="F376" s="7">
         <v>321</v>
@@ -13265,10 +13279,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I376" s="7">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c t="s" r="J376" s="7">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="K376" s="7"/>
       <c r="L376" s="7"/>
@@ -13286,7 +13300,7 @@
       </c>
       <c r="D377" s="7"/>
       <c t="s" r="E377" s="7">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="F377" s="7">
         <v>321</v>
@@ -13295,10 +13309,10 @@
         <v>41</v>
       </c>
       <c t="s" r="H377" s="8">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c t="s" r="I377" s="7">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c t="s" r="J377" s="7">
         <v>65</v>
@@ -13319,22 +13333,22 @@
       </c>
       <c r="D378" s="7"/>
       <c t="s" r="E378" s="7">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="F378" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G378" s="8">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c t="s" r="H378" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I378" s="7">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c t="s" r="J378" s="7">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="K378" s="7"/>
       <c r="L378" s="7"/>
@@ -13352,7 +13366,7 @@
       </c>
       <c r="D379" s="7"/>
       <c t="s" r="E379" s="7">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="F379" s="7">
         <v>321</v>
@@ -13364,10 +13378,10 @@
         <v>31</v>
       </c>
       <c t="s" r="I379" s="7">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c t="s" r="J379" s="7">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="K379" s="7"/>
       <c r="L379" s="7"/>
@@ -13400,7 +13414,7 @@
       </c>
       <c r="D381" s="7"/>
       <c t="s" r="E381" s="7">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="F381" s="7">
         <v>321</v>
@@ -13409,18 +13423,18 @@
         <v>41</v>
       </c>
       <c t="s" r="H381" s="8">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c t="s" r="I381" s="7">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c t="s" r="J381" s="7">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="K381" s="7"/>
       <c r="L381" s="7"/>
       <c t="s" r="M381" s="7">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="382" ht="14.25" customHeight="1">
@@ -13435,13 +13449,13 @@
       </c>
       <c r="D382" s="7"/>
       <c t="s" r="E382" s="7">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="F382" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G382" s="8">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c t="s" r="H382" s="8">
         <v>41</v>
@@ -13483,19 +13497,19 @@
       </c>
       <c r="D384" s="7"/>
       <c t="s" r="E384" s="7">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="F384" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G384" s="8">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c t="s" r="H384" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I384" s="7">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c t="s" r="J384" s="7">
         <v>19</v>
@@ -13503,7 +13517,7 @@
       <c r="K384" s="7"/>
       <c r="L384" s="7"/>
       <c t="s" r="M384" s="7">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="385" ht="15" customHeight="1">
@@ -13518,7 +13532,7 @@
       </c>
       <c r="D385" s="7"/>
       <c t="s" r="E385" s="7">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="F385" s="7">
         <v>321</v>
@@ -13551,7 +13565,7 @@
       </c>
       <c r="D386" s="7"/>
       <c t="s" r="E386" s="7">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="F386" s="7">
         <v>321</v>
@@ -13566,7 +13580,7 @@
         <v>123</v>
       </c>
       <c t="s" r="J386" s="7">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="K386" s="7"/>
       <c r="L386" s="7"/>
@@ -13584,7 +13598,7 @@
       </c>
       <c r="D387" s="7"/>
       <c t="s" r="E387" s="7">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="F387" s="7">
         <v>321</v>
@@ -13596,10 +13610,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I387" s="7">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c t="s" r="J387" s="7">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="K387" s="7"/>
       <c r="L387" s="7"/>
@@ -13632,7 +13646,7 @@
       </c>
       <c r="D389" s="7"/>
       <c t="s" r="E389" s="7">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="F389" s="7">
         <v>321</v>
@@ -13647,12 +13661,12 @@
         <v>56</v>
       </c>
       <c t="s" r="J389" s="7">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="K389" s="7"/>
       <c r="L389" s="7"/>
       <c t="s" r="M389" s="7">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="390" ht="15" customHeight="1">
@@ -13667,7 +13681,7 @@
       </c>
       <c r="D390" s="7"/>
       <c t="s" r="E390" s="7">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="F390" s="7">
         <v>321</v>
@@ -13679,15 +13693,15 @@
         <v>89</v>
       </c>
       <c t="s" r="I390" s="7">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c t="s" r="J390" s="7">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="K390" s="7"/>
       <c r="L390" s="7"/>
       <c t="s" r="M390" s="7">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="391" ht="14.25" customHeight="1">
@@ -13702,7 +13716,7 @@
       </c>
       <c r="D391" s="7"/>
       <c t="s" r="E391" s="7">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="F391" s="7">
         <v>321</v>
@@ -13711,13 +13725,13 @@
         <v>89</v>
       </c>
       <c t="s" r="H391" s="8">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c t="s" r="I391" s="7">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c t="s" r="J391" s="7">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="K391" s="7"/>
       <c r="L391" s="7"/>
@@ -13735,22 +13749,22 @@
       </c>
       <c r="D392" s="7"/>
       <c t="s" r="E392" s="7">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="F392" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G392" s="8">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c t="s" r="H392" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I392" s="7">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c t="s" r="J392" s="7">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="K392" s="7"/>
       <c r="L392" s="7"/>
@@ -13768,7 +13782,7 @@
       </c>
       <c r="D393" s="7"/>
       <c t="s" r="E393" s="7">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="F393" s="7">
         <v>321</v>
@@ -13777,13 +13791,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H393" s="8">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c t="s" r="I393" s="7">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c t="s" r="J393" s="7">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="K393" s="7"/>
       <c r="L393" s="7"/>
@@ -13801,22 +13815,22 @@
       </c>
       <c r="D394" s="7"/>
       <c t="s" r="E394" s="7">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="F394" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G394" s="8">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c t="s" r="H394" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I394" s="7">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c t="s" r="J394" s="7">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="K394" s="7"/>
       <c r="L394" s="7"/>
@@ -13849,7 +13863,7 @@
       </c>
       <c r="D396" s="7"/>
       <c t="s" r="E396" s="7">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="F396" s="7">
         <v>321</v>
@@ -13861,15 +13875,15 @@
         <v>31</v>
       </c>
       <c t="s" r="I396" s="7">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c t="s" r="J396" s="7">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="K396" s="7"/>
       <c r="L396" s="7"/>
       <c t="s" r="M396" s="7">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="397" ht="14.25" customHeight="1">
@@ -13884,7 +13898,7 @@
       </c>
       <c r="D397" s="7"/>
       <c t="s" r="E397" s="7">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="F397" s="7">
         <v>321</v>
@@ -13896,10 +13910,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I397" s="7">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c t="s" r="J397" s="7">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="K397" s="7"/>
       <c r="L397" s="7"/>
@@ -13917,7 +13931,7 @@
       </c>
       <c r="D398" s="7"/>
       <c t="s" r="E398" s="7">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="F398" s="7">
         <v>321</v>
@@ -13926,13 +13940,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H398" s="8">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c t="s" r="I398" s="7">
         <v>50</v>
       </c>
       <c t="s" r="J398" s="7">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="K398" s="7"/>
       <c r="L398" s="7"/>
@@ -13950,22 +13964,22 @@
       </c>
       <c r="D399" s="7"/>
       <c t="s" r="E399" s="7">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="F399" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G399" s="8">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c t="s" r="H399" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I399" s="7">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c t="s" r="J399" s="7">
-        <v>194</v>
+        <v>177</v>
       </c>
       <c r="K399" s="7"/>
       <c r="L399" s="7"/>
@@ -13983,7 +13997,7 @@
       </c>
       <c r="D400" s="7"/>
       <c t="s" r="E400" s="7">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="F400" s="7">
         <v>321</v>
@@ -13995,10 +14009,10 @@
         <v>89</v>
       </c>
       <c t="s" r="I400" s="7">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c t="s" r="J400" s="7">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="K400" s="7"/>
       <c r="L400" s="7"/>
@@ -14016,7 +14030,7 @@
       </c>
       <c r="D401" s="7"/>
       <c t="s" r="E401" s="7">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="F401" s="7">
         <v>321</v>
@@ -14028,10 +14042,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I401" s="7">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c t="s" r="J401" s="7">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="K401" s="7"/>
       <c r="L401" s="7"/>
@@ -14049,7 +14063,7 @@
       </c>
       <c r="D402" s="7"/>
       <c t="s" r="E402" s="7">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="F402" s="7">
         <v>321</v>
@@ -14061,10 +14075,10 @@
         <v>31</v>
       </c>
       <c t="s" r="I402" s="7">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c t="s" r="J402" s="7">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="K402" s="7"/>
       <c r="L402" s="7"/>
@@ -14097,7 +14111,7 @@
       </c>
       <c r="D404" s="7"/>
       <c t="s" r="E404" s="7">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="F404" s="7">
         <v>320</v>
@@ -14109,15 +14123,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I404" s="7">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c t="s" r="J404" s="7">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="K404" s="7"/>
       <c r="L404" s="7"/>
       <c t="s" r="M404" s="7">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="405" ht="15" customHeight="1">
@@ -14132,7 +14146,7 @@
       </c>
       <c r="D405" s="7"/>
       <c t="s" r="E405" s="7">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="F405" s="7">
         <v>320</v>
@@ -14144,10 +14158,10 @@
         <v>31</v>
       </c>
       <c t="s" r="I405" s="7">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c t="s" r="J405" s="7">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="K405" s="7"/>
       <c r="L405" s="7"/>
@@ -14167,7 +14181,7 @@
       </c>
       <c r="D406" s="7"/>
       <c t="s" r="E406" s="7">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="F406" s="7">
         <v>320</v>
@@ -14179,10 +14193,10 @@
         <v>127</v>
       </c>
       <c t="s" r="I406" s="7">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c t="s" r="J406" s="7">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="K406" s="7"/>
       <c r="L406" s="7"/>
@@ -14200,7 +14214,7 @@
       </c>
       <c r="D407" s="7"/>
       <c t="s" r="E407" s="7">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="F407" s="7">
         <v>320</v>
@@ -14215,7 +14229,7 @@
         <v>49</v>
       </c>
       <c t="s" r="J407" s="7">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="K407" s="7"/>
       <c r="L407" s="7"/>
@@ -14233,7 +14247,7 @@
       </c>
       <c r="D408" s="7"/>
       <c t="s" r="E408" s="7">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="F408" s="7">
         <v>320</v>
@@ -14245,7 +14259,7 @@
         <v>42</v>
       </c>
       <c t="s" r="I408" s="7">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c t="s" r="J408" s="7">
         <v>64</v>
@@ -14266,7 +14280,7 @@
       </c>
       <c r="D409" s="7"/>
       <c t="s" r="E409" s="7">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="F409" s="7">
         <v>320</v>
@@ -14278,10 +14292,10 @@
         <v>31</v>
       </c>
       <c t="s" r="I409" s="7">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c t="s" r="J409" s="7">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="K409" s="7"/>
       <c r="L409" s="7"/>
@@ -14314,27 +14328,27 @@
       </c>
       <c r="D411" s="7"/>
       <c t="s" r="E411" s="7">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="F411" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G411" s="8">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c t="s" r="H411" s="8">
         <v>58</v>
       </c>
       <c t="s" r="I411" s="7">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c t="s" r="J411" s="7">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="K411" s="7"/>
       <c r="L411" s="7"/>
       <c t="s" r="M411" s="7">
-        <v>208</v>
+        <v>213</v>
       </c>
     </row>
     <row r="412" ht="14.25" customHeight="1">
@@ -14349,7 +14363,7 @@
       </c>
       <c r="D412" s="7"/>
       <c t="s" r="E412" s="7">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="F412" s="7">
         <v>321</v>
@@ -14358,10 +14372,10 @@
         <v>58</v>
       </c>
       <c t="s" r="H412" s="8">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c t="s" r="I412" s="7">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c t="s" r="J412" s="7">
         <v>50</v>
@@ -14384,19 +14398,19 @@
       </c>
       <c r="D413" s="7"/>
       <c t="s" r="E413" s="7">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="F413" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G413" s="8">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c t="s" r="H413" s="8">
         <v>58</v>
       </c>
       <c t="s" r="I413" s="7">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c t="s" r="J413" s="7">
         <v>111</v>
@@ -14417,7 +14431,7 @@
       </c>
       <c r="D414" s="7"/>
       <c t="s" r="E414" s="7">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="F414" s="7">
         <v>321</v>
@@ -14426,13 +14440,13 @@
         <v>58</v>
       </c>
       <c t="s" r="H414" s="8">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c t="s" r="I414" s="7">
         <v>123</v>
       </c>
       <c t="s" r="J414" s="7">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="K414" s="7"/>
       <c r="L414" s="7"/>
@@ -14465,7 +14479,7 @@
       </c>
       <c r="D416" s="7"/>
       <c t="s" r="E416" s="7">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="F416" s="7">
         <v>321</v>
@@ -14474,13 +14488,13 @@
         <v>89</v>
       </c>
       <c t="s" r="H416" s="8">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c t="s" r="I416" s="7">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c t="s" r="J416" s="7">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="K416" s="7"/>
       <c r="L416" s="7"/>
@@ -14498,22 +14512,22 @@
       </c>
       <c r="D417" s="7"/>
       <c t="s" r="E417" s="7">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="F417" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G417" s="8">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c t="s" r="H417" s="8">
         <v>89</v>
       </c>
       <c t="s" r="I417" s="7">
-        <v>194</v>
+        <v>177</v>
       </c>
       <c t="s" r="J417" s="7">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="K417" s="7"/>
       <c r="L417" s="7"/>
@@ -14531,7 +14545,7 @@
       </c>
       <c r="D418" s="7"/>
       <c t="s" r="E418" s="7">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="F418" s="7">
         <v>321</v>
@@ -14543,7 +14557,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I418" s="7">
-        <v>174</v>
+        <v>248</v>
       </c>
       <c t="s" r="J418" s="7">
         <v>43</v>
@@ -14579,7 +14593,7 @@
       </c>
       <c r="D420" s="7"/>
       <c t="s" r="E420" s="7">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="F420" s="7">
         <v>321</v>
@@ -14588,10 +14602,10 @@
         <v>41</v>
       </c>
       <c t="s" r="H420" s="8">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c t="s" r="I420" s="7">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c t="s" r="J420" s="7">
         <v>20</v>
@@ -14599,7 +14613,7 @@
       <c r="K420" s="7"/>
       <c r="L420" s="7"/>
       <c t="s" r="M420" s="7">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="421" ht="14.25" customHeight="1">
@@ -14614,19 +14628,19 @@
       </c>
       <c r="D421" s="7"/>
       <c t="s" r="E421" s="7">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="F421" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G421" s="8">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c t="s" r="H421" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I421" s="7">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c t="s" r="J421" s="7">
         <v>109</v>
@@ -14647,7 +14661,7 @@
       </c>
       <c r="D422" s="7"/>
       <c t="s" r="E422" s="7">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="F422" s="7">
         <v>321</v>
@@ -14662,7 +14676,7 @@
         <v>36</v>
       </c>
       <c t="s" r="J422" s="7">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K422" s="7"/>
       <c r="L422" s="7"/>
@@ -14680,7 +14694,7 @@
       </c>
       <c r="D423" s="7"/>
       <c t="s" r="E423" s="7">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="F423" s="7">
         <v>321</v>
@@ -14692,10 +14706,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I423" s="7">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c t="s" r="J423" s="7">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="K423" s="7"/>
       <c r="L423" s="7"/>
@@ -14728,7 +14742,7 @@
       </c>
       <c r="D425" s="7"/>
       <c t="s" r="E425" s="7">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="F425" s="7">
         <v>320</v>
@@ -14737,13 +14751,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H425" s="8">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c t="s" r="I425" s="7">
         <v>78</v>
       </c>
       <c t="s" r="J425" s="7">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="K425" s="7"/>
       <c r="L425" s="7"/>
@@ -14763,13 +14777,13 @@
       </c>
       <c r="D426" s="7"/>
       <c t="s" r="E426" s="7">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="F426" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G426" s="8">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c t="s" r="H426" s="8">
         <v>41</v>
@@ -14778,7 +14792,7 @@
         <v>60</v>
       </c>
       <c t="s" r="J426" s="7">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="K426" s="7"/>
       <c r="L426" s="7"/>
@@ -14796,7 +14810,7 @@
       </c>
       <c r="D427" s="7"/>
       <c t="s" r="E427" s="7">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="F427" s="7">
         <v>320</v>
@@ -14808,10 +14822,10 @@
         <v>31</v>
       </c>
       <c t="s" r="I427" s="7">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c t="s" r="J427" s="7">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="K427" s="7"/>
       <c r="L427" s="7"/>
@@ -14829,7 +14843,7 @@
       </c>
       <c r="D428" s="7"/>
       <c t="s" r="E428" s="7">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="F428" s="7">
         <v>320</v>
@@ -14844,7 +14858,7 @@
         <v>111</v>
       </c>
       <c t="s" r="J428" s="7">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="K428" s="7"/>
       <c r="L428" s="7"/>
@@ -14877,7 +14891,7 @@
       </c>
       <c r="D430" s="7"/>
       <c t="s" r="E430" s="7">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="F430" s="7">
         <v>330</v>
@@ -14896,7 +14910,9 @@
       </c>
       <c r="K430" s="7"/>
       <c r="L430" s="7"/>
-      <c r="M430" s="7"/>
+      <c t="s" r="M430" s="7">
+        <v>154</v>
+      </c>
     </row>
     <row r="431" ht="14.25" customHeight="1">
       <c t="s" r="A431" s="6">
@@ -14910,7 +14926,7 @@
       </c>
       <c r="D431" s="7"/>
       <c t="s" r="E431" s="7">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="F431" s="7">
         <v>330</v>
@@ -14922,7 +14938,7 @@
         <v>31</v>
       </c>
       <c t="s" r="I431" s="7">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c t="s" r="J431" s="7">
         <v>51</v>
@@ -14943,7 +14959,7 @@
       </c>
       <c r="D432" s="7"/>
       <c t="s" r="E432" s="7">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="F432" s="7">
         <v>330</v>
@@ -14955,7 +14971,7 @@
         <v>41</v>
       </c>
       <c t="s" r="I432" s="7">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c t="s" r="J432" s="7">
         <v>65</v>
@@ -14991,7 +15007,7 @@
       </c>
       <c r="D434" s="7"/>
       <c t="s" r="E434" s="7">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="F434" s="7">
         <v>330</v>
@@ -15000,7 +15016,7 @@
         <v>89</v>
       </c>
       <c t="s" r="H434" s="8">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c t="s" r="I434" s="7">
         <v>43</v>
@@ -15011,7 +15027,7 @@
       <c r="K434" s="7"/>
       <c r="L434" s="7"/>
       <c t="s" r="M434" s="7">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="435" ht="15" customHeight="1">
@@ -15026,13 +15042,13 @@
       </c>
       <c r="D435" s="7"/>
       <c t="s" r="E435" s="7">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="F435" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G435" s="8">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c t="s" r="H435" s="8">
         <v>89</v>
@@ -15041,7 +15057,7 @@
         <v>109</v>
       </c>
       <c t="s" r="J435" s="7">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="K435" s="7"/>
       <c r="L435" s="7"/>
@@ -15074,7 +15090,7 @@
       </c>
       <c r="D437" s="7"/>
       <c t="s" r="E437" s="7">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="F437" s="7">
         <v>330</v>
@@ -15109,7 +15125,7 @@
       </c>
       <c r="D438" s="7"/>
       <c t="s" r="E438" s="7">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="F438" s="7">
         <v>330</v>
@@ -15118,13 +15134,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H438" s="8">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c t="s" r="I438" s="7">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c t="s" r="J438" s="7">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="K438" s="7"/>
       <c r="L438" s="7"/>
@@ -15157,7 +15173,7 @@
       </c>
       <c r="D440" s="7"/>
       <c t="s" r="E440" s="7">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="F440" s="7">
         <v>330</v>
@@ -15166,13 +15182,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H440" s="8">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c t="s" r="I440" s="7">
         <v>124</v>
       </c>
       <c t="s" r="J440" s="7">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="K440" s="7"/>
       <c r="L440" s="7"/>
@@ -15190,22 +15206,22 @@
       </c>
       <c r="D441" s="7"/>
       <c t="s" r="E441" s="7">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="F441" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G441" s="8">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c t="s" r="H441" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I441" s="7">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c t="s" r="J441" s="7">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="K441" s="7"/>
       <c r="L441" s="7"/>
@@ -15238,27 +15254,27 @@
       </c>
       <c r="D443" s="7"/>
       <c t="s" r="E443" s="7">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="F443" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G443" s="8">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c t="s" r="H443" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I443" s="7">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c t="s" r="J443" s="7">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="K443" s="7"/>
       <c r="L443" s="7"/>
       <c t="s" r="M443" s="7">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="444" ht="14.25" customHeight="1">
@@ -15273,7 +15289,7 @@
       </c>
       <c r="D444" s="7"/>
       <c t="s" r="E444" s="7">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="F444" s="7">
         <v>330</v>
@@ -15282,13 +15298,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H444" s="8">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c t="s" r="I444" s="7">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c t="s" r="J444" s="7">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="K444" s="7"/>
       <c r="L444" s="7"/>
@@ -15321,7 +15337,7 @@
       </c>
       <c r="D446" s="7"/>
       <c t="s" r="E446" s="7">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="F446" s="7">
         <v>330</v>
@@ -15330,7 +15346,7 @@
         <v>41</v>
       </c>
       <c t="s" r="H446" s="8">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c t="s" r="I446" s="7">
         <v>60</v>
@@ -15354,19 +15370,19 @@
       </c>
       <c r="D447" s="7"/>
       <c t="s" r="E447" s="7">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="F447" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G447" s="8">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c t="s" r="H447" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I447" s="7">
-        <v>174</v>
+        <v>248</v>
       </c>
       <c t="s" r="J447" s="7">
         <v>113</v>
@@ -15377,7 +15393,7 @@
     </row>
     <row r="448" ht="15.75" customHeight="1">
       <c t="s" r="A448" s="9">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B448" s="9"/>
       <c r="C448" s="9"/>
@@ -15397,7 +15413,7 @@
     <row r="449" ht="65.25" customHeight="1"/>
     <row r="450" ht="17.25" customHeight="1">
       <c t="s" r="A450" s="10">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="B450" s="10"/>
       <c r="C450" s="10"/>
@@ -15410,7 +15426,7 @@
       <c r="J450" s="10"/>
       <c r="K450" s="10"/>
       <c t="s" r="L450" s="11">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="M450" s="11"/>
       <c r="N450" s="11"/>
